--- a/output/Tables/2019/cases_prev_2019_sex_age.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex_age.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1206,7 +1206,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1220,22 +1220,22 @@
         </is>
       </c>
       <c r="D30">
-        <v>2.251861781613458</v>
+        <v>7.753489986796596</v>
       </c>
       <c r="E30">
-        <v>0.4447968387276301</v>
+        <v>1.516999442875644</v>
       </c>
       <c r="F30">
-        <v>2.854411183532116</v>
+        <v>0.2965358579940802</v>
       </c>
       <c r="G30">
-        <v>1.221316572084207</v>
+        <v>15.69994569378816</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1249,22 +1249,22 @@
         </is>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>4.791538675093026</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>0.9011903685245432</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>0.173721996363095</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>9.693295819211164</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="D32">
-        <v>68.18480456069702</v>
+        <v>56.02709710526626</v>
       </c>
       <c r="E32">
-        <v>12.45158012039505</v>
+        <v>10.05772679205928</v>
       </c>
       <c r="F32">
-        <v>86.23773337342405</v>
+        <v>1.354757674051808</v>
       </c>
       <c r="G32">
-        <v>37.13077617335094</v>
+        <v>113.3764320097071</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1307,22 +1307,22 @@
         </is>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>21.12993950627974</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>3.620608063180764</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>0.5609879070726218</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>42.65319813169481</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="D34">
-        <v>341.0597591587584</v>
+        <v>154.7223093218356</v>
       </c>
       <c r="E34">
-        <v>55.71417725415568</v>
+        <v>25.74500400236991</v>
       </c>
       <c r="F34">
-        <v>426.098189645625</v>
+        <v>3.63584329129158</v>
       </c>
       <c r="G34">
-        <v>189.9197277338661</v>
+        <v>312.3351725868083</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>95.12402916810167</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>19.25270420578076</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>2.865858057138944</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>192.1553202415448</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1394,22 +1394,22 @@
         </is>
       </c>
       <c r="D36">
-        <v>470.788633898062</v>
+        <v>207.3307400341226</v>
       </c>
       <c r="E36">
-        <v>79.04268107851766</v>
+        <v>34.28214259560028</v>
       </c>
       <c r="F36">
-        <v>594.453616671099</v>
+        <v>7.175997971304034</v>
       </c>
       <c r="G36">
-        <v>257.3199071631601</v>
+        <v>419.6437340088478</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>203.3160003961902</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>33.7898154218939</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>6.783166473679788</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>411.5187447474956</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1452,22 +1452,22 @@
         </is>
       </c>
       <c r="D38">
-        <v>937.5433559555294</v>
+        <v>556.5873096343158</v>
       </c>
       <c r="E38">
-        <v>152.3033150881094</v>
+        <v>89.83905234014546</v>
       </c>
       <c r="F38">
-        <v>1176.814284451161</v>
+        <v>10.10673487194112</v>
       </c>
       <c r="G38">
-        <v>517.6930081930591</v>
+        <v>1125.698609244572</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,22 +1481,22 @@
         </is>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>881.107107175667</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>124.8072072443794</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>-1.136049345829136</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1778.29107582161</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1510,22 +1510,22 @@
         </is>
       </c>
       <c r="D40">
-        <v>1159.000728351748</v>
+        <v>750.8933789186796</v>
       </c>
       <c r="E40">
-        <v>184.5884423126578</v>
+        <v>120.9135288756254</v>
       </c>
       <c r="F40">
-        <v>1462.345239830937</v>
+        <v>16.7999070901332</v>
       </c>
       <c r="G40">
-        <v>633.1467441642445</v>
+        <v>1518.445107853114</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1539,22 +1539,22 @@
         </is>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>814.864076114769</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>114.9101932830803</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>9.063068411180476</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1642.594633824997</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1568,22 +1568,22 @@
         </is>
       </c>
       <c r="D42">
-        <v>650.78454835952</v>
+        <v>613.9100792520594</v>
       </c>
       <c r="E42">
-        <v>98.30328557446187</v>
+        <v>94.02178536654297</v>
       </c>
       <c r="F42">
-        <v>829.5681880812833</v>
+        <v>33.79159451094418</v>
       </c>
       <c r="G42">
-        <v>351.1353162743995</v>
+        <v>1245.038301400591</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1597,22 +1597,22 @@
         </is>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>509.2366163555211</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>79.84383600196131</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>15.9254000057911</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1029.215143777309</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1626,22 +1626,22 @@
         </is>
       </c>
       <c r="D44">
-        <v>7.753489986796596</v>
+        <v>26.37472421520761</v>
       </c>
       <c r="E44">
-        <v>1.516999442875644</v>
+        <v>5.17432270341177</v>
       </c>
       <c r="F44">
-        <v>0.2965358579940802</v>
+        <v>-0.6435224407938687</v>
       </c>
       <c r="G44">
-        <v>15.69994569378816</v>
+        <v>49.29046714330751</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="D45">
-        <v>4.791538675093026</v>
+        <v>18.84992961181364</v>
       </c>
       <c r="E45">
-        <v>0.9011903685245432</v>
+        <v>3.550344611599527</v>
       </c>
       <c r="F45">
-        <v>0.173721996363095</v>
+        <v>-0.4338878519107666</v>
       </c>
       <c r="G45">
-        <v>9.693295819211164</v>
+        <v>35.13719808486548</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1684,22 +1684,22 @@
         </is>
       </c>
       <c r="D46">
-        <v>56.02709710526626</v>
+        <v>91.63650096592163</v>
       </c>
       <c r="E46">
-        <v>10.05772679205928</v>
+        <v>16.45507177666171</v>
       </c>
       <c r="F46">
-        <v>1.354757674051808</v>
+        <v>-1.85723965753136</v>
       </c>
       <c r="G46">
-        <v>113.3764320097071</v>
+        <v>170.5641544868471</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1713,22 +1713,22 @@
         </is>
       </c>
       <c r="D47">
-        <v>21.12993950627974</v>
+        <v>49.493021259959</v>
       </c>
       <c r="E47">
-        <v>3.620608063180764</v>
+        <v>8.479948909340782</v>
       </c>
       <c r="F47">
-        <v>0.5609879070726218</v>
+        <v>-0.9651030906547192</v>
       </c>
       <c r="G47">
-        <v>42.65319813169481</v>
+        <v>92.03233205733679</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1742,22 +1742,22 @@
         </is>
       </c>
       <c r="D48">
-        <v>154.7223093218356</v>
+        <v>211.9590256878334</v>
       </c>
       <c r="E48">
-        <v>25.74500400236991</v>
+        <v>35.25283490076471</v>
       </c>
       <c r="F48">
-        <v>3.63584329129158</v>
+        <v>-3.673698331469673</v>
       </c>
       <c r="G48">
-        <v>312.3351725868083</v>
+        <v>391.3266690642212</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1771,22 +1771,22 @@
         </is>
       </c>
       <c r="D49">
-        <v>95.12402916810167</v>
+        <v>210.3446424449039</v>
       </c>
       <c r="E49">
-        <v>19.25270420578076</v>
+        <v>42.60164601386627</v>
       </c>
       <c r="F49">
-        <v>2.865858057138944</v>
+        <v>-4.364551261876571</v>
       </c>
       <c r="G49">
-        <v>192.1553202415448</v>
+        <v>391.321635417835</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1800,22 +1800,22 @@
         </is>
       </c>
       <c r="D50">
-        <v>207.3307400341226</v>
+        <v>316.025032749713</v>
       </c>
       <c r="E50">
-        <v>34.28214259560028</v>
+        <v>52.34811425371102</v>
       </c>
       <c r="F50">
-        <v>7.175997971304034</v>
+        <v>-7.284284640573616</v>
       </c>
       <c r="G50">
-        <v>419.6437340088478</v>
+        <v>589.4137693367397</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1829,22 +1829,22 @@
         </is>
       </c>
       <c r="D51">
-        <v>203.3160003961902</v>
+        <v>349.3889145684437</v>
       </c>
       <c r="E51">
-        <v>33.7898154218939</v>
+        <v>58.08011968257829</v>
       </c>
       <c r="F51">
-        <v>6.783166473679788</v>
+        <v>-7.824514599269855</v>
       </c>
       <c r="G51">
-        <v>411.5187447474956</v>
+        <v>650.5107843701344</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1858,22 +1858,22 @@
         </is>
       </c>
       <c r="D52">
-        <v>556.5873096343158</v>
+        <v>1007.550981633505</v>
       </c>
       <c r="E52">
-        <v>89.83905234014546</v>
+        <v>162.7373369475614</v>
       </c>
       <c r="F52">
-        <v>10.10673487194112</v>
+        <v>-17.47600994823951</v>
       </c>
       <c r="G52">
-        <v>1125.698609244572</v>
+        <v>1863.821466713548</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1887,22 +1887,22 @@
         </is>
       </c>
       <c r="D53">
-        <v>881.107107175667</v>
+        <v>1126.976775001094</v>
       </c>
       <c r="E53">
-        <v>124.8072072443794</v>
+        <v>159.625644554717</v>
       </c>
       <c r="F53">
-        <v>-1.136049345829136</v>
+        <v>-10.14003776751773</v>
       </c>
       <c r="G53">
-        <v>1778.29107582161</v>
+        <v>2053.891895047056</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1916,22 +1916,22 @@
         </is>
       </c>
       <c r="D54">
-        <v>750.8933789186796</v>
+        <v>1114.092762092152</v>
       </c>
       <c r="E54">
-        <v>120.9135288756254</v>
+        <v>179.3443259710884</v>
       </c>
       <c r="F54">
-        <v>16.7999070901332</v>
+        <v>-20.79611135804836</v>
       </c>
       <c r="G54">
-        <v>1518.445107853114</v>
+        <v>2064.422780222847</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1945,22 +1945,22 @@
         </is>
       </c>
       <c r="D55">
-        <v>814.864076114769</v>
+        <v>1049.538758709682</v>
       </c>
       <c r="E55">
-        <v>114.9101932830803</v>
+        <v>148.1028680912809</v>
       </c>
       <c r="F55">
-        <v>9.063068411180476</v>
+        <v>-13.64844790195101</v>
       </c>
       <c r="G55">
-        <v>1642.594633824997</v>
+        <v>1927.985490450226</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1974,22 +1974,22 @@
         </is>
       </c>
       <c r="D56">
-        <v>613.9100792520594</v>
+        <v>470.0037282158446</v>
       </c>
       <c r="E56">
-        <v>94.02178536654297</v>
+        <v>71.98314771040324</v>
       </c>
       <c r="F56">
-        <v>33.79159451094418</v>
+        <v>-14.63751464114057</v>
       </c>
       <c r="G56">
-        <v>1245.038301400591</v>
+        <v>887.9384426484394</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2003,22 +2003,22 @@
         </is>
       </c>
       <c r="D57">
-        <v>509.2366163555211</v>
+        <v>418.323516331683</v>
       </c>
       <c r="E57">
-        <v>79.84383600196131</v>
+        <v>65.67410629447623</v>
       </c>
       <c r="F57">
-        <v>15.9254000057911</v>
+        <v>-8.431541213566685</v>
       </c>
       <c r="G57">
-        <v>1029.215143777309</v>
+        <v>774.4861830395084</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2032,22 +2032,22 @@
         </is>
       </c>
       <c r="D58">
-        <v>26.37472421520761</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>5.17432270341177</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>-0.6435224407938687</v>
+        <v>0</v>
       </c>
       <c r="G58">
-        <v>49.29046714330751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2061,22 +2061,22 @@
         </is>
       </c>
       <c r="D59">
-        <v>18.84992961181364</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>3.550344611599527</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>-0.4338878519107666</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>35.13719808486548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2090,22 +2090,22 @@
         </is>
       </c>
       <c r="D60">
-        <v>91.63650096592163</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>16.45507177666171</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>-1.85723965753136</v>
+        <v>0</v>
       </c>
       <c r="G60">
-        <v>170.5641544868471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2119,22 +2119,22 @@
         </is>
       </c>
       <c r="D61">
-        <v>49.493021259959</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>8.479948909340782</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>-0.9651030906547192</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>92.03233205733679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2148,22 +2148,22 @@
         </is>
       </c>
       <c r="D62">
-        <v>211.9590256878334</v>
+        <v>0.752693498956816</v>
       </c>
       <c r="E62">
-        <v>35.25283490076471</v>
+        <v>0.1287694653428949</v>
       </c>
       <c r="F62">
-        <v>-3.673698331469673</v>
+        <v>0.5451580658020282</v>
       </c>
       <c r="G62">
-        <v>391.3266690642212</v>
+        <v>0.9371774707816141</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2177,22 +2177,22 @@
         </is>
       </c>
       <c r="D63">
-        <v>210.3446424449039</v>
+        <v>1.870649334246026</v>
       </c>
       <c r="E63">
-        <v>42.60164601386627</v>
+        <v>0.3575951546425103</v>
       </c>
       <c r="F63">
-        <v>-4.364551261876571</v>
+        <v>1.35119886828296</v>
       </c>
       <c r="G63">
-        <v>391.321635417835</v>
+        <v>2.331339705285234</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="D64">
-        <v>316.025032749713</v>
+        <v>6.715569815673259</v>
       </c>
       <c r="E64">
-        <v>52.34811425371102</v>
+        <v>1.072386449352358</v>
       </c>
       <c r="F64">
-        <v>-7.284284640573616</v>
+        <v>4.87186231668871</v>
       </c>
       <c r="G64">
-        <v>589.4137693367397</v>
+        <v>8.360004456824004</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2235,22 +2235,22 @@
         </is>
       </c>
       <c r="D65">
-        <v>349.3889145684437</v>
+        <v>6.780308310437436</v>
       </c>
       <c r="E65">
-        <v>58.08011968257829</v>
+        <v>1.132839295175753</v>
       </c>
       <c r="F65">
-        <v>-7.824514599269855</v>
+        <v>4.906367351573829</v>
       </c>
       <c r="G65">
-        <v>650.5107843701344</v>
+        <v>8.454024890391915</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2264,22 +2264,22 @@
         </is>
       </c>
       <c r="D66">
-        <v>1007.550981633505</v>
+        <v>68.36763978029055</v>
       </c>
       <c r="E66">
-        <v>162.7373369475614</v>
+        <v>10.86767022860119</v>
       </c>
       <c r="F66">
-        <v>-17.47600994823951</v>
+        <v>49.20095731483639</v>
       </c>
       <c r="G66">
-        <v>1863.821466713548</v>
+        <v>85.34606148286863</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2293,22 +2293,22 @@
         </is>
       </c>
       <c r="D67">
-        <v>1126.976775001094</v>
+        <v>58.83300403330446</v>
       </c>
       <c r="E67">
-        <v>159.625644554717</v>
+        <v>8.729778660382999</v>
       </c>
       <c r="F67">
-        <v>-10.14003776751773</v>
+        <v>42.71604651537288</v>
       </c>
       <c r="G67">
-        <v>2053.891895047056</v>
+        <v>73.02700535863781</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2322,22 +2322,22 @@
         </is>
       </c>
       <c r="D68">
-        <v>1114.092762092152</v>
+        <v>415.5102488441664</v>
       </c>
       <c r="E68">
-        <v>179.3443259710884</v>
+        <v>68.52209719730368</v>
       </c>
       <c r="F68">
-        <v>-20.79611135804836</v>
+        <v>300.0154000533234</v>
       </c>
       <c r="G68">
-        <v>2064.422780222847</v>
+        <v>517.8791326321398</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2351,22 +2351,22 @@
         </is>
       </c>
       <c r="D69">
-        <v>1049.538758709682</v>
+        <v>253.4873579949261</v>
       </c>
       <c r="E69">
-        <v>148.1028680912809</v>
+        <v>35.85255096277303</v>
       </c>
       <c r="F69">
-        <v>-13.64844790195101</v>
+        <v>184.5046324859482</v>
       </c>
       <c r="G69">
-        <v>1927.985490450226</v>
+        <v>314.1625903888029</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2380,22 +2380,22 @@
         </is>
       </c>
       <c r="D70">
-        <v>470.0037282158446</v>
+        <v>1893.102251797338</v>
       </c>
       <c r="E70">
-        <v>71.98314771040324</v>
+        <v>295.0503436135965</v>
       </c>
       <c r="F70">
-        <v>-14.63751464114057</v>
+        <v>1363.764821148761</v>
       </c>
       <c r="G70">
-        <v>887.9384426484394</v>
+        <v>2368.725518566815</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2409,22 +2409,22 @@
         </is>
       </c>
       <c r="D71">
-        <v>418.323516331683</v>
+        <v>869.7306909056242</v>
       </c>
       <c r="E71">
-        <v>65.67410629447623</v>
+        <v>131.9767000907348</v>
       </c>
       <c r="F71">
-        <v>-8.431541213566685</v>
+        <v>625.3072125003119</v>
       </c>
       <c r="G71">
-        <v>774.4861830395084</v>
+        <v>1088.450524972352</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2438,22 +2438,22 @@
         </is>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>11040.12965882238</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>2138.532217777936</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>8183.374989190699</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>13370.63870850162</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2467,22 +2467,22 @@
         </is>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>4842.783397916417</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>904.3467692432251</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>3596.597844490422</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>5861.594933983818</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2496,22 +2496,22 @@
         </is>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>27125.60817627047</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>4854.773079003411</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>20141.89177630313</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>32798.58345993355</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2525,22 +2525,22 @@
         </is>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>9106.403478834725</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>1551.742354872491</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>6768.626365737306</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>11004.42288704877</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2554,22 +2554,22 @@
         </is>
       </c>
       <c r="D76">
-        <v>0.752693498956816</v>
+        <v>30566.8199983484</v>
       </c>
       <c r="E76">
-        <v>0.1287694653428949</v>
+        <v>5093.478987973128</v>
       </c>
       <c r="F76">
-        <v>0.5451580658020282</v>
+        <v>22852.05440470973</v>
       </c>
       <c r="G76">
-        <v>0.9371774707816141</v>
+        <v>36913.70885044193</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2583,22 +2583,22 @@
         </is>
       </c>
       <c r="D77">
-        <v>1.870649334246026</v>
+        <v>11932.64544715409</v>
       </c>
       <c r="E77">
-        <v>0.3575951546425103</v>
+        <v>2394.045906704672</v>
       </c>
       <c r="F77">
-        <v>1.35119886828296</v>
+        <v>8870.704440358919</v>
       </c>
       <c r="G77">
-        <v>2.331339705285234</v>
+        <v>14430.88104815267</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2612,22 +2612,22 @@
         </is>
       </c>
       <c r="D78">
-        <v>6.715569815673259</v>
+        <v>17913.30409801184</v>
       </c>
       <c r="E78">
-        <v>1.072386449352358</v>
+        <v>2941.654553154101</v>
       </c>
       <c r="F78">
-        <v>4.87186231668871</v>
+        <v>13295.66838065507</v>
       </c>
       <c r="G78">
-        <v>8.360004456824004</v>
+        <v>21685.24466446849</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2641,22 +2641,22 @@
         </is>
       </c>
       <c r="D79">
-        <v>6.780308310437436</v>
+        <v>6716.490798347496</v>
       </c>
       <c r="E79">
-        <v>1.132839295175753</v>
+        <v>1116.995950848847</v>
       </c>
       <c r="F79">
-        <v>4.906367351573829</v>
+        <v>4991.765669096125</v>
       </c>
       <c r="G79">
-        <v>8.454024890391915</v>
+        <v>8128.775933441339</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2670,22 +2670,22 @@
         </is>
       </c>
       <c r="D80">
-        <v>68.36763978029055</v>
+        <v>28286.29246790826</v>
       </c>
       <c r="E80">
-        <v>10.86767022860119</v>
+        <v>4552.373918203514</v>
       </c>
       <c r="F80">
-        <v>49.20095731483639</v>
+        <v>21097.97823339399</v>
       </c>
       <c r="G80">
-        <v>85.34606148286863</v>
+        <v>34158.8971776227</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2699,22 +2699,22 @@
         </is>
       </c>
       <c r="D81">
-        <v>58.83300403330446</v>
+        <v>8796.924291187395</v>
       </c>
       <c r="E81">
-        <v>8.729778660382999</v>
+        <v>1249.771898239861</v>
       </c>
       <c r="F81">
-        <v>42.71604651537288</v>
+        <v>6628.561567883887</v>
       </c>
       <c r="G81">
-        <v>73.02700535863781</v>
+        <v>10584.67148834002</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2728,22 +2728,22 @@
         </is>
       </c>
       <c r="D82">
-        <v>415.5102488441664</v>
+        <v>17582.35879292406</v>
       </c>
       <c r="E82">
-        <v>68.52209719730368</v>
+        <v>2834.246301528237</v>
       </c>
       <c r="F82">
-        <v>300.0154000533234</v>
+        <v>13103.47422138236</v>
       </c>
       <c r="G82">
-        <v>517.8791326321398</v>
+        <v>21249.08668753976</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2757,22 +2757,22 @@
         </is>
       </c>
       <c r="D83">
-        <v>253.4873579949261</v>
+        <v>4467.186042483597</v>
       </c>
       <c r="E83">
-        <v>35.85255096277303</v>
+        <v>629.3019169849349</v>
       </c>
       <c r="F83">
-        <v>184.5046324859482</v>
+        <v>3348.872890097372</v>
       </c>
       <c r="G83">
-        <v>314.1625903888029</v>
+        <v>5384.834948468118</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2786,22 +2786,22 @@
         </is>
       </c>
       <c r="D84">
-        <v>1893.102251797338</v>
+        <v>0</v>
       </c>
       <c r="E84">
-        <v>295.0503436135965</v>
+        <v>0</v>
       </c>
       <c r="F84">
-        <v>1363.764821148761</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>2368.725518566815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2815,22 +2815,22 @@
         </is>
       </c>
       <c r="D85">
-        <v>869.7306909056242</v>
+        <v>0</v>
       </c>
       <c r="E85">
-        <v>131.9767000907348</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>625.3072125003119</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>1088.450524972352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2844,22 +2844,19 @@
         </is>
       </c>
       <c r="D86">
-        <v>11040.12965882238</v>
-      </c>
-      <c r="E86">
-        <v>2138.532217777936</v>
+        <v>11089.91631488185</v>
       </c>
       <c r="F86">
-        <v>8183.374989190699</v>
+        <v>8192.774554383426</v>
       </c>
       <c r="G86">
-        <v>13370.63870850162</v>
+        <v>13457.06347127016</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2873,22 +2870,19 @@
         </is>
       </c>
       <c r="D87">
-        <v>4842.783397916417</v>
-      </c>
-      <c r="E87">
-        <v>904.3467692432251</v>
+        <v>4879.790139481021</v>
       </c>
       <c r="F87">
-        <v>3596.597844490422</v>
+        <v>3604.798303677122</v>
       </c>
       <c r="G87">
-        <v>5861.594933983818</v>
+        <v>5924.58244435953</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2902,22 +2896,19 @@
         </is>
       </c>
       <c r="D88">
-        <v>27125.60817627047</v>
-      </c>
-      <c r="E88">
-        <v>4854.773079003411</v>
+        <v>27312.91840561766</v>
       </c>
       <c r="F88">
-        <v>20141.89177630313</v>
+        <v>20166.15693143889</v>
       </c>
       <c r="G88">
-        <v>32798.58345993355</v>
+        <v>33136.41201825882</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2931,22 +2922,19 @@
         </is>
       </c>
       <c r="D89">
-        <v>9106.403478834725</v>
-      </c>
-      <c r="E89">
-        <v>1551.742354872491</v>
+        <v>9212.282375028595</v>
       </c>
       <c r="F89">
-        <v>6768.626365737306</v>
+        <v>6790.548024308879</v>
       </c>
       <c r="G89">
-        <v>11004.42288704877</v>
+        <v>11186.82703035573</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2960,22 +2948,19 @@
         </is>
       </c>
       <c r="D90">
-        <v>30566.8199983484</v>
-      </c>
-      <c r="E90">
-        <v>5093.478987973128</v>
+        <v>31024.18334374379</v>
       </c>
       <c r="F90">
-        <v>22852.05440470973</v>
+        <v>22910.15952910739</v>
       </c>
       <c r="G90">
-        <v>36913.70885044193</v>
+        <v>37739.5514538143</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2989,22 +2974,19 @@
         </is>
       </c>
       <c r="D91">
-        <v>11932.64544715409</v>
-      </c>
-      <c r="E91">
-        <v>2394.045906704672</v>
+        <v>12416.4305276137</v>
       </c>
       <c r="F91">
-        <v>8870.704440358919</v>
+        <v>8981.384590772732</v>
       </c>
       <c r="G91">
-        <v>14430.88104815267</v>
+        <v>15256.58877294761</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3018,22 +3000,19 @@
         </is>
       </c>
       <c r="D92">
-        <v>17913.30409801184</v>
-      </c>
-      <c r="E92">
-        <v>2941.654553154101</v>
+        <v>18616.77011924723</v>
       </c>
       <c r="F92">
-        <v>13295.66838065507</v>
+        <v>13409.72265372803</v>
       </c>
       <c r="G92">
-        <v>21685.24466446849</v>
+        <v>22938.39660192939</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3047,22 +3026,19 @@
         </is>
       </c>
       <c r="D93">
-        <v>6716.490798347496</v>
-      </c>
-      <c r="E93">
-        <v>1116.995950848847</v>
+        <v>7688.231729937813</v>
       </c>
       <c r="F93">
-        <v>4991.765669096125</v>
+        <v>5255.628757667087</v>
       </c>
       <c r="G93">
-        <v>8128.775933441339</v>
+        <v>9759.726982794458</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3076,22 +3052,19 @@
         </is>
       </c>
       <c r="D94">
-        <v>28286.29246790826</v>
-      </c>
-      <c r="E94">
-        <v>4552.373918203514</v>
+        <v>30649.21046115956</v>
       </c>
       <c r="F94">
-        <v>21097.97823339399</v>
+        <v>21600.09823218037</v>
       </c>
       <c r="G94">
-        <v>34158.8971776227</v>
+        <v>38222.75794743204</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3105,22 +3078,19 @@
         </is>
       </c>
       <c r="D95">
-        <v>8796.924291187395</v>
-      </c>
-      <c r="E95">
-        <v>1249.771898239861</v>
+        <v>12305.75557308536</v>
       </c>
       <c r="F95">
-        <v>6628.561567883887</v>
+        <v>7603.630166699609</v>
       </c>
       <c r="G95">
-        <v>10584.67148834002</v>
+        <v>16402.88207420219</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3134,22 +3104,19 @@
         </is>
       </c>
       <c r="D96">
-        <v>17582.35879292406</v>
-      </c>
-      <c r="E96">
-        <v>2834.246301528237</v>
+        <v>21420.33767860292</v>
       </c>
       <c r="F96">
-        <v>13103.47422138236</v>
+        <v>14382.04515098126</v>
       </c>
       <c r="G96">
-        <v>21249.08668753976</v>
+        <v>27458.98164180435</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3163,22 +3130,19 @@
         </is>
       </c>
       <c r="D97">
-        <v>4467.186042483597</v>
-      </c>
-      <c r="E97">
-        <v>629.3019169849349</v>
+        <v>8712.541203591623</v>
       </c>
       <c r="F97">
-        <v>3348.872890097372</v>
+        <v>4903.885199675899</v>
       </c>
       <c r="G97">
-        <v>5384.834948468118</v>
+        <v>12113.51229262429</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3192,22 +3156,19 @@
         </is>
       </c>
       <c r="D98">
-        <v>0</v>
-      </c>
-      <c r="E98">
-        <v>0</v>
+        <v>4938.846357791779</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>2588.140177960457</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>7209.424443559883</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3221,16 +3182,377 @@
         </is>
       </c>
       <c r="D99">
-        <v>0</v>
-      </c>
-      <c r="E99">
-        <v>0</v>
+        <v>3557.652830172036</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>1748.958911957898</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>5282.03935434891</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="D100">
+        <v>11123.64787044601</v>
+      </c>
+      <c r="F100">
+        <v>8221.21480149644</v>
+      </c>
+      <c r="G100">
+        <v>13495.71595579373</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="D101">
+        <v>4951.776969571572</v>
+      </c>
+      <c r="F101">
+        <v>3666.415856953488</v>
+      </c>
+      <c r="G101">
+        <v>6006.262634312626</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="D102">
+        <v>27424.16676629207</v>
+      </c>
+      <c r="F102">
+        <v>20260.16693682062</v>
+      </c>
+      <c r="G102">
+        <v>33263.69199424963</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="D103">
+        <v>9374.643061919149</v>
+      </c>
+      <c r="F103">
+        <v>6929.116048066413</v>
+      </c>
+      <c r="G103">
+        <v>11371.34350163655</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="D104">
+        <v>31340.60626758653</v>
+      </c>
+      <c r="F104">
+        <v>23178.57817198212</v>
+      </c>
+      <c r="G104">
+        <v>38100.58542918289</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="D105">
+        <v>12959.5832209349</v>
+      </c>
+      <c r="F105">
+        <v>9440.030700068635</v>
+      </c>
+      <c r="G105">
+        <v>15878.10396723663</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="D106">
+        <v>19177.99669028749</v>
+      </c>
+      <c r="F106">
+        <v>13889.29845434625</v>
+      </c>
+      <c r="G106">
+        <v>23575.88050603362</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="D107">
+        <v>8641.177048130347</v>
+      </c>
+      <c r="F107">
+        <v>6065.39070291527</v>
+      </c>
+      <c r="G107">
+        <v>10846.11535388343</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="D108">
+        <v>32382.39121917433</v>
+      </c>
+      <c r="F108">
+        <v>23060.98147825914</v>
+      </c>
+      <c r="G108">
+        <v>40208.80039546132</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="D109">
+        <v>15248.42922814298</v>
+      </c>
+      <c r="F109">
+        <v>10121.19535585014</v>
+      </c>
+      <c r="G109">
+        <v>19741.71689071353</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="D110">
+        <v>24843.42730167746</v>
+      </c>
+      <c r="F110">
+        <v>17278.63485947257</v>
+      </c>
+      <c r="G110">
+        <v>31371.48523420727</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="D111">
+        <v>14359.1173509739</v>
+      </c>
+      <c r="F111">
+        <v>9736.605180833478</v>
+      </c>
+      <c r="G111">
+        <v>18517.31085334914</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="D112">
+        <v>14696.76394778419</v>
+      </c>
+      <c r="F112">
+        <v>10825.60154933172</v>
+      </c>
+      <c r="G112">
+        <v>18382.2691203891</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="D113">
+        <v>14958.53023870037</v>
+      </c>
+      <c r="F113">
+        <v>11360.77437508401</v>
+      </c>
+      <c r="G113">
+        <v>18344.09088635373</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019_sex_age.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex_age.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,32 +362,72 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>age_grp10</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>sex</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>age_grp10</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases</t>
+          <t>tot_cases_mid</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_se</t>
+          <t>tot_cases_low</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_low</t>
+          <t>tot_cases_up</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_up</t>
+          <t>tot_daly_mid</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_mid</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_mid</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
         </is>
       </c>
     </row>
@@ -399,25 +439,49 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Female</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>20-24</t>
         </is>
       </c>
       <c r="D2">
         <v>33.73155556416154</v>
       </c>
       <c r="E2">
-        <v>6.058461012596456</v>
+        <v>28.44024711301454</v>
       </c>
       <c r="F2">
-        <v>28.44024711301454</v>
+        <v>38.65248452356747</v>
       </c>
       <c r="G2">
-        <v>38.65248452356747</v>
+        <v>359.1976900447485</v>
+      </c>
+      <c r="H2">
+        <v>302.7592819698499</v>
+      </c>
+      <c r="I2">
+        <v>411.6799576485938</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>47773292.77595156</v>
+      </c>
+      <c r="N2">
+        <v>40266984.50199004</v>
+      </c>
+      <c r="O2">
+        <v>54753434.36726297</v>
       </c>
     </row>
     <row r="3">
@@ -428,25 +492,49 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Male</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>20-24</t>
         </is>
       </c>
       <c r="D3">
         <v>71.9868300905522</v>
       </c>
       <c r="E3">
-        <v>13.49381683732895</v>
+        <v>61.61755327636659</v>
       </c>
       <c r="F3">
-        <v>61.61755327636659</v>
+        <v>81.68018995309556</v>
       </c>
       <c r="G3">
-        <v>81.68018995309556</v>
+        <v>691.501751833359</v>
+      </c>
+      <c r="H3">
+        <v>591.8893598842803</v>
+      </c>
+      <c r="I3">
+        <v>784.6233417882453</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>91969732.99383675</v>
+      </c>
+      <c r="N3">
+        <v>78721284.86460929</v>
+      </c>
+      <c r="O3">
+        <v>104354904.4578366</v>
       </c>
     </row>
     <row r="4">
@@ -457,25 +545,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Female</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>25-34</t>
         </is>
       </c>
       <c r="D4">
         <v>111.248360674411</v>
       </c>
       <c r="E4">
-        <v>19.5437939885089</v>
+        <v>94.0100053817347</v>
       </c>
       <c r="F4">
-        <v>94.0100053817347</v>
+        <v>127.2799759908105</v>
       </c>
       <c r="G4">
-        <v>127.2799759908105</v>
+        <v>1029.353703571502</v>
+      </c>
+      <c r="H4">
+        <v>870.0747929747733</v>
+      </c>
+      <c r="I4">
+        <v>1177.485469847092</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>136904042.5750098</v>
+      </c>
+      <c r="N4">
+        <v>115719947.4656449</v>
+      </c>
+      <c r="O4">
+        <v>156605567.4896633</v>
       </c>
     </row>
     <row r="5">
@@ -486,25 +598,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Male</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>25-34</t>
         </is>
       </c>
       <c r="D5">
         <v>162.3606868905531</v>
       </c>
       <c r="E5">
-        <v>28.46850170019018</v>
+        <v>138.568023757534</v>
       </c>
       <c r="F5">
-        <v>138.568023757534</v>
+        <v>184.5164712808136</v>
       </c>
       <c r="G5">
-        <v>184.5164712808136</v>
+        <v>1336.703097668464</v>
+      </c>
+      <c r="H5">
+        <v>1141.2902335964</v>
+      </c>
+      <c r="I5">
+        <v>1518.692754688266</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>177781511.9899057</v>
+      </c>
+      <c r="N5">
+        <v>151791601.0683212</v>
+      </c>
+      <c r="O5">
+        <v>201986136.3735393</v>
       </c>
     </row>
     <row r="6">
@@ -515,25 +651,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Female</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>35-44</t>
         </is>
       </c>
       <c r="D6">
         <v>316.4229238427401</v>
       </c>
       <c r="E6">
-        <v>56.2974896166387</v>
+        <v>268.4186428747261</v>
       </c>
       <c r="F6">
-        <v>268.4186428747261</v>
+        <v>361.0339753685875</v>
       </c>
       <c r="G6">
-        <v>361.0339753685875</v>
+        <v>2403.998713618664</v>
+      </c>
+      <c r="H6">
+        <v>2040.312296248112</v>
+      </c>
+      <c r="I6">
+        <v>2742.034483789603</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>319731828.9112823</v>
+      </c>
+      <c r="N6">
+        <v>271361535.4009989</v>
+      </c>
+      <c r="O6">
+        <v>364690586.3440172</v>
       </c>
     </row>
     <row r="7">
@@ -544,25 +704,49 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Male</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>35-44</t>
         </is>
       </c>
       <c r="D7">
         <v>543.1526933211968</v>
       </c>
       <c r="E7">
-        <v>101.4580245595181</v>
+        <v>458.6461092959026</v>
       </c>
       <c r="F7">
-        <v>458.6461092959026</v>
+        <v>621.5151942890192</v>
       </c>
       <c r="G7">
-        <v>621.5151942890192</v>
+        <v>3498.165503751029</v>
+      </c>
+      <c r="H7">
+        <v>2954.423756939525</v>
+      </c>
+      <c r="I7">
+        <v>4002.45213849572</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>465256011.9988868</v>
+      </c>
+      <c r="N7">
+        <v>392938359.6729568</v>
+      </c>
+      <c r="O7">
+        <v>532326134.4199308</v>
       </c>
     </row>
     <row r="8">
@@ -573,25 +757,49 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Female</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>45-54</t>
         </is>
       </c>
       <c r="D8">
         <v>561.2265710402642</v>
       </c>
       <c r="E8">
-        <v>88.81255927337929</v>
+        <v>479.5758006182195</v>
       </c>
       <c r="F8">
-        <v>479.5758006182195</v>
+        <v>637.48390410423</v>
       </c>
       <c r="G8">
-        <v>637.48390410423</v>
+        <v>3334.617144621437</v>
+      </c>
+      <c r="H8">
+        <v>2849.103662092875</v>
+      </c>
+      <c r="I8">
+        <v>3788.063644099511</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>443504080.2346511</v>
+      </c>
+      <c r="N8">
+        <v>378930787.0583524</v>
+      </c>
+      <c r="O8">
+        <v>503812464.6652349</v>
       </c>
     </row>
     <row r="9">
@@ -602,25 +810,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Male</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>45-54</t>
         </is>
       </c>
       <c r="D9">
         <v>952.9453181925342</v>
       </c>
       <c r="E9">
-        <v>166.6252813097423</v>
+        <v>809.761945248182</v>
       </c>
       <c r="F9">
-        <v>809.761945248182</v>
+        <v>1086.388371088974</v>
       </c>
       <c r="G9">
-        <v>1086.388371088974</v>
+        <v>4630.790004463996</v>
+      </c>
+      <c r="H9">
+        <v>3937.866993800328</v>
+      </c>
+      <c r="I9">
+        <v>5276.692038359389</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>615895070.5937114</v>
+      </c>
+      <c r="N9">
+        <v>523736310.1754436</v>
+      </c>
+      <c r="O9">
+        <v>701800041.1017987</v>
       </c>
     </row>
     <row r="10">
@@ -631,25 +863,49 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Female</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>55-64</t>
         </is>
       </c>
       <c r="D10">
         <v>1733.180758014774</v>
       </c>
       <c r="E10">
-        <v>269.2105935099418</v>
+        <v>1460.883246078769</v>
       </c>
       <c r="F10">
-        <v>1460.883246078769</v>
+        <v>1986.042448029276</v>
       </c>
       <c r="G10">
-        <v>1986.042448029276</v>
+        <v>7394.311597242272</v>
+      </c>
+      <c r="H10">
+        <v>6231.563673378272</v>
+      </c>
+      <c r="I10">
+        <v>8474.076369438657</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>983443442.4332222</v>
+      </c>
+      <c r="N10">
+        <v>828797968.5593102</v>
+      </c>
+      <c r="O10">
+        <v>1127052157.135341</v>
       </c>
     </row>
     <row r="11">
@@ -660,25 +916,49 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Male</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>55-64</t>
         </is>
       </c>
       <c r="D11">
         <v>2942.673655057622</v>
       </c>
       <c r="E11">
-        <v>445.7556997417301</v>
+        <v>2517.565189150537</v>
       </c>
       <c r="F11">
-        <v>2517.565189150537</v>
+        <v>3338.834816511353</v>
       </c>
       <c r="G11">
-        <v>3338.834816511353</v>
+        <v>9435.315583812251</v>
+      </c>
+      <c r="H11">
+        <v>8070.837992217282</v>
+      </c>
+      <c r="I11">
+        <v>10707.08491360095</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1254896972.647029</v>
+      </c>
+      <c r="N11">
+        <v>1073421452.964898</v>
+      </c>
+      <c r="O11">
+        <v>1424042293.508926</v>
       </c>
     </row>
     <row r="12">
@@ -689,25 +969,49 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Female</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>65-75</t>
         </is>
       </c>
       <c r="D12">
         <v>3423.089623074543</v>
       </c>
       <c r="E12">
-        <v>588.1957987650528</v>
+        <v>2896.589708491311</v>
       </c>
       <c r="F12">
-        <v>2896.589708491311</v>
+        <v>3912.503592402919</v>
       </c>
       <c r="G12">
-        <v>3912.503592402919</v>
+        <v>8893.413817349227</v>
+      </c>
+      <c r="H12">
+        <v>7526.342374301729</v>
+      </c>
+      <c r="I12">
+        <v>10164.12766497885</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1182824037.707447</v>
+      </c>
+      <c r="N12">
+        <v>1001003535.78213</v>
+      </c>
+      <c r="O12">
+        <v>1351828979.442188</v>
       </c>
     </row>
     <row r="13">
@@ -718,25 +1022,49 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Male</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>65-75</t>
         </is>
       </c>
       <c r="D13">
         <v>5646.576147382279</v>
       </c>
       <c r="E13">
-        <v>809.8761393516506</v>
+        <v>4832.719981157579</v>
       </c>
       <c r="F13">
-        <v>4832.719981157579</v>
+        <v>6403.798560724857</v>
       </c>
       <c r="G13">
-        <v>6403.798560724857</v>
+        <v>8501.366275351864</v>
+      </c>
+      <c r="H13">
+        <v>7264.351602977488</v>
+      </c>
+      <c r="I13">
+        <v>9651.877343700249</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1130681714.621798</v>
+      </c>
+      <c r="N13">
+        <v>966158763.1960059</v>
+      </c>
+      <c r="O13">
+        <v>1283699686.712133</v>
       </c>
     </row>
     <row r="14">
@@ -747,25 +1075,49 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Female</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>75-89</t>
         </is>
       </c>
       <c r="D14">
         <v>9757.91758999241</v>
       </c>
       <c r="E14">
-        <v>1522.6122194206</v>
+        <v>8237.46137137127</v>
       </c>
       <c r="F14">
-        <v>8237.46137137127</v>
+        <v>11172.84467682922</v>
       </c>
       <c r="G14">
-        <v>11172.84467682922</v>
+        <v>5177.347567577035</v>
+      </c>
+      <c r="H14">
+        <v>4386.921918459004</v>
+      </c>
+      <c r="I14">
+        <v>5914.577536462799</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>688587226.4877456</v>
+      </c>
+      <c r="N14">
+        <v>583460615.1550475</v>
+      </c>
+      <c r="O14">
+        <v>786638812.3495523</v>
       </c>
     </row>
     <row r="15">
@@ -776,2783 +1128,4501 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Male</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>75-89</t>
         </is>
       </c>
       <c r="D15">
         <v>11400.87740852834</v>
       </c>
       <c r="E15">
-        <v>1718.452853591265</v>
+        <v>9611.815463126108</v>
       </c>
       <c r="F15">
-        <v>9611.815463126108</v>
+        <v>13062.05153200482</v>
       </c>
       <c r="G15">
-        <v>13062.05153200482</v>
+        <v>862.1609989919623</v>
+      </c>
+      <c r="H15">
+        <v>720.6172635886692</v>
+      </c>
+      <c r="I15">
+        <v>993.1451306939399</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>114667412.865931</v>
+      </c>
+      <c r="N15">
+        <v>95842096.057293</v>
+      </c>
+      <c r="O15">
+        <v>132088302.382294</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D16">
-        <v>15.65844185747065</v>
+        <v>0.4811756832426659</v>
       </c>
       <c r="E16">
-        <v>2.890180037040302</v>
+        <v>0.0184027894946961</v>
       </c>
       <c r="F16">
-        <v>9.74655177552656</v>
+        <v>0.9743266721109717</v>
       </c>
       <c r="G16">
-        <v>21.43434993144515</v>
+        <v>0.3536293150686622</v>
+      </c>
+      <c r="H16">
+        <v>0.0101291958914045</v>
+      </c>
+      <c r="I16">
+        <v>0.9059464237880119</v>
+      </c>
+      <c r="J16">
+        <v>21213.5923471194</v>
+      </c>
+      <c r="K16">
+        <v>811.3237804526665</v>
+      </c>
+      <c r="L16">
+        <v>42955.13999335643</v>
+      </c>
+      <c r="M16">
+        <v>47032.69890413207</v>
+      </c>
+      <c r="N16">
+        <v>1347.183053556798</v>
+      </c>
+      <c r="O16">
+        <v>120490.8743638056</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D17">
-        <v>13.36527327769648</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>2.436930592064923</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>8.46062504224734</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>18.15701647163543</v>
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D18">
-        <v>39.64663127599601</v>
+        <v>14.78225957431938</v>
       </c>
       <c r="E18">
-        <v>7.040936122382409</v>
+        <v>0.3574409639769225</v>
       </c>
       <c r="F18">
-        <v>24.76763711923716</v>
+        <v>29.91338002803883</v>
       </c>
       <c r="G18">
-        <v>53.88797182871738</v>
+        <v>9.535234739210624</v>
+      </c>
+      <c r="H18">
+        <v>0.1725888337449444</v>
+      </c>
+      <c r="I18">
+        <v>24.41095407050661</v>
+      </c>
+      <c r="J18">
+        <v>651705.4778530187</v>
+      </c>
+      <c r="K18">
+        <v>15758.4997788506</v>
+      </c>
+      <c r="L18">
+        <v>1318791.185296148</v>
+      </c>
+      <c r="M18">
+        <v>1268186.220315013</v>
+      </c>
+      <c r="N18">
+        <v>22954.3148880776</v>
+      </c>
+      <c r="O18">
+        <v>3246656.891377379</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D19">
-        <v>35.25593542763083</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>5.922557359977524</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>22.32577375515558</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>47.71861311792934</v>
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D20">
-        <v>89.92931688675669</v>
+        <v>71.71405270548057</v>
       </c>
       <c r="E20">
-        <v>15.27551879712771</v>
+        <v>1.685219530159597</v>
       </c>
       <c r="F20">
-        <v>57.59782137204075</v>
+        <v>144.7678820645978</v>
       </c>
       <c r="G20">
-        <v>121.2435842505599</v>
+        <v>38.37585674864433</v>
+      </c>
+      <c r="H20">
+        <v>0.6553017863383896</v>
+      </c>
+      <c r="I20">
+        <v>98.00718317873748</v>
+      </c>
+      <c r="J20">
+        <v>3161657.441626522</v>
+      </c>
+      <c r="K20">
+        <v>74296.27342614617</v>
+      </c>
+      <c r="L20">
+        <v>6382381.616581927</v>
+      </c>
+      <c r="M20">
+        <v>5103988.947569696</v>
+      </c>
+      <c r="N20">
+        <v>87155.13758300582</v>
+      </c>
+      <c r="O20">
+        <v>13034955.36277208</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D21">
-        <v>176.4457595123615</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>33.90179298884983</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>110.8276447502678</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>239.8994294302815</v>
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D22">
-        <v>173.3946786358773</v>
+        <v>99.86136336436159</v>
       </c>
       <c r="E22">
-        <v>27.71731865410911</v>
+        <v>3.456337158669162</v>
       </c>
       <c r="F22">
-        <v>109.2906974255399</v>
+        <v>202.1224416530715</v>
       </c>
       <c r="G22">
-        <v>235.7344296584907</v>
+        <v>41.54024374891247</v>
+      </c>
+      <c r="H22">
+        <v>1.089324497072089</v>
+      </c>
+      <c r="I22">
+        <v>106.3782939086072</v>
+      </c>
+      <c r="J22">
+        <v>4402587.926644609</v>
+      </c>
+      <c r="K22">
+        <v>152379.5363142475</v>
+      </c>
+      <c r="L22">
+        <v>8910972.085158965</v>
+      </c>
+      <c r="M22">
+        <v>5524852.418605358</v>
+      </c>
+      <c r="N22">
+        <v>144880.1581105878</v>
+      </c>
+      <c r="O22">
+        <v>14148313.08984476</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D23">
-        <v>412.2557083152455</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>68.98702985067963</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>259.9980693449789</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>560.4674953450967</v>
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D24">
-        <v>730.4120622031838</v>
+        <v>200.6540472952413</v>
       </c>
       <c r="E24">
-        <v>116.1988517104469</v>
+        <v>3.643556405063075</v>
       </c>
       <c r="F24">
-        <v>460.2883165478444</v>
+        <v>405.8230902317031</v>
       </c>
       <c r="G24">
-        <v>988.994632368345</v>
+        <v>60.14218339964285</v>
+      </c>
+      <c r="H24">
+        <v>0.8285387312624466</v>
+      </c>
+      <c r="I24">
+        <v>153.9021209075388</v>
+      </c>
+      <c r="J24">
+        <v>8846234.983105302</v>
+      </c>
+      <c r="K24">
+        <v>160633.4712300158</v>
+      </c>
+      <c r="L24">
+        <v>17891522.5790451</v>
+      </c>
+      <c r="M24">
+        <v>7998910.392152499</v>
+      </c>
+      <c r="N24">
+        <v>110195.6512579054</v>
+      </c>
+      <c r="O24">
+        <v>20468982.08070267</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D25">
-        <v>1441.914395687903</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>211.930096182176</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>943.6286394136956</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>1913.000609634863</v>
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D26">
-        <v>1557.482495823861</v>
+        <v>251.6200954558331</v>
       </c>
       <c r="E26">
-        <v>255.5586543064512</v>
+        <v>5.629553202021572</v>
       </c>
       <c r="F26">
-        <v>982.5517338134912</v>
+        <v>508.8223091441347</v>
       </c>
       <c r="G26">
-        <v>2109.147933556491</v>
+        <v>47.41950463140582</v>
+      </c>
+      <c r="H26">
+        <v>0.7832655253959596</v>
+      </c>
+      <c r="I26">
+        <v>121.2980221681931</v>
+      </c>
+      <c r="J26">
+        <v>11093175.14836132</v>
+      </c>
+      <c r="K26">
+        <v>248190.1120175248</v>
+      </c>
+      <c r="L26">
+        <v>22432449.14323746</v>
+      </c>
+      <c r="M26">
+        <v>6306794.115976974</v>
+      </c>
+      <c r="N26">
+        <v>104174.3148776626</v>
+      </c>
+      <c r="O26">
+        <v>16132636.94836968</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D27">
-        <v>2127.464968288651</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>299.917616641968</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>1375.093056583348</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>2843.934629492145</v>
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D28">
-        <v>1961.830298526537</v>
+        <v>138.2776627984971</v>
       </c>
       <c r="E28">
-        <v>304.4379704480472</v>
+        <v>7.61124938183234</v>
       </c>
       <c r="F28">
-        <v>1205.221276941892</v>
+        <v>280.4335557123156</v>
       </c>
       <c r="G28">
-        <v>2707.722180944038</v>
+        <v>8.056121472218216</v>
+      </c>
+      <c r="H28">
+        <v>0.3018447192721767</v>
+      </c>
+      <c r="I28">
+        <v>20.67703070222404</v>
+      </c>
+      <c r="J28">
+        <v>6096247.319797342</v>
+      </c>
+      <c r="K28">
+        <v>335557.1514968425</v>
+      </c>
+      <c r="L28">
+        <v>12363474.17068886</v>
+      </c>
+      <c r="M28">
+        <v>1071464.155805023</v>
+      </c>
+      <c r="N28">
+        <v>40145.34766319949</v>
+      </c>
+      <c r="O28">
+        <v>2750045.083395798</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D29">
-        <v>1760.362006579208</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>266.9634864615925</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>1116.157840665361</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>2389.88750255974</v>
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D30">
-        <v>7.753489986796596</v>
+        <v>15.65844185747065</v>
       </c>
       <c r="E30">
-        <v>1.516999442875644</v>
+        <v>9.74655177552656</v>
       </c>
       <c r="F30">
-        <v>0.2965358579940802</v>
+        <v>21.43434993144515</v>
       </c>
       <c r="G30">
-        <v>15.69994569378816</v>
+        <v>10.86136084411592</v>
+      </c>
+      <c r="H30">
+        <v>5.305592588444431</v>
+      </c>
+      <c r="I30">
+        <v>18.1239674304828</v>
+      </c>
+      <c r="J30">
+        <v>872206.5283448303</v>
+      </c>
+      <c r="K30">
+        <v>542902.4270003805</v>
+      </c>
+      <c r="L30">
+        <v>1193936.159881358</v>
+      </c>
+      <c r="M30">
+        <v>1444560.992267417</v>
+      </c>
+      <c r="N30">
+        <v>705643.8142631094</v>
+      </c>
+      <c r="O30">
+        <v>2410487.668254213</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D31">
-        <v>4.791538675093026</v>
+        <v>13.36527327769648</v>
       </c>
       <c r="E31">
-        <v>0.9011903685245432</v>
+        <v>8.46062504224734</v>
       </c>
       <c r="F31">
-        <v>0.173721996363095</v>
+        <v>18.15701647163543</v>
       </c>
       <c r="G31">
-        <v>9.693295819211164</v>
+        <v>8.370378677242181</v>
+      </c>
+      <c r="H31">
+        <v>4.158937486452693</v>
+      </c>
+      <c r="I31">
+        <v>13.86110985945021</v>
+      </c>
+      <c r="J31">
+        <v>744472.4521142491</v>
+      </c>
+      <c r="K31">
+        <v>471273.7361032611</v>
+      </c>
+      <c r="L31">
+        <v>1011382.131503036</v>
+      </c>
+      <c r="M31">
+        <v>1113260.36407321</v>
+      </c>
+      <c r="N31">
+        <v>553138.6856982082</v>
+      </c>
+      <c r="O31">
+        <v>1843527.611306877</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D32">
-        <v>56.02709710526626</v>
+        <v>39.64663127599601</v>
       </c>
       <c r="E32">
-        <v>10.05772679205928</v>
+        <v>24.76763711923716</v>
       </c>
       <c r="F32">
-        <v>1.354757674051808</v>
+        <v>53.88797182871738</v>
       </c>
       <c r="G32">
-        <v>113.3764320097071</v>
+        <v>24.14052571481144</v>
+      </c>
+      <c r="H32">
+        <v>11.83965255904364</v>
+      </c>
+      <c r="I32">
+        <v>39.9899109339809</v>
+      </c>
+      <c r="J32">
+        <v>2208396.655335527</v>
+      </c>
+      <c r="K32">
+        <v>1379606.922815748</v>
+      </c>
+      <c r="L32">
+        <v>3001667.806803215</v>
+      </c>
+      <c r="M32">
+        <v>3210689.920069922</v>
+      </c>
+      <c r="N32">
+        <v>1574673.790352805</v>
+      </c>
+      <c r="O32">
+        <v>5318658.15421946</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D33">
-        <v>21.12993950627974</v>
+        <v>35.25593542763083</v>
       </c>
       <c r="E33">
-        <v>3.620608063180764</v>
+        <v>22.32577375515558</v>
       </c>
       <c r="F33">
-        <v>0.5609879070726218</v>
+        <v>47.71861311792934</v>
       </c>
       <c r="G33">
-        <v>42.65319813169481</v>
+        <v>19.02298143870285</v>
+      </c>
+      <c r="H33">
+        <v>9.458138854840872</v>
+      </c>
+      <c r="I33">
+        <v>31.3804242114227</v>
+      </c>
+      <c r="J33">
+        <v>1963826.115189891</v>
+      </c>
+      <c r="K33">
+        <v>1243590.249709676</v>
+      </c>
+      <c r="L33">
+        <v>2658022.1878949</v>
+      </c>
+      <c r="M33">
+        <v>2530056.531347479</v>
+      </c>
+      <c r="N33">
+        <v>1257932.467693836</v>
+      </c>
+      <c r="O33">
+        <v>4173596.420119219</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D34">
-        <v>154.7223093218356</v>
+        <v>89.92931688675669</v>
       </c>
       <c r="E34">
-        <v>25.74500400236991</v>
+        <v>57.59782137204075</v>
       </c>
       <c r="F34">
-        <v>3.63584329129158</v>
+        <v>121.2435842505599</v>
       </c>
       <c r="G34">
-        <v>312.3351725868083</v>
+        <v>45.36740283139999</v>
+      </c>
+      <c r="H34">
+        <v>22.82474422823565</v>
+      </c>
+      <c r="I34">
+        <v>74.51505593706531</v>
+      </c>
+      <c r="J34">
+        <v>5009242.809226119</v>
+      </c>
+      <c r="K34">
+        <v>3208313.846065413</v>
+      </c>
+      <c r="L34">
+        <v>6753510.129924685</v>
+      </c>
+      <c r="M34">
+        <v>6033864.576576199</v>
+      </c>
+      <c r="N34">
+        <v>3035690.982355341</v>
+      </c>
+      <c r="O34">
+        <v>9910502.439629687</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D35">
-        <v>95.12402916810167</v>
+        <v>176.4457595123615</v>
       </c>
       <c r="E35">
-        <v>19.25270420578076</v>
+        <v>110.8276447502678</v>
       </c>
       <c r="F35">
-        <v>2.865858057138944</v>
+        <v>239.8994294302815</v>
       </c>
       <c r="G35">
-        <v>192.1553202415448</v>
+        <v>75.25001782581086</v>
+      </c>
+      <c r="H35">
+        <v>37.09079540609216</v>
+      </c>
+      <c r="I35">
+        <v>124.7417972915256</v>
+      </c>
+      <c r="J35">
+        <v>9828381.696357548</v>
+      </c>
+      <c r="K35">
+        <v>6173321.467879418</v>
+      </c>
+      <c r="L35">
+        <v>13362878.01812555</v>
+      </c>
+      <c r="M35">
+        <v>10008252.37083284</v>
+      </c>
+      <c r="N35">
+        <v>4933075.789010257</v>
+      </c>
+      <c r="O35">
+        <v>16590659.0397729</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D36">
-        <v>207.3307400341226</v>
+        <v>173.3946786358773</v>
       </c>
       <c r="E36">
-        <v>34.28214259560028</v>
+        <v>109.2906974255399</v>
       </c>
       <c r="F36">
-        <v>7.175997971304034</v>
+        <v>235.7344296584907</v>
       </c>
       <c r="G36">
-        <v>419.6437340088478</v>
+        <v>68.1884798753934</v>
+      </c>
+      <c r="H36">
+        <v>33.7204959600146</v>
+      </c>
+      <c r="I36">
+        <v>113.0299870038063</v>
+      </c>
+      <c r="J36">
+        <v>9658430.389375642</v>
+      </c>
+      <c r="K36">
+        <v>6087710.427997423</v>
+      </c>
+      <c r="L36">
+        <v>13130879.20083725</v>
+      </c>
+      <c r="M36">
+        <v>9069067.823427321</v>
+      </c>
+      <c r="N36">
+        <v>4484825.962681942</v>
+      </c>
+      <c r="O36">
+        <v>15032988.27150624</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D37">
-        <v>203.3160003961902</v>
+        <v>412.2557083152455</v>
       </c>
       <c r="E37">
-        <v>33.7898154218939</v>
+        <v>259.9980693449789</v>
       </c>
       <c r="F37">
-        <v>6.783166473679788</v>
+        <v>560.4674953450967</v>
       </c>
       <c r="G37">
-        <v>411.5187447474956</v>
+        <v>133.5942475225474</v>
+      </c>
+      <c r="H37">
+        <v>66.13697227687024</v>
+      </c>
+      <c r="I37">
+        <v>221.3690107587159</v>
+      </c>
+      <c r="J37">
+        <v>22963467.4645758</v>
+      </c>
+      <c r="K37">
+        <v>14482412.45865401</v>
+      </c>
+      <c r="L37">
+        <v>31219160.42571257</v>
+      </c>
+      <c r="M37">
+        <v>17768034.92049881</v>
+      </c>
+      <c r="N37">
+        <v>8796217.312823743</v>
+      </c>
+      <c r="O37">
+        <v>29442078.43090922</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D38">
-        <v>556.5873096343158</v>
+        <v>730.4120622031838</v>
       </c>
       <c r="E38">
-        <v>89.83905234014546</v>
+        <v>460.2883165478444</v>
       </c>
       <c r="F38">
-        <v>10.10673487194112</v>
+        <v>988.994632368345</v>
       </c>
       <c r="G38">
-        <v>1125.698609244572</v>
+        <v>206.6503539955195</v>
+      </c>
+      <c r="H38">
+        <v>102.2143807648071</v>
+      </c>
+      <c r="I38">
+        <v>341.1096367567193</v>
+      </c>
+      <c r="J38">
+        <v>40685412.6888418</v>
+      </c>
+      <c r="K38">
+        <v>25638979.80834805</v>
+      </c>
+      <c r="L38">
+        <v>55088979.01218158</v>
+      </c>
+      <c r="M38">
+        <v>27484497.08140409</v>
+      </c>
+      <c r="N38">
+        <v>13594512.64171934</v>
+      </c>
+      <c r="O38">
+        <v>45367581.68864367</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D39">
-        <v>881.107107175667</v>
+        <v>1441.914395687903</v>
       </c>
       <c r="E39">
-        <v>124.8072072443794</v>
+        <v>943.6286394136956</v>
       </c>
       <c r="F39">
-        <v>-1.136049345829136</v>
+        <v>1913.000609634863</v>
       </c>
       <c r="G39">
-        <v>1778.29107582161</v>
+        <v>309.2683466556646</v>
+      </c>
+      <c r="H39">
+        <v>158.5768341074325</v>
+      </c>
+      <c r="I39">
+        <v>500.704615643464</v>
+      </c>
+      <c r="J39">
+        <v>80317515.66860761</v>
+      </c>
+      <c r="K39">
+        <v>52562002.47262167</v>
+      </c>
+      <c r="L39">
+        <v>106557959.9578812</v>
+      </c>
+      <c r="M39">
+        <v>41132690.10520339</v>
+      </c>
+      <c r="N39">
+        <v>21090718.93628852</v>
+      </c>
+      <c r="O39">
+        <v>66593713.88058071</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D40">
-        <v>750.8933789186796</v>
+        <v>1557.482495823861</v>
       </c>
       <c r="E40">
-        <v>120.9135288756254</v>
+        <v>982.5517338134912</v>
       </c>
       <c r="F40">
-        <v>16.7999070901332</v>
+        <v>2109.147933556491</v>
       </c>
       <c r="G40">
-        <v>1518.445107853114</v>
+        <v>276.3820045261133</v>
+      </c>
+      <c r="H40">
+        <v>137.0364657882728</v>
+      </c>
+      <c r="I40">
+        <v>455.9821824004919</v>
+      </c>
+      <c r="J40">
+        <v>86754889.98238067</v>
+      </c>
+      <c r="K40">
+        <v>54730096.67687915</v>
+      </c>
+      <c r="L40">
+        <v>117483758.1949636</v>
+      </c>
+      <c r="M40">
+        <v>36758806.60197306</v>
+      </c>
+      <c r="N40">
+        <v>18225849.94984028</v>
+      </c>
+      <c r="O40">
+        <v>60645630.25926542</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D41">
-        <v>814.864076114769</v>
+        <v>2127.464968288651</v>
       </c>
       <c r="E41">
-        <v>114.9101932830803</v>
+        <v>1375.093056583348</v>
       </c>
       <c r="F41">
-        <v>9.063068411180476</v>
+        <v>2843.934629492145</v>
       </c>
       <c r="G41">
-        <v>1642.594633824997</v>
+        <v>225.8249041166049</v>
+      </c>
+      <c r="H41">
+        <v>114.8090309965968</v>
+      </c>
+      <c r="I41">
+        <v>367.6648511820628</v>
+      </c>
+      <c r="J41">
+        <v>118504053.6636145</v>
+      </c>
+      <c r="K41">
+        <v>76595433.43780571</v>
+      </c>
+      <c r="L41">
+        <v>158412846.7319715</v>
+      </c>
+      <c r="M41">
+        <v>30034712.24750845</v>
+      </c>
+      <c r="N41">
+        <v>15269601.12254738</v>
+      </c>
+      <c r="O41">
+        <v>48899425.20721435</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D42">
-        <v>613.9100792520594</v>
+        <v>1961.830298526537</v>
       </c>
       <c r="E42">
-        <v>94.02178536654297</v>
+        <v>1205.221276941892</v>
       </c>
       <c r="F42">
-        <v>33.79159451094418</v>
+        <v>2707.722180944038</v>
       </c>
       <c r="G42">
-        <v>1245.038301400591</v>
+        <v>107.5512614393857</v>
+      </c>
+      <c r="H42">
+        <v>51.91584374776237</v>
+      </c>
+      <c r="I42">
+        <v>180.6289560122385</v>
+      </c>
+      <c r="J42">
+        <v>109277871.2885252</v>
+      </c>
+      <c r="K42">
+        <v>67133235.56821728</v>
+      </c>
+      <c r="L42">
+        <v>150825540.9229448</v>
+      </c>
+      <c r="M42">
+        <v>14304317.7714383</v>
+      </c>
+      <c r="N42">
+        <v>6904807.218452395</v>
+      </c>
+      <c r="O42">
+        <v>24023651.14962772</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D43">
-        <v>509.2366163555211</v>
+        <v>1760.362006579208</v>
       </c>
       <c r="E43">
-        <v>79.84383600196131</v>
+        <v>1116.157840665361</v>
       </c>
       <c r="F43">
-        <v>15.9254000057911</v>
+        <v>2389.88750255974</v>
       </c>
       <c r="G43">
-        <v>1029.215143777309</v>
+        <v>14.85124574767428</v>
+      </c>
+      <c r="H43">
+        <v>7.289259211316919</v>
+      </c>
+      <c r="I43">
+        <v>24.72403846638741</v>
+      </c>
+      <c r="J43">
+        <v>98055684.49047504</v>
+      </c>
+      <c r="K43">
+        <v>62172224.04074202</v>
+      </c>
+      <c r="L43">
+        <v>133121513.6675825</v>
+      </c>
+      <c r="M43">
+        <v>1975215.684440679</v>
+      </c>
+      <c r="N43">
+        <v>969471.4751051503</v>
+      </c>
+      <c r="O43">
+        <v>3288297.116029526</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D44">
-        <v>26.37472421520761</v>
+        <v>7.753489986796596</v>
       </c>
       <c r="E44">
-        <v>5.17432270341177</v>
+        <v>0.2965358579940802</v>
       </c>
       <c r="F44">
-        <v>-0.6435224407938687</v>
+        <v>15.69994569378816</v>
       </c>
       <c r="G44">
-        <v>49.29046714330751</v>
+        <v>4.616127858763421</v>
+      </c>
+      <c r="H44">
+        <v>0.1390944302312838</v>
+      </c>
+      <c r="I44">
+        <v>10.79334840649877</v>
+      </c>
+      <c r="J44">
+        <v>114805.9262344972</v>
+      </c>
+      <c r="K44">
+        <v>4390.80644931835</v>
+      </c>
+      <c r="L44">
+        <v>232469.0958879214</v>
+      </c>
+      <c r="M44">
+        <v>613945.0052155349</v>
+      </c>
+      <c r="N44">
+        <v>18499.55922076074</v>
+      </c>
+      <c r="O44">
+        <v>1435515.338064336</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D45">
-        <v>18.84992961181364</v>
+        <v>4.791538675093026</v>
       </c>
       <c r="E45">
-        <v>3.550344611599527</v>
+        <v>0.173721996363095</v>
       </c>
       <c r="F45">
-        <v>-0.4338878519107666</v>
+        <v>9.693295819211164</v>
       </c>
       <c r="G45">
-        <v>35.13719808486548</v>
+        <v>2.574925055211647</v>
+      </c>
+      <c r="H45">
+        <v>0.07353714318230664</v>
+      </c>
+      <c r="I45">
+        <v>6.014984526210608</v>
+      </c>
+      <c r="J45">
+        <v>70948.31316210247</v>
+      </c>
+      <c r="K45">
+        <v>2572.301600148348</v>
+      </c>
+      <c r="L45">
+        <v>143528.6311950597</v>
+      </c>
+      <c r="M45">
+        <v>342465.0323431491</v>
+      </c>
+      <c r="N45">
+        <v>9780.440043246783</v>
+      </c>
+      <c r="O45">
+        <v>799992.9419860108</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D46">
-        <v>91.63650096592163</v>
+        <v>56.02709710526626</v>
       </c>
       <c r="E46">
-        <v>16.45507177666171</v>
+        <v>1.354757674051808</v>
       </c>
       <c r="F46">
-        <v>-1.85723965753136</v>
+        <v>113.3764320097071</v>
       </c>
       <c r="G46">
-        <v>170.5641544868471</v>
+        <v>29.27687355647484</v>
+      </c>
+      <c r="H46">
+        <v>0.5574567803126325</v>
+      </c>
+      <c r="I46">
+        <v>68.40725649829207</v>
+      </c>
+      <c r="J46">
+        <v>829593.226837678</v>
+      </c>
+      <c r="K46">
+        <v>20059.89687968514</v>
+      </c>
+      <c r="L46">
+        <v>1678764.828767733</v>
+      </c>
+      <c r="M46">
+        <v>3893824.183011154</v>
+      </c>
+      <c r="N46">
+        <v>74141.75178158011</v>
+      </c>
+      <c r="O46">
+        <v>9098165.114272846</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D47">
-        <v>49.493021259959</v>
+        <v>21.12993950627974</v>
       </c>
       <c r="E47">
-        <v>8.479948909340782</v>
+        <v>0.5609879070726218</v>
       </c>
       <c r="F47">
-        <v>-0.9651030906547192</v>
+        <v>42.65319813169481</v>
       </c>
       <c r="G47">
-        <v>92.03233205733679</v>
+        <v>9.781673915024305</v>
+      </c>
+      <c r="H47">
+        <v>0.2046407803271518</v>
+      </c>
+      <c r="I47">
+        <v>22.79919207565393</v>
+      </c>
+      <c r="J47">
+        <v>312871.014269484</v>
+      </c>
+      <c r="K47">
+        <v>8306.547940024313</v>
+      </c>
+      <c r="L47">
+        <v>631565.9047360052</v>
+      </c>
+      <c r="M47">
+        <v>1300962.630698232</v>
+      </c>
+      <c r="N47">
+        <v>27217.22378351118</v>
+      </c>
+      <c r="O47">
+        <v>3032292.546061973</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D48">
-        <v>211.9590256878334</v>
+        <v>154.7223093218356</v>
       </c>
       <c r="E48">
-        <v>35.25283490076471</v>
+        <v>3.63584329129158</v>
       </c>
       <c r="F48">
-        <v>-3.673698331469673</v>
+        <v>312.3351725868083</v>
       </c>
       <c r="G48">
-        <v>391.3266690642212</v>
+        <v>67.07223343082113</v>
+      </c>
+      <c r="H48">
+        <v>1.204845155244067</v>
+      </c>
+      <c r="I48">
+        <v>156.3387742849098</v>
+      </c>
+      <c r="J48">
+        <v>2290973.234128423</v>
+      </c>
+      <c r="K48">
+        <v>53835.93161415438</v>
+      </c>
+      <c r="L48">
+        <v>4624746.900492872</v>
+      </c>
+      <c r="M48">
+        <v>8920607.04629921</v>
+      </c>
+      <c r="N48">
+        <v>160244.405647461</v>
+      </c>
+      <c r="O48">
+        <v>20793056.979893</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D49">
-        <v>210.3446424449039</v>
+        <v>95.12402916810167</v>
       </c>
       <c r="E49">
-        <v>42.60164601386627</v>
+        <v>2.865858057138944</v>
       </c>
       <c r="F49">
-        <v>-4.364551261876571</v>
+        <v>192.1553202415448</v>
       </c>
       <c r="G49">
-        <v>391.321635417835</v>
+        <v>34.75977793927188</v>
+      </c>
+      <c r="H49">
+        <v>0.8398536427830877</v>
+      </c>
+      <c r="I49">
+        <v>81.08694221307705</v>
+      </c>
+      <c r="J49">
+        <v>1408501.499892083</v>
+      </c>
+      <c r="K49">
+        <v>42434.76025205635</v>
+      </c>
+      <c r="L49">
+        <v>2845243.826816553</v>
+      </c>
+      <c r="M49">
+        <v>4623050.465923159</v>
+      </c>
+      <c r="N49">
+        <v>111700.5344901507</v>
+      </c>
+      <c r="O49">
+        <v>10784563.31433925</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D50">
-        <v>316.025032749713</v>
+        <v>207.3307400341226</v>
       </c>
       <c r="E50">
-        <v>52.34811425371102</v>
+        <v>7.175997971304034</v>
       </c>
       <c r="F50">
-        <v>-7.284284640573616</v>
+        <v>419.6437340088478</v>
       </c>
       <c r="G50">
-        <v>589.4137693367397</v>
+        <v>69.8668653078319</v>
+      </c>
+      <c r="H50">
+        <v>1.927368195245277</v>
+      </c>
+      <c r="I50">
+        <v>163.2974301607178</v>
+      </c>
+      <c r="J50">
+        <v>3069946.267685253</v>
+      </c>
+      <c r="K50">
+        <v>106255.0019610988</v>
+      </c>
+      <c r="L50">
+        <v>6213664.769469017</v>
+      </c>
+      <c r="M50">
+        <v>9292293.085941643</v>
+      </c>
+      <c r="N50">
+        <v>256339.9699676218</v>
+      </c>
+      <c r="O50">
+        <v>21718558.21137546</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D51">
-        <v>349.3889145684437</v>
+        <v>203.3160003961902</v>
       </c>
       <c r="E51">
-        <v>58.08011968257829</v>
+        <v>6.783166473679788</v>
       </c>
       <c r="F51">
-        <v>-7.824514599269855</v>
+        <v>411.5187447474956</v>
       </c>
       <c r="G51">
-        <v>650.5107843701344</v>
+        <v>56.45953122717071</v>
+      </c>
+      <c r="H51">
+        <v>1.503039251990599</v>
+      </c>
+      <c r="I51">
+        <v>131.9510565066432</v>
+      </c>
+      <c r="J51">
+        <v>3010500.01786639</v>
+      </c>
+      <c r="K51">
+        <v>100438.3459757767</v>
+      </c>
+      <c r="L51">
+        <v>6093358.053476171</v>
+      </c>
+      <c r="M51">
+        <v>7509117.653213705</v>
+      </c>
+      <c r="N51">
+        <v>199904.2205147496</v>
+      </c>
+      <c r="O51">
+        <v>17549490.51538355</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D52">
-        <v>1007.550981633505</v>
+        <v>556.5873096343158</v>
       </c>
       <c r="E52">
-        <v>162.7373369475614</v>
+        <v>10.10673487194112</v>
       </c>
       <c r="F52">
-        <v>-17.47600994823951</v>
+        <v>1125.698609244572</v>
       </c>
       <c r="G52">
-        <v>1863.821466713548</v>
+        <v>135.1451851459087</v>
+      </c>
+      <c r="H52">
+        <v>1.958571370603013</v>
+      </c>
+      <c r="I52">
+        <v>315.6385963050998</v>
+      </c>
+      <c r="J52">
+        <v>8241388.293755315</v>
+      </c>
+      <c r="K52">
+        <v>149650.4232488321</v>
+      </c>
+      <c r="L52">
+        <v>16668219.3070844</v>
+      </c>
+      <c r="M52">
+        <v>17974309.62440585</v>
+      </c>
+      <c r="N52">
+        <v>260489.9922902007</v>
+      </c>
+      <c r="O52">
+        <v>41979933.30857828</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D53">
-        <v>1126.976775001094</v>
+        <v>881.107107175667</v>
       </c>
       <c r="E53">
-        <v>159.625644554717</v>
+        <v>-1.136049345829136</v>
       </c>
       <c r="F53">
-        <v>-10.14003776751773</v>
+        <v>1778.29107582161</v>
       </c>
       <c r="G53">
-        <v>2053.891895047056</v>
+        <v>161.371116360344</v>
+      </c>
+      <c r="H53">
+        <v>-0.02654216879805724</v>
+      </c>
+      <c r="I53">
+        <v>376.1382164519218</v>
+      </c>
+      <c r="J53">
+        <v>13046552.93595009</v>
+      </c>
+      <c r="K53">
+        <v>-16821.48266369192</v>
+      </c>
+      <c r="L53">
+        <v>26331155.95969056</v>
+      </c>
+      <c r="M53">
+        <v>21462358.47592575</v>
+      </c>
+      <c r="N53">
+        <v>-3530.108450141614</v>
+      </c>
+      <c r="O53">
+        <v>50026382.7881056</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D54">
-        <v>1114.092762092152</v>
+        <v>750.8933789186796</v>
       </c>
       <c r="E54">
-        <v>179.3443259710884</v>
+        <v>16.7999070901332</v>
       </c>
       <c r="F54">
-        <v>-20.79611135804836</v>
+        <v>1518.445107853114</v>
       </c>
       <c r="G54">
-        <v>2064.422780222847</v>
+        <v>114.6373071614391</v>
+      </c>
+      <c r="H54">
+        <v>1.991971750396658</v>
+      </c>
+      <c r="I54">
+        <v>267.6373950550436</v>
+      </c>
+      <c r="J54">
+        <v>11118478.26164889</v>
+      </c>
+      <c r="K54">
+        <v>248756.2242836022</v>
+      </c>
+      <c r="L54">
+        <v>22483616.71198107</v>
+      </c>
+      <c r="M54">
+        <v>15246761.8524714</v>
+      </c>
+      <c r="N54">
+        <v>264932.2428027556</v>
+      </c>
+      <c r="O54">
+        <v>35595773.5423208</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D55">
-        <v>1049.538758709682</v>
+        <v>814.864076114769</v>
       </c>
       <c r="E55">
-        <v>148.1028680912809</v>
+        <v>9.063068411180476</v>
       </c>
       <c r="F55">
-        <v>-13.64844790195101</v>
+        <v>1642.594633824997</v>
       </c>
       <c r="G55">
-        <v>1927.985490450226</v>
+        <v>74.7712015258212</v>
+      </c>
+      <c r="H55">
+        <v>0.5858860975933923</v>
+      </c>
+      <c r="I55">
+        <v>174.0509183961958</v>
+      </c>
+      <c r="J55">
+        <v>12065692.37503138</v>
+      </c>
+      <c r="K55">
+        <v>134196.8539643494</v>
+      </c>
+      <c r="L55">
+        <v>24321898.74304673</v>
+      </c>
+      <c r="M55">
+        <v>9944569.80293422</v>
+      </c>
+      <c r="N55">
+        <v>77922.85097992118</v>
+      </c>
+      <c r="O55">
+        <v>23148772.14669405</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D56">
-        <v>470.0037282158446</v>
+        <v>613.9100792520594</v>
       </c>
       <c r="E56">
-        <v>71.98314771040324</v>
+        <v>33.79159451094418</v>
       </c>
       <c r="F56">
-        <v>-14.63751464114057</v>
+        <v>1245.038301400591</v>
       </c>
       <c r="G56">
-        <v>887.9384426484394</v>
+        <v>28.97441994317001</v>
+      </c>
+      <c r="H56">
+        <v>1.142030037195692</v>
+      </c>
+      <c r="I56">
+        <v>67.87362247830248</v>
+      </c>
+      <c r="J56">
+        <v>9090166.543485235</v>
+      </c>
+      <c r="K56">
+        <v>500352.13992355</v>
+      </c>
+      <c r="L56">
+        <v>18435282.12883855</v>
+      </c>
+      <c r="M56">
+        <v>3853597.852441611</v>
+      </c>
+      <c r="N56">
+        <v>151889.994947027</v>
+      </c>
+      <c r="O56">
+        <v>9027191.78961423</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D57">
-        <v>418.323516331683</v>
+        <v>509.2366163555211</v>
       </c>
       <c r="E57">
-        <v>65.67410629447623</v>
+        <v>15.9254000057911</v>
       </c>
       <c r="F57">
-        <v>-8.431541213566685</v>
+        <v>1029.215143777309</v>
       </c>
       <c r="G57">
-        <v>774.4861830395084</v>
+        <v>3.61918452564459</v>
+      </c>
+      <c r="H57">
+        <v>0.0996458478201723</v>
+      </c>
+      <c r="I57">
+        <v>8.449931602280962</v>
+      </c>
+      <c r="J57">
+        <v>7540266.578376192</v>
+      </c>
+      <c r="K57">
+        <v>235807.3978857488</v>
+      </c>
+      <c r="L57">
+        <v>15239588.63391061</v>
+      </c>
+      <c r="M57">
+        <v>481351.5419107305</v>
+      </c>
+      <c r="N57">
+        <v>13252.89776008292</v>
+      </c>
+      <c r="O57">
+        <v>1123840.903103368</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D58">
-        <v>0</v>
+        <v>26.37472421520761</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>-0.6435224407938687</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>49.29046714330751</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>19.38922256952089</v>
+      </c>
+      <c r="H58">
+        <v>-0.3513052045093759</v>
+      </c>
+      <c r="I58">
+        <v>46.00028425227256</v>
+      </c>
+      <c r="J58">
+        <v>1983405.635707828</v>
+      </c>
+      <c r="K58">
+        <v>-48393.53107013973</v>
+      </c>
+      <c r="L58">
+        <v>3706692.41964387</v>
+      </c>
+      <c r="M58">
+        <v>2578766.601746278</v>
+      </c>
+      <c r="N58">
+        <v>-46723.59219974699</v>
+      </c>
+      <c r="O58">
+        <v>6118037.805552251</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D59">
-        <v>0</v>
+        <v>18.84992961181364</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>-0.4338878519107666</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>35.13719808486548</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>12.50798449093572</v>
+      </c>
+      <c r="H59">
+        <v>-0.2138049486193068</v>
+      </c>
+      <c r="I59">
+        <v>29.60043390068797</v>
+      </c>
+      <c r="J59">
+        <v>1417533.556737998</v>
+      </c>
+      <c r="K59">
+        <v>-32628.80035154156</v>
+      </c>
+      <c r="L59">
+        <v>2642352.433179968</v>
+      </c>
+      <c r="M59">
+        <v>1663561.93729445</v>
+      </c>
+      <c r="N59">
+        <v>-28436.05816636781</v>
+      </c>
+      <c r="O59">
+        <v>3936857.7087915</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D60">
-        <v>0</v>
+        <v>91.63650096592163</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>-1.85723965753136</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>170.5641544868471</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>59.12435885743663</v>
+      </c>
+      <c r="H60">
+        <v>-0.8893156782105415</v>
+      </c>
+      <c r="I60">
+        <v>139.7076600583434</v>
+      </c>
+      <c r="J60">
+        <v>6891156.50913828</v>
+      </c>
+      <c r="K60">
+        <v>-139666.2794860157</v>
+      </c>
+      <c r="L60">
+        <v>12826594.98156539</v>
+      </c>
+      <c r="M60">
+        <v>7863539.728039072</v>
+      </c>
+      <c r="N60">
+        <v>-118278.985202002</v>
+      </c>
+      <c r="O60">
+        <v>18581118.78775967</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D61">
-        <v>0</v>
+        <v>49.493021259959</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>-0.9651030906547192</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>92.03233205733679</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>28.28998274065563</v>
+      </c>
+      <c r="H61">
+        <v>-0.4094729168839421</v>
+      </c>
+      <c r="I61">
+        <v>66.78765936342241</v>
+      </c>
+      <c r="J61">
+        <v>3721924.69177018</v>
+      </c>
+      <c r="K61">
+        <v>-72576.71752032555</v>
+      </c>
+      <c r="L61">
+        <v>6920923.403043785</v>
+      </c>
+      <c r="M61">
+        <v>3762567.7045072</v>
+      </c>
+      <c r="N61">
+        <v>-54459.8979455643</v>
+      </c>
+      <c r="O61">
+        <v>8882758.69533518</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D62">
-        <v>0.752693498956816</v>
+        <v>211.9590256878334</v>
       </c>
       <c r="E62">
-        <v>0.1287694653428949</v>
+        <v>-3.673698331469673</v>
       </c>
       <c r="F62">
-        <v>0.5451580658020282</v>
+        <v>391.3266690642212</v>
       </c>
       <c r="G62">
-        <v>0.9371774707816141</v>
+        <v>113.4595903524618</v>
+      </c>
+      <c r="H62">
+        <v>-1.440706609502771</v>
+      </c>
+      <c r="I62">
+        <v>265.8563161282482</v>
+      </c>
+      <c r="J62">
+        <v>15939530.69075076</v>
+      </c>
+      <c r="K62">
+        <v>-276265.7882248508</v>
+      </c>
+      <c r="L62">
+        <v>29428156.84029851</v>
+      </c>
+      <c r="M62">
+        <v>15090125.51687742</v>
+      </c>
+      <c r="N62">
+        <v>-191613.9790638686</v>
+      </c>
+      <c r="O62">
+        <v>35358890.04505701</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D63">
-        <v>1.870649334246026</v>
+        <v>210.3446424449039</v>
       </c>
       <c r="E63">
-        <v>0.3575951546425103</v>
+        <v>-4.364551261876571</v>
       </c>
       <c r="F63">
-        <v>1.35119886828296</v>
+        <v>391.321635417835</v>
       </c>
       <c r="G63">
-        <v>2.331339705285234</v>
+        <v>94.90880028415972</v>
+      </c>
+      <c r="H63">
+        <v>-1.477838457590684</v>
+      </c>
+      <c r="I63">
+        <v>224.2243824351148</v>
+      </c>
+      <c r="J63">
+        <v>15818127.45649923</v>
+      </c>
+      <c r="K63">
+        <v>-328218.61944438</v>
+      </c>
+      <c r="L63">
+        <v>29427778.3050566</v>
+      </c>
+      <c r="M63">
+        <v>12622870.43779324</v>
+      </c>
+      <c r="N63">
+        <v>-196552.5148595609</v>
+      </c>
+      <c r="O63">
+        <v>29821842.86387027</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D64">
-        <v>6.715569815673259</v>
+        <v>316.025032749713</v>
       </c>
       <c r="E64">
-        <v>1.072386449352358</v>
+        <v>-7.284284640573616</v>
       </c>
       <c r="F64">
-        <v>4.87186231668871</v>
+        <v>589.4137693367397</v>
       </c>
       <c r="G64">
-        <v>8.360004456824004</v>
+        <v>131.4929706221666</v>
+      </c>
+      <c r="H64">
+        <v>-2.267323926179421</v>
+      </c>
+      <c r="I64">
+        <v>311.4405900708423</v>
+      </c>
+      <c r="J64">
+        <v>23765398.48781117</v>
+      </c>
+      <c r="K64">
+        <v>-547785.4892557764</v>
+      </c>
+      <c r="L64">
+        <v>44324504.86789218</v>
+      </c>
+      <c r="M64">
+        <v>17488565.09274816</v>
+      </c>
+      <c r="N64">
+        <v>-301554.082181863</v>
+      </c>
+      <c r="O64">
+        <v>41421598.47942203</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D65">
-        <v>6.780308310437436</v>
+        <v>349.3889145684437</v>
       </c>
       <c r="E65">
-        <v>1.132839295175753</v>
+        <v>-7.824514599269855</v>
       </c>
       <c r="F65">
-        <v>4.906367351573829</v>
+        <v>650.5107843701344</v>
       </c>
       <c r="G65">
-        <v>8.454024890391915</v>
+        <v>119.788396008309</v>
+      </c>
+      <c r="H65">
+        <v>-2.006192001756038</v>
+      </c>
+      <c r="I65">
+        <v>283.2185234013367</v>
+      </c>
+      <c r="J65">
+        <v>26274395.76446153</v>
+      </c>
+      <c r="K65">
+        <v>-588411.3223796919</v>
+      </c>
+      <c r="L65">
+        <v>48919061.4954185</v>
+      </c>
+      <c r="M65">
+        <v>15931856.6691051</v>
+      </c>
+      <c r="N65">
+        <v>-266823.536233553</v>
+      </c>
+      <c r="O65">
+        <v>37668063.61237778</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D66">
-        <v>68.36763978029055</v>
+        <v>1007.550981633505</v>
       </c>
       <c r="E66">
-        <v>10.86767022860119</v>
+        <v>-17.47600994823951</v>
       </c>
       <c r="F66">
-        <v>49.20095731483639</v>
+        <v>1863.821466713548</v>
       </c>
       <c r="G66">
-        <v>85.34606148286863</v>
+        <v>302.0941009389279</v>
+      </c>
+      <c r="H66">
+        <v>-3.909114548285431</v>
+      </c>
+      <c r="I66">
+        <v>709.4172865151839</v>
+      </c>
+      <c r="J66">
+        <v>75768841.36982118</v>
+      </c>
+      <c r="K66">
+        <v>-1314213.424117558</v>
+      </c>
+      <c r="L66">
+        <v>140161238.1183255</v>
+      </c>
+      <c r="M66">
+        <v>40178515.42487741</v>
+      </c>
+      <c r="N66">
+        <v>-519912.2349219623</v>
+      </c>
+      <c r="O66">
+        <v>94352499.10651946</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D67">
-        <v>58.83300403330446</v>
+        <v>1126.976775001094</v>
       </c>
       <c r="E67">
-        <v>8.729778660382999</v>
+        <v>-10.14003776751773</v>
       </c>
       <c r="F67">
-        <v>42.71604651537288</v>
+        <v>2053.891895047056</v>
       </c>
       <c r="G67">
-        <v>73.02700535863781</v>
+        <v>254.8390716296747</v>
+      </c>
+      <c r="H67">
+        <v>-1.798293914851551</v>
+      </c>
+      <c r="I67">
+        <v>590.17976072839</v>
+      </c>
+      <c r="J67">
+        <v>84749780.45685738</v>
+      </c>
+      <c r="K67">
+        <v>-762540.9801551001</v>
+      </c>
+      <c r="L67">
+        <v>154454724.3994337</v>
+      </c>
+      <c r="M67">
+        <v>33893596.52674674</v>
+      </c>
+      <c r="N67">
+        <v>-239173.0906752563</v>
+      </c>
+      <c r="O67">
+        <v>78493908.17687586</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D68">
-        <v>415.5102488441664</v>
+        <v>1114.092762092152</v>
       </c>
       <c r="E68">
-        <v>68.52209719730368</v>
+        <v>-20.79611135804836</v>
       </c>
       <c r="F68">
-        <v>300.0154000533234</v>
+        <v>2064.422780222847</v>
       </c>
       <c r="G68">
-        <v>517.8791326321398</v>
+        <v>210.0223631006641</v>
+      </c>
+      <c r="H68">
+        <v>-2.874019196076723</v>
+      </c>
+      <c r="I68">
+        <v>493.8449558782468</v>
+      </c>
+      <c r="J68">
+        <v>83780889.80209187</v>
+      </c>
+      <c r="K68">
+        <v>-1563888.370236593</v>
+      </c>
+      <c r="L68">
+        <v>155246657.4955382</v>
+      </c>
+      <c r="M68">
+        <v>27932974.29238832</v>
+      </c>
+      <c r="N68">
+        <v>-382244.5530782041</v>
+      </c>
+      <c r="O68">
+        <v>65681379.13180683</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D69">
-        <v>253.4873579949261</v>
+        <v>1049.538758709682</v>
       </c>
       <c r="E69">
-        <v>35.85255096277303</v>
+        <v>-13.64844790195101</v>
       </c>
       <c r="F69">
-        <v>184.5046324859482</v>
+        <v>1927.985490450226</v>
       </c>
       <c r="G69">
-        <v>314.1625903888029</v>
+        <v>118.9596269928029</v>
+      </c>
+      <c r="H69">
+        <v>-1.099879069836721</v>
+      </c>
+      <c r="I69">
+        <v>277.0143360324025</v>
+      </c>
+      <c r="J69">
+        <v>78926364.19372678</v>
+      </c>
+      <c r="K69">
+        <v>-1026376.930674618</v>
+      </c>
+      <c r="L69">
+        <v>144986436.8673475</v>
+      </c>
+      <c r="M69">
+        <v>15821630.39004279</v>
+      </c>
+      <c r="N69">
+        <v>-146283.9162882839</v>
+      </c>
+      <c r="O69">
+        <v>36842906.69230954</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D70">
-        <v>1893.102251797338</v>
+        <v>470.0037282158446</v>
       </c>
       <c r="E70">
-        <v>295.0503436135965</v>
+        <v>-14.63751464114057</v>
       </c>
       <c r="F70">
-        <v>1363.764821148761</v>
+        <v>887.9384426484394</v>
       </c>
       <c r="G70">
-        <v>2368.725518566815</v>
+        <v>27.40031978876461</v>
+      </c>
+      <c r="H70">
+        <v>-0.6081923580574616</v>
+      </c>
+      <c r="I70">
+        <v>65.65738511630721</v>
+      </c>
+      <c r="J70">
+        <v>35344750.36555971</v>
+      </c>
+      <c r="K70">
+        <v>-1100755.738528411</v>
+      </c>
+      <c r="L70">
+        <v>66773858.82560536</v>
+      </c>
+      <c r="M70">
+        <v>3644242.531905693</v>
+      </c>
+      <c r="N70">
+        <v>-80889.58362164239</v>
+      </c>
+      <c r="O70">
+        <v>8732432.220468858</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D71">
-        <v>869.7306909056242</v>
+        <v>418.323516331683</v>
       </c>
       <c r="E71">
-        <v>131.9767000907348</v>
+        <v>-8.431541213566685</v>
       </c>
       <c r="F71">
-        <v>625.3072125003119</v>
+        <v>774.4861830395084</v>
       </c>
       <c r="G71">
-        <v>1088.450524972352</v>
+        <v>3.668468909831707</v>
+      </c>
+      <c r="H71">
+        <v>-0.06001953188271275</v>
+      </c>
+      <c r="I71">
+        <v>8.657175371169654</v>
+      </c>
+      <c r="J71">
+        <v>31458346.75165891</v>
+      </c>
+      <c r="K71">
+        <v>-634060.3308014286</v>
+      </c>
+      <c r="L71">
+        <v>58242135.45075408</v>
+      </c>
+      <c r="M71">
+        <v>487906.365007617</v>
+      </c>
+      <c r="N71">
+        <v>-7982.597740400796</v>
+      </c>
+      <c r="O71">
+        <v>1151404.324365564</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D72">
-        <v>11040.12965882238</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>2138.532217777936</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>8183.374989190699</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>13370.63870850162</v>
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D73">
-        <v>4842.783397916417</v>
+        <v>0</v>
       </c>
       <c r="E73">
-        <v>904.3467692432251</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>3596.597844490422</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>5861.594933983818</v>
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D74">
-        <v>27125.60817627047</v>
+        <v>0</v>
       </c>
       <c r="E74">
-        <v>4854.773079003411</v>
+        <v>0</v>
       </c>
       <c r="F74">
-        <v>20141.89177630313</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>32798.58345993355</v>
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D75">
-        <v>9106.403478834725</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>1551.742354872491</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>6768.626365737306</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>11004.42288704877</v>
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D76">
-        <v>30566.8199983484</v>
+        <v>0.752693498956816</v>
       </c>
       <c r="E76">
-        <v>5093.478987973128</v>
+        <v>0.5451580658020282</v>
       </c>
       <c r="F76">
-        <v>22852.05440470973</v>
+        <v>0.9371774707816141</v>
       </c>
       <c r="G76">
-        <v>36913.70885044193</v>
+        <v>1.208735743851216</v>
+      </c>
+      <c r="H76">
+        <v>0.7022889255897696</v>
+      </c>
+      <c r="I76">
+        <v>1.713557433089257</v>
+      </c>
+      <c r="J76">
+        <v>12674.60582893382</v>
+      </c>
+      <c r="K76">
+        <v>9179.916670040351</v>
+      </c>
+      <c r="L76">
+        <v>15781.13143049159</v>
+      </c>
+      <c r="M76">
+        <v>160761.8539322117</v>
+      </c>
+      <c r="N76">
+        <v>93404.42710343936</v>
+      </c>
+      <c r="O76">
+        <v>227903.1386008712</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D77">
-        <v>11932.64544715409</v>
+        <v>1.870649334246026</v>
       </c>
       <c r="E77">
-        <v>2394.045906704672</v>
+        <v>1.35119886828296</v>
       </c>
       <c r="F77">
-        <v>8870.704440358919</v>
+        <v>2.331339705285234</v>
       </c>
       <c r="G77">
-        <v>14430.88104815267</v>
+        <v>2.539848348655287</v>
+      </c>
+      <c r="H77">
+        <v>1.471204858308528</v>
+      </c>
+      <c r="I77">
+        <v>3.605157230140842</v>
+      </c>
+      <c r="J77">
+        <v>31499.8641393688</v>
+      </c>
+      <c r="K77">
+        <v>22752.83774301676</v>
+      </c>
+      <c r="L77">
+        <v>39257.42929729808</v>
+      </c>
+      <c r="M77">
+        <v>337799.8303711532</v>
+      </c>
+      <c r="N77">
+        <v>195670.2461550343</v>
+      </c>
+      <c r="O77">
+        <v>479485.911608732</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D78">
-        <v>17913.30409801184</v>
+        <v>6.715569815673259</v>
       </c>
       <c r="E78">
-        <v>2941.654553154101</v>
+        <v>4.87186231668871</v>
       </c>
       <c r="F78">
-        <v>13295.66838065507</v>
+        <v>8.360004456824004</v>
       </c>
       <c r="G78">
-        <v>21685.24466446849</v>
+        <v>8.409597472602824</v>
+      </c>
+      <c r="H78">
+        <v>4.892215080341418</v>
+      </c>
+      <c r="I78">
+        <v>11.92308773395681</v>
+      </c>
+      <c r="J78">
+        <v>113083.480126122</v>
+      </c>
+      <c r="K78">
+        <v>82037.28955072112</v>
+      </c>
+      <c r="L78">
+        <v>140774.1150484594</v>
+      </c>
+      <c r="M78">
+        <v>1118476.463856176</v>
+      </c>
+      <c r="N78">
+        <v>650664.6056854086</v>
+      </c>
+      <c r="O78">
+        <v>1585770.668616256</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D79">
-        <v>6716.490798347496</v>
+        <v>6.780308310437436</v>
       </c>
       <c r="E79">
-        <v>1116.995950848847</v>
+        <v>4.906367351573829</v>
       </c>
       <c r="F79">
-        <v>4991.765669096125</v>
+        <v>8.454024890391915</v>
       </c>
       <c r="G79">
-        <v>8128.775933441339</v>
+        <v>6.997973403336917</v>
+      </c>
+      <c r="H79">
+        <v>4.063247071701373</v>
+      </c>
+      <c r="I79">
+        <v>9.93379400234247</v>
+      </c>
+      <c r="J79">
+        <v>114173.6116394559</v>
+      </c>
+      <c r="K79">
+        <v>82618.31983315181</v>
+      </c>
+      <c r="L79">
+        <v>142357.3251293096</v>
+      </c>
+      <c r="M79">
+        <v>930730.46264381</v>
+      </c>
+      <c r="N79">
+        <v>540411.8605362826</v>
+      </c>
+      <c r="O79">
+        <v>1321194.602311549</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D80">
-        <v>28286.29246790826</v>
+        <v>68.36763978029055</v>
       </c>
       <c r="E80">
-        <v>4552.373918203514</v>
+        <v>49.20095731483639</v>
       </c>
       <c r="F80">
-        <v>21097.97823339399</v>
+        <v>85.34606148286863</v>
       </c>
       <c r="G80">
-        <v>34158.8971776227</v>
+        <v>61.55652052526607</v>
+      </c>
+      <c r="H80">
+        <v>35.51433431681684</v>
+      </c>
+      <c r="I80">
+        <v>87.5365796162652</v>
+      </c>
+      <c r="J80">
+        <v>1151242.68626031</v>
+      </c>
+      <c r="K80">
+        <v>828494.9202245307</v>
+      </c>
+      <c r="L80">
+        <v>1437142.329310026</v>
+      </c>
+      <c r="M80">
+        <v>8187017.229860387</v>
+      </c>
+      <c r="N80">
+        <v>4723406.464136641</v>
+      </c>
+      <c r="O80">
+        <v>11642365.08896327</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D81">
-        <v>8796.924291187395</v>
+        <v>58.83300403330446</v>
       </c>
       <c r="E81">
-        <v>1249.771898239861</v>
+        <v>42.71604651537288</v>
       </c>
       <c r="F81">
-        <v>6628.561567883887</v>
+        <v>73.02700535863781</v>
       </c>
       <c r="G81">
-        <v>10584.67148834002</v>
+        <v>40.20849558178615</v>
+      </c>
+      <c r="H81">
+        <v>23.40620320414661</v>
+      </c>
+      <c r="I81">
+        <v>56.85184802534004</v>
+      </c>
+      <c r="J81">
+        <v>990688.9549168139</v>
+      </c>
+      <c r="K81">
+        <v>719295.5072723641</v>
+      </c>
+      <c r="L81">
+        <v>1229701.743234102</v>
+      </c>
+      <c r="M81">
+        <v>5347729.912377558</v>
+      </c>
+      <c r="N81">
+        <v>3113025.026151499</v>
+      </c>
+      <c r="O81">
+        <v>7561295.787370225</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D82">
-        <v>17582.35879292406</v>
+        <v>415.5102488441664</v>
       </c>
       <c r="E82">
-        <v>2834.246301528237</v>
+        <v>300.0154000533234</v>
       </c>
       <c r="F82">
-        <v>13103.47422138236</v>
+        <v>517.8791326321398</v>
       </c>
       <c r="G82">
-        <v>21249.08668753976</v>
+        <v>234.5706944939671</v>
+      </c>
+      <c r="H82">
+        <v>135.8444285847585</v>
+      </c>
+      <c r="I82">
+        <v>332.9323787394349</v>
+      </c>
+      <c r="J82">
+        <v>6996777.080286915</v>
+      </c>
+      <c r="K82">
+        <v>5051959.32149792</v>
+      </c>
+      <c r="L82">
+        <v>8720566.714392597</v>
+      </c>
+      <c r="M82">
+        <v>31197902.36769762</v>
+      </c>
+      <c r="N82">
+        <v>18067309.00177288</v>
+      </c>
+      <c r="O82">
+        <v>44280006.37234484</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D83">
-        <v>4467.186042483597</v>
+        <v>253.4873579949261</v>
       </c>
       <c r="E83">
-        <v>629.3019169849349</v>
+        <v>184.5046324859482</v>
       </c>
       <c r="F83">
-        <v>3348.872890097372</v>
+        <v>314.1625903888029</v>
       </c>
       <c r="G83">
-        <v>5384.834948468118</v>
+        <v>85.43295298805478</v>
+      </c>
+      <c r="H83">
+        <v>49.80661842745749</v>
+      </c>
+      <c r="I83">
+        <v>120.6891459899655</v>
+      </c>
+      <c r="J83">
+        <v>4268473.621276561</v>
+      </c>
+      <c r="K83">
+        <v>3106873.506430882</v>
+      </c>
+      <c r="L83">
+        <v>5290183.859557058</v>
+      </c>
+      <c r="M83">
+        <v>11362582.74741129</v>
+      </c>
+      <c r="N83">
+        <v>6624280.250851845</v>
+      </c>
+      <c r="O83">
+        <v>16051656.41666541</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D84">
-        <v>0</v>
+        <v>1893.102251797338</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>1363.764821148761</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>2368.725518566815</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>330.7098601386747</v>
+      </c>
+      <c r="H84">
+        <v>191.2085504883106</v>
+      </c>
+      <c r="I84">
+        <v>470.8186140213916</v>
+      </c>
+      <c r="J84">
+        <v>31877948.81801539</v>
+      </c>
+      <c r="K84">
+        <v>22964435.82332399</v>
+      </c>
+      <c r="L84">
+        <v>39886969.00714657</v>
+      </c>
+      <c r="M84">
+        <v>43984411.39844374</v>
+      </c>
+      <c r="N84">
+        <v>25430737.21494531</v>
+      </c>
+      <c r="O84">
+        <v>62618875.66484508</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D85">
-        <v>0</v>
+        <v>869.7306909056242</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>625.3072125003119</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>1088.450524972352</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>23.50940673596779</v>
+      </c>
+      <c r="H85">
+        <v>13.49449459462594</v>
+      </c>
+      <c r="I85">
+        <v>33.57721147548644</v>
+      </c>
+      <c r="J85">
+        <v>14645395.10415981</v>
+      </c>
+      <c r="K85">
+        <v>10529548.15129275</v>
+      </c>
+      <c r="L85">
+        <v>18328418.39000943</v>
+      </c>
+      <c r="M85">
+        <v>3126751.095883715</v>
+      </c>
+      <c r="N85">
+        <v>1794767.78108525</v>
+      </c>
+      <c r="O85">
+        <v>4465769.126239696</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D86">
-        <v>11089.91631488185</v>
+        <v>11040.12965882238</v>
+      </c>
+      <c r="E86">
+        <v>8183.374989190699</v>
       </c>
       <c r="F86">
-        <v>8192.774554383426</v>
+        <v>13370.63870850162</v>
       </c>
       <c r="G86">
-        <v>13457.06347127016</v>
+        <v>19931.10956648468</v>
+      </c>
+      <c r="H86">
+        <v>9139.684252963147</v>
+      </c>
+      <c r="I86">
+        <v>36884.65271254427</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>2650837572.342462</v>
+      </c>
+      <c r="N86">
+        <v>1215578005.644099</v>
+      </c>
+      <c r="O86">
+        <v>4905658810.768389</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
       <c r="D87">
-        <v>4879.790139481021</v>
+        <v>4842.783397916417</v>
+      </c>
+      <c r="E87">
+        <v>3596.597844490422</v>
       </c>
       <c r="F87">
-        <v>3604.798303677122</v>
+        <v>5861.594933983818</v>
       </c>
       <c r="G87">
-        <v>5924.58244435953</v>
+        <v>7892.102478751623</v>
+      </c>
+      <c r="H87">
+        <v>3625.79406662439</v>
+      </c>
+      <c r="I87">
+        <v>14596.27872452403</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>1049649629.673966</v>
+      </c>
+      <c r="N87">
+        <v>482230610.8610439</v>
+      </c>
+      <c r="O87">
+        <v>1941305070.361696</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D88">
-        <v>27312.91840561766</v>
+        <v>27125.60817627047</v>
+      </c>
+      <c r="E88">
+        <v>20141.89177630313</v>
       </c>
       <c r="F88">
-        <v>20166.15693143889</v>
+        <v>32798.58345993355</v>
       </c>
       <c r="G88">
-        <v>33136.41201825882</v>
+        <v>42979.76078014533</v>
+      </c>
+      <c r="H88">
+        <v>19743.42716980368</v>
+      </c>
+      <c r="I88">
+        <v>79410.62648664869</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>5716308183.759329</v>
+      </c>
+      <c r="N88">
+        <v>2625875813.583889</v>
+      </c>
+      <c r="O88">
+        <v>10561613322.72428</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
       <c r="D89">
-        <v>9212.282375028595</v>
+        <v>9106.403478834725</v>
+      </c>
+      <c r="E89">
+        <v>6768.626365737306</v>
       </c>
       <c r="F89">
-        <v>6790.548024308879</v>
+        <v>11004.42288704877</v>
       </c>
       <c r="G89">
-        <v>11186.82703035573</v>
+        <v>12784.15042305171</v>
+      </c>
+      <c r="H89">
+        <v>5877.996537869359</v>
+      </c>
+      <c r="I89">
+        <v>23605.78786677541</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>1700292006.265877</v>
+      </c>
+      <c r="N89">
+        <v>781773539.5366247</v>
+      </c>
+      <c r="O89">
+        <v>3139569786.281129</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D90">
-        <v>31024.18334374379</v>
+        <v>30566.8199983484</v>
+      </c>
+      <c r="E90">
+        <v>22852.05440470973</v>
       </c>
       <c r="F90">
-        <v>22910.15952910739</v>
+        <v>36913.70885044193</v>
       </c>
       <c r="G90">
-        <v>37739.5514538143</v>
+        <v>40173.36485736874</v>
+      </c>
+      <c r="H90">
+        <v>18582.65586204777</v>
+      </c>
+      <c r="I90">
+        <v>74125.01066749955</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>5343057526.030043</v>
+      </c>
+      <c r="N90">
+        <v>2471493229.652354</v>
+      </c>
+      <c r="O90">
+        <v>9858626418.777439</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
       <c r="D91">
-        <v>12416.4305276137</v>
+        <v>11932.64544715409</v>
+      </c>
+      <c r="E91">
+        <v>8870.704440358919</v>
       </c>
       <c r="F91">
-        <v>8981.384590772732</v>
+        <v>14430.88104815267</v>
       </c>
       <c r="G91">
-        <v>15256.58877294761</v>
+        <v>13226.05705968724</v>
+      </c>
+      <c r="H91">
+        <v>6081.282837558426</v>
+      </c>
+      <c r="I91">
+        <v>24443.26849249514</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>1759065588.938403</v>
+      </c>
+      <c r="N91">
+        <v>808810617.3952706</v>
+      </c>
+      <c r="O91">
+        <v>3250954709.501853</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D92">
-        <v>18616.77011924723</v>
+        <v>17913.30409801184</v>
+      </c>
+      <c r="E92">
+        <v>13295.66838065507</v>
       </c>
       <c r="F92">
-        <v>13409.72265372803</v>
+        <v>21685.24466446849</v>
       </c>
       <c r="G92">
-        <v>22938.39660192939</v>
+        <v>18309.38076192352</v>
+      </c>
+      <c r="H92">
+        <v>8405.085020758535</v>
+      </c>
+      <c r="I92">
+        <v>33870.56476117945</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>2435147641.335828</v>
+      </c>
+      <c r="N92">
+        <v>1117876307.760885</v>
+      </c>
+      <c r="O92">
+        <v>4504785113.236867</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
       <c r="D93">
-        <v>7688.231729937813</v>
+        <v>6716.490798347496</v>
+      </c>
+      <c r="E93">
+        <v>4991.765669096125</v>
       </c>
       <c r="F93">
-        <v>5255.628757667087</v>
+        <v>8128.775933441339</v>
       </c>
       <c r="G93">
-        <v>9759.726982794458</v>
+        <v>5656.133166496538</v>
+      </c>
+      <c r="H93">
+        <v>2600.082431355514</v>
+      </c>
+      <c r="I93">
+        <v>10461.16312347522</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>752265711.1440396</v>
+      </c>
+      <c r="N93">
+        <v>345810963.3702834</v>
+      </c>
+      <c r="O93">
+        <v>1391334695.422205</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D94">
-        <v>30649.21046115956</v>
+        <v>28286.29246790826</v>
+      </c>
+      <c r="E94">
+        <v>21097.97823339399</v>
       </c>
       <c r="F94">
-        <v>21600.09823218037</v>
+        <v>34158.8971776227</v>
       </c>
       <c r="G94">
-        <v>38222.75794743204</v>
+        <v>20827.24781104255</v>
+      </c>
+      <c r="H94">
+        <v>9610.845684688626</v>
+      </c>
+      <c r="I94">
+        <v>38434.55093724855</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>2770023958.86866</v>
+      </c>
+      <c r="N94">
+        <v>1278242476.063587</v>
+      </c>
+      <c r="O94">
+        <v>5111795274.654057</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
       <c r="D95">
-        <v>12305.75557308536</v>
+        <v>8796.924291187395</v>
+      </c>
+      <c r="E95">
+        <v>6628.561567883887</v>
       </c>
       <c r="F95">
-        <v>7603.630166699609</v>
+        <v>10584.67148834002</v>
       </c>
       <c r="G95">
-        <v>16402.88207420219</v>
+        <v>4889.137710202765</v>
+      </c>
+      <c r="H95">
+        <v>2277.500623804011</v>
+      </c>
+      <c r="I95">
+        <v>8990.91089784396</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>650255315.4569678</v>
+      </c>
+      <c r="N95">
+        <v>302907582.9659335</v>
+      </c>
+      <c r="O95">
+        <v>1195791149.413247</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D96">
-        <v>21420.33767860292</v>
+        <v>17582.35879292406</v>
+      </c>
+      <c r="E96">
+        <v>13103.47422138236</v>
       </c>
       <c r="F96">
-        <v>14382.04515098126</v>
+        <v>21249.08668753976</v>
       </c>
       <c r="G96">
-        <v>27458.98164180435</v>
+        <v>8137.718939232554</v>
+      </c>
+      <c r="H96">
+        <v>3753.05386291972</v>
+      </c>
+      <c r="I96">
+        <v>15026.20102024828</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>1082316618.91793</v>
+      </c>
+      <c r="N96">
+        <v>499156163.7683228</v>
+      </c>
+      <c r="O96">
+        <v>1998484735.693022</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>65-75</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
       <c r="D97">
-        <v>8712.541203591623</v>
+        <v>4467.186042483597</v>
+      </c>
+      <c r="E97">
+        <v>3348.872890097372</v>
       </c>
       <c r="F97">
-        <v>4903.885199675899</v>
+        <v>5384.834948468118</v>
       </c>
       <c r="G97">
-        <v>12113.51229262429</v>
+        <v>1242.058158569045</v>
+      </c>
+      <c r="H97">
+        <v>576.6670197498282</v>
+      </c>
+      <c r="I97">
+        <v>2287.311762177931</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>165193735.0896829</v>
+      </c>
+      <c r="N97">
+        <v>76696713.62672715</v>
+      </c>
+      <c r="O97">
+        <v>304212464.3696648</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D98">
-        <v>4938.846357791779</v>
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
       </c>
       <c r="F98">
-        <v>2588.140177960457</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>7209.424443559883</v>
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
       <c r="D99">
-        <v>3557.652830172036</v>
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
       </c>
       <c r="F99">
-        <v>1748.958911957898</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>5282.03935434891</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
-      <c r="D100">
-        <v>11123.64787044601</v>
-      </c>
-      <c r="F100">
-        <v>8221.21480149644</v>
-      </c>
-      <c r="G100">
-        <v>13495.71595579373</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>20-24</t>
-        </is>
-      </c>
-      <c r="D101">
-        <v>4951.776969571572</v>
-      </c>
-      <c r="F101">
-        <v>3666.415856953488</v>
-      </c>
-      <c r="G101">
-        <v>6006.262634312626</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
-      <c r="D102">
-        <v>27424.16676629207</v>
-      </c>
-      <c r="F102">
-        <v>20260.16693682062</v>
-      </c>
-      <c r="G102">
-        <v>33263.69199424963</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>25-34</t>
-        </is>
-      </c>
-      <c r="D103">
-        <v>9374.643061919149</v>
-      </c>
-      <c r="F103">
-        <v>6929.116048066413</v>
-      </c>
-      <c r="G103">
-        <v>11371.34350163655</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
-      <c r="D104">
-        <v>31340.60626758653</v>
-      </c>
-      <c r="F104">
-        <v>23178.57817198212</v>
-      </c>
-      <c r="G104">
-        <v>38100.58542918289</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
-      <c r="D105">
-        <v>12959.5832209349</v>
-      </c>
-      <c r="F105">
-        <v>9440.030700068635</v>
-      </c>
-      <c r="G105">
-        <v>15878.10396723663</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
-      <c r="D106">
-        <v>19177.99669028749</v>
-      </c>
-      <c r="F106">
-        <v>13889.29845434625</v>
-      </c>
-      <c r="G106">
-        <v>23575.88050603362</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
-      <c r="D107">
-        <v>8641.177048130347</v>
-      </c>
-      <c r="F107">
-        <v>6065.39070291527</v>
-      </c>
-      <c r="G107">
-        <v>10846.11535388343</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
-      <c r="D108">
-        <v>32382.39121917433</v>
-      </c>
-      <c r="F108">
-        <v>23060.98147825914</v>
-      </c>
-      <c r="G108">
-        <v>40208.80039546132</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
-      <c r="D109">
-        <v>15248.42922814298</v>
-      </c>
-      <c r="F109">
-        <v>10121.19535585014</v>
-      </c>
-      <c r="G109">
-        <v>19741.71689071353</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
-      <c r="D110">
-        <v>24843.42730167746</v>
-      </c>
-      <c r="F110">
-        <v>17278.63485947257</v>
-      </c>
-      <c r="G110">
-        <v>31371.48523420727</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>65-75</t>
-        </is>
-      </c>
-      <c r="D111">
-        <v>14359.1173509739</v>
-      </c>
-      <c r="F111">
-        <v>9736.605180833478</v>
-      </c>
-      <c r="G111">
-        <v>18517.31085334914</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
-      <c r="D112">
-        <v>14696.76394778419</v>
-      </c>
-      <c r="F112">
-        <v>10825.60154933172</v>
-      </c>
-      <c r="G112">
-        <v>18382.2691203891</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
-      <c r="D113">
-        <v>14958.53023870037</v>
-      </c>
-      <c r="F113">
-        <v>11360.77437508401</v>
-      </c>
-      <c r="G113">
-        <v>18344.09088635373</v>
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019_sex_age.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex_age.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="D2">
-        <v>33.73155556416154</v>
+        <v>75.46658577584586</v>
       </c>
       <c r="E2">
-        <v>28.44024711301454</v>
+        <v>63.78167054760382</v>
       </c>
       <c r="F2">
-        <v>38.65248452356747</v>
+        <v>86.33856521930689</v>
       </c>
       <c r="G2">
-        <v>359.1976900447485</v>
+        <v>766.6065521224076</v>
       </c>
       <c r="H2">
-        <v>302.7592819698499</v>
+        <v>647.822260930569</v>
       </c>
       <c r="I2">
-        <v>411.6799576485938</v>
+        <v>877.1154872858963</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -475,13 +475,13 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>47773292.77595156</v>
+        <v>101958671.4322802</v>
       </c>
       <c r="N2">
-        <v>40266984.50199004</v>
+        <v>86160360.70376568</v>
       </c>
       <c r="O2">
-        <v>54753434.36726297</v>
+        <v>116656359.8090242</v>
       </c>
     </row>
     <row r="3">
@@ -492,7 +492,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="D3">
-        <v>71.9868300905522</v>
+        <v>135.0279993445354</v>
       </c>
       <c r="E3">
-        <v>61.61755327636659</v>
+        <v>116.1514830926358</v>
       </c>
       <c r="F3">
-        <v>81.68018995309556</v>
+        <v>152.6913615631354</v>
       </c>
       <c r="G3">
-        <v>691.501751833359</v>
+        <v>1241.831168920141</v>
       </c>
       <c r="H3">
-        <v>591.8893598842803</v>
+        <v>1067.929390549624</v>
       </c>
       <c r="I3">
-        <v>784.6233417882453</v>
+        <v>1404.542210973916</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -528,13 +528,13 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>91969732.99383675</v>
+        <v>165163545.4663788</v>
       </c>
       <c r="N3">
-        <v>78721284.86460929</v>
+        <v>142034608.9431</v>
       </c>
       <c r="O3">
-        <v>104354904.4578366</v>
+        <v>186804114.0595308</v>
       </c>
     </row>
     <row r="4">
@@ -545,7 +545,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="D4">
-        <v>111.248360674411</v>
+        <v>174.7504153122268</v>
       </c>
       <c r="E4">
-        <v>94.0100053817347</v>
+        <v>148.4220934893205</v>
       </c>
       <c r="F4">
-        <v>127.2799759908105</v>
+        <v>199.2494923886062</v>
       </c>
       <c r="G4">
-        <v>1029.353703571502</v>
+        <v>1477.037837771903</v>
       </c>
       <c r="H4">
-        <v>870.0747929747733</v>
+        <v>1254.54348259462</v>
       </c>
       <c r="I4">
-        <v>1177.485469847092</v>
+        <v>1684.078840629878</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -581,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>136904042.5750098</v>
+        <v>196446032.4236631</v>
       </c>
       <c r="N4">
-        <v>115719947.4656449</v>
+        <v>166854283.1850845</v>
       </c>
       <c r="O4">
-        <v>156605567.4896633</v>
+        <v>223982485.8037737</v>
       </c>
     </row>
     <row r="5">
@@ -598,7 +598,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="D5">
-        <v>162.3606868905531</v>
+        <v>253.0962697708379</v>
       </c>
       <c r="E5">
-        <v>138.568023757534</v>
+        <v>215.0348220916965</v>
       </c>
       <c r="F5">
-        <v>184.5164712808136</v>
+        <v>288.511495516572</v>
       </c>
       <c r="G5">
-        <v>1336.703097668464</v>
+        <v>1868.845353666589</v>
       </c>
       <c r="H5">
-        <v>1141.2902335964</v>
+        <v>1587.323198980217</v>
       </c>
       <c r="I5">
-        <v>1518.692754688266</v>
+        <v>2130.750805052999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -634,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>177781511.9899057</v>
+        <v>248556432.0376563</v>
       </c>
       <c r="N5">
-        <v>151791601.0683212</v>
+        <v>211113985.4643689</v>
       </c>
       <c r="O5">
-        <v>201986136.3735393</v>
+        <v>283389857.0720488</v>
       </c>
     </row>
     <row r="6">
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="D6">
-        <v>316.4229238427401</v>
+        <v>429.0392552891504</v>
       </c>
       <c r="E6">
-        <v>268.4186428747261</v>
+        <v>364.3765101939348</v>
       </c>
       <c r="F6">
-        <v>361.0339753685875</v>
+        <v>489.2711283207537</v>
       </c>
       <c r="G6">
-        <v>2403.998713618664</v>
+        <v>2956.260125109597</v>
       </c>
       <c r="H6">
-        <v>2040.312296248112</v>
+        <v>2511.014777967759</v>
       </c>
       <c r="I6">
-        <v>2742.034483789603</v>
+        <v>3370.954056584703</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>319731828.9112823</v>
+        <v>393182596.6395764</v>
       </c>
       <c r="N6">
-        <v>271361535.4009989</v>
+        <v>333964965.469712</v>
       </c>
       <c r="O6">
-        <v>364690586.3440172</v>
+        <v>448336889.5257655</v>
       </c>
     </row>
     <row r="7">
@@ -704,7 +704,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="D7">
-        <v>543.1526933211968</v>
+        <v>699.9470006557981</v>
       </c>
       <c r="E7">
-        <v>458.6461092959026</v>
+        <v>595.0124278828351</v>
       </c>
       <c r="F7">
-        <v>621.5151942890192</v>
+        <v>797.4727856187401</v>
       </c>
       <c r="G7">
-        <v>3498.165503751029</v>
+        <v>4104.484214358044</v>
       </c>
       <c r="H7">
-        <v>2954.423756939525</v>
+        <v>3486.150392948167</v>
       </c>
       <c r="I7">
-        <v>4002.45213849572</v>
+        <v>4678.93763605671</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -740,13 +740,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>465256011.9988868</v>
+        <v>545896400.50962</v>
       </c>
       <c r="N7">
-        <v>392938359.6729568</v>
+        <v>463658002.2621062</v>
       </c>
       <c r="O7">
-        <v>532326134.4199308</v>
+        <v>622298705.5955424</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="D8">
-        <v>561.2265710402642</v>
+        <v>985.9623437442004</v>
       </c>
       <c r="E8">
-        <v>479.5758006182195</v>
+        <v>834.7251738634495</v>
       </c>
       <c r="F8">
-        <v>637.48390410423</v>
+        <v>1126.69488501962</v>
       </c>
       <c r="G8">
-        <v>3334.617144621437</v>
+        <v>5025.315326745968</v>
       </c>
       <c r="H8">
-        <v>2849.103662092875</v>
+        <v>4255.716978842612</v>
       </c>
       <c r="I8">
-        <v>3788.063644099511</v>
+        <v>5741.499221267677</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -793,13 +793,13 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>443504080.2346511</v>
+        <v>668366938.4572138</v>
       </c>
       <c r="N8">
-        <v>378930787.0583524</v>
+        <v>566010358.1860673</v>
       </c>
       <c r="O8">
-        <v>503812464.6652349</v>
+        <v>763619396.428601</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -819,22 +819,22 @@
         </is>
       </c>
       <c r="D9">
-        <v>952.9453181925342</v>
+        <v>1712.248296007034</v>
       </c>
       <c r="E9">
-        <v>809.761945248182</v>
+        <v>1453.747175658893</v>
       </c>
       <c r="F9">
-        <v>1086.388371088974</v>
+        <v>1953.194307270423</v>
       </c>
       <c r="G9">
-        <v>4630.790004463996</v>
+        <v>6987.590203667648</v>
       </c>
       <c r="H9">
-        <v>3937.866993800328</v>
+        <v>5931.878372095574</v>
       </c>
       <c r="I9">
-        <v>5276.692038359389</v>
+        <v>7971.612981508385</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -846,13 +846,13 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>615895070.5937114</v>
+        <v>929349497.0877972</v>
       </c>
       <c r="N9">
-        <v>523736310.1754436</v>
+        <v>788939823.4887114</v>
       </c>
       <c r="O9">
-        <v>701800041.1017987</v>
+        <v>1060224526.540615</v>
       </c>
     </row>
     <row r="10">
@@ -863,7 +863,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="D10">
-        <v>1733.180758014774</v>
+        <v>2345.27849203719</v>
       </c>
       <c r="E10">
-        <v>1460.883246078769</v>
+        <v>1986.086606147771</v>
       </c>
       <c r="F10">
-        <v>1986.042448029276</v>
+        <v>2679.361847837946</v>
       </c>
       <c r="G10">
-        <v>7394.311597242272</v>
+        <v>8216.598175538849</v>
       </c>
       <c r="H10">
-        <v>6231.563673378272</v>
+        <v>6955.615793389191</v>
       </c>
       <c r="I10">
-        <v>8474.076369438657</v>
+        <v>9389.067709001542</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>983443442.4332222</v>
+        <v>1092807557.346667</v>
       </c>
       <c r="N10">
-        <v>828797968.5593102</v>
+        <v>925096900.5207624</v>
       </c>
       <c r="O10">
-        <v>1127052157.135341</v>
+        <v>1248746005.297205</v>
       </c>
     </row>
     <row r="11">
@@ -916,7 +916,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -925,22 +925,22 @@
         </is>
       </c>
       <c r="D11">
-        <v>2942.673655057622</v>
+        <v>3872.06563675863</v>
       </c>
       <c r="E11">
-        <v>2517.565189150537</v>
+        <v>3314.38556672829</v>
       </c>
       <c r="F11">
-        <v>3338.834816511353</v>
+        <v>4390.954078650022</v>
       </c>
       <c r="G11">
-        <v>9435.315583812251</v>
+        <v>9515.144865540602</v>
       </c>
       <c r="H11">
-        <v>8070.837992217282</v>
+        <v>8146.956061710737</v>
       </c>
       <c r="I11">
-        <v>10707.08491360095</v>
+        <v>10788.42389547658</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -952,13 +952,13 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>1254896972.647029</v>
+        <v>1265514267.1169</v>
       </c>
       <c r="N11">
-        <v>1073421452.964898</v>
+        <v>1083545156.207528</v>
       </c>
       <c r="O11">
-        <v>1424042293.508926</v>
+        <v>1434860378.098385</v>
       </c>
     </row>
     <row r="12">
@@ -969,7 +969,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -978,22 +978,22 @@
         </is>
       </c>
       <c r="D12">
-        <v>3423.089623074543</v>
+        <v>4178.141656889408</v>
       </c>
       <c r="E12">
-        <v>2896.589708491311</v>
+        <v>3539.119751228761</v>
       </c>
       <c r="F12">
-        <v>3912.503592402919</v>
+        <v>4772.942473572602</v>
       </c>
       <c r="G12">
-        <v>8893.413817349227</v>
+        <v>7846.078028406036</v>
       </c>
       <c r="H12">
-        <v>7526.342374301729</v>
+        <v>6637.403284501275</v>
       </c>
       <c r="I12">
-        <v>10164.12766497885</v>
+        <v>8970.209980039806</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>1182824037.707447</v>
+        <v>1043528377.778003</v>
       </c>
       <c r="N12">
-        <v>1001003535.78213</v>
+        <v>882774636.8386697</v>
       </c>
       <c r="O12">
-        <v>1351828979.442188</v>
+        <v>1193037927.345294</v>
       </c>
     </row>
     <row r="13">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1031,22 +1031,22 @@
         </is>
       </c>
       <c r="D13">
-        <v>5646.576147382279</v>
+        <v>6444.886495960352</v>
       </c>
       <c r="E13">
-        <v>4832.719981157579</v>
+        <v>5473.793139029212</v>
       </c>
       <c r="F13">
-        <v>6403.798560724857</v>
+        <v>7346.798889672174</v>
       </c>
       <c r="G13">
-        <v>8501.366275351864</v>
+        <v>5238.107409719903</v>
       </c>
       <c r="H13">
-        <v>7264.351602977488</v>
+        <v>4461.039786719651</v>
       </c>
       <c r="I13">
-        <v>9651.877343700249</v>
+        <v>5960.300132258168</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1058,13 +1058,13 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>1130681714.621798</v>
+        <v>696668285.4927471</v>
       </c>
       <c r="N13">
-        <v>966158763.1960059</v>
+        <v>593318291.6337135</v>
       </c>
       <c r="O13">
-        <v>1283699686.712133</v>
+        <v>792719917.5903363</v>
       </c>
     </row>
     <row r="14">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1084,22 +1084,22 @@
         </is>
       </c>
       <c r="D14">
-        <v>9757.91758999241</v>
+        <v>7748.178633155296</v>
       </c>
       <c r="E14">
-        <v>8237.46137137127</v>
+        <v>6528.867216458206</v>
       </c>
       <c r="F14">
-        <v>11172.84467682922</v>
+        <v>8881.982664889774</v>
       </c>
       <c r="G14">
-        <v>5177.347567577035</v>
+        <v>2304.344188330134</v>
       </c>
       <c r="H14">
-        <v>4386.921918459004</v>
+        <v>1944.961421198586</v>
       </c>
       <c r="I14">
-        <v>5914.577536462799</v>
+        <v>2639.119831455626</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>688587226.4877456</v>
+        <v>306477777.0479079</v>
       </c>
       <c r="N14">
-        <v>583460615.1550475</v>
+        <v>258679869.0194119</v>
       </c>
       <c r="O14">
-        <v>786638812.3495523</v>
+        <v>351002937.5835983</v>
       </c>
     </row>
     <row r="15">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1137,22 +1137,22 @@
         </is>
       </c>
       <c r="D15">
-        <v>11400.87740852834</v>
+        <v>8603.301040965889</v>
       </c>
       <c r="E15">
-        <v>9611.815463126108</v>
+        <v>7262.569650528651</v>
       </c>
       <c r="F15">
-        <v>13062.05153200482</v>
+        <v>9849.162217561867</v>
       </c>
       <c r="G15">
-        <v>862.1609989919623</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>720.6172635886692</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>993.1451306939399</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1164,13 +1164,13 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>114667412.865931</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>95842096.057293</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>132088302.382294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1190,40 +1190,40 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.4811756832426659</v>
+        <v>3.968345451658665</v>
       </c>
       <c r="E16">
-        <v>0.0184027894946961</v>
+        <v>0.09493327046116273</v>
       </c>
       <c r="F16">
-        <v>0.9743266721109717</v>
+        <v>8.037721197671246</v>
       </c>
       <c r="G16">
-        <v>0.3536293150686622</v>
+        <v>2.708239966257546</v>
       </c>
       <c r="H16">
-        <v>0.0101291958914045</v>
+        <v>0.04885772022287677</v>
       </c>
       <c r="I16">
-        <v>0.9059464237880119</v>
+        <v>6.939261118596278</v>
       </c>
       <c r="J16">
-        <v>21213.5923471194</v>
+        <v>174952.4459272755</v>
       </c>
       <c r="K16">
-        <v>811.3237804526665</v>
+        <v>4185.323094821285</v>
       </c>
       <c r="L16">
-        <v>42955.13999335643</v>
+        <v>354359.0144417322</v>
       </c>
       <c r="M16">
-        <v>47032.69890413207</v>
+        <v>360195.9155122536</v>
       </c>
       <c r="N16">
-        <v>1347.183053556798</v>
+        <v>6498.07678964261</v>
       </c>
       <c r="O16">
-        <v>120490.8743638056</v>
+        <v>922921.728773305</v>
       </c>
     </row>
     <row r="17">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D18">
-        <v>14.78225957431938</v>
+        <v>37.23082390997307</v>
       </c>
       <c r="E18">
-        <v>0.3574409639769225</v>
+        <v>0.7034182571442329</v>
       </c>
       <c r="F18">
-        <v>29.91338002803883</v>
+        <v>75.19959897106902</v>
       </c>
       <c r="G18">
-        <v>9.535234739210624</v>
+        <v>21.70436938296352</v>
       </c>
       <c r="H18">
-        <v>0.1725888337449444</v>
+        <v>0.3105658675703101</v>
       </c>
       <c r="I18">
-        <v>24.41095407050661</v>
+        <v>55.46332278116513</v>
       </c>
       <c r="J18">
-        <v>651705.4778530187</v>
+        <v>1641395.333718983</v>
       </c>
       <c r="K18">
-        <v>15758.4997788506</v>
+        <v>31011.6007027178</v>
       </c>
       <c r="L18">
-        <v>1318791.185296148</v>
+        <v>3315324.719837523</v>
       </c>
       <c r="M18">
-        <v>1268186.220315013</v>
+        <v>2886681.127934149</v>
       </c>
       <c r="N18">
-        <v>22954.3148880776</v>
+        <v>41305.26038685124</v>
       </c>
       <c r="O18">
-        <v>3246656.891377379</v>
+        <v>7376621.929894961</v>
       </c>
     </row>
     <row r="19">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1402,40 +1402,40 @@
         </is>
       </c>
       <c r="D20">
-        <v>71.71405270548057</v>
+        <v>96.22792041855813</v>
       </c>
       <c r="E20">
-        <v>1.685219530159597</v>
+        <v>3.353054199646356</v>
       </c>
       <c r="F20">
-        <v>144.7678820645978</v>
+        <v>194.5896195549847</v>
       </c>
       <c r="G20">
-        <v>38.37585674864433</v>
+        <v>46.33747748158078</v>
       </c>
       <c r="H20">
-        <v>0.6553017863383896</v>
+        <v>1.193518615964372</v>
       </c>
       <c r="I20">
-        <v>98.00718317873748</v>
+        <v>118.5289522483102</v>
       </c>
       <c r="J20">
-        <v>3161657.441626522</v>
+        <v>4242400.32749297</v>
       </c>
       <c r="K20">
-        <v>74296.27342614617</v>
+        <v>147826.1004998089</v>
       </c>
       <c r="L20">
-        <v>6382381.616581927</v>
+        <v>8578872.557320615</v>
       </c>
       <c r="M20">
-        <v>5103988.947569696</v>
+        <v>6162884.505050243</v>
       </c>
       <c r="N20">
-        <v>87155.13758300582</v>
+        <v>158737.9759232614</v>
       </c>
       <c r="O20">
-        <v>13034955.36277208</v>
+        <v>15764350.64902525</v>
       </c>
     </row>
     <row r="21">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1508,40 +1508,40 @@
         </is>
       </c>
       <c r="D22">
-        <v>99.86136336436159</v>
+        <v>148.3371649340797</v>
       </c>
       <c r="E22">
-        <v>3.456337158669162</v>
+        <v>3.770806575184802</v>
       </c>
       <c r="F22">
-        <v>202.1224416530715</v>
+        <v>300.0982079681253</v>
       </c>
       <c r="G22">
-        <v>41.54024374891247</v>
+        <v>52.64561650813813</v>
       </c>
       <c r="H22">
-        <v>1.089324497072089</v>
+        <v>1.01656610341947</v>
       </c>
       <c r="I22">
-        <v>106.3782939086072</v>
+        <v>134.7469946478816</v>
       </c>
       <c r="J22">
-        <v>4402587.926644609</v>
+        <v>6539740.590448772</v>
       </c>
       <c r="K22">
-        <v>152379.5363142475</v>
+        <v>166243.5494801723</v>
       </c>
       <c r="L22">
-        <v>8910972.085158965</v>
+        <v>13230429.69469074</v>
       </c>
       <c r="M22">
-        <v>5524852.418605358</v>
+        <v>7001866.995582371</v>
       </c>
       <c r="N22">
-        <v>144880.1581105878</v>
+        <v>135203.2917547895</v>
       </c>
       <c r="O22">
-        <v>14148313.08984476</v>
+        <v>17921350.28816826</v>
       </c>
     </row>
     <row r="23">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1614,40 +1614,40 @@
         </is>
       </c>
       <c r="D24">
-        <v>200.6540472952413</v>
+        <v>257.4227678424729</v>
       </c>
       <c r="E24">
-        <v>3.643556405063075</v>
+        <v>4.888234347635923</v>
       </c>
       <c r="F24">
-        <v>405.8230902317031</v>
+        <v>520.4409048835685</v>
       </c>
       <c r="G24">
-        <v>60.14218339964285</v>
+        <v>63.74158655077549</v>
       </c>
       <c r="H24">
-        <v>0.8285387312624466</v>
+        <v>0.8730224252353372</v>
       </c>
       <c r="I24">
-        <v>153.9021209075388</v>
+        <v>163.022821019701</v>
       </c>
       <c r="J24">
-        <v>8846234.983105302</v>
+        <v>11348997.5658711</v>
       </c>
       <c r="K24">
-        <v>160633.4712300158</v>
+        <v>215507.5876842251</v>
       </c>
       <c r="L24">
-        <v>17891522.5790451</v>
+        <v>22944678.17360187</v>
       </c>
       <c r="M24">
-        <v>7998910.392152499</v>
+        <v>8477631.011253141</v>
       </c>
       <c r="N24">
-        <v>110195.6512579054</v>
+        <v>116111.9825562999</v>
       </c>
       <c r="O24">
-        <v>20468982.08070267</v>
+        <v>21682035.19562024</v>
       </c>
     </row>
     <row r="25">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1720,40 +1720,40 @@
         </is>
       </c>
       <c r="D26">
-        <v>251.6200954558331</v>
+        <v>196.2670850979809</v>
       </c>
       <c r="E26">
-        <v>5.629553202021572</v>
+        <v>5.909279227355991</v>
       </c>
       <c r="F26">
-        <v>508.8223091441347</v>
+        <v>397.1974517969588</v>
       </c>
       <c r="G26">
-        <v>47.41950463140582</v>
+        <v>28.34726298095331</v>
       </c>
       <c r="H26">
-        <v>0.7832655253959596</v>
+        <v>0.5653481253851278</v>
       </c>
       <c r="I26">
-        <v>121.2980221681931</v>
+        <v>72.56144492408794</v>
       </c>
       <c r="J26">
-        <v>11093175.14836132</v>
+        <v>8652826.980714688</v>
       </c>
       <c r="K26">
-        <v>248190.1120175248</v>
+        <v>260522.3932964433</v>
       </c>
       <c r="L26">
-        <v>22432449.14323746</v>
+        <v>17511244.05737253</v>
       </c>
       <c r="M26">
-        <v>6306794.115976974</v>
+        <v>3770185.976466791</v>
       </c>
       <c r="N26">
-        <v>104174.3148776626</v>
+        <v>75191.300676222</v>
       </c>
       <c r="O26">
-        <v>16132636.94836968</v>
+        <v>9650672.174903696</v>
       </c>
     </row>
     <row r="27">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1826,40 +1826,40 @@
         </is>
       </c>
       <c r="D28">
-        <v>138.2776627984971</v>
+        <v>90.91604349406296</v>
       </c>
       <c r="E28">
-        <v>7.61124938183234</v>
+        <v>5.246340910867564</v>
       </c>
       <c r="F28">
-        <v>280.4335557123156</v>
+        <v>184.4254956816728</v>
       </c>
       <c r="G28">
-        <v>8.056121472218216</v>
+        <v>2.64056716344368</v>
       </c>
       <c r="H28">
-        <v>0.3018447192721767</v>
+        <v>0.09984077948208851</v>
       </c>
       <c r="I28">
-        <v>20.67703070222404</v>
+        <v>6.783973567832462</v>
       </c>
       <c r="J28">
-        <v>6096247.319797342</v>
+        <v>4008215.609522753</v>
       </c>
       <c r="K28">
-        <v>335557.1514968425</v>
+        <v>231295.4317374183</v>
       </c>
       <c r="L28">
-        <v>12363474.17068886</v>
+        <v>8130766.828117906</v>
       </c>
       <c r="M28">
-        <v>1071464.155805023</v>
+        <v>351195.4327380095</v>
       </c>
       <c r="N28">
-        <v>40145.34766319949</v>
+        <v>13278.82367111777</v>
       </c>
       <c r="O28">
-        <v>2750045.083395798</v>
+        <v>902268.4845217175</v>
       </c>
     </row>
     <row r="29">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1932,40 +1932,40 @@
         </is>
       </c>
       <c r="D30">
-        <v>15.65844185747065</v>
+        <v>51.60203867264304</v>
       </c>
       <c r="E30">
-        <v>9.74655177552656</v>
+        <v>32.15170670147795</v>
       </c>
       <c r="F30">
-        <v>21.43434993144515</v>
+        <v>70.28929056978059</v>
       </c>
       <c r="G30">
-        <v>10.86136084411592</v>
+        <v>33.985204008786</v>
       </c>
       <c r="H30">
-        <v>5.305592588444431</v>
+        <v>16.62277676142345</v>
       </c>
       <c r="I30">
-        <v>18.1239674304828</v>
+        <v>56.43244387872133</v>
       </c>
       <c r="J30">
-        <v>872206.5283448303</v>
+        <v>2874336.75814356</v>
       </c>
       <c r="K30">
-        <v>542902.4270003805</v>
+        <v>1790914.366685724</v>
       </c>
       <c r="L30">
-        <v>1193936.159881358</v>
+        <v>3915254.063317915</v>
       </c>
       <c r="M30">
-        <v>1444560.992267417</v>
+        <v>4520032.133168538</v>
       </c>
       <c r="N30">
-        <v>705643.8142631094</v>
+        <v>2210829.309269318</v>
       </c>
       <c r="O30">
-        <v>2410487.668254213</v>
+        <v>7505515.035869936</v>
       </c>
     </row>
     <row r="31">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1985,40 +1985,40 @@
         </is>
       </c>
       <c r="D31">
-        <v>13.36527327769648</v>
+        <v>63.04929440713324</v>
       </c>
       <c r="E31">
-        <v>8.46062504224734</v>
+        <v>40.12652590797343</v>
       </c>
       <c r="F31">
-        <v>18.15701647163543</v>
+        <v>85.2426597704968</v>
       </c>
       <c r="G31">
-        <v>8.370378677242181</v>
+        <v>37.67006033575466</v>
       </c>
       <c r="H31">
-        <v>4.158937486452693</v>
+        <v>18.81185629090525</v>
       </c>
       <c r="I31">
-        <v>13.86110985945021</v>
+        <v>62.10060349518186</v>
       </c>
       <c r="J31">
-        <v>744472.4521142491</v>
+        <v>3511971.797066136</v>
       </c>
       <c r="K31">
-        <v>471273.7361032611</v>
+        <v>2235127.746125937</v>
       </c>
       <c r="L31">
-        <v>1011382.131503036</v>
+        <v>4748186.634536215</v>
       </c>
       <c r="M31">
-        <v>1113260.36407321</v>
+        <v>5010118.02465537</v>
       </c>
       <c r="N31">
-        <v>553138.6856982082</v>
+        <v>2501976.886690399</v>
       </c>
       <c r="O31">
-        <v>1843527.611306877</v>
+        <v>8259380.264859187</v>
       </c>
     </row>
     <row r="32">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2038,40 +2038,40 @@
         </is>
       </c>
       <c r="D32">
-        <v>39.64663127599601</v>
+        <v>113.4614014840003</v>
       </c>
       <c r="E32">
-        <v>24.76763711923716</v>
+        <v>72.21884956214207</v>
       </c>
       <c r="F32">
-        <v>53.88797182871738</v>
+        <v>153.0836879458678</v>
       </c>
       <c r="G32">
-        <v>24.14052571481144</v>
+        <v>63.03126002162933</v>
       </c>
       <c r="H32">
-        <v>11.83965255904364</v>
+        <v>31.47662636820128</v>
       </c>
       <c r="I32">
-        <v>39.9899109339809</v>
+        <v>103.6856825274162</v>
       </c>
       <c r="J32">
-        <v>2208396.655335527</v>
+        <v>6320026.985461784</v>
       </c>
       <c r="K32">
-        <v>1379606.922815748</v>
+        <v>4022734.358310437</v>
       </c>
       <c r="L32">
-        <v>3001667.806803215</v>
+        <v>8527067.585960729</v>
       </c>
       <c r="M32">
-        <v>3210689.920069922</v>
+        <v>8383157.582876701</v>
       </c>
       <c r="N32">
-        <v>1574673.790352805</v>
+        <v>4186391.30697077</v>
       </c>
       <c r="O32">
-        <v>5318658.15421946</v>
+        <v>13790195.77614636</v>
       </c>
     </row>
     <row r="33">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2091,40 +2091,40 @@
         </is>
       </c>
       <c r="D33">
-        <v>35.25593542763083</v>
+        <v>144.9566986862602</v>
       </c>
       <c r="E33">
-        <v>22.32577375515558</v>
+        <v>91.02752257121668</v>
       </c>
       <c r="F33">
-        <v>47.71861311792934</v>
+        <v>197.4779450911588</v>
       </c>
       <c r="G33">
-        <v>19.02298143870285</v>
+        <v>69.94147962712528</v>
       </c>
       <c r="H33">
-        <v>9.458138854840872</v>
+        <v>34.47208781667207</v>
       </c>
       <c r="I33">
-        <v>31.3804242114227</v>
+        <v>116.139004350089</v>
       </c>
       <c r="J33">
-        <v>1963826.115189891</v>
+        <v>8074378.030222058</v>
       </c>
       <c r="K33">
-        <v>1243590.249709676</v>
+        <v>5070415.062261915</v>
       </c>
       <c r="L33">
-        <v>2658022.1878949</v>
+        <v>10999916.49746772</v>
       </c>
       <c r="M33">
-        <v>2530056.531347479</v>
+        <v>9302216.790407661</v>
       </c>
       <c r="N33">
-        <v>1257932.467693836</v>
+        <v>4584787.679617384</v>
       </c>
       <c r="O33">
-        <v>4173596.420119219</v>
+        <v>15446487.57856183</v>
       </c>
     </row>
     <row r="34">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2144,40 +2144,40 @@
         </is>
       </c>
       <c r="D34">
-        <v>89.92931688675669</v>
+        <v>324.5746703158406</v>
       </c>
       <c r="E34">
-        <v>57.59782137204075</v>
+        <v>204.9005864909905</v>
       </c>
       <c r="F34">
-        <v>121.2435842505599</v>
+        <v>441.4456234333737</v>
       </c>
       <c r="G34">
-        <v>45.36740283139999</v>
+        <v>146.8947367362028</v>
       </c>
       <c r="H34">
-        <v>22.82474422823565</v>
+        <v>72.85389640964388</v>
       </c>
       <c r="I34">
-        <v>74.51505593706531</v>
+        <v>243.4152975727331</v>
       </c>
       <c r="J34">
-        <v>5009242.809226119</v>
+        <v>18079458.28593294</v>
       </c>
       <c r="K34">
-        <v>3208313.846065413</v>
+        <v>11413372.46872116</v>
       </c>
       <c r="L34">
-        <v>6753510.129924685</v>
+        <v>24589404.11648578</v>
       </c>
       <c r="M34">
-        <v>6033864.576576199</v>
+        <v>19536999.98591498</v>
       </c>
       <c r="N34">
-        <v>3035690.982355341</v>
+        <v>9689568.222482637</v>
       </c>
       <c r="O34">
-        <v>9910502.439629687</v>
+        <v>32374234.5771735</v>
       </c>
     </row>
     <row r="35">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2197,40 +2197,40 @@
         </is>
       </c>
       <c r="D35">
-        <v>176.4457595123615</v>
+        <v>515.5692054126631</v>
       </c>
       <c r="E35">
-        <v>110.8276447502678</v>
+        <v>325.5763123457898</v>
       </c>
       <c r="F35">
-        <v>239.8994294302815</v>
+        <v>698.5486045809236</v>
       </c>
       <c r="G35">
-        <v>75.25001782581086</v>
+        <v>198.5742854868599</v>
       </c>
       <c r="H35">
-        <v>37.09079540609216</v>
+        <v>98.36304686746588</v>
       </c>
       <c r="I35">
-        <v>124.7417972915256</v>
+        <v>328.0192601719195</v>
       </c>
       <c r="J35">
-        <v>9828381.696357548</v>
+        <v>28718235.87989615</v>
       </c>
       <c r="K35">
-        <v>6173321.467879418</v>
+        <v>18135251.75028518</v>
       </c>
       <c r="L35">
-        <v>13362878.01812555</v>
+        <v>38910554.37236659</v>
       </c>
       <c r="M35">
-        <v>10008252.37083284</v>
+        <v>26410379.96975237</v>
       </c>
       <c r="N35">
-        <v>4933075.789010257</v>
+        <v>13082285.23337296</v>
       </c>
       <c r="O35">
-        <v>16590659.0397729</v>
+        <v>43626561.60286529</v>
       </c>
     </row>
     <row r="36">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2250,40 +2250,40 @@
         </is>
       </c>
       <c r="D36">
-        <v>173.3946786358773</v>
+        <v>909.3896988072495</v>
       </c>
       <c r="E36">
-        <v>109.2906974255399</v>
+        <v>573.0959394838003</v>
       </c>
       <c r="F36">
-        <v>235.7344296584907</v>
+        <v>1233.653821010878</v>
       </c>
       <c r="G36">
-        <v>68.1884798753934</v>
+        <v>300.9145460036423</v>
       </c>
       <c r="H36">
-        <v>33.7204959600146</v>
+        <v>148.8835002498759</v>
       </c>
       <c r="I36">
-        <v>113.0299870038063</v>
+        <v>497.5652201488579</v>
       </c>
       <c r="J36">
-        <v>9658430.389375642</v>
+        <v>50654825.00296144</v>
       </c>
       <c r="K36">
-        <v>6087710.427997423</v>
+        <v>31922590.02112663</v>
       </c>
       <c r="L36">
-        <v>13130879.20083725</v>
+        <v>68716985.1379479</v>
       </c>
       <c r="M36">
-        <v>9069067.823427321</v>
+        <v>40021634.61848442</v>
       </c>
       <c r="N36">
-        <v>4484825.962681942</v>
+        <v>19801505.53323349</v>
       </c>
       <c r="O36">
-        <v>15032988.27150624</v>
+        <v>66176174.2797981</v>
       </c>
     </row>
     <row r="37">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2303,40 +2303,40 @@
         </is>
       </c>
       <c r="D37">
-        <v>412.2557083152455</v>
+        <v>1393.356793344317</v>
       </c>
       <c r="E37">
-        <v>259.9980693449789</v>
+        <v>887.5653728943762</v>
       </c>
       <c r="F37">
-        <v>560.4674953450967</v>
+        <v>1881.047516703437</v>
       </c>
       <c r="G37">
-        <v>133.5942475225474</v>
+        <v>368.9530561639641</v>
       </c>
       <c r="H37">
-        <v>66.13697227687024</v>
+        <v>184.2487868718189</v>
       </c>
       <c r="I37">
-        <v>221.3690107587159</v>
+        <v>607.6610666149978</v>
       </c>
       <c r="J37">
-        <v>22963467.4645758</v>
+        <v>77612760.10286522</v>
       </c>
       <c r="K37">
-        <v>14482412.45865401</v>
+        <v>49439166.40096256</v>
       </c>
       <c r="L37">
-        <v>31219160.42571257</v>
+        <v>104778108.775415</v>
       </c>
       <c r="M37">
-        <v>17768034.92049881</v>
+        <v>49070756.46980722</v>
       </c>
       <c r="N37">
-        <v>8796217.312823743</v>
+        <v>24505088.65395191</v>
       </c>
       <c r="O37">
-        <v>29442078.43090922</v>
+        <v>80818921.85979471</v>
       </c>
     </row>
     <row r="38">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2356,40 +2356,40 @@
         </is>
       </c>
       <c r="D38">
-        <v>730.4120622031838</v>
+        <v>3175.622266792217</v>
       </c>
       <c r="E38">
-        <v>460.2883165478444</v>
+        <v>2008.95291199628</v>
       </c>
       <c r="F38">
-        <v>988.994632368345</v>
+        <v>4294.680358474303</v>
       </c>
       <c r="G38">
-        <v>206.6503539955195</v>
+        <v>724.7704176102262</v>
       </c>
       <c r="H38">
-        <v>102.2143807648071</v>
+        <v>360.07310301757</v>
       </c>
       <c r="I38">
-        <v>341.1096367567193</v>
+        <v>1194.252537723487</v>
       </c>
       <c r="J38">
-        <v>40685412.6888418</v>
+        <v>176888511.5048601</v>
       </c>
       <c r="K38">
-        <v>25638979.80834805</v>
+        <v>111902695.1040167</v>
       </c>
       <c r="L38">
-        <v>55088979.01218158</v>
+        <v>239222285.3277356</v>
       </c>
       <c r="M38">
-        <v>27484497.08140409</v>
+        <v>96394465.54216009</v>
       </c>
       <c r="N38">
-        <v>13594512.64171934</v>
+        <v>47889722.70133681</v>
       </c>
       <c r="O38">
-        <v>45367581.68864367</v>
+        <v>158835587.5172238</v>
       </c>
     </row>
     <row r="39">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2409,40 +2409,40 @@
         </is>
       </c>
       <c r="D39">
-        <v>1441.914395687903</v>
+        <v>4005.067332852071</v>
       </c>
       <c r="E39">
-        <v>943.6286394136956</v>
+        <v>2643.387569507857</v>
       </c>
       <c r="F39">
-        <v>1913.000609634863</v>
+        <v>5287.582009184902</v>
       </c>
       <c r="G39">
-        <v>309.2683466556646</v>
+        <v>644.8763446667579</v>
       </c>
       <c r="H39">
-        <v>158.5768341074325</v>
+        <v>334.3031424987208</v>
       </c>
       <c r="I39">
-        <v>500.704615643464</v>
+        <v>1037.199458068209</v>
       </c>
       <c r="J39">
-        <v>80317515.66860761</v>
+        <v>223090260.574526</v>
       </c>
       <c r="K39">
-        <v>52562002.47262167</v>
+        <v>147241974.3967266</v>
       </c>
       <c r="L39">
-        <v>106557959.9578812</v>
+        <v>294528893.0756176</v>
       </c>
       <c r="M39">
-        <v>41132690.10520339</v>
+        <v>85768553.8406788</v>
       </c>
       <c r="N39">
-        <v>21090718.93628852</v>
+        <v>44462317.95232987</v>
       </c>
       <c r="O39">
-        <v>66593713.88058071</v>
+        <v>137947527.9230719</v>
       </c>
     </row>
     <row r="40">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2462,40 +2462,40 @@
         </is>
       </c>
       <c r="D40">
-        <v>1557.482495823861</v>
+        <v>4479.480484231186</v>
       </c>
       <c r="E40">
-        <v>982.5517338134912</v>
+        <v>2797.47292440388</v>
       </c>
       <c r="F40">
-        <v>2109.147933556491</v>
+        <v>6105.556798548041</v>
       </c>
       <c r="G40">
-        <v>276.3820045261133</v>
+        <v>582.8803535793467</v>
       </c>
       <c r="H40">
-        <v>137.0364657882728</v>
+        <v>286.3610732577195</v>
       </c>
       <c r="I40">
-        <v>455.9821824004919</v>
+        <v>966.4623001484823</v>
       </c>
       <c r="J40">
-        <v>86754889.98238067</v>
+        <v>249516021.9326456</v>
       </c>
       <c r="K40">
-        <v>54730096.67687915</v>
+        <v>155824836.8351449</v>
       </c>
       <c r="L40">
-        <v>117483758.1949636</v>
+        <v>340091724.7927228</v>
       </c>
       <c r="M40">
-        <v>36758806.60197306</v>
+        <v>77523087.0260531</v>
       </c>
       <c r="N40">
-        <v>18225849.94984028</v>
+        <v>38086022.74327669</v>
       </c>
       <c r="O40">
-        <v>60645630.25926542</v>
+        <v>128539485.9197481</v>
       </c>
     </row>
     <row r="41">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2515,40 +2515,40 @@
         </is>
       </c>
       <c r="D41">
-        <v>2127.464968288651</v>
+        <v>4541.998095536226</v>
       </c>
       <c r="E41">
-        <v>1375.093056583348</v>
+        <v>2887.438917494981</v>
       </c>
       <c r="F41">
-        <v>2843.934629492145</v>
+        <v>6132.944535637363</v>
       </c>
       <c r="G41">
-        <v>225.8249041166049</v>
+        <v>270.6005525675304</v>
       </c>
       <c r="H41">
-        <v>114.8090309965968</v>
+        <v>134.8294769009641</v>
       </c>
       <c r="I41">
-        <v>367.6648511820628</v>
+        <v>445.7597756001137</v>
       </c>
       <c r="J41">
-        <v>118504053.6636145</v>
+        <v>252998377.9175589</v>
       </c>
       <c r="K41">
-        <v>76595433.43780571</v>
+        <v>160836122.5823054</v>
       </c>
       <c r="L41">
-        <v>158412846.7319715</v>
+        <v>341617276.5240725</v>
       </c>
       <c r="M41">
-        <v>30034712.24750845</v>
+        <v>35989873.49148155</v>
       </c>
       <c r="N41">
-        <v>15269601.12254738</v>
+        <v>17932320.42782823</v>
       </c>
       <c r="O41">
-        <v>48899425.20721435</v>
+        <v>59286050.15481512</v>
       </c>
     </row>
     <row r="42">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2568,40 +2568,40 @@
         </is>
       </c>
       <c r="D42">
-        <v>1961.830298526537</v>
+        <v>3397.035893112754</v>
       </c>
       <c r="E42">
-        <v>1205.221276941892</v>
+        <v>2080.348507489474</v>
       </c>
       <c r="F42">
-        <v>2707.722180944038</v>
+        <v>4697.342015246241</v>
       </c>
       <c r="G42">
-        <v>107.5512614393857</v>
+        <v>89.04706635905116</v>
       </c>
       <c r="H42">
-        <v>51.91584374776237</v>
+        <v>42.58895036309688</v>
       </c>
       <c r="I42">
-        <v>180.6289560122385</v>
+        <v>149.9836584614279</v>
       </c>
       <c r="J42">
-        <v>109277871.2885252</v>
+        <v>189221693.3181666</v>
       </c>
       <c r="K42">
-        <v>67133235.56821728</v>
+        <v>115879572.5641787</v>
       </c>
       <c r="L42">
-        <v>150825540.9229448</v>
+        <v>261651344.9332462</v>
       </c>
       <c r="M42">
-        <v>14304317.7714383</v>
+        <v>11843259.8257538</v>
       </c>
       <c r="N42">
-        <v>6904807.218452395</v>
+        <v>5664330.398291885</v>
       </c>
       <c r="O42">
-        <v>24023651.14962772</v>
+        <v>19947826.57536991</v>
       </c>
     </row>
     <row r="43">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2621,40 +2621,40 @@
         </is>
       </c>
       <c r="D43">
-        <v>1760.362006579208</v>
+        <v>3106.212669676418</v>
       </c>
       <c r="E43">
-        <v>1116.157840665361</v>
+        <v>1971.125081413632</v>
       </c>
       <c r="F43">
-        <v>2389.88750255974</v>
+        <v>4220.660026133406</v>
       </c>
       <c r="G43">
-        <v>14.85124574767428</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>7.289259211316919</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>24.72403846638741</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>98055684.49047504</v>
+        <v>173022258.1263159</v>
       </c>
       <c r="K43">
-        <v>62172224.04074202</v>
+        <v>109795609.2849021</v>
       </c>
       <c r="L43">
-        <v>133121513.6675825</v>
+        <v>235099204.775683</v>
       </c>
       <c r="M43">
-        <v>1975215.684440679</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>969471.4751051503</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>3288297.116029526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2674,40 +2674,40 @@
         </is>
       </c>
       <c r="D44">
-        <v>7.753489986796596</v>
+        <v>892.3675613542109</v>
       </c>
       <c r="E44">
-        <v>0.2965358579940802</v>
+        <v>25.18555826788544</v>
       </c>
       <c r="F44">
-        <v>15.69994569378816</v>
+        <v>1807.300831117199</v>
       </c>
       <c r="G44">
-        <v>4.616127858763421</v>
+        <v>504.7412906361791</v>
       </c>
       <c r="H44">
-        <v>0.1390944302312838</v>
+        <v>11.35838852823281</v>
       </c>
       <c r="I44">
-        <v>10.79334840649877</v>
+        <v>1180.310664170527</v>
       </c>
       <c r="J44">
-        <v>114805.9262344972</v>
+        <v>13213286.48097179</v>
       </c>
       <c r="K44">
-        <v>4390.80644931835</v>
+        <v>372922.5612725797</v>
       </c>
       <c r="L44">
-        <v>232469.0958879214</v>
+        <v>26760703.40635238</v>
       </c>
       <c r="M44">
-        <v>613945.0052155349</v>
+        <v>67130591.65461183</v>
       </c>
       <c r="N44">
-        <v>18499.55922076074</v>
+        <v>1510665.674254963</v>
       </c>
       <c r="O44">
-        <v>1435515.338064336</v>
+        <v>156981318.3346801</v>
       </c>
     </row>
     <row r="45">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2727,40 +2727,40 @@
         </is>
       </c>
       <c r="D45">
-        <v>4.791538675093026</v>
+        <v>171.4342258815747</v>
       </c>
       <c r="E45">
-        <v>0.173721996363095</v>
+        <v>4.829878499809547</v>
       </c>
       <c r="F45">
-        <v>9.693295819211164</v>
+        <v>346.4008159598162</v>
       </c>
       <c r="G45">
-        <v>2.574925055211647</v>
+        <v>88.01981626291048</v>
       </c>
       <c r="H45">
-        <v>0.07353714318230664</v>
+        <v>1.999410889428863</v>
       </c>
       <c r="I45">
-        <v>6.014984526210608</v>
+        <v>205.3771683372946</v>
       </c>
       <c r="J45">
-        <v>70948.31316210247</v>
+        <v>2538426.582628476</v>
       </c>
       <c r="K45">
-        <v>2572.301600148348</v>
+        <v>71516.01094667987</v>
       </c>
       <c r="L45">
-        <v>143528.6311950597</v>
+        <v>5129156.881917</v>
       </c>
       <c r="M45">
-        <v>342465.0323431491</v>
+        <v>11706635.56296709</v>
       </c>
       <c r="N45">
-        <v>9780.440043246783</v>
+        <v>265921.6482940387</v>
       </c>
       <c r="O45">
-        <v>799992.9419860108</v>
+        <v>27315163.38886018</v>
       </c>
     </row>
     <row r="46">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2780,40 +2780,40 @@
         </is>
       </c>
       <c r="D46">
-        <v>56.02709710526626</v>
+        <v>1659.55570747895</v>
       </c>
       <c r="E46">
-        <v>1.354757674051808</v>
+        <v>33.66082668190062</v>
       </c>
       <c r="F46">
-        <v>113.3764320097071</v>
+        <v>3352.653359392894</v>
       </c>
       <c r="G46">
-        <v>29.27687355647484</v>
+        <v>792.8790565464445</v>
       </c>
       <c r="H46">
-        <v>0.5574567803126325</v>
+        <v>12.83983927797351</v>
       </c>
       <c r="I46">
-        <v>68.40725649829207</v>
+        <v>1849.584493877979</v>
       </c>
       <c r="J46">
-        <v>829593.226837678</v>
+        <v>24573041.3606408</v>
       </c>
       <c r="K46">
-        <v>20059.89687968514</v>
+        <v>498415.8606789021</v>
       </c>
       <c r="L46">
-        <v>1678764.828767733</v>
+        <v>49642738.29253062</v>
       </c>
       <c r="M46">
-        <v>3893824.183011154</v>
+        <v>105452914.5206771</v>
       </c>
       <c r="N46">
-        <v>74141.75178158011</v>
+        <v>1707698.623970477</v>
       </c>
       <c r="O46">
-        <v>9098165.114272846</v>
+        <v>245994737.6857713</v>
       </c>
     </row>
     <row r="47">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2833,40 +2833,40 @@
         </is>
       </c>
       <c r="D47">
-        <v>21.12993950627974</v>
+        <v>281.3537328122181</v>
       </c>
       <c r="E47">
-        <v>0.5609879070726218</v>
+        <v>10.37868189831975</v>
       </c>
       <c r="F47">
-        <v>42.65319813169481</v>
+        <v>568.6346584878924</v>
       </c>
       <c r="G47">
-        <v>9.781673915024305</v>
+        <v>117.2730767802147</v>
       </c>
       <c r="H47">
-        <v>0.2046407803271518</v>
+        <v>3.395879900169663</v>
       </c>
       <c r="I47">
-        <v>22.79919207565393</v>
+        <v>273.6757464265531</v>
       </c>
       <c r="J47">
-        <v>312871.014269484</v>
+        <v>4166004.721750514</v>
       </c>
       <c r="K47">
-        <v>8306.547940024313</v>
+        <v>153677.1428684203</v>
       </c>
       <c r="L47">
-        <v>631565.9047360052</v>
+        <v>8419773.388230218</v>
       </c>
       <c r="M47">
-        <v>1300962.630698232</v>
+        <v>15597319.21176856</v>
       </c>
       <c r="N47">
-        <v>27217.22378351118</v>
+        <v>451652.0267225652</v>
       </c>
       <c r="O47">
-        <v>3032292.546061973</v>
+        <v>36398874.27473157</v>
       </c>
     </row>
     <row r="48">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2886,40 +2886,40 @@
         </is>
       </c>
       <c r="D48">
-        <v>154.7223093218356</v>
+        <v>1874.829582968575</v>
       </c>
       <c r="E48">
-        <v>3.63584329129158</v>
+        <v>64.39434383150237</v>
       </c>
       <c r="F48">
-        <v>312.3351725868083</v>
+        <v>3790.293243318657</v>
       </c>
       <c r="G48">
-        <v>67.07223343082113</v>
+        <v>737.3151899813795</v>
       </c>
       <c r="H48">
-        <v>1.204845155244067</v>
+        <v>19.67787162849394</v>
       </c>
       <c r="I48">
-        <v>156.3387742849098</v>
+        <v>1720.937030005389</v>
       </c>
       <c r="J48">
-        <v>2290973.234128423</v>
+        <v>27760601.63501567</v>
       </c>
       <c r="K48">
-        <v>53835.93161415438</v>
+        <v>953487.0491130555</v>
       </c>
       <c r="L48">
-        <v>4624746.900492872</v>
+        <v>56122872.05381934</v>
       </c>
       <c r="M48">
-        <v>8920607.04629921</v>
+        <v>98062920.26752347</v>
       </c>
       <c r="N48">
-        <v>160244.405647461</v>
+        <v>2617156.926589694</v>
       </c>
       <c r="O48">
-        <v>20793056.979893</v>
+        <v>228884624.9907168</v>
       </c>
     </row>
     <row r="49">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2939,40 +2939,40 @@
         </is>
       </c>
       <c r="D49">
-        <v>95.12402916810167</v>
+        <v>574.9603930556484</v>
       </c>
       <c r="E49">
-        <v>2.865858057138944</v>
+        <v>15.36141297870392</v>
       </c>
       <c r="F49">
-        <v>192.1553202415448</v>
+        <v>1161.369614953971</v>
       </c>
       <c r="G49">
-        <v>34.75977793927188</v>
+        <v>191.0554091479422</v>
       </c>
       <c r="H49">
-        <v>0.8398536427830877</v>
+        <v>3.991809663669203</v>
       </c>
       <c r="I49">
-        <v>81.08694221307705</v>
+        <v>445.5948399918154</v>
       </c>
       <c r="J49">
-        <v>1408501.499892083</v>
+        <v>8513438.539974988</v>
       </c>
       <c r="K49">
-        <v>42434.76025205635</v>
+        <v>227456.4419756691</v>
       </c>
       <c r="L49">
-        <v>2845243.826816553</v>
+        <v>17196399.88862347</v>
       </c>
       <c r="M49">
-        <v>4623050.465923159</v>
+        <v>25410369.41667632</v>
       </c>
       <c r="N49">
-        <v>111700.5344901507</v>
+        <v>530910.685268004</v>
       </c>
       <c r="O49">
-        <v>10784563.31433925</v>
+        <v>59264113.71891145</v>
       </c>
     </row>
     <row r="50">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2992,40 +2992,40 @@
         </is>
       </c>
       <c r="D50">
-        <v>207.3307400341226</v>
+        <v>2338.283113218043</v>
       </c>
       <c r="E50">
-        <v>7.175997971304034</v>
+        <v>59.39935979917791</v>
       </c>
       <c r="F50">
-        <v>419.6437340088478</v>
+        <v>4730.547029080816</v>
       </c>
       <c r="G50">
-        <v>69.8668653078319</v>
+        <v>672.0617354811139</v>
       </c>
       <c r="H50">
-        <v>1.927368195245277</v>
+        <v>13.64203425625179</v>
       </c>
       <c r="I50">
-        <v>163.2974301607178</v>
+        <v>1569.969006450934</v>
       </c>
       <c r="J50">
-        <v>3069946.267685253</v>
+        <v>34622958.05741961</v>
       </c>
       <c r="K50">
-        <v>106255.0019610988</v>
+        <v>879526.3205464281</v>
       </c>
       <c r="L50">
-        <v>6213664.769469017</v>
+        <v>70045209.85959974</v>
       </c>
       <c r="M50">
-        <v>9292293.085941643</v>
+        <v>89384210.81898816</v>
       </c>
       <c r="N50">
-        <v>256339.9699676218</v>
+        <v>1814390.556081488</v>
       </c>
       <c r="O50">
-        <v>21718558.21137546</v>
+        <v>208805877.8579743</v>
       </c>
     </row>
     <row r="51">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3045,40 +3045,40 @@
         </is>
       </c>
       <c r="D51">
-        <v>203.3160003961902</v>
+        <v>1077.240851987055</v>
       </c>
       <c r="E51">
-        <v>6.783166473679788</v>
+        <v>20.95631777573008</v>
       </c>
       <c r="F51">
-        <v>411.5187447474956</v>
+        <v>2179.848925375994</v>
       </c>
       <c r="G51">
-        <v>56.45953122717071</v>
+        <v>245.1505475051655</v>
       </c>
       <c r="H51">
-        <v>1.503039251990599</v>
+        <v>4.014623911781316</v>
       </c>
       <c r="I51">
-        <v>131.9510565066432</v>
+        <v>572.8566916209329</v>
       </c>
       <c r="J51">
-        <v>3010500.01786639</v>
+        <v>15950705.2953723</v>
       </c>
       <c r="K51">
-        <v>100438.3459757767</v>
+        <v>310300.1973052357</v>
       </c>
       <c r="L51">
-        <v>6093358.053476171</v>
+        <v>32277023.03804236</v>
       </c>
       <c r="M51">
-        <v>7509117.653213705</v>
+        <v>32605022.81818701</v>
       </c>
       <c r="N51">
-        <v>199904.2205147496</v>
+        <v>533944.9802669149</v>
       </c>
       <c r="O51">
-        <v>17549490.51538355</v>
+        <v>76189939.98558408</v>
       </c>
     </row>
     <row r="52">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3098,40 +3098,40 @@
         </is>
       </c>
       <c r="D52">
-        <v>556.5873096343158</v>
+        <v>3204.395558770877</v>
       </c>
       <c r="E52">
-        <v>10.10673487194112</v>
+        <v>59.6279857373482</v>
       </c>
       <c r="F52">
-        <v>1125.698609244572</v>
+        <v>6478.361069384148</v>
       </c>
       <c r="G52">
-        <v>135.1451851459087</v>
+        <v>649.3567290001453</v>
       </c>
       <c r="H52">
-        <v>1.958571370603013</v>
+        <v>9.17005882782354</v>
       </c>
       <c r="I52">
-        <v>315.6385963050998</v>
+        <v>1515.760531839607</v>
       </c>
       <c r="J52">
-        <v>8241388.293755315</v>
+        <v>47447485.03872035</v>
       </c>
       <c r="K52">
-        <v>149650.4232488321</v>
+        <v>882911.5848129153</v>
       </c>
       <c r="L52">
-        <v>16668219.3070844</v>
+        <v>95925092.3543711</v>
       </c>
       <c r="M52">
-        <v>17974309.62440585</v>
+        <v>86364444.95701931</v>
       </c>
       <c r="N52">
-        <v>260489.9922902007</v>
+        <v>1219617.824100531</v>
       </c>
       <c r="O52">
-        <v>41979933.30857828</v>
+        <v>201596150.7346677</v>
       </c>
     </row>
     <row r="53">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3151,40 +3151,40 @@
         </is>
       </c>
       <c r="D53">
-        <v>881.107107175667</v>
+        <v>2387.044269267524</v>
       </c>
       <c r="E53">
-        <v>-1.136049345829136</v>
+        <v>-12.13048710375368</v>
       </c>
       <c r="F53">
-        <v>1778.29107582161</v>
+        <v>4810.387569251569</v>
       </c>
       <c r="G53">
-        <v>161.371116360344</v>
+        <v>336.9409257304102</v>
       </c>
       <c r="H53">
-        <v>-0.02654216879805724</v>
+        <v>-1.614513026790192</v>
       </c>
       <c r="I53">
-        <v>376.1382164519218</v>
+        <v>784.0779579029135</v>
       </c>
       <c r="J53">
-        <v>13046552.93595009</v>
+        <v>35344964.49504425</v>
       </c>
       <c r="K53">
-        <v>-16821.48266369192</v>
+        <v>-179616.1225452806</v>
       </c>
       <c r="L53">
-        <v>26331155.95969056</v>
+        <v>71227408.73790796</v>
       </c>
       <c r="M53">
-        <v>21462358.47592575</v>
+        <v>44813143.12214456</v>
       </c>
       <c r="N53">
-        <v>-3530.108450141614</v>
+        <v>-214730.2325630955</v>
       </c>
       <c r="O53">
-        <v>50026382.7881056</v>
+        <v>104282368.4010875</v>
       </c>
     </row>
     <row r="54">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3204,40 +3204,40 @@
         </is>
       </c>
       <c r="D54">
-        <v>750.8933789186796</v>
+        <v>1895.839969438789</v>
       </c>
       <c r="E54">
-        <v>16.7999070901332</v>
+        <v>56.74312746462657</v>
       </c>
       <c r="F54">
-        <v>1518.445107853114</v>
+        <v>3836.676155314164</v>
       </c>
       <c r="G54">
-        <v>114.6373071614391</v>
+        <v>222.5149744274863</v>
       </c>
       <c r="H54">
-        <v>1.991971750396658</v>
+        <v>4.644205333110031</v>
       </c>
       <c r="I54">
-        <v>267.6373950550436</v>
+        <v>519.8438066846277</v>
       </c>
       <c r="J54">
-        <v>11118478.26164889</v>
+        <v>28071702.42748018</v>
       </c>
       <c r="K54">
-        <v>248756.2242836022</v>
+        <v>840195.4883687255</v>
       </c>
       <c r="L54">
-        <v>22483616.71198107</v>
+        <v>56809663.83173686</v>
       </c>
       <c r="M54">
-        <v>15246761.8524714</v>
+        <v>29594491.59885568</v>
       </c>
       <c r="N54">
-        <v>264932.2428027556</v>
+        <v>617679.3093036341</v>
       </c>
       <c r="O54">
-        <v>35595773.5423208</v>
+        <v>69139226.28905548</v>
       </c>
     </row>
     <row r="55">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3257,40 +3257,40 @@
         </is>
       </c>
       <c r="D55">
-        <v>814.864076114769</v>
+        <v>1869.704863231315</v>
       </c>
       <c r="E55">
-        <v>9.063068411180476</v>
+        <v>43.57510460035616</v>
       </c>
       <c r="F55">
-        <v>1642.594633824997</v>
+        <v>3771.886538211892</v>
       </c>
       <c r="G55">
-        <v>74.7712015258212</v>
+        <v>97.96048014854087</v>
       </c>
       <c r="H55">
-        <v>0.5858860975933923</v>
+        <v>1.966227183322263</v>
       </c>
       <c r="I55">
-        <v>174.0509183961958</v>
+        <v>228.1566039164414</v>
       </c>
       <c r="J55">
-        <v>12065692.37503138</v>
+        <v>27684719.90986606</v>
       </c>
       <c r="K55">
-        <v>134196.8539643494</v>
+        <v>645216.5738174735</v>
       </c>
       <c r="L55">
-        <v>24321898.74304673</v>
+        <v>55850323.97130349</v>
       </c>
       <c r="M55">
-        <v>9944569.80293422</v>
+        <v>13028743.85975594</v>
       </c>
       <c r="N55">
-        <v>77922.85097992118</v>
+        <v>261508.215381861</v>
       </c>
       <c r="O55">
-        <v>23148772.14669405</v>
+        <v>30344828.32088671</v>
       </c>
     </row>
     <row r="56">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3310,40 +3310,40 @@
         </is>
       </c>
       <c r="D56">
-        <v>613.9100792520594</v>
+        <v>743.0794561616414</v>
       </c>
       <c r="E56">
-        <v>33.79159451094418</v>
+        <v>42.50149019738067</v>
       </c>
       <c r="F56">
-        <v>1245.038301400591</v>
+        <v>1507.440002989461</v>
       </c>
       <c r="G56">
-        <v>28.97441994317001</v>
+        <v>18.14299690420975</v>
       </c>
       <c r="H56">
-        <v>1.142030037195692</v>
+        <v>0.7203061171341595</v>
       </c>
       <c r="I56">
-        <v>67.87362247830248</v>
+        <v>42.54238416540365</v>
       </c>
       <c r="J56">
-        <v>9090166.543485235</v>
+        <v>11002777.50738541</v>
       </c>
       <c r="K56">
-        <v>500352.13992355</v>
+        <v>629319.5653526157</v>
       </c>
       <c r="L56">
-        <v>18435282.12883855</v>
+        <v>22320664.12426494</v>
       </c>
       <c r="M56">
-        <v>3853597.852441611</v>
+        <v>2413018.588259896</v>
       </c>
       <c r="N56">
-        <v>151889.994947027</v>
+        <v>95800.71357884321</v>
       </c>
       <c r="O56">
-        <v>9027191.78961423</v>
+        <v>5658137.093998685</v>
       </c>
     </row>
     <row r="57">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3363,40 +3363,40 @@
         </is>
       </c>
       <c r="D57">
-        <v>509.2366163555211</v>
+        <v>919.1823583469801</v>
       </c>
       <c r="E57">
-        <v>15.9254000057911</v>
+        <v>30.29484794151709</v>
       </c>
       <c r="F57">
-        <v>1029.215143777309</v>
+        <v>1858.599708120841</v>
       </c>
       <c r="G57">
-        <v>3.61918452564459</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>0.0996458478201723</v>
+        <v>0</v>
       </c>
       <c r="I57">
-        <v>8.449931602280962</v>
+        <v>0</v>
       </c>
       <c r="J57">
-        <v>7540266.578376192</v>
+        <v>13610333.18004373</v>
       </c>
       <c r="K57">
-        <v>235807.3978857488</v>
+        <v>448575.8134700438</v>
       </c>
       <c r="L57">
-        <v>15239588.63391061</v>
+        <v>27520285.87814532</v>
       </c>
       <c r="M57">
-        <v>481351.5419107305</v>
+        <v>0</v>
       </c>
       <c r="N57">
-        <v>13252.89776008292</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>1123840.903103368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3416,40 +3416,40 @@
         </is>
       </c>
       <c r="D58">
-        <v>26.37472421520761</v>
+        <v>108.1288129312694</v>
       </c>
       <c r="E58">
-        <v>-0.6435224407938687</v>
+        <v>-2.37071088813032</v>
       </c>
       <c r="F58">
-        <v>49.29046714330751</v>
+        <v>201.5308084819005</v>
       </c>
       <c r="G58">
-        <v>19.38922256952089</v>
+        <v>75.64871965702211</v>
       </c>
       <c r="H58">
-        <v>-0.3513052045093759</v>
+        <v>-1.234991414014957</v>
       </c>
       <c r="I58">
-        <v>46.00028425227256</v>
+        <v>179.0052211890219</v>
       </c>
       <c r="J58">
-        <v>1983405.635707828</v>
+        <v>8131394.861244395</v>
       </c>
       <c r="K58">
-        <v>-48393.53107013973</v>
+        <v>-178279.8294982883</v>
       </c>
       <c r="L58">
-        <v>3706692.41964387</v>
+        <v>15155318.3286474</v>
       </c>
       <c r="M58">
-        <v>2578766.601746278</v>
+        <v>10061279.71438394</v>
       </c>
       <c r="N58">
-        <v>-46723.59219974699</v>
+        <v>-164253.8580639893</v>
       </c>
       <c r="O58">
-        <v>6118037.805552251</v>
+        <v>23807694.41813991</v>
       </c>
     </row>
     <row r="59">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3469,40 +3469,40 @@
         </is>
       </c>
       <c r="D59">
-        <v>18.84992961181364</v>
+        <v>104.8277122654415</v>
       </c>
       <c r="E59">
-        <v>-0.4338878519107666</v>
+        <v>-2.111266523660144</v>
       </c>
       <c r="F59">
-        <v>35.13719808486548</v>
+        <v>195.016656719411</v>
       </c>
       <c r="G59">
-        <v>12.50798449093572</v>
+        <v>66.32015097543015</v>
       </c>
       <c r="H59">
-        <v>-0.2138049486193068</v>
+        <v>-1.00243624714775</v>
       </c>
       <c r="I59">
-        <v>29.60043390068797</v>
+        <v>156.6641665590359</v>
       </c>
       <c r="J59">
-        <v>1417533.556737998</v>
+        <v>7883148.790073464</v>
       </c>
       <c r="K59">
-        <v>-32628.80035154156</v>
+        <v>-158769.3538457664</v>
       </c>
       <c r="L59">
-        <v>2642352.433179968</v>
+        <v>14665447.60195644</v>
       </c>
       <c r="M59">
-        <v>1663561.93729445</v>
+        <v>8820580.079732209</v>
       </c>
       <c r="N59">
-        <v>-28436.05816636781</v>
+        <v>-133324.0208706507</v>
       </c>
       <c r="O59">
-        <v>3936857.7087915</v>
+        <v>20836334.15235177</v>
       </c>
     </row>
     <row r="60">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3522,40 +3522,40 @@
         </is>
       </c>
       <c r="D60">
-        <v>91.63650096592163</v>
+        <v>177.0237210853076</v>
       </c>
       <c r="E60">
-        <v>-1.85723965753136</v>
+        <v>-3.071573754779624</v>
       </c>
       <c r="F60">
-        <v>170.5641544868471</v>
+        <v>327.5162297973724</v>
       </c>
       <c r="G60">
-        <v>59.12435885743663</v>
+        <v>104.4832253057902</v>
       </c>
       <c r="H60">
-        <v>-0.8893156782105415</v>
+        <v>-1.355825283956349</v>
       </c>
       <c r="I60">
-        <v>139.7076600583434</v>
+        <v>245.4858032822516</v>
       </c>
       <c r="J60">
-        <v>6891156.50913828</v>
+        <v>13312360.84933621</v>
       </c>
       <c r="K60">
-        <v>-139666.2794860157</v>
+        <v>-230985.4179331824</v>
       </c>
       <c r="L60">
-        <v>12826594.98156539</v>
+        <v>24629547.99699222</v>
       </c>
       <c r="M60">
-        <v>7863539.728039072</v>
+        <v>13896268.9656701</v>
       </c>
       <c r="N60">
-        <v>-118278.985202002</v>
+        <v>-180324.7627661945</v>
       </c>
       <c r="O60">
-        <v>18581118.78775967</v>
+        <v>32649611.83653946</v>
       </c>
     </row>
     <row r="61">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3575,40 +3575,40 @@
         </is>
       </c>
       <c r="D61">
-        <v>49.493021259959</v>
+        <v>193.1746814811071</v>
       </c>
       <c r="E61">
-        <v>-0.9651030906547192</v>
+        <v>-4.476054544691863</v>
       </c>
       <c r="F61">
-        <v>92.03233205733679</v>
+        <v>360.4911907940175</v>
       </c>
       <c r="G61">
-        <v>28.28998274065563</v>
+        <v>99.27647070981553</v>
       </c>
       <c r="H61">
-        <v>-0.4094729168839421</v>
+        <v>-1.703487792470013</v>
       </c>
       <c r="I61">
-        <v>66.78765936342241</v>
+        <v>235.1672014330553</v>
       </c>
       <c r="J61">
-        <v>3721924.69177018</v>
+        <v>14526929.22206073</v>
       </c>
       <c r="K61">
-        <v>-72576.71752032555</v>
+        <v>-336603.7778153728</v>
       </c>
       <c r="L61">
-        <v>6920923.403043785</v>
+        <v>27109298.03890093</v>
       </c>
       <c r="M61">
-        <v>3762567.7045072</v>
+        <v>13203770.60440546</v>
       </c>
       <c r="N61">
-        <v>-54459.8979455643</v>
+        <v>-226563.8763985117</v>
       </c>
       <c r="O61">
-        <v>8882758.69533518</v>
+        <v>31277237.79059635</v>
       </c>
     </row>
     <row r="62">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3628,40 +3628,40 @@
         </is>
       </c>
       <c r="D62">
-        <v>211.9590256878334</v>
+        <v>204.0356442391022</v>
       </c>
       <c r="E62">
-        <v>-3.673698331469673</v>
+        <v>-4.484322534516597</v>
       </c>
       <c r="F62">
-        <v>391.3266690642212</v>
+        <v>379.5874683437099</v>
       </c>
       <c r="G62">
-        <v>113.4595903524618</v>
+        <v>98.94872001899164</v>
       </c>
       <c r="H62">
-        <v>-1.440706609502771</v>
+        <v>-1.595974589227644</v>
       </c>
       <c r="I62">
-        <v>265.8563161282482</v>
+        <v>233.6085403605556</v>
       </c>
       <c r="J62">
-        <v>15939530.69075076</v>
+        <v>15343684.48242473</v>
       </c>
       <c r="K62">
-        <v>-276265.7882248508</v>
+        <v>-337225.5389181826</v>
       </c>
       <c r="L62">
-        <v>29428156.84029851</v>
+        <v>28545357.2069153</v>
       </c>
       <c r="M62">
-        <v>15090125.51687742</v>
+        <v>13160179.76252589</v>
       </c>
       <c r="N62">
-        <v>-191613.9790638686</v>
+        <v>-212264.6203672767</v>
       </c>
       <c r="O62">
-        <v>35358890.04505701</v>
+        <v>31069935.8679539</v>
       </c>
     </row>
     <row r="63">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3681,40 +3681,40 @@
         </is>
       </c>
       <c r="D63">
-        <v>210.3446424449039</v>
+        <v>355.9518753757611</v>
       </c>
       <c r="E63">
-        <v>-4.364551261876571</v>
+        <v>-6.944100124585168</v>
       </c>
       <c r="F63">
-        <v>391.321635417835</v>
+        <v>660.9169290838478</v>
       </c>
       <c r="G63">
-        <v>94.90880028415972</v>
+        <v>146.8196334485428</v>
       </c>
       <c r="H63">
-        <v>-1.477838457590684</v>
+        <v>-2.120724272681494</v>
       </c>
       <c r="I63">
-        <v>224.2243824351148</v>
+        <v>346.0962655224327</v>
       </c>
       <c r="J63">
-        <v>15818127.45649923</v>
+        <v>26767936.9801326</v>
       </c>
       <c r="K63">
-        <v>-328218.61944438</v>
+        <v>-522203.2734689292</v>
       </c>
       <c r="L63">
-        <v>29427778.3050566</v>
+        <v>49701613.98403445</v>
       </c>
       <c r="M63">
-        <v>12622870.43779324</v>
+        <v>19527011.2486562</v>
       </c>
       <c r="N63">
-        <v>-196552.5148595609</v>
+        <v>-282056.3282666387</v>
       </c>
       <c r="O63">
-        <v>29821842.86387027</v>
+        <v>46030803.31448355</v>
       </c>
     </row>
     <row r="64">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3734,40 +3734,40 @@
         </is>
       </c>
       <c r="D64">
-        <v>316.025032749713</v>
+        <v>441.1293358455573</v>
       </c>
       <c r="E64">
-        <v>-7.284284640573616</v>
+        <v>-8.592364857012884</v>
       </c>
       <c r="F64">
-        <v>589.4137693367397</v>
+        <v>817.9475785437104</v>
       </c>
       <c r="G64">
-        <v>131.4929706221666</v>
+        <v>154.7128071187202</v>
       </c>
       <c r="H64">
-        <v>-2.267323926179421</v>
+        <v>-2.24844375749751</v>
       </c>
       <c r="I64">
-        <v>311.4405900708423</v>
+        <v>364.2063914475593</v>
       </c>
       <c r="J64">
-        <v>23765398.48781117</v>
+        <v>33173367.18492175</v>
       </c>
       <c r="K64">
-        <v>-547785.4892557764</v>
+        <v>-646154.4296122257</v>
       </c>
       <c r="L64">
-        <v>44324504.86789218</v>
+        <v>61510475.85406553</v>
       </c>
       <c r="M64">
-        <v>17488565.09274816</v>
+        <v>20576803.34678979</v>
       </c>
       <c r="N64">
-        <v>-301554.082181863</v>
+        <v>-299043.0197471688</v>
       </c>
       <c r="O64">
-        <v>41421598.47942203</v>
+        <v>48439450.06252538</v>
       </c>
     </row>
     <row r="65">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3787,40 +3787,40 @@
         </is>
       </c>
       <c r="D65">
-        <v>349.3889145684437</v>
+        <v>533.4463724358683</v>
       </c>
       <c r="E65">
-        <v>-7.824514599269855</v>
+        <v>-9.382862628217586</v>
       </c>
       <c r="F65">
-        <v>650.5107843701344</v>
+        <v>985.710872597725</v>
       </c>
       <c r="G65">
-        <v>119.788396008309</v>
+        <v>150.3057329893078</v>
       </c>
       <c r="H65">
-        <v>-2.006192001756038</v>
+        <v>-2.020304900428425</v>
       </c>
       <c r="I65">
-        <v>283.2185234013367</v>
+        <v>352.9012737819559</v>
       </c>
       <c r="J65">
-        <v>26274395.76446153</v>
+        <v>40115700.65354975</v>
       </c>
       <c r="K65">
-        <v>-588411.3223796919</v>
+        <v>-705600.6525045907</v>
       </c>
       <c r="L65">
-        <v>48919061.4954185</v>
+        <v>74126443.33022156</v>
       </c>
       <c r="M65">
-        <v>15931856.6691051</v>
+        <v>19990662.48757793</v>
       </c>
       <c r="N65">
-        <v>-266823.536233553</v>
+        <v>-268700.5517569806</v>
       </c>
       <c r="O65">
-        <v>37668063.61237778</v>
+        <v>46935869.41300014</v>
       </c>
     </row>
     <row r="66">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3840,40 +3840,40 @@
         </is>
       </c>
       <c r="D66">
-        <v>1007.550981633505</v>
+        <v>768.6437991013445</v>
       </c>
       <c r="E66">
-        <v>-17.47600994823951</v>
+        <v>-13.31806126554081</v>
       </c>
       <c r="F66">
-        <v>1863.821466713548</v>
+        <v>1422.190046841291</v>
       </c>
       <c r="G66">
-        <v>302.0941009389279</v>
+        <v>192.1869453353128</v>
       </c>
       <c r="H66">
-        <v>-3.909114548285431</v>
+        <v>-2.433801114608553</v>
       </c>
       <c r="I66">
-        <v>709.4172865151839</v>
+        <v>451.2522207896084</v>
       </c>
       <c r="J66">
-        <v>75768841.36982118</v>
+        <v>57802782.3362202</v>
       </c>
       <c r="K66">
-        <v>-1314213.424117558</v>
+        <v>-1001531.525229935</v>
       </c>
       <c r="L66">
-        <v>140161238.1183255</v>
+        <v>106950113.7125119</v>
       </c>
       <c r="M66">
-        <v>40178515.42487741</v>
+        <v>25560863.7295966</v>
       </c>
       <c r="N66">
-        <v>-519912.2349219623</v>
+        <v>-323695.5482429375</v>
       </c>
       <c r="O66">
-        <v>94352499.10651946</v>
+        <v>60016545.36501791</v>
       </c>
     </row>
     <row r="67">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3893,40 +3893,40 @@
         </is>
       </c>
       <c r="D67">
-        <v>1126.976775001094</v>
+        <v>746.2032382180146</v>
       </c>
       <c r="E67">
-        <v>-10.14003776751773</v>
+        <v>-4.806768922978267</v>
       </c>
       <c r="F67">
-        <v>2053.891895047056</v>
+        <v>1353.861368652298</v>
       </c>
       <c r="G67">
-        <v>254.8390716296747</v>
+        <v>134.0607718475322</v>
       </c>
       <c r="H67">
-        <v>-1.798293914851551</v>
+        <v>-0.6125146617821932</v>
       </c>
       <c r="I67">
-        <v>590.17976072839</v>
+        <v>308.6678839784914</v>
       </c>
       <c r="J67">
-        <v>84749780.45685738</v>
+        <v>56115229.71723291</v>
       </c>
       <c r="K67">
-        <v>-762540.9801551001</v>
+        <v>-361473.8297768884</v>
       </c>
       <c r="L67">
-        <v>154454724.3994337</v>
+        <v>101811728.7840214</v>
       </c>
       <c r="M67">
-        <v>33893596.52674674</v>
+        <v>17830082.65572178</v>
       </c>
       <c r="N67">
-        <v>-239173.0906752563</v>
+        <v>-81464.45001703169</v>
       </c>
       <c r="O67">
-        <v>78493908.17687586</v>
+        <v>41052828.56913935</v>
       </c>
     </row>
     <row r="68">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3946,40 +3946,40 @@
         </is>
       </c>
       <c r="D68">
-        <v>1114.092762092152</v>
+        <v>291.8692436729297</v>
       </c>
       <c r="E68">
-        <v>-20.79611135804836</v>
+        <v>-5.963897442042409</v>
       </c>
       <c r="F68">
-        <v>2064.422780222847</v>
+        <v>542.4664884609232</v>
       </c>
       <c r="G68">
-        <v>210.0223631006641</v>
+        <v>44.89814723492645</v>
       </c>
       <c r="H68">
-        <v>-2.874019196076723</v>
+        <v>-0.649376661744649</v>
       </c>
       <c r="I68">
-        <v>493.8449558782468</v>
+        <v>105.7731082856237</v>
       </c>
       <c r="J68">
-        <v>83780889.80209187</v>
+        <v>21948858.99344795</v>
       </c>
       <c r="K68">
-        <v>-1563888.370236593</v>
+        <v>-448491.0515390311</v>
       </c>
       <c r="L68">
-        <v>155246657.4955382</v>
+        <v>40794022.39874988</v>
       </c>
       <c r="M68">
-        <v>27932974.29238832</v>
+        <v>5971453.582245218</v>
       </c>
       <c r="N68">
-        <v>-382244.5530782041</v>
+        <v>-86367.09601203832</v>
       </c>
       <c r="O68">
-        <v>65681379.13180683</v>
+        <v>14067823.40198795</v>
       </c>
     </row>
     <row r="69">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3999,40 +3999,40 @@
         </is>
       </c>
       <c r="D69">
-        <v>1049.538758709682</v>
+        <v>205.7682707726343</v>
       </c>
       <c r="E69">
-        <v>-13.64844790195101</v>
+        <v>-3.748507839004846</v>
       </c>
       <c r="F69">
-        <v>1927.985490450226</v>
+        <v>381.7344066699958</v>
       </c>
       <c r="G69">
-        <v>118.9596269928029</v>
+        <v>15.70796788506472</v>
       </c>
       <c r="H69">
-        <v>-1.099879069836721</v>
+        <v>-0.2209150993383896</v>
       </c>
       <c r="I69">
-        <v>277.0143360324025</v>
+        <v>37.04067036216222</v>
       </c>
       <c r="J69">
-        <v>78926364.19372678</v>
+        <v>15473979.73037287</v>
       </c>
       <c r="K69">
-        <v>-1026376.930674618</v>
+        <v>-281891.5380010035</v>
       </c>
       <c r="L69">
-        <v>144986436.8673475</v>
+        <v>28706809.11599034</v>
       </c>
       <c r="M69">
-        <v>15821630.39004279</v>
+        <v>2089159.728713608</v>
       </c>
       <c r="N69">
-        <v>-146283.9162882839</v>
+        <v>-29381.70821200581</v>
       </c>
       <c r="O69">
-        <v>36842906.69230954</v>
+        <v>4926409.158167575</v>
       </c>
     </row>
     <row r="70">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4052,40 +4052,40 @@
         </is>
       </c>
       <c r="D70">
-        <v>470.0037282158446</v>
+        <v>13.47889906923202</v>
       </c>
       <c r="E70">
-        <v>-14.63751464114057</v>
+        <v>-0.4249121631109685</v>
       </c>
       <c r="F70">
-        <v>887.9384426484394</v>
+        <v>25.47297894998426</v>
       </c>
       <c r="G70">
-        <v>27.40031978876461</v>
+        <v>0.4675404461018447</v>
       </c>
       <c r="H70">
-        <v>-0.6081923580574616</v>
+        <v>-0.01065194026547702</v>
       </c>
       <c r="I70">
-        <v>65.65738511630721</v>
+        <v>1.12148989158737</v>
       </c>
       <c r="J70">
-        <v>35344750.36555971</v>
+        <v>1013626.688905317</v>
       </c>
       <c r="K70">
-        <v>-1100755.738528411</v>
+        <v>-31953.81957810797</v>
       </c>
       <c r="L70">
-        <v>66773858.82560536</v>
+        <v>1915593.490017766</v>
       </c>
       <c r="M70">
-        <v>3644242.531905693</v>
+        <v>62182.87933154534</v>
       </c>
       <c r="N70">
-        <v>-80889.58362164239</v>
+        <v>-1416.708055308444</v>
       </c>
       <c r="O70">
-        <v>8732432.220468858</v>
+        <v>149158.1555811202</v>
       </c>
     </row>
     <row r="71">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4105,40 +4105,40 @@
         </is>
       </c>
       <c r="D71">
-        <v>418.323516331683</v>
+        <v>8.668563419980824</v>
       </c>
       <c r="E71">
-        <v>-8.431541213566685</v>
+        <v>-0.1636770258101142</v>
       </c>
       <c r="F71">
-        <v>774.4861830395084</v>
+        <v>16.00172410197061</v>
       </c>
       <c r="G71">
-        <v>3.668468909831707</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>-0.06001953188271275</v>
+        <v>0</v>
       </c>
       <c r="I71">
-        <v>8.657175371169654</v>
+        <v>0</v>
       </c>
       <c r="J71">
-        <v>31458346.75165891</v>
+        <v>651884.6377459782</v>
       </c>
       <c r="K71">
-        <v>-634060.3308014286</v>
+        <v>-12308.6760179464</v>
       </c>
       <c r="L71">
-        <v>58242135.45075408</v>
+        <v>1203345.654192291</v>
       </c>
       <c r="M71">
-        <v>487906.365007617</v>
+        <v>0</v>
       </c>
       <c r="N71">
-        <v>-7982.597740400796</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>1151404.324365564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4370,40 +4370,40 @@
         </is>
       </c>
       <c r="D76">
-        <v>0.752693498956816</v>
+        <v>42.63926391863715</v>
       </c>
       <c r="E76">
-        <v>0.5451580658020282</v>
+        <v>30.85648793905659</v>
       </c>
       <c r="F76">
-        <v>0.9371774707816141</v>
+        <v>53.1642962766704</v>
       </c>
       <c r="G76">
-        <v>1.208735743851216</v>
+        <v>60.38199947025288</v>
       </c>
       <c r="H76">
-        <v>0.7022889255897696</v>
+        <v>35.04772818966983</v>
       </c>
       <c r="I76">
-        <v>1.713557433089257</v>
+        <v>85.72844920862217</v>
       </c>
       <c r="J76">
-        <v>12674.60582893382</v>
+        <v>718002.5651259314</v>
       </c>
       <c r="K76">
-        <v>9179.916670040351</v>
+        <v>519592.400405774</v>
       </c>
       <c r="L76">
-        <v>15781.13143049159</v>
+        <v>895233.585002852</v>
       </c>
       <c r="M76">
-        <v>160761.8539322117</v>
+        <v>8030805.929543633</v>
       </c>
       <c r="N76">
-        <v>93404.42710343936</v>
+        <v>4661347.849226086</v>
       </c>
       <c r="O76">
-        <v>227903.1386008712</v>
+        <v>11401883.74474675</v>
       </c>
     </row>
     <row r="77">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4423,40 +4423,40 @@
         </is>
       </c>
       <c r="D77">
-        <v>1.870649334246026</v>
+        <v>31.95250069317949</v>
       </c>
       <c r="E77">
-        <v>1.35119886828296</v>
+        <v>23.19430802841775</v>
       </c>
       <c r="F77">
-        <v>2.331339705285234</v>
+        <v>39.71693412717614</v>
       </c>
       <c r="G77">
-        <v>2.539848348655287</v>
+        <v>38.52202401684249</v>
       </c>
       <c r="H77">
-        <v>1.471204858308528</v>
+        <v>22.41387975129247</v>
       </c>
       <c r="I77">
-        <v>3.605157230140842</v>
+        <v>54.54232575581823</v>
       </c>
       <c r="J77">
-        <v>31499.8641393688</v>
+        <v>538048.1591724498</v>
       </c>
       <c r="K77">
-        <v>22752.83774301676</v>
+        <v>390568.9528905266</v>
       </c>
       <c r="L77">
-        <v>39257.42929729808</v>
+        <v>668793.4537675187</v>
       </c>
       <c r="M77">
-        <v>337799.8303711532</v>
+        <v>5123429.194240051</v>
       </c>
       <c r="N77">
-        <v>195670.2461550343</v>
+        <v>2981046.006921899</v>
       </c>
       <c r="O77">
-        <v>479485.911608732</v>
+        <v>7254129.325523825</v>
       </c>
     </row>
     <row r="78">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4476,40 +4476,40 @@
         </is>
       </c>
       <c r="D78">
-        <v>6.715569815673259</v>
+        <v>104.6033861742602</v>
       </c>
       <c r="E78">
-        <v>4.87186231668871</v>
+        <v>75.42043888526108</v>
       </c>
       <c r="F78">
-        <v>8.360004456824004</v>
+        <v>130.5681309072896</v>
       </c>
       <c r="G78">
-        <v>8.409597472602824</v>
+        <v>110.8015512701713</v>
       </c>
       <c r="H78">
-        <v>4.892215080341418</v>
+        <v>64.07603552548778</v>
       </c>
       <c r="I78">
-        <v>11.92308773395681</v>
+        <v>157.5040182974602</v>
       </c>
       <c r="J78">
-        <v>113083.480126122</v>
+        <v>1761416.419788368</v>
       </c>
       <c r="K78">
-        <v>82037.28955072112</v>
+        <v>1270004.77038891</v>
       </c>
       <c r="L78">
-        <v>140774.1150484594</v>
+        <v>2198636.756347848</v>
       </c>
       <c r="M78">
-        <v>1118476.463856176</v>
+        <v>14736606.31893278</v>
       </c>
       <c r="N78">
-        <v>650664.6056854086</v>
+        <v>8522112.724889874</v>
       </c>
       <c r="O78">
-        <v>1585770.668616256</v>
+        <v>20948034.43356221</v>
       </c>
     </row>
     <row r="79">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4529,40 +4529,40 @@
         </is>
       </c>
       <c r="D79">
-        <v>6.780308310437436</v>
+        <v>75.99581851394554</v>
       </c>
       <c r="E79">
-        <v>4.906367351573829</v>
+        <v>54.85484880058541</v>
       </c>
       <c r="F79">
-        <v>8.454024890391915</v>
+        <v>94.8102088127888</v>
       </c>
       <c r="G79">
-        <v>6.997973403336917</v>
+        <v>64.44820910148275</v>
       </c>
       <c r="H79">
-        <v>4.063247071701373</v>
+        <v>37.29919990453576</v>
       </c>
       <c r="I79">
-        <v>9.93379400234247</v>
+        <v>91.58588365884177</v>
       </c>
       <c r="J79">
-        <v>114173.6116394559</v>
+        <v>1279693.587956328</v>
       </c>
       <c r="K79">
-        <v>82618.31983315181</v>
+        <v>923700.7989530578</v>
       </c>
       <c r="L79">
-        <v>142357.3251293096</v>
+        <v>1596509.106198551</v>
       </c>
       <c r="M79">
-        <v>930730.46264381</v>
+        <v>8571611.810497206</v>
       </c>
       <c r="N79">
-        <v>540411.8605362826</v>
+        <v>4960793.587303257</v>
       </c>
       <c r="O79">
-        <v>1321194.602311549</v>
+        <v>12180922.52662596</v>
       </c>
     </row>
     <row r="80">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4582,40 +4582,40 @@
         </is>
       </c>
       <c r="D80">
-        <v>68.36763978029055</v>
+        <v>674.147219098443</v>
       </c>
       <c r="E80">
-        <v>49.20095731483639</v>
+        <v>487.0566854583059</v>
       </c>
       <c r="F80">
-        <v>85.34606148286863</v>
+        <v>839.930565306678</v>
       </c>
       <c r="G80">
-        <v>61.55652052526607</v>
+        <v>475.6784501800716</v>
       </c>
       <c r="H80">
-        <v>35.51433431681684</v>
+        <v>275.5673369499414</v>
       </c>
       <c r="I80">
-        <v>87.5365796162652</v>
+        <v>674.9436043852808</v>
       </c>
       <c r="J80">
-        <v>1151242.68626031</v>
+        <v>11351965.02239868</v>
       </c>
       <c r="K80">
-        <v>828494.9202245307</v>
+        <v>8201547.526432404</v>
       </c>
       <c r="L80">
-        <v>1437142.329310026</v>
+        <v>14143590.78919915</v>
       </c>
       <c r="M80">
-        <v>8187017.229860387</v>
+        <v>63265233.87394953</v>
       </c>
       <c r="N80">
-        <v>4723406.464136641</v>
+        <v>36650455.8143422</v>
       </c>
       <c r="O80">
-        <v>11642365.08896327</v>
+        <v>89767499.38324234</v>
       </c>
     </row>
     <row r="81">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4635,40 +4635,40 @@
         </is>
       </c>
       <c r="D81">
-        <v>58.83300403330446</v>
+        <v>462.7552402732253</v>
       </c>
       <c r="E81">
-        <v>42.71604651537288</v>
+        <v>336.4913051052114</v>
       </c>
       <c r="F81">
-        <v>73.02700535863781</v>
+        <v>573.700377012012</v>
       </c>
       <c r="G81">
-        <v>40.20849558178615</v>
+        <v>227.176417866477</v>
       </c>
       <c r="H81">
-        <v>23.40620320414661</v>
+        <v>132.466903427451</v>
       </c>
       <c r="I81">
-        <v>56.85184802534004</v>
+        <v>320.7474241280407</v>
       </c>
       <c r="J81">
-        <v>990688.9549168139</v>
+        <v>7792335.490960839</v>
       </c>
       <c r="K81">
-        <v>719295.5072723641</v>
+        <v>5666177.086666649</v>
       </c>
       <c r="L81">
-        <v>1229701.743234102</v>
+        <v>9660540.64850527</v>
       </c>
       <c r="M81">
-        <v>5347729.912377558</v>
+        <v>30214463.57624144</v>
       </c>
       <c r="N81">
-        <v>3113025.026151499</v>
+        <v>17618098.15585098</v>
       </c>
       <c r="O81">
-        <v>7561295.787370225</v>
+        <v>42659407.40902942</v>
       </c>
     </row>
     <row r="82">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4688,40 +4688,40 @@
         </is>
       </c>
       <c r="D82">
-        <v>415.5102488441664</v>
+        <v>2077.879648182955</v>
       </c>
       <c r="E82">
-        <v>300.0154000533234</v>
+        <v>1500.85923581139</v>
       </c>
       <c r="F82">
-        <v>517.8791326321398</v>
+        <v>2591.337769846061</v>
       </c>
       <c r="G82">
-        <v>234.5706944939671</v>
+        <v>826.0331791213767</v>
       </c>
       <c r="H82">
-        <v>135.8444285847585</v>
+        <v>478.1840001107287</v>
       </c>
       <c r="I82">
-        <v>332.9323787394349</v>
+        <v>1173.216381912288</v>
       </c>
       <c r="J82">
-        <v>6996777.080286915</v>
+        <v>34989415.39575279</v>
       </c>
       <c r="K82">
-        <v>5051959.32149792</v>
+        <v>25272968.67182795</v>
       </c>
       <c r="L82">
-        <v>8720566.714392597</v>
+        <v>43635536.7064378</v>
       </c>
       <c r="M82">
-        <v>31197902.36769762</v>
+        <v>109862412.8231431</v>
       </c>
       <c r="N82">
-        <v>18067309.00177288</v>
+        <v>63598472.01472691</v>
       </c>
       <c r="O82">
-        <v>44280006.37234484</v>
+        <v>156037778.7943343</v>
       </c>
     </row>
     <row r="83">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4741,40 +4741,40 @@
         </is>
       </c>
       <c r="D83">
-        <v>253.4873579949261</v>
+        <v>1323.539254567487</v>
       </c>
       <c r="E83">
-        <v>184.5046324859482</v>
+        <v>959.2618208156717</v>
       </c>
       <c r="F83">
-        <v>314.1625903888029</v>
+        <v>1645.377164790601</v>
       </c>
       <c r="G83">
-        <v>85.43295298805478</v>
+        <v>224.9888055651197</v>
       </c>
       <c r="H83">
-        <v>49.80661842745749</v>
+        <v>131.0338575042825</v>
       </c>
       <c r="I83">
-        <v>120.6891459899655</v>
+        <v>318.1503521713901</v>
       </c>
       <c r="J83">
-        <v>4268473.621276561</v>
+        <v>22287077.50766191</v>
       </c>
       <c r="K83">
-        <v>3106873.506430882</v>
+        <v>16153009.80071509</v>
       </c>
       <c r="L83">
-        <v>5290183.859557058</v>
+        <v>27706506.07790894</v>
       </c>
       <c r="M83">
-        <v>11362582.74741129</v>
+        <v>29923511.14016091</v>
       </c>
       <c r="N83">
-        <v>6624280.250851845</v>
+        <v>17427503.04806957</v>
       </c>
       <c r="O83">
-        <v>16051656.41666541</v>
+        <v>42313996.83879489</v>
       </c>
     </row>
     <row r="84">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4794,40 +4794,40 @@
         </is>
       </c>
       <c r="D84">
-        <v>1893.102251797338</v>
+        <v>2805.287221048945</v>
       </c>
       <c r="E84">
-        <v>1363.764821148761</v>
+        <v>2016.165491771166</v>
       </c>
       <c r="F84">
-        <v>2368.725518566815</v>
+        <v>3516.221526999453</v>
       </c>
       <c r="G84">
-        <v>330.7098601386747</v>
+        <v>223.1164414143566</v>
       </c>
       <c r="H84">
-        <v>191.2085504883106</v>
+        <v>128.5003508428737</v>
       </c>
       <c r="I84">
-        <v>470.8186140213916</v>
+        <v>318.3024053306148</v>
       </c>
       <c r="J84">
-        <v>31877948.81801539</v>
+        <v>47238231.51524317</v>
       </c>
       <c r="K84">
-        <v>22964435.82332399</v>
+        <v>33950210.71593466</v>
       </c>
       <c r="L84">
-        <v>39886969.00714657</v>
+        <v>59209654.29314372</v>
       </c>
       <c r="M84">
-        <v>43984411.39844374</v>
+        <v>29674486.70810943</v>
       </c>
       <c r="N84">
-        <v>25430737.21494531</v>
+        <v>17090546.6621022</v>
       </c>
       <c r="O84">
-        <v>62618875.66484508</v>
+        <v>42334219.90897176</v>
       </c>
     </row>
     <row r="85">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4847,40 +4847,40 @@
         </is>
       </c>
       <c r="D85">
-        <v>869.7306909056242</v>
+        <v>1743.984240103224</v>
       </c>
       <c r="E85">
-        <v>625.3072125003119</v>
+        <v>1253.423079096667</v>
       </c>
       <c r="F85">
-        <v>1088.450524972352</v>
+        <v>2185.167124968635</v>
       </c>
       <c r="G85">
-        <v>23.50940673596779</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>13.49449459462594</v>
+        <v>0</v>
       </c>
       <c r="I85">
-        <v>33.57721147548644</v>
+        <v>0</v>
       </c>
       <c r="J85">
-        <v>14645395.10415981</v>
+        <v>29366950.61909819</v>
       </c>
       <c r="K85">
-        <v>10529548.15129275</v>
+        <v>21106391.22890878</v>
       </c>
       <c r="L85">
-        <v>18328418.39000943</v>
+        <v>36796029.21734685</v>
       </c>
       <c r="M85">
-        <v>3126751.095883715</v>
+        <v>0</v>
       </c>
       <c r="N85">
-        <v>1794767.78108525</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>4465769.126239696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4900,22 +4900,22 @@
         </is>
       </c>
       <c r="D86">
-        <v>11040.12965882238</v>
+        <v>9380.744247623055</v>
       </c>
       <c r="E86">
-        <v>8183.374989190699</v>
+        <v>6961.560468224564</v>
       </c>
       <c r="F86">
-        <v>13370.63870850162</v>
+        <v>11353.72567431491</v>
       </c>
       <c r="G86">
-        <v>19931.10956648468</v>
+        <v>16179.50226769469</v>
       </c>
       <c r="H86">
-        <v>9139.684252963147</v>
+        <v>7427.785367960292</v>
       </c>
       <c r="I86">
-        <v>36884.65271254427</v>
+        <v>29923.18110898441</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -4927,13 +4927,13 @@
         <v>0</v>
       </c>
       <c r="M86">
-        <v>2650837572.342462</v>
+        <v>2151873801.603393</v>
       </c>
       <c r="N86">
-        <v>1215578005.644099</v>
+        <v>987895453.9387189</v>
       </c>
       <c r="O86">
-        <v>4905658810.768389</v>
+        <v>3979783087.494927</v>
       </c>
     </row>
     <row r="87">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4953,22 +4953,22 @@
         </is>
       </c>
       <c r="D87">
-        <v>4842.783397916417</v>
+        <v>3439.580129767593</v>
       </c>
       <c r="E87">
-        <v>3596.597844490422</v>
+        <v>2555.570461528388</v>
       </c>
       <c r="F87">
-        <v>5861.594933983818</v>
+        <v>4157.461542842709</v>
       </c>
       <c r="G87">
-        <v>7892.102478751623</v>
+        <v>5374.351278317644</v>
       </c>
       <c r="H87">
-        <v>3625.79406662439</v>
+        <v>2470.039438519512</v>
       </c>
       <c r="I87">
-        <v>14596.27872452403</v>
+        <v>9927.217391390803</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -4980,13 +4980,13 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>1049649629.673966</v>
+        <v>714788720.0162467</v>
       </c>
       <c r="N87">
-        <v>482230610.8610439</v>
+        <v>328515245.3230951</v>
       </c>
       <c r="O87">
-        <v>1941305070.361696</v>
+        <v>1320319913.054977</v>
       </c>
     </row>
     <row r="88">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5006,22 +5006,22 @@
         </is>
       </c>
       <c r="D88">
-        <v>27125.60817627047</v>
+        <v>11199.33326526875</v>
       </c>
       <c r="E88">
-        <v>20141.89177630313</v>
+        <v>8350.58176127664</v>
       </c>
       <c r="F88">
-        <v>32798.58345993355</v>
+        <v>13523.43964544568</v>
       </c>
       <c r="G88">
-        <v>42979.76078014533</v>
+        <v>16301.4719448873</v>
       </c>
       <c r="H88">
-        <v>19743.42716980368</v>
+        <v>7517.546169829367</v>
       </c>
       <c r="I88">
-        <v>79410.62648664869</v>
+        <v>30079.6634702745</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5033,13 +5033,13 @@
         <v>0</v>
       </c>
       <c r="M88">
-        <v>5716308183.759329</v>
+        <v>2168095768.670011</v>
       </c>
       <c r="N88">
-        <v>2625875813.583889</v>
+        <v>999833640.5873058</v>
       </c>
       <c r="O88">
-        <v>10561613322.72428</v>
+        <v>4000595241.546509</v>
       </c>
     </row>
     <row r="89">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5059,22 +5059,22 @@
         </is>
       </c>
       <c r="D89">
-        <v>9106.403478834725</v>
+        <v>3654.60419283493</v>
       </c>
       <c r="E89">
-        <v>6768.626365737306</v>
+        <v>2712.601085011853</v>
       </c>
       <c r="F89">
-        <v>11004.42288704877</v>
+        <v>4424.300588961863</v>
       </c>
       <c r="G89">
-        <v>12784.15042305171</v>
+        <v>4648.005215522508</v>
       </c>
       <c r="H89">
-        <v>5877.996537869359</v>
+        <v>2134.413213735746</v>
       </c>
       <c r="I89">
-        <v>23605.78786677541</v>
+        <v>8598.039897146207</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5086,13 +5086,13 @@
         <v>0</v>
       </c>
       <c r="M89">
-        <v>1700292006.265877</v>
+        <v>618184693.6644937</v>
       </c>
       <c r="N89">
-        <v>781773539.5366247</v>
+        <v>283876957.4268543</v>
       </c>
       <c r="O89">
-        <v>3139569786.281129</v>
+        <v>1143539306.320446</v>
       </c>
     </row>
     <row r="90">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5112,22 +5112,22 @@
         </is>
       </c>
       <c r="D90">
-        <v>30566.8199983484</v>
+        <v>9456.521597367808</v>
       </c>
       <c r="E90">
-        <v>22852.05440470973</v>
+        <v>7035.710213306085</v>
       </c>
       <c r="F90">
-        <v>36913.70885044193</v>
+        <v>11440.94911965025</v>
       </c>
       <c r="G90">
-        <v>40173.36485736874</v>
+        <v>11316.74886201125</v>
       </c>
       <c r="H90">
-        <v>18582.65586204777</v>
+        <v>5210.018479686638</v>
       </c>
       <c r="I90">
-        <v>74125.01066749955</v>
+        <v>20918.73722242245</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5139,13 +5139,13 @@
         <v>0</v>
       </c>
       <c r="M90">
-        <v>5343057526.030043</v>
+        <v>1505127598.647496</v>
       </c>
       <c r="N90">
-        <v>2471493229.652354</v>
+        <v>692932457.7983228</v>
       </c>
       <c r="O90">
-        <v>9858626418.777439</v>
+        <v>2782192050.582185</v>
       </c>
     </row>
     <row r="91">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5165,22 +5165,22 @@
         </is>
       </c>
       <c r="D91">
-        <v>11932.64544715409</v>
+        <v>4681.502448717208</v>
       </c>
       <c r="E91">
-        <v>8870.704440358919</v>
+        <v>3484.726698952489</v>
       </c>
       <c r="F91">
-        <v>14430.88104815267</v>
+        <v>5659.07026777832</v>
       </c>
       <c r="G91">
-        <v>13226.05705968724</v>
+        <v>4761.547841957752</v>
       </c>
       <c r="H91">
-        <v>6081.282837558426</v>
+        <v>2192.45014629351</v>
       </c>
       <c r="I91">
-        <v>24443.26849249514</v>
+        <v>8794.779344579007</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5192,13 +5192,13 @@
         <v>0</v>
       </c>
       <c r="M91">
-        <v>1759065588.938403</v>
+        <v>633285862.980381</v>
       </c>
       <c r="N91">
-        <v>808810617.3952706</v>
+        <v>291595869.4570369</v>
       </c>
       <c r="O91">
-        <v>3250954709.501853</v>
+        <v>1169705652.829008</v>
       </c>
     </row>
     <row r="92">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5218,22 +5218,22 @@
         </is>
       </c>
       <c r="D92">
-        <v>17913.30409801184</v>
+        <v>9743.24923177754</v>
       </c>
       <c r="E92">
-        <v>13295.66838065507</v>
+        <v>7257.598194730519</v>
       </c>
       <c r="F92">
-        <v>21685.24466446849</v>
+        <v>11779.16793836737</v>
       </c>
       <c r="G92">
-        <v>18309.38076192352</v>
+        <v>8512.720485066291</v>
       </c>
       <c r="H92">
-        <v>8405.085020758535</v>
+        <v>3922.680513162982</v>
       </c>
       <c r="I92">
-        <v>33870.56476117945</v>
+        <v>15726.89156228439</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5245,13 +5245,13 @@
         <v>0</v>
       </c>
       <c r="M92">
-        <v>2435147641.335828</v>
+        <v>1132191824.513817</v>
       </c>
       <c r="N92">
-        <v>1117876307.760885</v>
+        <v>521716508.2506766</v>
       </c>
       <c r="O92">
-        <v>4504785113.236867</v>
+        <v>2091676577.783823</v>
       </c>
     </row>
     <row r="93">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5271,22 +5271,22 @@
         </is>
       </c>
       <c r="D93">
-        <v>6716.490798347496</v>
+        <v>4266.701220354023</v>
       </c>
       <c r="E93">
-        <v>4991.765669096125</v>
+        <v>3184.11712286428</v>
       </c>
       <c r="F93">
-        <v>8128.775933441339</v>
+        <v>5153.522800394068</v>
       </c>
       <c r="G93">
-        <v>5656.133166496538</v>
+        <v>2991.042643175893</v>
       </c>
       <c r="H93">
-        <v>2600.082431355514</v>
+        <v>1380.000938571025</v>
       </c>
       <c r="I93">
-        <v>10461.16312347522</v>
+        <v>5521.619034228957</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -5298,13 +5298,13 @@
         <v>0</v>
       </c>
       <c r="M93">
-        <v>752265711.1440396</v>
+        <v>397808671.5423938</v>
       </c>
       <c r="N93">
-        <v>345810963.3702834</v>
+        <v>183540124.8299463</v>
       </c>
       <c r="O93">
-        <v>1391334695.422205</v>
+        <v>734375331.5524514</v>
       </c>
     </row>
     <row r="94">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="D94">
-        <v>28286.29246790826</v>
+        <v>13715.64580850632</v>
       </c>
       <c r="E94">
-        <v>21097.97823339399</v>
+        <v>10228.33020417827</v>
       </c>
       <c r="F94">
-        <v>34158.8971776227</v>
+        <v>16562.58206480319</v>
       </c>
       <c r="G94">
-        <v>20827.24781104255</v>
+        <v>8381.379994685749</v>
       </c>
       <c r="H94">
-        <v>9610.845684688626</v>
+        <v>3867.700250193326</v>
       </c>
       <c r="I94">
-        <v>38434.55093724855</v>
+        <v>15463.7380083734</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5351,13 +5351,13 @@
         <v>0</v>
       </c>
       <c r="M94">
-        <v>2770023958.86866</v>
+        <v>1114723539.293205</v>
       </c>
       <c r="N94">
-        <v>1278242476.063587</v>
+        <v>514404133.2757123</v>
       </c>
       <c r="O94">
-        <v>5111795274.654057</v>
+        <v>2056677155.113663</v>
       </c>
     </row>
     <row r="95">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5377,22 +5377,22 @@
         </is>
       </c>
       <c r="D95">
-        <v>8796.924291187395</v>
+        <v>5758.846642493606</v>
       </c>
       <c r="E95">
-        <v>6628.561567883887</v>
+        <v>4352.721027720814</v>
       </c>
       <c r="F95">
-        <v>10584.67148834002</v>
+        <v>6922.851834767459</v>
       </c>
       <c r="G95">
-        <v>4889.137710202765</v>
+        <v>2498.105862859464</v>
       </c>
       <c r="H95">
-        <v>2277.500623804011</v>
+        <v>1168.317246083429</v>
       </c>
       <c r="I95">
-        <v>8990.91089784396</v>
+        <v>4588.182866820063</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5404,13 +5404,13 @@
         <v>0</v>
       </c>
       <c r="M95">
-        <v>650255315.4569678</v>
+        <v>332248079.7603087</v>
       </c>
       <c r="N95">
-        <v>302907582.9659335</v>
+        <v>155386193.7290961</v>
       </c>
       <c r="O95">
-        <v>1195791149.413247</v>
+        <v>610228321.2870684</v>
       </c>
     </row>
     <row r="96">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5430,22 +5430,22 @@
         </is>
       </c>
       <c r="D96">
-        <v>17582.35879292406</v>
+        <v>9659.298797959802</v>
       </c>
       <c r="E96">
-        <v>13103.47422138236</v>
+        <v>7170.464310593789</v>
       </c>
       <c r="F96">
-        <v>21249.08668753976</v>
+        <v>11689.61913808694</v>
       </c>
       <c r="G96">
-        <v>8137.718939232554</v>
+        <v>3385.71215311648</v>
       </c>
       <c r="H96">
-        <v>3753.05386291972</v>
+        <v>1557.169239455291</v>
       </c>
       <c r="I96">
-        <v>15026.20102024828</v>
+        <v>6257.892273667786</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5457,13 +5457,13 @@
         <v>0</v>
       </c>
       <c r="M96">
-        <v>1082316618.91793</v>
+        <v>450299716.3644918</v>
       </c>
       <c r="N96">
-        <v>499156163.7683228</v>
+        <v>207103508.8475537</v>
       </c>
       <c r="O96">
-        <v>1998484735.693022</v>
+        <v>832299672.3978156</v>
       </c>
     </row>
     <row r="97">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5483,22 +5483,22 @@
         </is>
       </c>
       <c r="D97">
-        <v>4467.186042483597</v>
+        <v>3690.778522982434</v>
       </c>
       <c r="E97">
-        <v>3348.872890097372</v>
+        <v>2751.394275948482</v>
       </c>
       <c r="F97">
-        <v>5384.834948468118</v>
+        <v>4457.620403426329</v>
       </c>
       <c r="G97">
-        <v>1242.058158569045</v>
+        <v>583.200890925389</v>
       </c>
       <c r="H97">
-        <v>576.6670197498282</v>
+        <v>268.636204318358</v>
       </c>
       <c r="I97">
-        <v>2287.311762177931</v>
+        <v>1076.643571299618</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -5510,13 +5510,13 @@
         <v>0</v>
       </c>
       <c r="M97">
-        <v>165193735.0896829</v>
+        <v>77565718.49307674</v>
       </c>
       <c r="N97">
-        <v>76696713.62672715</v>
+        <v>35728615.17434161</v>
       </c>
       <c r="O97">
-        <v>304212464.3696648</v>
+        <v>143193594.9828492</v>
       </c>
     </row>
     <row r="98">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5536,22 +5536,22 @@
         </is>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>4432.459166516505</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>3262.511855087479</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>5386.735981390131</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>324.4113803684724</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>147.60623695091</v>
       </c>
       <c r="I98">
-        <v>0</v>
+        <v>602.0782547810345</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -5563,13 +5563,13 @@
         <v>0</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>43146713.58900683</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>19631629.51447103</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>80076407.88587759</v>
       </c>
     </row>
     <row r="99">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5589,13 +5589,13 @@
         </is>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>1826.771995270673</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>1364.912367212454</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>2209.660127774706</v>
       </c>
       <c r="G99">
         <v>0</v>

--- a/output/Tables/2019/cases_prev_2019_sex_age.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex_age.xlsx
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="D2">
-        <v>135.7895157631368</v>
+        <v>146.4221301187112</v>
       </c>
       <c r="E2">
-        <v>116.7875792284561</v>
+        <v>125.6170451611738</v>
       </c>
       <c r="F2">
-        <v>153.59694664536</v>
+        <v>165.8811944921929</v>
       </c>
       <c r="G2">
-        <v>1387.116372356811</v>
+        <v>1496.082302404835</v>
       </c>
       <c r="H2">
-        <v>1192.840232689203</v>
+        <v>1283.443729065773</v>
       </c>
       <c r="I2">
-        <v>1569.167814508856</v>
+        <v>1694.95694261862</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -475,13 +475,13 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>184486477.5234558</v>
+        <v>198978946.2198431</v>
       </c>
       <c r="N2">
-        <v>158647750.947664</v>
+        <v>170698015.9657478</v>
       </c>
       <c r="O2">
-        <v>208699319.3296778</v>
+        <v>225429273.3682764</v>
       </c>
     </row>
     <row r="3">
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="D3">
-        <v>279.7957243507805</v>
+        <v>304.3972071285506</v>
       </c>
       <c r="E3">
-        <v>242.1645243134496</v>
+        <v>260.7233686243825</v>
       </c>
       <c r="F3">
-        <v>315.0827040323298</v>
+        <v>345.2228136533533</v>
       </c>
       <c r="G3">
-        <v>2570.894029288436</v>
+        <v>2800.345654439644</v>
       </c>
       <c r="H3">
-        <v>2225.049180486455</v>
+        <v>2398.034280840755</v>
       </c>
       <c r="I3">
-        <v>2895.182027095895</v>
+        <v>3176.382346427662</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -528,13 +528,13 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>341928905.895362</v>
+        <v>372445972.0404727</v>
       </c>
       <c r="N3">
-        <v>295931541.0046985</v>
+        <v>318938559.3518204</v>
       </c>
       <c r="O3">
-        <v>385059209.603754</v>
+        <v>422458852.0748791</v>
       </c>
     </row>
     <row r="4">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="D4">
-        <v>295.7892128425489</v>
+        <v>320.6350513976859</v>
       </c>
       <c r="E4">
-        <v>256.0027201730931</v>
+        <v>275.8725218057071</v>
       </c>
       <c r="F4">
-        <v>333.1780793841243</v>
+        <v>362.5262480925129</v>
       </c>
       <c r="G4">
-        <v>2494.381749618108</v>
+        <v>2705.146397241027</v>
       </c>
       <c r="H4">
-        <v>2159.37755986788</v>
+        <v>2327.685596863201</v>
       </c>
       <c r="I4">
-        <v>2809.232613838797</v>
+        <v>3058.406615907943</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -581,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>331752772.6992083</v>
+        <v>359784470.8330566</v>
       </c>
       <c r="N4">
-        <v>287197215.462428</v>
+        <v>309582184.3828058</v>
       </c>
       <c r="O4">
-        <v>373627937.64056</v>
+        <v>406768079.9157563</v>
       </c>
     </row>
     <row r="5">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="D5">
-        <v>521.9196886041157</v>
+        <v>547.6914754482884</v>
       </c>
       <c r="E5">
-        <v>454.1530508325517</v>
+        <v>474.7018882877405</v>
       </c>
       <c r="F5">
-        <v>585.745850392413</v>
+        <v>616.2518630465624</v>
       </c>
       <c r="G5">
-        <v>3840.48821649448</v>
+        <v>4029.499713532268</v>
       </c>
       <c r="H5">
-        <v>3340.48747997913</v>
+        <v>3491.224258063326</v>
       </c>
       <c r="I5">
-        <v>4311.283359115113</v>
+        <v>4535.009658516861</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -634,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>510784932.7937658</v>
+        <v>535923461.8997917</v>
       </c>
       <c r="N5">
-        <v>444284834.8372242</v>
+        <v>464332826.3224223</v>
       </c>
       <c r="O5">
-        <v>573400686.76231</v>
+        <v>603156284.5827426</v>
       </c>
     </row>
     <row r="6">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="D6">
-        <v>770.0417631305222</v>
+        <v>822.7254609748222</v>
       </c>
       <c r="E6">
-        <v>670.0653246993221</v>
+        <v>711.9296848723443</v>
       </c>
       <c r="F6">
-        <v>864.328047307856</v>
+        <v>926.9011848085071</v>
       </c>
       <c r="G6">
-        <v>5297.59568221121</v>
+        <v>5656.876426994456</v>
       </c>
       <c r="H6">
-        <v>4609.299648182503</v>
+        <v>4894.003826190119</v>
       </c>
       <c r="I6">
-        <v>5946.613515338825</v>
+        <v>6374.022438857703</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>704580225.7340909</v>
+        <v>752364564.7902626</v>
       </c>
       <c r="N6">
-        <v>613036853.2082729</v>
+        <v>650902508.8832859</v>
       </c>
       <c r="O6">
-        <v>790899597.5400637</v>
+        <v>847744984.3680744</v>
       </c>
     </row>
     <row r="7">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="D7">
-        <v>1388.044505150483</v>
+        <v>1481.265888707133</v>
       </c>
       <c r="E7">
-        <v>1209.438012698557</v>
+        <v>1279.464861840598</v>
       </c>
       <c r="F7">
-        <v>1556.310494590707</v>
+        <v>1670.533151363413</v>
       </c>
       <c r="G7">
-        <v>8060.197903529598</v>
+        <v>8599.472770575207</v>
       </c>
       <c r="H7">
-        <v>7017.392398122302</v>
+        <v>7423.277370577485</v>
       </c>
       <c r="I7">
-        <v>9042.212800203841</v>
+        <v>9702.215277464307</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -740,13 +740,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>1072006321.169437</v>
+        <v>1143729878.486502</v>
       </c>
       <c r="N7">
-        <v>933313188.9502662</v>
+        <v>987295890.2868055</v>
       </c>
       <c r="O7">
-        <v>1202614302.427111</v>
+        <v>1290394631.902753</v>
       </c>
     </row>
     <row r="8">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="D8">
-        <v>1721.347654868854</v>
+        <v>1897.984648076764</v>
       </c>
       <c r="E8">
-        <v>1495.696923581329</v>
+        <v>1636.768813818004</v>
       </c>
       <c r="F8">
-        <v>1933.840843349269</v>
+        <v>2143.156166310431</v>
       </c>
       <c r="G8">
-        <v>8803.063174934938</v>
+        <v>9706.167113044785</v>
       </c>
       <c r="H8">
-        <v>7648.724379137484</v>
+        <v>8368.761807126506</v>
       </c>
       <c r="I8">
-        <v>9890.01604130454</v>
+        <v>10961.19088231394</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -793,13 +793,13 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>1170807402.266347</v>
+        <v>1290920226.034956</v>
       </c>
       <c r="N8">
-        <v>1017280342.425285</v>
+        <v>1113045320.347825</v>
       </c>
       <c r="O8">
-        <v>1315372133.493504</v>
+        <v>1457838387.347754</v>
       </c>
     </row>
     <row r="9">
@@ -819,22 +819,22 @@
         </is>
       </c>
       <c r="D9">
-        <v>2857.515757290142</v>
+        <v>3016.209784570601</v>
       </c>
       <c r="E9">
-        <v>2475.87173490037</v>
+        <v>2596.782406610738</v>
       </c>
       <c r="F9">
-        <v>3216.062172160624</v>
+        <v>3409.465336409344</v>
       </c>
       <c r="G9">
-        <v>11697.88931849</v>
+        <v>12346.31833067548</v>
       </c>
       <c r="H9">
-        <v>10138.49016989617</v>
+        <v>10631.88461958973</v>
       </c>
       <c r="I9">
-        <v>13163.31602067603</v>
+        <v>13953.96005931906</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -846,13 +846,13 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>1555819279.359171</v>
+        <v>1642060337.979839</v>
       </c>
       <c r="N9">
-        <v>1348419192.596191</v>
+        <v>1414040654.405434</v>
       </c>
       <c r="O9">
-        <v>1750721030.749912</v>
+        <v>1855876687.889435</v>
       </c>
     </row>
     <row r="10">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="D10">
-        <v>3252.970522067571</v>
+        <v>3688.375714897353</v>
       </c>
       <c r="E10">
-        <v>2816.814064718356</v>
+        <v>3179.497927524445</v>
       </c>
       <c r="F10">
-        <v>3662.625138516344</v>
+        <v>4165.532253838414</v>
       </c>
       <c r="G10">
-        <v>11448.41423075072</v>
+        <v>12972.43251385566</v>
       </c>
       <c r="H10">
-        <v>9915.777023591296</v>
+        <v>11181.21154945163</v>
       </c>
       <c r="I10">
-        <v>12887.85579818644</v>
+        <v>14651.76612133568</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>1522639092.689846</v>
+        <v>1725333524.342802</v>
       </c>
       <c r="N10">
-        <v>1318798344.137642</v>
+        <v>1487101136.077066</v>
       </c>
       <c r="O10">
-        <v>1714084821.158797</v>
+        <v>1948684894.137646</v>
       </c>
     </row>
     <row r="11">
@@ -925,22 +925,22 @@
         </is>
       </c>
       <c r="D11">
-        <v>6190.23027551658</v>
+        <v>6786.538776640228</v>
       </c>
       <c r="E11">
-        <v>5416.027147269588</v>
+        <v>5889.43064407622</v>
       </c>
       <c r="F11">
-        <v>6919.929772248878</v>
+        <v>7628.432254583518</v>
       </c>
       <c r="G11">
-        <v>15443.13602428717</v>
+        <v>16869.17480792842</v>
       </c>
       <c r="H11">
-        <v>13505.7956226997</v>
+        <v>14629.24119403579</v>
       </c>
       <c r="I11">
-        <v>17269.40486179595</v>
+        <v>18970.71215493152</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -952,13 +952,13 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2053937091.230194</v>
+        <v>2243600249.45448</v>
       </c>
       <c r="N11">
-        <v>1796270817.81906</v>
+        <v>1945689078.80676</v>
       </c>
       <c r="O11">
-        <v>2296830846.618862</v>
+        <v>2523104716.605892</v>
       </c>
     </row>
     <row r="12">
@@ -978,22 +978,22 @@
         </is>
       </c>
       <c r="D12">
-        <v>5462.266004302733</v>
+        <v>6476.304467184525</v>
       </c>
       <c r="E12">
-        <v>4746.352247967895</v>
+        <v>5548.101733530149</v>
       </c>
       <c r="F12">
-        <v>6135.284025777381</v>
+        <v>7344.113239621301</v>
       </c>
       <c r="G12">
-        <v>10248.30197415718</v>
+        <v>12122.10086710747</v>
       </c>
       <c r="H12">
-        <v>8901.814157091321</v>
+        <v>10380.37294653721</v>
       </c>
       <c r="I12">
-        <v>11513.97685269445</v>
+        <v>13749.89273968116</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>1363024162.562905</v>
+        <v>1612239415.325294</v>
       </c>
       <c r="N12">
-        <v>1183941282.893146</v>
+        <v>1380589601.889449</v>
       </c>
       <c r="O12">
-        <v>1531358921.408362</v>
+        <v>1828735734.377594</v>
       </c>
     </row>
     <row r="13">
@@ -1031,22 +1031,22 @@
         </is>
       </c>
       <c r="D13">
-        <v>9391.753145266708</v>
+        <v>10374.11596772373</v>
       </c>
       <c r="E13">
-        <v>8203.40798256736</v>
+        <v>8964.720314821185</v>
       </c>
       <c r="F13">
-        <v>10510.67866531439</v>
+        <v>11695.0433994739</v>
       </c>
       <c r="G13">
-        <v>7876.386842891694</v>
+        <v>8702.163562565755</v>
       </c>
       <c r="H13">
-        <v>6903.893007015873</v>
+        <v>7546.0060668481</v>
       </c>
       <c r="I13">
-        <v>8793.74715332133</v>
+        <v>9787.488074784149</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1058,13 +1058,13 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>1047559450.104595</v>
+        <v>1157387753.821245</v>
       </c>
       <c r="N13">
-        <v>918217769.9331111</v>
+        <v>1003618806.890797</v>
       </c>
       <c r="O13">
-        <v>1169568371.391737</v>
+        <v>1301735913.946292</v>
       </c>
     </row>
     <row r="14">
@@ -1084,22 +1084,22 @@
         </is>
       </c>
       <c r="D14">
-        <v>8825.172602790961</v>
+        <v>11248.50302481298</v>
       </c>
       <c r="E14">
-        <v>7737.438288902115</v>
+        <v>9611.811879420429</v>
       </c>
       <c r="F14">
-        <v>9853.093347736551</v>
+        <v>12778.40144615328</v>
       </c>
       <c r="G14">
-        <v>2748.235296991658</v>
+        <v>3339.754822551085</v>
       </c>
       <c r="H14">
-        <v>2375.614414284361</v>
+        <v>2857.539313176464</v>
       </c>
       <c r="I14">
-        <v>3097.862343933533</v>
+        <v>3791.12580927367</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>365515294.4998906</v>
+        <v>444187391.3992943</v>
       </c>
       <c r="N14">
-        <v>315956717.0998201</v>
+        <v>380052728.6524696</v>
       </c>
       <c r="O14">
-        <v>412015691.7431599</v>
+        <v>504219732.6333981</v>
       </c>
     </row>
     <row r="15">
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>9997.08388726774</v>
+        <v>11697.55894851393</v>
       </c>
       <c r="E15">
-        <v>8776.061199472455</v>
+        <v>10127.7552612112</v>
       </c>
       <c r="F15">
-        <v>11150.95848252141</v>
+        <v>13171.26556683537</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1190,40 +1190,40 @@
         </is>
       </c>
       <c r="D16">
-        <v>5.648212249650857</v>
+        <v>6.524435643742579</v>
       </c>
       <c r="E16">
-        <v>0.3621844078418725</v>
+        <v>0.3141200395219647</v>
       </c>
       <c r="F16">
-        <v>11.44168189896307</v>
+        <v>13.19337676748551</v>
       </c>
       <c r="G16">
-        <v>3.86216340590345</v>
+        <v>4.46811642609897</v>
       </c>
       <c r="H16">
-        <v>0.1879803768290355</v>
+        <v>0.1631381998496042</v>
       </c>
       <c r="I16">
-        <v>9.898106036390448</v>
+        <v>11.43081632210524</v>
       </c>
       <c r="J16">
-        <v>249012.7334503571</v>
+        <v>287642.7942256792</v>
       </c>
       <c r="K16">
-        <v>15967.62398852464</v>
+        <v>13848.61018240486</v>
       </c>
       <c r="L16">
-        <v>504429.4298795849</v>
+        <v>581656.4015481338</v>
       </c>
       <c r="M16">
-        <v>513667.7329851588</v>
+        <v>594259.4846711629</v>
       </c>
       <c r="N16">
-        <v>25001.39011826172</v>
+        <v>21697.38057999736</v>
       </c>
       <c r="O16">
-        <v>1316448.10283993</v>
+        <v>1520298.570839996</v>
       </c>
     </row>
     <row r="17">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D18">
-        <v>52.72333797502797</v>
+        <v>60.8230847273533</v>
       </c>
       <c r="E18">
-        <v>2.881443117656295</v>
+        <v>2.600466091717347</v>
       </c>
       <c r="F18">
-        <v>106.7062404007115</v>
+        <v>122.9740691242863</v>
       </c>
       <c r="G18">
-        <v>30.74686849117606</v>
+        <v>35.47867666754749</v>
       </c>
       <c r="H18">
-        <v>1.251412081701897</v>
+        <v>1.129745594172115</v>
       </c>
       <c r="I18">
-        <v>78.72781876590606</v>
+        <v>90.75018249868283</v>
       </c>
       <c r="J18">
-        <v>2324413.801305056</v>
+        <v>2681507.336374827</v>
       </c>
       <c r="K18">
-        <v>127034.1827281129</v>
+        <v>114646.7485855427</v>
       </c>
       <c r="L18">
-        <v>4704358.020546167</v>
+        <v>5421557.785482411</v>
       </c>
       <c r="M18">
-        <v>4089333.509326416</v>
+        <v>4718663.996783816</v>
       </c>
       <c r="N18">
-        <v>166437.8068663523</v>
+        <v>150256.1640248913</v>
       </c>
       <c r="O18">
-        <v>10470799.89586551</v>
+        <v>12069774.27232482</v>
       </c>
     </row>
     <row r="19">
@@ -1402,40 +1402,40 @@
         </is>
       </c>
       <c r="D20">
-        <v>149.5886849177654</v>
+        <v>165.5730040268811</v>
       </c>
       <c r="E20">
-        <v>9.274773585647608</v>
+        <v>9.092994146509604</v>
       </c>
       <c r="F20">
-        <v>303.0888539868454</v>
+        <v>335.4170811235969</v>
       </c>
       <c r="G20">
-        <v>71.96867933563917</v>
+        <v>79.5616186131642</v>
       </c>
       <c r="H20">
-        <v>3.304973882658583</v>
+        <v>3.244602233317705</v>
       </c>
       <c r="I20">
-        <v>184.4588680812973</v>
+        <v>203.890212974138</v>
       </c>
       <c r="J20">
-        <v>6594916.351969528</v>
+        <v>7299617.028533106</v>
       </c>
       <c r="K20">
-        <v>408896.9430704461</v>
+        <v>400882.8329371688</v>
       </c>
       <c r="L20">
-        <v>13362278.30571806</v>
+        <v>14787532.85549601</v>
       </c>
       <c r="M20">
-        <v>9571834.351640008</v>
+        <v>10581695.27555084</v>
       </c>
       <c r="N20">
-        <v>439561.5263935915</v>
+        <v>431532.0970312547</v>
       </c>
       <c r="O20">
-        <v>24533029.45481253</v>
+        <v>27117398.32556035</v>
       </c>
     </row>
     <row r="21">
@@ -1508,40 +1508,40 @@
         </is>
       </c>
       <c r="D22">
-        <v>219.5783082373668</v>
+        <v>251.7812498928661</v>
       </c>
       <c r="E22">
-        <v>13.22799247824839</v>
+        <v>12.8785804021203</v>
       </c>
       <c r="F22">
-        <v>444.9502984211164</v>
+        <v>510.2430559632525</v>
       </c>
       <c r="G22">
-        <v>78.2176998449265</v>
+        <v>89.75016191643006</v>
       </c>
       <c r="H22">
-        <v>3.571004785713078</v>
+        <v>3.477210200320016</v>
       </c>
       <c r="I22">
-        <v>200.513974961397</v>
+        <v>230.1009824764288</v>
       </c>
       <c r="J22">
-        <v>9680548.875260813</v>
+        <v>11100279.96402676</v>
       </c>
       <c r="K22">
-        <v>583182.5043885368</v>
+        <v>567777.9741882789</v>
       </c>
       <c r="L22">
-        <v>19616523.80649174</v>
+        <v>22495085.6082519</v>
       </c>
       <c r="M22">
-        <v>10402954.07937522</v>
+        <v>11936771.5348852</v>
       </c>
       <c r="N22">
-        <v>474943.6364998394</v>
+        <v>462468.9566425622</v>
       </c>
       <c r="O22">
-        <v>26668358.6698658</v>
+        <v>30603430.66936503</v>
       </c>
     </row>
     <row r="23">
@@ -1614,40 +1614,40 @@
         </is>
       </c>
       <c r="D24">
-        <v>310.922814020667</v>
+        <v>367.3515897515194</v>
       </c>
       <c r="E24">
-        <v>14.60788347555417</v>
+        <v>13.49720200439301</v>
       </c>
       <c r="F24">
-        <v>628.8859536044117</v>
+        <v>743.2102578403769</v>
       </c>
       <c r="G24">
-        <v>77.30620578833496</v>
+        <v>91.19776900880296</v>
       </c>
       <c r="H24">
-        <v>2.692584935843128</v>
+        <v>2.480569511427557</v>
       </c>
       <c r="I24">
-        <v>197.8017641005916</v>
+        <v>233.4223465919159</v>
       </c>
       <c r="J24">
-        <v>13707654.10172914</v>
+        <v>16195429.53737525</v>
       </c>
       <c r="K24">
-        <v>644017.7587867565</v>
+        <v>595051.1447676739</v>
       </c>
       <c r="L24">
-        <v>27725695.03655771</v>
+        <v>32765910.63740879</v>
       </c>
       <c r="M24">
-        <v>10281725.36984855</v>
+        <v>12129303.27817079</v>
       </c>
       <c r="N24">
-        <v>358113.7964671361</v>
+        <v>329915.7450198651</v>
       </c>
       <c r="O24">
-        <v>26307634.62537868</v>
+        <v>31045172.09672482</v>
       </c>
     </row>
     <row r="25">
@@ -1720,40 +1720,40 @@
         </is>
       </c>
       <c r="D26">
-        <v>221.6265704376152</v>
+        <v>273.0790990765894</v>
       </c>
       <c r="E26">
-        <v>13.07549093564863</v>
+        <v>13.90786850031806</v>
       </c>
       <c r="F26">
-        <v>448.1896492260935</v>
+        <v>552.7241661333888</v>
       </c>
       <c r="G26">
-        <v>31.66973841904342</v>
+        <v>39.11984434386886</v>
       </c>
       <c r="H26">
-        <v>1.319772768810313</v>
+        <v>1.387639785026647</v>
       </c>
       <c r="I26">
-        <v>81.01833217666875</v>
+        <v>100.1545251339946</v>
       </c>
       <c r="J26">
-        <v>9770850.610883132</v>
+        <v>12039238.24098959</v>
       </c>
       <c r="K26">
-        <v>576459.1688799412</v>
+        <v>613156.1985735222</v>
       </c>
       <c r="L26">
-        <v>19759337.0654308</v>
+        <v>24367950.31232272</v>
       </c>
       <c r="M26">
-        <v>4212075.209732776</v>
+        <v>5202939.297734558</v>
       </c>
       <c r="N26">
-        <v>175529.7782517716</v>
+        <v>184556.0914085441</v>
       </c>
       <c r="O26">
-        <v>10775438.17949694</v>
+        <v>13320551.84282129</v>
       </c>
     </row>
     <row r="27">
@@ -1826,40 +1826,40 @@
         </is>
       </c>
       <c r="D28">
-        <v>96.04940078976152</v>
+        <v>123.4803524342697</v>
       </c>
       <c r="E28">
-        <v>7.500285785623698</v>
+        <v>9.002095304720594</v>
       </c>
       <c r="F28">
-        <v>194.3075535567516</v>
+        <v>250.3981351859366</v>
       </c>
       <c r="G28">
-        <v>2.86614444876792</v>
+        <v>3.546360748528262</v>
       </c>
       <c r="H28">
-        <v>0.169590709246417</v>
+        <v>0.1843717431331704</v>
       </c>
       <c r="I28">
-        <v>7.342817845337044</v>
+        <v>9.103980108572381</v>
       </c>
       <c r="J28">
-        <v>4234529.932618215</v>
+        <v>5443878.29776965</v>
       </c>
       <c r="K28">
-        <v>330665.0994307922</v>
+        <v>396875.3756992168</v>
       </c>
       <c r="L28">
-        <v>8566437.113656508</v>
+        <v>11039302.58594238</v>
       </c>
       <c r="M28">
-        <v>381197.2116861334</v>
+        <v>471665.9795542589</v>
       </c>
       <c r="N28">
-        <v>22555.56432977346</v>
+        <v>24521.44183671167</v>
       </c>
       <c r="O28">
-        <v>976594.7734298268</v>
+        <v>1210829.354440127</v>
       </c>
     </row>
     <row r="29">
@@ -1932,40 +1932,40 @@
         </is>
       </c>
       <c r="D30">
-        <v>83.23995056055985</v>
+        <v>92.77833442522571</v>
       </c>
       <c r="E30">
-        <v>51.84586475245128</v>
+        <v>57.99792248019556</v>
       </c>
       <c r="F30">
-        <v>114.6193677084371</v>
+        <v>127.1325348205727</v>
       </c>
       <c r="G30">
-        <v>55.08889656388022</v>
+        <v>61.42946942770202</v>
       </c>
       <c r="H30">
-        <v>26.92621126566889</v>
+        <v>30.13737672852331</v>
       </c>
       <c r="I30">
-        <v>92.49111916220072</v>
+        <v>102.6262506101235</v>
       </c>
       <c r="J30">
-        <v>4636631.726124305</v>
+        <v>5167938.784153922</v>
       </c>
       <c r="K30">
-        <v>2887918.358441039</v>
+        <v>3230600.277991856</v>
       </c>
       <c r="L30">
-        <v>6384528.02009536</v>
+        <v>7081536.454575542</v>
       </c>
       <c r="M30">
-        <v>7326823.242996069</v>
+        <v>8170119.433884369</v>
       </c>
       <c r="N30">
-        <v>3581186.098333962</v>
+        <v>4008271.104893601</v>
       </c>
       <c r="O30">
-        <v>12301318.8485727</v>
+        <v>13649291.33114643</v>
       </c>
     </row>
     <row r="31">
@@ -1985,40 +1985,40 @@
         </is>
       </c>
       <c r="D31">
-        <v>123.6661342565049</v>
+        <v>135.6490637347129</v>
       </c>
       <c r="E31">
-        <v>78.59796934804</v>
+        <v>85.00723101728489</v>
       </c>
       <c r="F31">
-        <v>168.2059483029122</v>
+        <v>185.620177680754</v>
       </c>
       <c r="G31">
-        <v>73.83635698688491</v>
+        <v>81.138962121977</v>
       </c>
       <c r="H31">
-        <v>36.82290584637317</v>
+        <v>39.89563651265448</v>
       </c>
       <c r="I31">
-        <v>122.4589015916569</v>
+        <v>135.3803452680405</v>
       </c>
       <c r="J31">
-        <v>6888451.010355827</v>
+        <v>7555924.148150986</v>
       </c>
       <c r="K31">
-        <v>4378064.088624521</v>
+        <v>4735072.782124808</v>
       </c>
       <c r="L31">
-        <v>9369407.732368816</v>
+        <v>10339415.13717336</v>
       </c>
       <c r="M31">
-        <v>9820235.479255693</v>
+        <v>10791481.96222294</v>
       </c>
       <c r="N31">
-        <v>4897446.477567633</v>
+        <v>5306119.656183046</v>
       </c>
       <c r="O31">
-        <v>16287033.91169036</v>
+        <v>18005585.92064938</v>
       </c>
     </row>
     <row r="32">
@@ -2038,40 +2038,40 @@
         </is>
       </c>
       <c r="D32">
-        <v>174.5695854183504</v>
+        <v>195.2293645175942</v>
       </c>
       <c r="E32">
-        <v>110.4654304018826</v>
+        <v>123.8561689258144</v>
       </c>
       <c r="F32">
-        <v>238.0225161287533</v>
+        <v>265.1937626766019</v>
       </c>
       <c r="G32">
-        <v>96.81216549512811</v>
+        <v>108.3376296269377</v>
       </c>
       <c r="H32">
-        <v>48.10707000881698</v>
+        <v>53.96135828771729</v>
       </c>
       <c r="I32">
-        <v>160.8561639532861</v>
+        <v>179.3516605761055</v>
       </c>
       <c r="J32">
-        <v>9723875.046972953</v>
+        <v>10874666.06235905</v>
       </c>
       <c r="K32">
-        <v>6153145.404245665</v>
+        <v>6899036.321505706</v>
       </c>
       <c r="L32">
-        <v>13258330.19340383</v>
+        <v>14771822.9686121</v>
       </c>
       <c r="M32">
-        <v>12876018.01085204</v>
+        <v>14408904.74038271</v>
       </c>
       <c r="N32">
-        <v>6398240.311172659</v>
+        <v>7176860.652266399</v>
       </c>
       <c r="O32">
-        <v>21393869.80578705</v>
+        <v>23853770.85662203</v>
       </c>
     </row>
     <row r="33">
@@ -2091,40 +2091,40 @@
         </is>
       </c>
       <c r="D33">
-        <v>274.6410210162461</v>
+        <v>290.5251973567622</v>
       </c>
       <c r="E33">
-        <v>173.8993934985107</v>
+        <v>183.4611080398511</v>
       </c>
       <c r="F33">
-        <v>375.5859466031761</v>
+        <v>397.6873695018385</v>
       </c>
       <c r="G33">
-        <v>132.0626626377148</v>
+        <v>139.6333650110806</v>
       </c>
       <c r="H33">
-        <v>65.60929893397358</v>
+        <v>69.18023231637781</v>
       </c>
       <c r="I33">
-        <v>220.167912191197</v>
+        <v>233.0173230220718</v>
       </c>
       <c r="J33">
-        <v>15298054.15264693</v>
+        <v>16182834.54316638</v>
       </c>
       <c r="K33">
-        <v>9686544.016654037</v>
+        <v>10219150.64003578</v>
       </c>
       <c r="L33">
-        <v>20920888.39769012</v>
+        <v>22151981.8559914</v>
       </c>
       <c r="M33">
-        <v>17564334.13081606</v>
+        <v>18571237.54647372</v>
       </c>
       <c r="N33">
-        <v>8726036.758218486</v>
+        <v>9200970.89807825</v>
       </c>
       <c r="O33">
-        <v>29282332.32142921</v>
+        <v>30991303.96193555</v>
       </c>
     </row>
     <row r="34">
@@ -2144,40 +2144,40 @@
         </is>
       </c>
       <c r="D34">
-        <v>542.2066209444051</v>
+        <v>591.4152867432659</v>
       </c>
       <c r="E34">
-        <v>342.595309979795</v>
+        <v>372.9800503342093</v>
       </c>
       <c r="F34">
-        <v>741.3468722132409</v>
+        <v>807.869275902249</v>
       </c>
       <c r="G34">
-        <v>245.0782163581136</v>
+        <v>267.0613630733988</v>
       </c>
       <c r="H34">
-        <v>121.6331018224478</v>
+        <v>132.2738944773852</v>
       </c>
       <c r="I34">
-        <v>408.2793428679594</v>
+        <v>444.5322296392495</v>
       </c>
       <c r="J34">
-        <v>30201993.19984521</v>
+        <v>32943014.30217335</v>
       </c>
       <c r="K34">
-        <v>19083243.95649454</v>
+        <v>20775734.7637161</v>
       </c>
       <c r="L34">
-        <v>41294503.47602196</v>
+        <v>44999934.40630708</v>
       </c>
       <c r="M34">
-        <v>32595402.7756291</v>
+        <v>35519161.28876203</v>
       </c>
       <c r="N34">
-        <v>16177202.54238555</v>
+        <v>17592427.96549223</v>
       </c>
       <c r="O34">
-        <v>54301152.6014386</v>
+        <v>59122786.54202018</v>
       </c>
     </row>
     <row r="35">
@@ -2197,40 +2197,40 @@
         </is>
       </c>
       <c r="D35">
-        <v>902.6300302568013</v>
+        <v>982.7683579834647</v>
       </c>
       <c r="E35">
-        <v>568.8892136295945</v>
+        <v>615.3763349288367</v>
       </c>
       <c r="F35">
-        <v>1237.895948823289</v>
+        <v>1349.63274350066</v>
       </c>
       <c r="G35">
-        <v>344.2338781477428</v>
+        <v>374.903253678539</v>
       </c>
       <c r="H35">
-        <v>170.2317577727689</v>
+        <v>184.2100858497481</v>
       </c>
       <c r="I35">
-        <v>575.4829954186363</v>
+        <v>627.5560069111061</v>
       </c>
       <c r="J35">
-        <v>50278297.94536436</v>
+        <v>54742163.07639498</v>
       </c>
       <c r="K35">
-        <v>31688266.97759568</v>
+        <v>34277692.6082061</v>
       </c>
       <c r="L35">
-        <v>68953280.1413548</v>
+        <v>75177243.07847367</v>
       </c>
       <c r="M35">
-        <v>45783105.79364979</v>
+        <v>49862132.73924568</v>
       </c>
       <c r="N35">
-        <v>22640823.78377827</v>
+        <v>24499941.4180165</v>
       </c>
       <c r="O35">
-        <v>76539238.39067863</v>
+        <v>83464948.91917711</v>
       </c>
     </row>
     <row r="36">
@@ -2250,40 +2250,40 @@
         </is>
       </c>
       <c r="D36">
-        <v>1453.67405710854</v>
+        <v>1643.860926040004</v>
       </c>
       <c r="E36">
-        <v>917.1131584484921</v>
+        <v>1032.131013275483</v>
       </c>
       <c r="F36">
-        <v>1985.338082792959</v>
+        <v>2245.336771866513</v>
       </c>
       <c r="G36">
-        <v>482.6056910616156</v>
+        <v>545.9608688557387</v>
       </c>
       <c r="H36">
-        <v>238.9716338313551</v>
+        <v>269.0268349113249</v>
       </c>
       <c r="I36">
-        <v>803.5502015065956</v>
+        <v>909.1210516543928</v>
       </c>
       <c r="J36">
-        <v>80972552.32905979</v>
+        <v>91566341.30228034</v>
       </c>
       <c r="K36">
-        <v>51085037.15189792</v>
+        <v>57491761.70147098</v>
       </c>
       <c r="L36">
-        <v>110587301.8877332</v>
+        <v>125069748.8665085</v>
       </c>
       <c r="M36">
-        <v>64186556.91119488</v>
+        <v>72612795.55781324</v>
       </c>
       <c r="N36">
-        <v>31783227.29957023</v>
+        <v>35780569.04320621</v>
       </c>
       <c r="O36">
-        <v>106872176.8003772</v>
+        <v>120913099.8700342</v>
       </c>
     </row>
     <row r="37">
@@ -2303,40 +2303,40 @@
         </is>
       </c>
       <c r="D37">
-        <v>2145.698632075707</v>
+        <v>2281.869078717225</v>
       </c>
       <c r="E37">
-        <v>1362.178335160663</v>
+        <v>1440.796488924802</v>
       </c>
       <c r="F37">
-        <v>2920.352817249919</v>
+        <v>3113.417919483419</v>
       </c>
       <c r="G37">
-        <v>570.7024319680295</v>
+        <v>607.181641529824</v>
       </c>
       <c r="H37">
-        <v>284.1846553279411</v>
+        <v>300.7680878604466</v>
       </c>
       <c r="I37">
-        <v>947.2028688625136</v>
+        <v>1010.158823585343</v>
       </c>
       <c r="J37">
-        <v>119519705.2038811</v>
+        <v>127104671.4227068</v>
       </c>
       <c r="K37">
-        <v>75876057.62511928</v>
+        <v>80255246.02608931</v>
       </c>
       <c r="L37">
-        <v>162669492.626455</v>
+        <v>173423604.9510656</v>
       </c>
       <c r="M37">
-        <v>75903423.45174792</v>
+        <v>80755158.32346658</v>
       </c>
       <c r="N37">
-        <v>37796559.15861616</v>
+        <v>40002155.6854394</v>
       </c>
       <c r="O37">
-        <v>125977981.5587143</v>
+        <v>134351123.5368507</v>
       </c>
     </row>
     <row r="38">
@@ -2356,40 +2356,40 @@
         </is>
       </c>
       <c r="D38">
-        <v>4083.109740632935</v>
+        <v>4738.672408902913</v>
       </c>
       <c r="E38">
-        <v>2589.870361648168</v>
+        <v>3005.445021319446</v>
       </c>
       <c r="F38">
-        <v>5551.597873922985</v>
+        <v>6429.639299581467</v>
       </c>
       <c r="G38">
-        <v>936.2528338412366</v>
+        <v>1085.001380475874</v>
       </c>
       <c r="H38">
-        <v>466.4539852637737</v>
+        <v>540.3360058744925</v>
       </c>
       <c r="I38">
-        <v>1550.846727786276</v>
+        <v>1793.98927381985</v>
       </c>
       <c r="J38">
-        <v>227437378.7727357</v>
+        <v>263953530.5207101</v>
       </c>
       <c r="K38">
-        <v>144260958.884526</v>
+        <v>167409298.5775359</v>
       </c>
       <c r="L38">
-        <v>309235104.7732583</v>
+        <v>358143768.2652868</v>
       </c>
       <c r="M38">
-        <v>124521626.9008845</v>
+        <v>144305183.6032913</v>
       </c>
       <c r="N38">
-        <v>62038380.04008191</v>
+        <v>71864688.7813075</v>
       </c>
       <c r="O38">
-        <v>206262614.7955746</v>
+        <v>238600573.4180401</v>
       </c>
     </row>
     <row r="39">
@@ -2409,40 +2409,40 @@
         </is>
       </c>
       <c r="D39">
-        <v>5819.041918769583</v>
+        <v>6478.526685452082</v>
       </c>
       <c r="E39">
-        <v>3800.944081466854</v>
+        <v>4209.216951589732</v>
       </c>
       <c r="F39">
-        <v>7790.912306113683</v>
+        <v>8684.934272686958</v>
       </c>
       <c r="G39">
-        <v>951.6585372075313</v>
+        <v>1054.459666711367</v>
       </c>
       <c r="H39">
-        <v>487.4495006788249</v>
+        <v>537.3273599592111</v>
       </c>
       <c r="I39">
-        <v>1553.736930195819</v>
+        <v>1723.815101167645</v>
       </c>
       <c r="J39">
-        <v>324132272.9593034</v>
+        <v>360866893.4330518</v>
       </c>
       <c r="K39">
-        <v>211720187.2258669</v>
+        <v>234461802.6374513</v>
       </c>
       <c r="L39">
-        <v>433969397.2751447</v>
+        <v>483768208.8572096</v>
       </c>
       <c r="M39">
-        <v>126570585.4486017</v>
+        <v>140243135.6726118</v>
       </c>
       <c r="N39">
-        <v>64830783.59028371</v>
+        <v>71464538.87457508</v>
       </c>
       <c r="O39">
-        <v>206647011.7160439</v>
+        <v>229267408.4552968</v>
       </c>
     </row>
     <row r="40">
@@ -2462,40 +2462,40 @@
         </is>
       </c>
       <c r="D40">
-        <v>5377.052799538219</v>
+        <v>6558.472911335218</v>
       </c>
       <c r="E40">
-        <v>3397.94939500902</v>
+        <v>4097.272051516084</v>
       </c>
       <c r="F40">
-        <v>7344.804124695659</v>
+        <v>8984.354222218995</v>
       </c>
       <c r="G40">
-        <v>694.5433490688334</v>
+        <v>847.2615888878361</v>
       </c>
       <c r="H40">
-        <v>345.1247219361314</v>
+        <v>416.429569082312</v>
       </c>
       <c r="I40">
-        <v>1154.756226006886</v>
+        <v>1412.120715496651</v>
       </c>
       <c r="J40">
-        <v>299512595.0398781</v>
+        <v>365320058.1071944</v>
       </c>
       <c r="K40">
-        <v>189272577.2007926</v>
+        <v>228226247.8135489</v>
       </c>
       <c r="L40">
-        <v>409120279.3537972</v>
+        <v>500446498.8860425</v>
       </c>
       <c r="M40">
-        <v>92374265.42615485</v>
+        <v>112685791.3220822</v>
       </c>
       <c r="N40">
-        <v>45901588.01750547</v>
+        <v>55385132.6879475</v>
       </c>
       <c r="O40">
-        <v>153582578.0589158</v>
+        <v>187812055.1610546</v>
       </c>
     </row>
     <row r="41">
@@ -2515,40 +2515,40 @@
         </is>
       </c>
       <c r="D41">
-        <v>6216.59645856795</v>
+        <v>6878.835877345051</v>
       </c>
       <c r="E41">
-        <v>4023.402806464861</v>
+        <v>4399.644362797233</v>
       </c>
       <c r="F41">
-        <v>8365.54307168905</v>
+        <v>9314.878417584296</v>
       </c>
       <c r="G41">
-        <v>376.7846431853371</v>
+        <v>417.5674873303445</v>
       </c>
       <c r="H41">
-        <v>191.2313932225986</v>
+        <v>209.3890074401274</v>
       </c>
       <c r="I41">
-        <v>618.6677280986461</v>
+        <v>689.9516143915623</v>
       </c>
       <c r="J41">
-        <v>346276855.9351524</v>
+        <v>383164916.0398745</v>
       </c>
       <c r="K41">
-        <v>224111583.1257061</v>
+        <v>245068990.2965314</v>
       </c>
       <c r="L41">
-        <v>465977480.1792238</v>
+        <v>518857357.6162809</v>
       </c>
       <c r="M41">
-        <v>50112357.54364984</v>
+        <v>55536475.81493582</v>
       </c>
       <c r="N41">
-        <v>25433775.29860562</v>
+        <v>27848737.98953694</v>
       </c>
       <c r="O41">
-        <v>82282807.83711992</v>
+        <v>91763564.71407779</v>
       </c>
     </row>
     <row r="42">
@@ -2568,40 +2568,40 @@
         </is>
       </c>
       <c r="D42">
-        <v>3670.112414875829</v>
+        <v>4754.302361004454</v>
       </c>
       <c r="E42">
-        <v>2319.26669429189</v>
+        <v>2930.534283444486</v>
       </c>
       <c r="F42">
-        <v>5036.601376703374</v>
+        <v>6579.016104825467</v>
       </c>
       <c r="G42">
-        <v>98.46924870225052</v>
+        <v>122.9411265328773</v>
       </c>
       <c r="H42">
-        <v>48.3146828759921</v>
+        <v>59.33212498868297</v>
       </c>
       <c r="I42">
-        <v>165.4108939080201</v>
+        <v>207.3556559209103</v>
       </c>
       <c r="J42">
-        <v>204432601.7334136</v>
+        <v>264824150.11267</v>
       </c>
       <c r="K42">
-        <v>129187793.405447</v>
+        <v>163236620.6564246</v>
       </c>
       <c r="L42">
-        <v>280548769.8851314</v>
+        <v>366464355.070988</v>
       </c>
       <c r="M42">
-        <v>13096410.07739932</v>
+        <v>16351169.82887268</v>
       </c>
       <c r="N42">
-        <v>6425852.82250695</v>
+        <v>7891172.623494835</v>
       </c>
       <c r="O42">
-        <v>21999648.88976667</v>
+        <v>27578302.23748107</v>
       </c>
     </row>
     <row r="43">
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="D43">
-        <v>3442.307868291495</v>
+        <v>4035.360950613182</v>
       </c>
       <c r="E43">
-        <v>2232.285490209321</v>
+        <v>2578.007879354308</v>
       </c>
       <c r="F43">
-        <v>4650.063857689388</v>
+        <v>5490.355844215614</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2639,13 +2639,13 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>191743432.8795728</v>
+        <v>224777675.6710557</v>
       </c>
       <c r="K43">
-        <v>124342766.3756396</v>
+        <v>143600194.8957937</v>
       </c>
       <c r="L43">
-        <v>259017857.0010145</v>
+        <v>305823801.2344981</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -2674,40 +2674,40 @@
         </is>
       </c>
       <c r="D44">
-        <v>1335.370590986217</v>
+        <v>1529.967334197196</v>
       </c>
       <c r="E44">
-        <v>91.83848986409276</v>
+        <v>83.33406507317531</v>
       </c>
       <c r="F44">
-        <v>2704.291208140276</v>
+        <v>3096.145374802112</v>
       </c>
       <c r="G44">
-        <v>758.1572439702238</v>
+        <v>869.1926004040034</v>
       </c>
       <c r="H44">
-        <v>41.64471711629454</v>
+        <v>37.83097012377794</v>
       </c>
       <c r="I44">
-        <v>1772.865050482651</v>
+        <v>2031.115522954</v>
       </c>
       <c r="J44">
-        <v>19772832.34073291</v>
+        <v>22654226.31745791</v>
       </c>
       <c r="K44">
-        <v>1359852.519417622</v>
+        <v>1233927.501538506</v>
       </c>
       <c r="L44">
-        <v>40042439.91893309</v>
+        <v>45844624.5646948</v>
       </c>
       <c r="M44">
-        <v>100834913.4480398</v>
+        <v>115602615.8537325</v>
       </c>
       <c r="N44">
-        <v>5538747.376467173</v>
+        <v>5031519.026462466</v>
       </c>
       <c r="O44">
-        <v>235791051.7141925</v>
+        <v>270138364.5528821</v>
       </c>
     </row>
     <row r="45">
@@ -2727,40 +2727,40 @@
         </is>
       </c>
       <c r="D45">
-        <v>323.7867590721423</v>
+        <v>351.6245684794629</v>
       </c>
       <c r="E45">
-        <v>16.68319504152884</v>
+        <v>18.01541696591593</v>
       </c>
       <c r="F45">
-        <v>654.3640583517122</v>
+        <v>711.8170378773087</v>
       </c>
       <c r="G45">
-        <v>166.0034437932026</v>
+        <v>180.693015136505</v>
       </c>
       <c r="H45">
-        <v>6.865808856069485</v>
+        <v>7.390557765382594</v>
       </c>
       <c r="I45">
-        <v>387.3754638791266</v>
+        <v>422.3696147711037</v>
       </c>
       <c r="J45">
-        <v>4794310.541581211</v>
+        <v>5206504.985475406</v>
       </c>
       <c r="K45">
-        <v>247028.0689799178</v>
+        <v>266754.2790143174</v>
       </c>
       <c r="L45">
-        <v>9689168.612013798</v>
+        <v>10539874.8798493</v>
       </c>
       <c r="M45">
-        <v>22078458.02449594</v>
+        <v>24032171.01315516</v>
       </c>
       <c r="N45">
-        <v>913152.5778572415</v>
+        <v>982944.182795885</v>
       </c>
       <c r="O45">
-        <v>51520936.69592384</v>
+        <v>56175158.7645568</v>
       </c>
     </row>
     <row r="46">
@@ -2780,40 +2780,40 @@
         </is>
       </c>
       <c r="D46">
-        <v>2350.584020776749</v>
+        <v>2711.394525317037</v>
       </c>
       <c r="E46">
-        <v>124.53374623259</v>
+        <v>112.329351496371</v>
       </c>
       <c r="F46">
-        <v>4757.784478276796</v>
+        <v>5482.296495174682</v>
       </c>
       <c r="G46">
-        <v>1123.688682425456</v>
+        <v>1296.690736818641</v>
       </c>
       <c r="H46">
-        <v>46.64555467330781</v>
+        <v>42.06653654608095</v>
       </c>
       <c r="I46">
-        <v>2626.271760835872</v>
+        <v>3027.381826402629</v>
       </c>
       <c r="J46">
-        <v>34805097.59564131</v>
+        <v>40147618.73636941</v>
       </c>
       <c r="K46">
-        <v>1843971.180465963</v>
+        <v>1663260.707606766</v>
       </c>
       <c r="L46">
-        <v>70448514.76984458</v>
+        <v>81176364.20405152</v>
       </c>
       <c r="M46">
-        <v>149450594.7625857</v>
+        <v>172459867.9968793</v>
       </c>
       <c r="N46">
-        <v>6203858.771549938</v>
+        <v>5594849.360628767</v>
       </c>
       <c r="O46">
-        <v>349294144.191171</v>
+        <v>402641782.9115497</v>
       </c>
     </row>
     <row r="47">
@@ -2833,40 +2833,40 @@
         </is>
       </c>
       <c r="D47">
-        <v>498.4053473700117</v>
+        <v>528.5618048818598</v>
       </c>
       <c r="E47">
-        <v>32.57597053728416</v>
+        <v>33.71872067483555</v>
       </c>
       <c r="F47">
-        <v>1008.490348476556</v>
+        <v>1069.000295128041</v>
       </c>
       <c r="G47">
-        <v>206.9197219590953</v>
+        <v>219.2713320994015</v>
       </c>
       <c r="H47">
-        <v>10.67353927931632</v>
+        <v>11.04747824618347</v>
       </c>
       <c r="I47">
-        <v>483.4430083381172</v>
+        <v>512.079728938857</v>
       </c>
       <c r="J47">
-        <v>7379887.978507763</v>
+        <v>7826414.644885696</v>
       </c>
       <c r="K47">
-        <v>482352.3957455666</v>
+        <v>499273.0970322899</v>
       </c>
       <c r="L47">
-        <v>14932716.58989235</v>
+        <v>15828687.36996092</v>
       </c>
       <c r="M47">
-        <v>27520323.02055968</v>
+        <v>29163087.1692204</v>
       </c>
       <c r="N47">
-        <v>1419580.724149071</v>
+        <v>1469314.606742402</v>
       </c>
       <c r="O47">
-        <v>64297920.10896958</v>
+        <v>68106603.94886798</v>
       </c>
     </row>
     <row r="48">
@@ -2886,40 +2886,40 @@
         </is>
       </c>
       <c r="D48">
-        <v>2915.542314309878</v>
+        <v>3214.054712457849</v>
       </c>
       <c r="E48">
-        <v>174.9848709095844</v>
+        <v>172.628420995428</v>
       </c>
       <c r="F48">
-        <v>5906.141565928693</v>
+        <v>6509.922726056692</v>
       </c>
       <c r="G48">
-        <v>1145.547474125316</v>
+        <v>1261.304071258591</v>
       </c>
       <c r="H48">
-        <v>53.55836432258492</v>
+        <v>52.92188371853606</v>
       </c>
       <c r="I48">
-        <v>2679.2190589562</v>
+        <v>2949.626985287514</v>
       </c>
       <c r="J48">
-        <v>43170435.04798637</v>
+        <v>47590508.12736341</v>
       </c>
       <c r="K48">
-        <v>2591000.983558216</v>
+        <v>2556109.029679297</v>
       </c>
       <c r="L48">
-        <v>87452238.16670604</v>
+        <v>96392425.80472146</v>
       </c>
       <c r="M48">
-        <v>152357814.058667</v>
+        <v>167753441.4773926</v>
       </c>
       <c r="N48">
-        <v>7123262.454903794</v>
+        <v>7038610.534565296</v>
       </c>
       <c r="O48">
-        <v>356336134.8411746</v>
+        <v>392300389.0432394</v>
       </c>
     </row>
     <row r="49">
@@ -2939,40 +2939,40 @@
         </is>
       </c>
       <c r="D49">
-        <v>899.5817097839383</v>
+        <v>987.7020398794101</v>
       </c>
       <c r="E49">
-        <v>65.54013756198783</v>
+        <v>65.24137561308976</v>
       </c>
       <c r="F49">
-        <v>1820.291349665868</v>
+        <v>1998.590072062647</v>
       </c>
       <c r="G49">
-        <v>296.469011390438</v>
+        <v>325.5537866127615</v>
       </c>
       <c r="H49">
-        <v>16.893632746061</v>
+        <v>16.80710683320778</v>
       </c>
       <c r="I49">
-        <v>692.6882762139948</v>
+        <v>760.5995854750342</v>
       </c>
       <c r="J49">
-        <v>13320106.37677077</v>
+        <v>14624904.10449442</v>
       </c>
       <c r="K49">
-        <v>970452.8168803537</v>
+        <v>966029.0487030187</v>
       </c>
       <c r="L49">
-        <v>26953054.01450252</v>
+        <v>29593123.19703162</v>
       </c>
       <c r="M49">
-        <v>39430378.51492825</v>
+        <v>43298653.61949728</v>
       </c>
       <c r="N49">
-        <v>2246853.155226113</v>
+        <v>2235345.208816634</v>
       </c>
       <c r="O49">
-        <v>92127540.7364613</v>
+        <v>101159744.8681796</v>
       </c>
     </row>
     <row r="50">
@@ -2992,40 +2992,40 @@
         </is>
       </c>
       <c r="D50">
-        <v>3460.77293960008</v>
+        <v>3968.233975973964</v>
       </c>
       <c r="E50">
-        <v>208.3774141432357</v>
+        <v>202.8770975627731</v>
       </c>
       <c r="F50">
-        <v>7012.896777836362</v>
+        <v>8041.789182934462</v>
       </c>
       <c r="G50">
-        <v>998.345985325289</v>
+        <v>1145.51698401135</v>
       </c>
       <c r="H50">
-        <v>47.92265602378499</v>
+        <v>46.66458735289672</v>
       </c>
       <c r="I50">
-        <v>2335.861924730683</v>
+        <v>2680.467910382984</v>
       </c>
       <c r="J50">
-        <v>51243664.91665832</v>
+        <v>58757640.48224651</v>
       </c>
       <c r="K50">
-        <v>3085444.371218893</v>
+        <v>3004001.183611978</v>
       </c>
       <c r="L50">
-        <v>103839962.5894231</v>
+        <v>119074772.4317104</v>
       </c>
       <c r="M50">
-        <v>132780016.0482634</v>
+        <v>152353758.8735096</v>
       </c>
       <c r="N50">
-        <v>6373713.251163404</v>
+        <v>6206390.117935264</v>
       </c>
       <c r="O50">
-        <v>310669635.9891809</v>
+        <v>356502232.0809369</v>
       </c>
     </row>
     <row r="51">
@@ -3045,40 +3045,40 @@
         </is>
       </c>
       <c r="D51">
-        <v>1544.146685832242</v>
+        <v>1645.673537469884</v>
       </c>
       <c r="E51">
-        <v>80.46925568720364</v>
+        <v>80.88788067733796</v>
       </c>
       <c r="F51">
-        <v>3126.000627868866</v>
+        <v>3332.155664217125</v>
       </c>
       <c r="G51">
-        <v>353.2853818387192</v>
+        <v>376.9680308430953</v>
       </c>
       <c r="H51">
-        <v>14.77990469592172</v>
+        <v>14.84665188961193</v>
       </c>
       <c r="I51">
-        <v>825.9467883216313</v>
+        <v>881.3995247852351</v>
       </c>
       <c r="J51">
-        <v>22864179.97711799</v>
+        <v>24367488.06931661</v>
       </c>
       <c r="K51">
-        <v>1191508.268960425</v>
+        <v>1197706.849189342</v>
       </c>
       <c r="L51">
-        <v>46286691.29685428</v>
+        <v>49339228.9200629</v>
       </c>
       <c r="M51">
-        <v>46986955.78454965</v>
+        <v>50136748.10213168</v>
       </c>
       <c r="N51">
-        <v>1965727.324557589</v>
+        <v>1974604.701318387</v>
       </c>
       <c r="O51">
-        <v>109850922.846777</v>
+        <v>117226136.7964363</v>
       </c>
     </row>
     <row r="52">
@@ -3098,40 +3098,40 @@
         </is>
       </c>
       <c r="D52">
-        <v>3873.192544932659</v>
+        <v>4573.798369777716</v>
       </c>
       <c r="E52">
-        <v>181.5966231413001</v>
+        <v>167.0660242072252</v>
       </c>
       <c r="F52">
-        <v>7834.133472774869</v>
+        <v>9253.603057028466</v>
       </c>
       <c r="G52">
-        <v>788.0458167916096</v>
+        <v>929.3793407562565</v>
       </c>
       <c r="H52">
-        <v>28.85569043881138</v>
+        <v>26.45950049216434</v>
       </c>
       <c r="I52">
-        <v>1840.336449191583</v>
+        <v>2171.112393619836</v>
       </c>
       <c r="J52">
-        <v>57350362.01281789</v>
+        <v>67724232.46129867</v>
       </c>
       <c r="K52">
-        <v>2688901.198853238</v>
+        <v>2473746.620436382</v>
       </c>
       <c r="L52">
-        <v>116000014.3313776</v>
+        <v>137018100.4654205</v>
       </c>
       <c r="M52">
-        <v>104810093.6332841</v>
+        <v>123607452.3205821</v>
       </c>
       <c r="N52">
-        <v>3837806.828361914</v>
+        <v>3519113.565457857</v>
       </c>
       <c r="O52">
-        <v>244764747.7424805</v>
+        <v>288757948.3514381</v>
       </c>
     </row>
     <row r="53">
@@ -3151,40 +3151,40 @@
         </is>
       </c>
       <c r="D53">
-        <v>3153.424426433926</v>
+        <v>3535.693014630197</v>
       </c>
       <c r="E53">
-        <v>91.69095097842415</v>
+        <v>91.4188366895562</v>
       </c>
       <c r="F53">
-        <v>6365.003342355228</v>
+        <v>7137.909023429165</v>
       </c>
       <c r="G53">
-        <v>451.0430312370158</v>
+        <v>503.5032495395552</v>
       </c>
       <c r="H53">
-        <v>10.14706294286108</v>
+        <v>10.36754485924891</v>
       </c>
       <c r="I53">
-        <v>1051.40277744885</v>
+        <v>1173.790138559351</v>
       </c>
       <c r="J53">
-        <v>46692755.48220715</v>
+        <v>52353006.46762938</v>
       </c>
       <c r="K53">
-        <v>1357667.911137526</v>
+        <v>1353638.71486226</v>
       </c>
       <c r="L53">
-        <v>94246604.49025391</v>
+        <v>105691018.9099156</v>
       </c>
       <c r="M53">
-        <v>59988723.1545231</v>
+        <v>66965932.18876085</v>
       </c>
       <c r="N53">
-        <v>1349559.371400524</v>
+        <v>1378883.466280106</v>
       </c>
       <c r="O53">
-        <v>139836569.4006971</v>
+        <v>156114088.4283937</v>
       </c>
     </row>
     <row r="54">
@@ -3204,40 +3204,40 @@
         </is>
       </c>
       <c r="D54">
-        <v>2139.254228103157</v>
+        <v>2635.607819207387</v>
       </c>
       <c r="E54">
-        <v>125.8512076453739</v>
+        <v>133.8311871921268</v>
       </c>
       <c r="F54">
-        <v>4326.112872294473</v>
+        <v>5334.512462786269</v>
       </c>
       <c r="G54">
-        <v>248.4287419610189</v>
+        <v>306.835525252249</v>
       </c>
       <c r="H54">
-        <v>10.86282664931411</v>
+        <v>11.42046698749211</v>
       </c>
       <c r="I54">
-        <v>580.04285103886</v>
+        <v>716.9644692490142</v>
       </c>
       <c r="J54">
-        <v>31675937.35552348</v>
+        <v>39025444.97900375</v>
       </c>
       <c r="K54">
-        <v>1863478.831605051</v>
+        <v>1981638.388753821</v>
       </c>
       <c r="L54">
-        <v>64056753.30006436</v>
+        <v>78988126.03647611</v>
       </c>
       <c r="M54">
-        <v>33041022.68081552</v>
+        <v>40809124.85854912</v>
       </c>
       <c r="N54">
-        <v>1444755.944358776</v>
+        <v>1518922.10933645</v>
       </c>
       <c r="O54">
-        <v>77145699.18816838</v>
+        <v>95356274.41011889</v>
       </c>
     </row>
     <row r="55">
@@ -3257,40 +3257,40 @@
         </is>
       </c>
       <c r="D55">
-        <v>2488.372900310262</v>
+        <v>2730.305635799707</v>
       </c>
       <c r="E55">
-        <v>93.37016383342306</v>
+        <v>111.8619978530942</v>
       </c>
       <c r="F55">
-        <v>5025.933094678057</v>
+        <v>5514.504297107477</v>
       </c>
       <c r="G55">
-        <v>132.1069793577882</v>
+        <v>145.3161700600295</v>
       </c>
       <c r="H55">
-        <v>4.270524882600036</v>
+        <v>5.08233424612922</v>
       </c>
       <c r="I55">
-        <v>308.1720735803806</v>
+        <v>338.9129485692472</v>
       </c>
       <c r="J55">
-        <v>36845337.53489401</v>
+        <v>40427635.54928621</v>
       </c>
       <c r="K55">
-        <v>1382532.015881496</v>
+        <v>1656340.602210766</v>
       </c>
       <c r="L55">
-        <v>74418991.33289801</v>
+        <v>81653265.12727034</v>
       </c>
       <c r="M55">
-        <v>17570228.25458583</v>
+        <v>19327050.61798393</v>
       </c>
       <c r="N55">
-        <v>567979.8093858047</v>
+        <v>675950.4547351863</v>
       </c>
       <c r="O55">
-        <v>40986885.78619062</v>
+        <v>45075422.15970989</v>
       </c>
     </row>
     <row r="56">
@@ -3310,40 +3310,40 @@
         </is>
       </c>
       <c r="D56">
-        <v>783.4784407522719</v>
+        <v>1005.945474058246</v>
       </c>
       <c r="E56">
-        <v>61.32071946865155</v>
+        <v>73.20246357788145</v>
       </c>
       <c r="F56">
-        <v>1585.026927625566</v>
+        <v>2039.936758553812</v>
       </c>
       <c r="G56">
-        <v>19.67204734276698</v>
+        <v>24.33345064575613</v>
       </c>
       <c r="H56">
-        <v>1.224151040602105</v>
+        <v>1.331354206866746</v>
       </c>
       <c r="I56">
-        <v>45.99716847506586</v>
+        <v>57.01255285556171</v>
       </c>
       <c r="J56">
-        <v>11600965.27221889</v>
+        <v>14895034.63438045</v>
       </c>
       <c r="K56">
-        <v>907975.8931723232</v>
+        <v>1083908.87819769</v>
       </c>
       <c r="L56">
-        <v>23469493.71735172</v>
+        <v>30205343.5839063</v>
       </c>
       <c r="M56">
-        <v>2616382.296588008</v>
+        <v>3236348.935885565</v>
       </c>
       <c r="N56">
-        <v>162812.0884000799</v>
+        <v>177070.1095132772</v>
       </c>
       <c r="O56">
-        <v>6117623.407183759</v>
+        <v>7582669.529789708</v>
       </c>
     </row>
     <row r="57">
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="D57">
-        <v>975.5556632160118</v>
+        <v>1132.077078831487</v>
       </c>
       <c r="E57">
-        <v>50.28773564503242</v>
+        <v>59.67889344614661</v>
       </c>
       <c r="F57">
-        <v>1969.698200521325</v>
+        <v>2288.532401310512</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -3381,13 +3381,13 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <v>14445052.70523948</v>
+        <v>16762665.30625782</v>
       </c>
       <c r="K57">
-        <v>744610.5016959948</v>
+        <v>883665.3752570929</v>
       </c>
       <c r="L57">
-        <v>29165321.25511926</v>
+        <v>33886299.26620474</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -3416,40 +3416,40 @@
         </is>
       </c>
       <c r="D58">
-        <v>161.9814481320443</v>
+        <v>185.5870583814834</v>
       </c>
       <c r="E58">
-        <v>-5.597475635823818</v>
+        <v>-5.535978762212632</v>
       </c>
       <c r="F58">
-        <v>307.3214724419931</v>
+        <v>349.9266971862376</v>
       </c>
       <c r="G58">
-        <v>113.7542685305055</v>
+        <v>130.4110347305038</v>
       </c>
       <c r="H58">
-        <v>-2.940813179022365</v>
+        <v>-2.910620789542663</v>
       </c>
       <c r="I58">
-        <v>274.0743212846883</v>
+        <v>312.2254868667941</v>
       </c>
       <c r="J58">
-        <v>12181166.88097786</v>
+        <v>13956332.37734592</v>
       </c>
       <c r="K58">
-        <v>-420935.7652895867</v>
+        <v>-416311.1388971531</v>
       </c>
       <c r="L58">
-        <v>23110882.04911033</v>
+        <v>26314837.55510223</v>
       </c>
       <c r="M58">
-        <v>15129317.71455724</v>
+        <v>17344667.61915701</v>
       </c>
       <c r="N58">
-        <v>-391128.1528099746</v>
+        <v>-387112.5650091742</v>
       </c>
       <c r="O58">
-        <v>36451884.73086354</v>
+        <v>41525989.75328361</v>
       </c>
     </row>
     <row r="59">
@@ -3469,40 +3469,40 @@
         </is>
       </c>
       <c r="D59">
-        <v>197.929864339241</v>
+        <v>214.7218666703611</v>
       </c>
       <c r="E59">
-        <v>-5.417372906772999</v>
+        <v>-6.112084339133804</v>
       </c>
       <c r="F59">
-        <v>371.1513614166556</v>
+        <v>403.5188930345048</v>
       </c>
       <c r="G59">
-        <v>125.0384590065159</v>
+        <v>135.9660823255695</v>
       </c>
       <c r="H59">
-        <v>-2.567113690922502</v>
+        <v>-2.89382721847167</v>
       </c>
       <c r="I59">
-        <v>297.7864067181398</v>
+        <v>324.4783568379638</v>
       </c>
       <c r="J59">
-        <v>14884523.72817527</v>
+        <v>16147299.09547784</v>
       </c>
       <c r="K59">
-        <v>-407391.8599622367</v>
+        <v>-459634.8543872013</v>
       </c>
       <c r="L59">
-        <v>27910953.52989395</v>
+        <v>30345024.2750878</v>
       </c>
       <c r="M59">
-        <v>16630115.04786661</v>
+        <v>18083488.94930074</v>
       </c>
       <c r="N59">
-        <v>-341426.1208926928</v>
+        <v>-384879.0200567322</v>
       </c>
       <c r="O59">
-        <v>39605592.09351259</v>
+        <v>43155621.45944918</v>
       </c>
     </row>
     <row r="60">
@@ -3522,40 +3522,40 @@
         </is>
       </c>
       <c r="D60">
-        <v>250.3063170512841</v>
+        <v>288.8548853658369</v>
       </c>
       <c r="E60">
-        <v>-7.203809329624979</v>
+        <v>-7.06956250938481</v>
       </c>
       <c r="F60">
-        <v>470.6001182031237</v>
+        <v>539.5834476896604</v>
       </c>
       <c r="G60">
-        <v>147.8377826952922</v>
+        <v>170.6728081913638</v>
       </c>
       <c r="H60">
-        <v>-3.14648628795429</v>
+        <v>-3.089583002631229</v>
       </c>
       <c r="I60">
-        <v>352.7915071189137</v>
+        <v>404.7078300726433</v>
       </c>
       <c r="J60">
-        <v>18823285.34857363</v>
+        <v>21722176.23439629</v>
       </c>
       <c r="K60">
-        <v>-541733.6653971277</v>
+        <v>-531638.1702682467</v>
       </c>
       <c r="L60">
-        <v>35389599.48899308</v>
+        <v>40577214.84971017</v>
       </c>
       <c r="M60">
-        <v>19662425.09847387</v>
+        <v>22699483.48945139</v>
       </c>
       <c r="N60">
-        <v>-418482.6762979206</v>
+        <v>-410914.5393499535</v>
       </c>
       <c r="O60">
-        <v>46921270.44681553</v>
+        <v>53826141.39966156</v>
       </c>
     </row>
     <row r="61">
@@ -3575,40 +3575,40 @@
         </is>
       </c>
       <c r="D61">
-        <v>342.4148244845387</v>
+        <v>363.1262585033141</v>
       </c>
       <c r="E61">
-        <v>-11.1362061049067</v>
+        <v>-11.57891682177796</v>
       </c>
       <c r="F61">
-        <v>646.8277185311348</v>
+        <v>685.807835483507</v>
       </c>
       <c r="G61">
-        <v>175.2732336723141</v>
+        <v>185.7377676612409</v>
       </c>
       <c r="H61">
-        <v>-4.234018213272048</v>
+        <v>-4.403928931961301</v>
       </c>
       <c r="I61">
-        <v>420.3293810837594</v>
+        <v>445.3412141291859</v>
       </c>
       <c r="J61">
-        <v>25749937.21606178</v>
+        <v>27307457.76570769</v>
       </c>
       <c r="K61">
-        <v>-837453.8352950877</v>
+        <v>-870746.123914524</v>
       </c>
       <c r="L61">
-        <v>48642091.26125986</v>
+        <v>51573435.03619523</v>
       </c>
       <c r="M61">
-        <v>23311340.07841778</v>
+        <v>24703123.09894504</v>
       </c>
       <c r="N61">
-        <v>-563124.4223651823</v>
+        <v>-585722.547950853</v>
       </c>
       <c r="O61">
-        <v>55903807.68414</v>
+        <v>59230381.47918173</v>
       </c>
     </row>
     <row r="62">
@@ -3628,40 +3628,40 @@
         </is>
       </c>
       <c r="D62">
-        <v>316.8284326830265</v>
+        <v>349.6400497426122</v>
       </c>
       <c r="E62">
-        <v>-9.994133872562333</v>
+        <v>-10.27647781950786</v>
       </c>
       <c r="F62">
-        <v>597.6734754748146</v>
+        <v>657.3666085653582</v>
       </c>
       <c r="G62">
-        <v>153.514292867763</v>
+        <v>169.2069621788453</v>
       </c>
       <c r="H62">
-        <v>-3.558671196410516</v>
+        <v>-3.662157490433801</v>
       </c>
       <c r="I62">
-        <v>367.4620626245218</v>
+        <v>403.6982836839351</v>
       </c>
       <c r="J62">
-        <v>23825814.96619626</v>
+        <v>26293281.38069417</v>
       </c>
       <c r="K62">
-        <v>-751568.8613505601</v>
+        <v>-772801.4085048118</v>
       </c>
       <c r="L62">
-        <v>44945643.02918151</v>
+        <v>49434626.33072349</v>
       </c>
       <c r="M62">
-        <v>20417400.95141248</v>
+        <v>22504525.96978642</v>
       </c>
       <c r="N62">
-        <v>-473303.2691225986</v>
+        <v>-487066.9462276955</v>
       </c>
       <c r="O62">
-        <v>48872454.3290614</v>
+        <v>53691871.72996336</v>
       </c>
     </row>
     <row r="63">
@@ -3681,40 +3681,40 @@
         </is>
       </c>
       <c r="D63">
-        <v>547.5319378607518</v>
+        <v>601.2194305375543</v>
       </c>
       <c r="E63">
-        <v>-19.06675391427884</v>
+        <v>-19.79348812783699</v>
       </c>
       <c r="F63">
-        <v>1038.035599282739</v>
+        <v>1137.737098147544</v>
       </c>
       <c r="G63">
-        <v>224.1233454432226</v>
+        <v>246.1390817085248</v>
       </c>
       <c r="H63">
-        <v>-5.76007791787276</v>
+        <v>-5.976338751529815</v>
       </c>
       <c r="I63">
-        <v>539.2686876192545</v>
+        <v>591.1761328332046</v>
       </c>
       <c r="J63">
-        <v>41174949.25906642</v>
+        <v>45212302.39585465</v>
       </c>
       <c r="K63">
-        <v>-1433838.961107682</v>
+        <v>-1488490.100701469</v>
       </c>
       <c r="L63">
-        <v>78061315.10166119</v>
+        <v>85558967.51779336</v>
       </c>
       <c r="M63">
-        <v>29808404.9439486</v>
+        <v>32736497.8672338</v>
       </c>
       <c r="N63">
-        <v>-766090.3630770771</v>
+        <v>-794853.0539534653</v>
       </c>
       <c r="O63">
-        <v>71722735.45336084</v>
+        <v>78626425.66681622</v>
       </c>
     </row>
     <row r="64">
@@ -3734,40 +3734,40 @@
         </is>
       </c>
       <c r="D64">
-        <v>647.9015638665544</v>
+        <v>742.6712259895587</v>
       </c>
       <c r="E64">
-        <v>-20.42222629358</v>
+        <v>-21.45511446110956</v>
       </c>
       <c r="F64">
-        <v>1221.631133444352</v>
+        <v>1396.36199999997</v>
       </c>
       <c r="G64">
-        <v>227.8941752061617</v>
+        <v>261.4083494425415</v>
       </c>
       <c r="H64">
-        <v>-5.361439551847017</v>
+        <v>-5.633343856019666</v>
       </c>
       <c r="I64">
-        <v>545.619325323626</v>
+        <v>624.026168868519</v>
       </c>
       <c r="J64">
-        <v>48722845.50432879</v>
+        <v>55849618.86564091</v>
       </c>
       <c r="K64">
-        <v>-1535771.839503509</v>
+        <v>-1613446.062589898</v>
       </c>
       <c r="L64">
-        <v>91867882.86614874</v>
+        <v>105007818.7619977</v>
       </c>
       <c r="M64">
-        <v>30309925.30241951</v>
+        <v>34767310.47585802</v>
       </c>
       <c r="N64">
-        <v>-713071.4603956533</v>
+        <v>-749234.7328506155</v>
       </c>
       <c r="O64">
-        <v>72567370.26804225</v>
+        <v>82995480.45951302</v>
       </c>
     </row>
     <row r="65">
@@ -3787,40 +3787,40 @@
         </is>
       </c>
       <c r="D65">
-        <v>764.2023976976508</v>
+        <v>814.880542888134</v>
       </c>
       <c r="E65">
-        <v>-21.74946095064868</v>
+        <v>-22.52893429110872</v>
       </c>
       <c r="F65">
-        <v>1434.083960094601</v>
+        <v>1528.818449922504</v>
       </c>
       <c r="G65">
-        <v>216.5125765845519</v>
+        <v>231.1502660700459</v>
       </c>
       <c r="H65">
-        <v>-4.642695185845255</v>
+        <v>-4.800563633012048</v>
       </c>
       <c r="I65">
-        <v>516.1640727403776</v>
+        <v>550.8520345309101</v>
       </c>
       <c r="J65">
-        <v>57468784.50926106</v>
+        <v>61279831.70573061</v>
       </c>
       <c r="K65">
-        <v>-1635581.212949733</v>
+        <v>-1694198.387625668</v>
       </c>
       <c r="L65">
-        <v>107844547.8830741</v>
+        <v>114968676.2526224</v>
       </c>
       <c r="M65">
-        <v>28796172.68574541</v>
+        <v>30742985.3873161</v>
       </c>
       <c r="N65">
-        <v>-617478.4597174189</v>
+        <v>-638474.9631906024</v>
       </c>
       <c r="O65">
-        <v>68649821.67447022</v>
+        <v>73263320.59261104</v>
       </c>
     </row>
     <row r="66">
@@ -3840,40 +3840,40 @@
         </is>
       </c>
       <c r="D66">
-        <v>927.0951916318309</v>
+        <v>1095.890216667946</v>
       </c>
       <c r="E66">
-        <v>-24.70151464184361</v>
+        <v>-25.72924629957917</v>
       </c>
       <c r="F66">
-        <v>1738.409769287583</v>
+        <v>2046.207897595962</v>
       </c>
       <c r="G66">
-        <v>232.7311882407119</v>
+        <v>274.7539158188179</v>
       </c>
       <c r="H66">
-        <v>-4.570860782000951</v>
+        <v>-4.758718979091281</v>
       </c>
       <c r="I66">
-        <v>553.8481208304293</v>
+        <v>651.1179627372494</v>
       </c>
       <c r="J66">
-        <v>69718485.50590533</v>
+        <v>82412040.18364629</v>
       </c>
       <c r="K66">
-        <v>-1857578.602581278</v>
+        <v>-1934865.050974649</v>
       </c>
       <c r="L66">
-        <v>130730153.0601954</v>
+        <v>153876880.1071142</v>
       </c>
       <c r="M66">
-        <v>30953248.03601469</v>
+        <v>36542270.80390278</v>
       </c>
       <c r="N66">
-        <v>-607924.4840061264</v>
+        <v>-632909.6242191404</v>
       </c>
       <c r="O66">
-        <v>73661800.07044709</v>
+        <v>86598689.04405417</v>
       </c>
     </row>
     <row r="67">
@@ -3893,40 +3893,40 @@
         </is>
       </c>
       <c r="D67">
-        <v>989.3110289061162</v>
+        <v>1106.962372774894</v>
       </c>
       <c r="E67">
-        <v>-18.80979637136836</v>
+        <v>-19.9666257142896</v>
       </c>
       <c r="F67">
-        <v>1832.063285794005</v>
+        <v>2045.473937621291</v>
       </c>
       <c r="G67">
-        <v>180.210975639599</v>
+        <v>200.7837384350948</v>
       </c>
       <c r="H67">
-        <v>-2.540021053869079</v>
+        <v>-2.705926413869045</v>
       </c>
       <c r="I67">
-        <v>423.8020041310935</v>
+        <v>471.1049178034675</v>
       </c>
       <c r="J67">
-        <v>74397178.68476886</v>
+        <v>83244677.39504485</v>
       </c>
       <c r="K67">
-        <v>-1414515.496923273</v>
+        <v>-1501510.220340292</v>
       </c>
       <c r="L67">
-        <v>137772991.1549951</v>
+        <v>153821685.5830586</v>
       </c>
       <c r="M67">
-        <v>23968059.76006667</v>
+        <v>26704237.21186761</v>
       </c>
       <c r="N67">
-        <v>-337822.8001645875</v>
+        <v>-359888.2130445829</v>
       </c>
       <c r="O67">
-        <v>56365666.54943544</v>
+        <v>62656954.06786118</v>
       </c>
     </row>
     <row r="68">
@@ -3946,40 +3946,40 @@
         </is>
       </c>
       <c r="D68">
-        <v>323.9565399199727</v>
+        <v>398.5299843281929</v>
       </c>
       <c r="E68">
-        <v>-9.43667111782192</v>
+        <v>-10.84315553427804</v>
       </c>
       <c r="F68">
-        <v>609.6628542403355</v>
+        <v>747.8256084956678</v>
       </c>
       <c r="G68">
-        <v>49.40205344912905</v>
+        <v>60.93232883489566</v>
       </c>
       <c r="H68">
-        <v>-1.034489428451782</v>
+        <v>-1.184630615726227</v>
       </c>
       <c r="I68">
-        <v>117.8796528754833</v>
+        <v>144.9187440995535</v>
       </c>
       <c r="J68">
-        <v>24361855.75852187</v>
+        <v>29969853.35146445</v>
       </c>
       <c r="K68">
-        <v>-709647.1047313273</v>
+        <v>-815416.1393332428</v>
       </c>
       <c r="L68">
-        <v>45847256.30172744</v>
+        <v>56237233.58448276</v>
       </c>
       <c r="M68">
-        <v>6570473.108734163</v>
+        <v>8103999.735041123</v>
       </c>
       <c r="N68">
-        <v>-137587.0939840871</v>
+        <v>-157555.8718915882</v>
       </c>
       <c r="O68">
-        <v>15677993.83243928</v>
+        <v>19274192.96524062</v>
       </c>
     </row>
     <row r="69">
@@ -3999,40 +3999,40 @@
         </is>
       </c>
       <c r="D69">
-        <v>275.5390858121922</v>
+        <v>303.8251348119413</v>
       </c>
       <c r="E69">
-        <v>-6.417118738664891</v>
+        <v>-7.417590271593657</v>
       </c>
       <c r="F69">
-        <v>513.7231271652571</v>
+        <v>567.8345574952183</v>
       </c>
       <c r="G69">
-        <v>21.21912422483204</v>
+        <v>23.41839819098053</v>
       </c>
       <c r="H69">
-        <v>-0.3824267575916852</v>
+        <v>-0.4403010473792503</v>
       </c>
       <c r="I69">
-        <v>50.29669139650301</v>
+        <v>55.6418338330716</v>
       </c>
       <c r="J69">
-        <v>20720814.79216268</v>
+        <v>22847953.96299284</v>
       </c>
       <c r="K69">
-        <v>-482573.7462663385</v>
+        <v>-557810.206014114</v>
       </c>
       <c r="L69">
-        <v>38632492.88595451</v>
+        <v>42701726.55819789</v>
       </c>
       <c r="M69">
-        <v>2822143.521902661</v>
+        <v>3114646.95940041</v>
       </c>
       <c r="N69">
-        <v>-50862.75875969412</v>
+        <v>-58560.03930144029</v>
       </c>
       <c r="O69">
-        <v>6689459.9557349</v>
+        <v>7400363.899798523</v>
       </c>
     </row>
     <row r="70">
@@ -4052,40 +4052,40 @@
         </is>
       </c>
       <c r="D70">
-        <v>14.06710437057325</v>
+        <v>17.97861151488044</v>
       </c>
       <c r="E70">
-        <v>-0.5169592771139779</v>
+        <v>-0.6557477665686496</v>
       </c>
       <c r="F70">
-        <v>26.71963897398292</v>
+        <v>34.19631279876591</v>
       </c>
       <c r="G70">
-        <v>0.5040532076613802</v>
+        <v>0.6232964155976375</v>
       </c>
       <c r="H70">
-        <v>-0.01386186356136294</v>
+        <v>-0.01665892286453897</v>
       </c>
       <c r="I70">
-        <v>1.214843028754242</v>
+        <v>1.504730142508414</v>
       </c>
       <c r="J70">
-        <v>1057860.315771479</v>
+        <v>1352009.564530523</v>
       </c>
       <c r="K70">
-        <v>-38875.85459824826</v>
+        <v>-49312.88779372896</v>
       </c>
       <c r="L70">
-        <v>2009343.570482491</v>
+        <v>2571596.918779992</v>
       </c>
       <c r="M70">
-        <v>67039.07661896356</v>
+        <v>82898.42327448579</v>
       </c>
       <c r="N70">
-        <v>-1843.62785366127</v>
+        <v>-2215.636740983683</v>
       </c>
       <c r="O70">
-        <v>161574.1228243141</v>
+        <v>200129.1089536191</v>
       </c>
     </row>
     <row r="71">
@@ -4105,13 +4105,13 @@
         </is>
       </c>
       <c r="D71">
-        <v>9.263514640592479</v>
+        <v>10.75729720158576</v>
       </c>
       <c r="E71">
-        <v>-0.2218258848693071</v>
+        <v>-0.2716935592398143</v>
       </c>
       <c r="F71">
-        <v>17.24488381887562</v>
+        <v>20.07418993307511</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -4123,13 +4123,13 @@
         <v>0</v>
       </c>
       <c r="J71">
-        <v>696625.5644871948</v>
+        <v>808959.506856451</v>
       </c>
       <c r="K71">
-        <v>-16681.52836805675</v>
+        <v>-20431.62734839327</v>
       </c>
       <c r="L71">
-        <v>1296832.508063266</v>
+        <v>1509599.157157182</v>
       </c>
       <c r="M71">
         <v>0</v>
@@ -4370,40 +4370,40 @@
         </is>
       </c>
       <c r="D76">
-        <v>71.78025683747873</v>
+        <v>78.81472354754702</v>
       </c>
       <c r="E76">
-        <v>52.71621199352091</v>
+        <v>57.68380984517101</v>
       </c>
       <c r="F76">
-        <v>89.01497630941405</v>
+        <v>97.84732847367499</v>
       </c>
       <c r="G76">
-        <v>101.5231807581364</v>
+        <v>111.3782961590066</v>
       </c>
       <c r="H76">
-        <v>59.79027832776053</v>
+        <v>65.36389910255923</v>
       </c>
       <c r="I76">
-        <v>143.3760266898509</v>
+        <v>157.47955996414</v>
       </c>
       <c r="J76">
-        <v>1208707.744886302</v>
+        <v>1327161.129817144</v>
       </c>
       <c r="K76">
-        <v>887688.2937588983</v>
+        <v>971337.6739828344</v>
       </c>
       <c r="L76">
-        <v>1498923.186074225</v>
+        <v>1647651.164168213</v>
       </c>
       <c r="M76">
-        <v>13502583.04083214</v>
+        <v>14813313.38914788</v>
       </c>
       <c r="N76">
-        <v>7952107.017592151</v>
+        <v>8693398.580640377</v>
       </c>
       <c r="O76">
-        <v>19069011.54975017</v>
+        <v>20944781.47523061</v>
       </c>
     </row>
     <row r="77">
@@ -4423,40 +4423,40 @@
         </is>
       </c>
       <c r="D77">
-        <v>58.81577360709618</v>
+        <v>64.02498018495631</v>
       </c>
       <c r="E77">
-        <v>43.28385631179098</v>
+        <v>46.83274856631898</v>
       </c>
       <c r="F77">
-        <v>72.86028054970481</v>
+        <v>79.52992545629662</v>
       </c>
       <c r="G77">
-        <v>70.18977663190066</v>
+        <v>76.44006020217556</v>
       </c>
       <c r="H77">
-        <v>41.39818746361465</v>
+        <v>44.82125816680529</v>
       </c>
       <c r="I77">
-        <v>99.05332148719746</v>
+        <v>108.1533493245105</v>
       </c>
       <c r="J77">
-        <v>990398.811769892</v>
+        <v>1078116.641334481</v>
       </c>
       <c r="K77">
-        <v>728856.8564342492</v>
+        <v>788616.6531082448</v>
       </c>
       <c r="L77">
-        <v>1226894.26417648</v>
+        <v>1339204.41475858</v>
       </c>
       <c r="M77">
-        <v>9335240.292042788</v>
+        <v>10166528.00688935</v>
       </c>
       <c r="N77">
-        <v>5505958.932660748</v>
+        <v>5961227.336185103</v>
       </c>
       <c r="O77">
-        <v>13174091.75779726</v>
+        <v>14384395.46015989</v>
       </c>
     </row>
     <row r="78">
@@ -4476,40 +4476,40 @@
         </is>
       </c>
       <c r="D78">
-        <v>168.6242258887328</v>
+        <v>190.8241947023318</v>
       </c>
       <c r="E78">
-        <v>123.6564183981715</v>
+        <v>139.1735566697076</v>
       </c>
       <c r="F78">
-        <v>209.1487370232248</v>
+        <v>237.203009291265</v>
       </c>
       <c r="G78">
-        <v>179.2881162589703</v>
+        <v>202.9701457306445</v>
       </c>
       <c r="H78">
-        <v>105.4327923353563</v>
+        <v>118.7001501642673</v>
       </c>
       <c r="I78">
-        <v>253.2664003461016</v>
+        <v>287.3623383339132</v>
       </c>
       <c r="J78">
-        <v>2839463.339740365</v>
+        <v>3213288.614592566</v>
       </c>
       <c r="K78">
-        <v>2082250.429406808</v>
+        <v>2343543.52076121</v>
       </c>
       <c r="L78">
-        <v>3521855.582734085</v>
+        <v>3994261.473455612</v>
       </c>
       <c r="M78">
-        <v>23845319.46244305</v>
+        <v>26995029.38217571</v>
       </c>
       <c r="N78">
-        <v>14022561.38060238</v>
+        <v>15787119.97184755</v>
       </c>
       <c r="O78">
-        <v>33684431.24603152</v>
+        <v>38219190.99841046</v>
       </c>
     </row>
     <row r="79">
@@ -4529,40 +4529,40 @@
         </is>
       </c>
       <c r="D79">
-        <v>118.3358810719331</v>
+        <v>125.8624389674875</v>
       </c>
       <c r="E79">
-        <v>86.65800847252552</v>
+        <v>91.69998716402647</v>
       </c>
       <c r="F79">
-        <v>146.8353455769064</v>
+        <v>156.5641523631771</v>
       </c>
       <c r="G79">
-        <v>100.8102424360244</v>
+        <v>107.2715465897862</v>
       </c>
       <c r="H79">
-        <v>59.20883912898121</v>
+        <v>62.68593492958479</v>
       </c>
       <c r="I79">
-        <v>142.4570341040856</v>
+        <v>151.9575543277764</v>
       </c>
       <c r="J79">
-        <v>1992657.901370281</v>
+        <v>2119397.609773523</v>
       </c>
       <c r="K79">
-        <v>1459234.204668858</v>
+        <v>1544136.083855041</v>
       </c>
       <c r="L79">
-        <v>2472560.38416953</v>
+        <v>2636383.76164354</v>
       </c>
       <c r="M79">
-        <v>13407762.24399125</v>
+        <v>14267115.69644156</v>
       </c>
       <c r="N79">
-        <v>7874775.604154501</v>
+        <v>8337229.345634777</v>
       </c>
       <c r="O79">
-        <v>18946785.53584338</v>
+        <v>20210354.72559426</v>
       </c>
     </row>
     <row r="80">
@@ -4582,40 +4582,40 @@
         </is>
       </c>
       <c r="D80">
-        <v>867.8858697200926</v>
+        <v>1007.667677535077</v>
       </c>
       <c r="E80">
-        <v>636.056246756925</v>
+        <v>735.8342803088747</v>
       </c>
       <c r="F80">
-        <v>1075.319314276238</v>
+        <v>1250.08694930004</v>
       </c>
       <c r="G80">
-        <v>615.1882706793149</v>
+        <v>712.9134463510014</v>
       </c>
       <c r="H80">
-        <v>361.6544581752077</v>
+        <v>417.4538568379139</v>
       </c>
       <c r="I80">
-        <v>867.856736709562</v>
+        <v>1007.233628768734</v>
       </c>
       <c r="J80">
-        <v>14614330.16021663</v>
+        <v>16968116.02201313</v>
       </c>
       <c r="K80">
-        <v>10710551.13913984</v>
+        <v>12390713.44612116</v>
       </c>
       <c r="L80">
-        <v>18107301.93309756</v>
+        <v>21050214.13926338</v>
       </c>
       <c r="M80">
-        <v>81820040.00034888</v>
+        <v>94817488.3646832</v>
       </c>
       <c r="N80">
-        <v>48100042.93730263</v>
+        <v>55521362.95944255</v>
       </c>
       <c r="O80">
-        <v>115424945.9823717</v>
+        <v>133962072.6262416</v>
       </c>
     </row>
     <row r="81">
@@ -4635,40 +4635,40 @@
         </is>
       </c>
       <c r="D81">
-        <v>669.5162999589071</v>
+        <v>749.55045843161</v>
       </c>
       <c r="E81">
-        <v>494.1306839861319</v>
+        <v>550.0261126982699</v>
       </c>
       <c r="F81">
-        <v>825.7655026442524</v>
+        <v>927.1596598372792</v>
       </c>
       <c r="G81">
-        <v>333.0142613675428</v>
+        <v>371.2364812110662</v>
       </c>
       <c r="H81">
-        <v>196.9887901408655</v>
+        <v>218.3513579501413</v>
       </c>
       <c r="I81">
-        <v>467.9026207415419</v>
+        <v>523.131997144955</v>
       </c>
       <c r="J81">
-        <v>11273984.97500803</v>
+        <v>12621680.16952988</v>
       </c>
       <c r="K81">
-        <v>8320666.587642477</v>
+        <v>9261889.711726168</v>
       </c>
       <c r="L81">
-        <v>13905065.29902657</v>
+        <v>15612441.51199994</v>
       </c>
       <c r="M81">
-        <v>44290896.76188319</v>
+        <v>49374452.00107181</v>
       </c>
       <c r="N81">
-        <v>26199509.08873511</v>
+        <v>29040730.60736879</v>
       </c>
       <c r="O81">
-        <v>62231048.55862506</v>
+        <v>69576555.62027901</v>
       </c>
     </row>
     <row r="82">
@@ -4688,40 +4688,40 @@
         </is>
       </c>
       <c r="D82">
-        <v>2510.537591905565</v>
+        <v>3071.551786957531</v>
       </c>
       <c r="E82">
-        <v>1843.631150724938</v>
+        <v>2233.183554188456</v>
       </c>
       <c r="F82">
-        <v>3110.115603041751</v>
+        <v>3823.469986871721</v>
       </c>
       <c r="G82">
-        <v>991.9702276358529</v>
+        <v>1213.379958726188</v>
       </c>
       <c r="H82">
-        <v>584.0102691981972</v>
+        <v>707.2922720513924</v>
       </c>
       <c r="I82">
-        <v>1399.398580209518</v>
+        <v>1719.902597655054</v>
       </c>
       <c r="J82">
-        <v>42274942.51009779</v>
+        <v>51721860.54057793</v>
       </c>
       <c r="K82">
-        <v>31044904.94705728</v>
+        <v>37604577.8689794</v>
       </c>
       <c r="L82">
-        <v>52371236.63961997</v>
+        <v>64383411.1089329</v>
       </c>
       <c r="M82">
-        <v>131932040.2755684</v>
+        <v>161379534.510583</v>
       </c>
       <c r="N82">
-        <v>77673365.80336022</v>
+        <v>94069872.18283519</v>
       </c>
       <c r="O82">
-        <v>186120011.1678659</v>
+        <v>228747045.4881222</v>
       </c>
     </row>
     <row r="83">
@@ -4741,40 +4741,40 @@
         </is>
       </c>
       <c r="D83">
-        <v>1794.352199052507</v>
+        <v>1986.735739145131</v>
       </c>
       <c r="E83">
-        <v>1321.385012164347</v>
+        <v>1452.898277422683</v>
       </c>
       <c r="F83">
-        <v>2216.320286725013</v>
+        <v>2463.422558519686</v>
       </c>
       <c r="G83">
-        <v>310.879874321738</v>
+        <v>344.9907718881176</v>
       </c>
       <c r="H83">
-        <v>184.0494299776118</v>
+        <v>202.8020503910877</v>
       </c>
       <c r="I83">
-        <v>436.8130321412967</v>
+        <v>486.5852263867931</v>
       </c>
       <c r="J83">
-        <v>30215096.67984519</v>
+        <v>33454643.11146489</v>
       </c>
       <c r="K83">
-        <v>22250802.21983545</v>
+        <v>24465354.09352059</v>
       </c>
       <c r="L83">
-        <v>37320617.3081625</v>
+        <v>41481572.46291297</v>
       </c>
       <c r="M83">
-        <v>41347023.28479116</v>
+        <v>45883772.66111964</v>
       </c>
       <c r="N83">
-        <v>24478574.18702237</v>
+        <v>26972672.70201467</v>
       </c>
       <c r="O83">
-        <v>58096133.27479246</v>
+        <v>64715835.10944349</v>
       </c>
     </row>
     <row r="84">
@@ -4794,40 +4794,40 @@
         </is>
       </c>
       <c r="D84">
-        <v>3022.736619420754</v>
+        <v>3941.085840300363</v>
       </c>
       <c r="E84">
-        <v>2226.437549017685</v>
+        <v>2856.358363443716</v>
       </c>
       <c r="F84">
-        <v>3744.243934150904</v>
+        <v>4923.021060903316</v>
       </c>
       <c r="G84">
-        <v>244.849329742235</v>
+        <v>307.7947607111416</v>
       </c>
       <c r="H84">
-        <v>143.3929734965951</v>
+        <v>178.8113095766961</v>
       </c>
       <c r="I84">
-        <v>347.14538948986</v>
+        <v>437.7923355825072</v>
       </c>
       <c r="J84">
-        <v>50899861.93442607</v>
+        <v>66363944.46481781</v>
       </c>
       <c r="K84">
-        <v>37490981.88790877</v>
+        <v>48098218.48202874</v>
       </c>
       <c r="L84">
-        <v>63049323.60716704</v>
+        <v>82898751.64455095</v>
       </c>
       <c r="M84">
-        <v>32564960.85571725</v>
+        <v>40936703.17458183</v>
       </c>
       <c r="N84">
-        <v>19071265.47504716</v>
+        <v>23781904.17370058</v>
       </c>
       <c r="O84">
-        <v>46170336.80215137</v>
+        <v>58226380.63247345</v>
       </c>
     </row>
     <row r="85">
@@ -4847,13 +4847,13 @@
         </is>
       </c>
       <c r="D85">
-        <v>1935.533982526794</v>
+        <v>2273.320685652679</v>
       </c>
       <c r="E85">
-        <v>1430.885798799263</v>
+        <v>1665.015368791826</v>
       </c>
       <c r="F85">
-        <v>2390.53322468725</v>
+        <v>2822.755760294472</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -4865,13 +4865,13 @@
         <v>0</v>
       </c>
       <c r="J85">
-        <v>32592456.73176866</v>
+        <v>38280447.02570545</v>
       </c>
       <c r="K85">
-        <v>24094685.96598079</v>
+        <v>28037193.79508553</v>
       </c>
       <c r="L85">
-        <v>40254188.97050861</v>
+        <v>47532384.24759857</v>
       </c>
       <c r="M85">
         <v>0</v>
@@ -4900,22 +4900,22 @@
         </is>
       </c>
       <c r="D86">
-        <v>14407.68605269995</v>
+        <v>16392.98252007961</v>
       </c>
       <c r="E86">
-        <v>10582.74331542874</v>
+        <v>12083.57435196264</v>
       </c>
       <c r="F86">
-        <v>17522.00163265535</v>
+        <v>19901.29427048995</v>
       </c>
       <c r="G86">
-        <v>24949.92011085422</v>
+        <v>28398.13258960682</v>
       </c>
       <c r="H86">
-        <v>11335.21863804258</v>
+        <v>12948.68311739336</v>
       </c>
       <c r="I86">
-        <v>46369.04745575001</v>
+        <v>52685.92961516031</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -4927,13 +4927,13 @@
         <v>0</v>
       </c>
       <c r="M86">
-        <v>3318339374.743611</v>
+        <v>3776951634.417707</v>
       </c>
       <c r="N86">
-        <v>1507584078.859663</v>
+        <v>1722174854.613317</v>
       </c>
       <c r="O86">
-        <v>6167083311.614752</v>
+        <v>7007228638.816321</v>
       </c>
     </row>
     <row r="87">
@@ -4953,22 +4953,22 @@
         </is>
       </c>
       <c r="D87">
-        <v>6518.491975681241</v>
+        <v>7110.117771149636</v>
       </c>
       <c r="E87">
-        <v>4825.891803258834</v>
+        <v>5254.831696050213</v>
       </c>
       <c r="F87">
-        <v>7906.22082881819</v>
+        <v>8626.329747679581</v>
       </c>
       <c r="G87">
-        <v>10171.38366111264</v>
+        <v>11118.97675265317</v>
       </c>
       <c r="H87">
-        <v>4657.268385867408</v>
+        <v>5082.726250966446</v>
       </c>
       <c r="I87">
-        <v>18852.86931420858</v>
+        <v>20614.5959872095</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -4980,13 +4980,13 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>1352794026.927981</v>
+        <v>1478823908.102871</v>
       </c>
       <c r="N87">
-        <v>619416695.3203653</v>
+        <v>676002591.3785373</v>
       </c>
       <c r="O87">
-        <v>2507431618.789741</v>
+        <v>2741741266.298863</v>
       </c>
     </row>
     <row r="88">
@@ -5006,22 +5006,22 @@
         </is>
       </c>
       <c r="D88">
-        <v>16049.64855052269</v>
+        <v>18417.76191922239</v>
       </c>
       <c r="E88">
-        <v>11859.92302629972</v>
+        <v>13663.69636938972</v>
       </c>
       <c r="F88">
-        <v>19471.63246649463</v>
+        <v>22307.72267598314</v>
       </c>
       <c r="G88">
-        <v>23368.78713651701</v>
+        <v>26832.05612924271</v>
       </c>
       <c r="H88">
-        <v>10683.99071054704</v>
+        <v>12314.86746749361</v>
       </c>
       <c r="I88">
-        <v>43319.62338583999</v>
+        <v>49656.86630062746</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5033,13 +5033,13 @@
         <v>0</v>
       </c>
       <c r="M88">
-        <v>3108048689.156762</v>
+        <v>3568663465.189281</v>
       </c>
       <c r="N88">
-        <v>1420970764.502757</v>
+        <v>1637877373.17665</v>
       </c>
       <c r="O88">
-        <v>5761509910.316719</v>
+        <v>6604363217.983452</v>
       </c>
     </row>
     <row r="89">
@@ -5059,22 +5059,22 @@
         </is>
       </c>
       <c r="D89">
-        <v>6488.16533511138</v>
+        <v>6872.920857533825</v>
       </c>
       <c r="E89">
-        <v>4783.409080174257</v>
+        <v>5066.274169008526</v>
       </c>
       <c r="F89">
-        <v>7883.639641444655</v>
+        <v>8348.531445157996</v>
       </c>
       <c r="G89">
-        <v>8219.575137876638</v>
+        <v>8700.112312060433</v>
       </c>
       <c r="H89">
-        <v>3748.846869813239</v>
+        <v>3967.347784869025</v>
       </c>
       <c r="I89">
-        <v>15261.23123113501</v>
+        <v>16148.7798491276</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5086,13 +5086,13 @@
         <v>0</v>
       </c>
       <c r="M89">
-        <v>1093203493.337593</v>
+        <v>1157114937.504038</v>
       </c>
       <c r="N89">
-        <v>498596633.6851608</v>
+        <v>527657255.3875804</v>
       </c>
       <c r="O89">
-        <v>2029743753.740956</v>
+        <v>2147787719.933971</v>
       </c>
     </row>
     <row r="90">
@@ -5112,22 +5112,22 @@
         </is>
       </c>
       <c r="D90">
-        <v>14858.20693541972</v>
+        <v>16304.61165668253</v>
       </c>
       <c r="E90">
-        <v>10962.0493564648</v>
+        <v>12054.10465935661</v>
       </c>
       <c r="F90">
-        <v>18046.5787799395</v>
+        <v>19790.34066210408</v>
       </c>
       <c r="G90">
-        <v>17763.56951516938</v>
+        <v>19470.64289486219</v>
       </c>
       <c r="H90">
-        <v>8109.938319850646</v>
+        <v>8907.556884643174</v>
       </c>
       <c r="I90">
-        <v>32962.97511505639</v>
+        <v>36108.5952990493</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5139,13 +5139,13 @@
         <v>0</v>
       </c>
       <c r="M90">
-        <v>2362554745.517528</v>
+        <v>2589595505.016671</v>
       </c>
       <c r="N90">
-        <v>1078621796.540136</v>
+        <v>1184705065.657542</v>
       </c>
       <c r="O90">
-        <v>4384075690.3025</v>
+        <v>4802443174.773557</v>
       </c>
     </row>
     <row r="91">
@@ -5165,22 +5165,22 @@
         </is>
       </c>
       <c r="D91">
-        <v>7255.567983563782</v>
+        <v>7951.868893953908</v>
       </c>
       <c r="E91">
-        <v>5336.529168942925</v>
+        <v>5852.496497627419</v>
       </c>
       <c r="F91">
-        <v>8825.069120139862</v>
+        <v>9664.121978587777</v>
       </c>
       <c r="G91">
-        <v>7325.291965613137</v>
+        <v>8030.069447388422</v>
       </c>
       <c r="H91">
-        <v>3333.50978239888</v>
+        <v>3656.589743574377</v>
       </c>
       <c r="I91">
-        <v>13612.9939003752</v>
+        <v>14910.57616794854</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5192,13 +5192,13 @@
         <v>0</v>
       </c>
       <c r="M91">
-        <v>974263831.4265473</v>
+        <v>1067999236.50266</v>
       </c>
       <c r="N91">
-        <v>443356801.0590511</v>
+        <v>486326435.8953922</v>
       </c>
       <c r="O91">
-        <v>1810528188.749902</v>
+        <v>1983106630.337156</v>
       </c>
     </row>
     <row r="92">
@@ -5218,22 +5218,22 @@
         </is>
       </c>
       <c r="D92">
-        <v>14610.90401793144</v>
+        <v>16719.62657776469</v>
       </c>
       <c r="E92">
-        <v>10775.72430020099</v>
+        <v>12349.12784650684</v>
       </c>
       <c r="F92">
-        <v>17759.19847855886</v>
+        <v>20296.77562773579</v>
       </c>
       <c r="G92">
-        <v>12816.08372550309</v>
+        <v>14673.83054846922</v>
       </c>
       <c r="H92">
-        <v>5846.56915219922</v>
+        <v>6704.55830156084</v>
       </c>
       <c r="I92">
-        <v>23804.48052176213</v>
+        <v>27221.50161609571</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5245,13 +5245,13 @@
         <v>0</v>
       </c>
       <c r="M92">
-        <v>1704539135.491911</v>
+        <v>1951619462.946406</v>
       </c>
       <c r="N92">
-        <v>777593697.2424963</v>
+        <v>891706254.1075917</v>
       </c>
       <c r="O92">
-        <v>3165995909.394362</v>
+        <v>3620459714.940729</v>
       </c>
     </row>
     <row r="93">
@@ -5271,22 +5271,22 @@
         </is>
       </c>
       <c r="D93">
-        <v>6249.81692405865</v>
+        <v>6669.909313277104</v>
       </c>
       <c r="E93">
-        <v>4623.172089535371</v>
+        <v>4933.018668473821</v>
       </c>
       <c r="F93">
-        <v>7585.816082659519</v>
+        <v>8089.542324447979</v>
       </c>
       <c r="G93">
-        <v>4405.911137831044</v>
+        <v>4707.841022134857</v>
       </c>
       <c r="H93">
-        <v>2015.204010847694</v>
+        <v>2153.142382624314</v>
       </c>
       <c r="I93">
-        <v>8172.927786089193</v>
+        <v>8726.082762189822</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -5298,13 +5298,13 @@
         <v>0</v>
       </c>
       <c r="M93">
-        <v>585986181.3315288</v>
+        <v>626142855.943936</v>
       </c>
       <c r="N93">
-        <v>268022133.4427434</v>
+        <v>286367936.8890337</v>
       </c>
       <c r="O93">
-        <v>1086999395.549863</v>
+        <v>1160569007.371246</v>
       </c>
     </row>
     <row r="94">
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="D94">
-        <v>16733.46999042323</v>
+        <v>19712.33820978573</v>
       </c>
       <c r="E94">
-        <v>12381.73012078117</v>
+        <v>14618.95049821876</v>
       </c>
       <c r="F94">
-        <v>20286.21689155983</v>
+        <v>23863.05711640364</v>
       </c>
       <c r="G94">
-        <v>10267.32731421313</v>
+        <v>12079.51484187171</v>
       </c>
       <c r="H94">
-        <v>4700.857011253979</v>
+        <v>5542.79959588416</v>
       </c>
       <c r="I94">
-        <v>19018.49604685021</v>
+        <v>22343.10362120064</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5351,13 +5351,13 @@
         <v>0</v>
       </c>
       <c r="M94">
-        <v>1365554532.790347</v>
+        <v>1606575473.968937</v>
       </c>
       <c r="N94">
-        <v>625213982.4967792</v>
+        <v>737192346.2525933</v>
       </c>
       <c r="O94">
-        <v>2529459974.231078</v>
+        <v>2971632781.619685</v>
       </c>
     </row>
     <row r="95">
@@ -5377,22 +5377,22 @@
         </is>
       </c>
       <c r="D95">
-        <v>7744.91461809242</v>
+        <v>8657.924928560615</v>
       </c>
       <c r="E95">
-        <v>5779.159939661111</v>
+        <v>6470.064105095283</v>
       </c>
       <c r="F95">
-        <v>9356.761247364104</v>
+        <v>10458.23621344677</v>
       </c>
       <c r="G95">
-        <v>3407.771533607122</v>
+        <v>3792.1251764541</v>
       </c>
       <c r="H95">
-        <v>1572.490660095038</v>
+        <v>1752.840095954526</v>
       </c>
       <c r="I95">
-        <v>6290.125404896396</v>
+        <v>6999.695153604019</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5404,13 +5404,13 @@
         <v>0</v>
       </c>
       <c r="M95">
-        <v>453233613.9697472</v>
+        <v>504352648.4683953</v>
       </c>
       <c r="N95">
-        <v>209141257.79264</v>
+        <v>233127732.761952</v>
       </c>
       <c r="O95">
-        <v>836586678.8512206</v>
+        <v>930959455.4293345</v>
       </c>
     </row>
     <row r="96">
@@ -5430,22 +5430,22 @@
         </is>
       </c>
       <c r="D96">
-        <v>11034.30924722068</v>
+        <v>13570.30213594289</v>
       </c>
       <c r="E96">
-        <v>8136.607285842162</v>
+        <v>10021.05669725616</v>
       </c>
       <c r="F96">
-        <v>13398.6885719837</v>
+        <v>16467.27459488635</v>
       </c>
       <c r="G96">
-        <v>3828.761039196782</v>
+        <v>4718.059403513306</v>
       </c>
       <c r="H96">
-        <v>1748.234856891416</v>
+        <v>2158.299978985651</v>
       </c>
       <c r="I96">
-        <v>7100.169697118195</v>
+        <v>8743.77789040644</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5457,13 +5457,13 @@
         <v>0</v>
       </c>
       <c r="M96">
-        <v>509225218.2131721</v>
+        <v>627501900.6672697</v>
       </c>
       <c r="N96">
-        <v>232515235.9665583</v>
+        <v>287053897.2050915</v>
       </c>
       <c r="O96">
-        <v>944322569.71672</v>
+        <v>1162922459.424057</v>
       </c>
     </row>
     <row r="97">
@@ -5483,22 +5483,22 @@
         </is>
       </c>
       <c r="D97">
-        <v>4934.313095632836</v>
+        <v>5423.362314402823</v>
       </c>
       <c r="E97">
-        <v>3670.266151198911</v>
+        <v>4026.582730604539</v>
       </c>
       <c r="F97">
-        <v>5971.100601094356</v>
+        <v>6565.508442163536</v>
       </c>
       <c r="G97">
-        <v>790.4974107465291</v>
+        <v>871.0274545805394</v>
       </c>
       <c r="H97">
-        <v>363.2652624155946</v>
+        <v>399.5124967465052</v>
       </c>
       <c r="I97">
-        <v>1462.595737532716</v>
+        <v>1612.10357327812</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -5510,13 +5510,13 @@
         <v>0</v>
       </c>
       <c r="M97">
-        <v>105136155.6292884</v>
+        <v>115846651.4592117</v>
       </c>
       <c r="N97">
-        <v>48314279.90127408</v>
+        <v>53135162.06728519</v>
       </c>
       <c r="O97">
-        <v>194525233.0918512</v>
+        <v>214409775.2459899</v>
       </c>
     </row>
     <row r="98">
@@ -5536,22 +5536,22 @@
         </is>
       </c>
       <c r="D98">
-        <v>4696.876497177538</v>
+        <v>6035.532292732965</v>
       </c>
       <c r="E98">
-        <v>3450.605087430015</v>
+        <v>4427.506242407031</v>
       </c>
       <c r="F98">
-        <v>5716.894638811459</v>
+        <v>7347.834034972147</v>
       </c>
       <c r="G98">
-        <v>353.155129292014</v>
+        <v>437.531938912835</v>
       </c>
       <c r="H98">
-        <v>160.6146508910358</v>
+        <v>198.4693368672236</v>
       </c>
       <c r="I98">
-        <v>657.3428992963209</v>
+        <v>813.6597572813315</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -5563,13 +5563,13 @@
         <v>0</v>
       </c>
       <c r="M98">
-        <v>46969632.19583786</v>
+        <v>58191747.87540706</v>
       </c>
       <c r="N98">
-        <v>21361748.56850776</v>
+        <v>26396421.80334074</v>
       </c>
       <c r="O98">
-        <v>87426605.60641068</v>
+        <v>108216747.7184171</v>
       </c>
     </row>
     <row r="99">
@@ -5589,13 +5589,13 @@
         </is>
       </c>
       <c r="D99">
-        <v>1951.902717108013</v>
+        <v>2269.508437172638</v>
       </c>
       <c r="E99">
-        <v>1450.361495365073</v>
+        <v>1683.498291941293</v>
       </c>
       <c r="F99">
-        <v>2365.951389430288</v>
+        <v>2752.103781982716</v>
       </c>
       <c r="G99">
         <v>0</v>

--- a/output/Tables/2019/cases_prev_2019_sex_age.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex_age.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -457,13 +457,13 @@
         <v>165.8811944921929</v>
       </c>
       <c r="G2">
-        <v>1496.082302404835</v>
+        <v>8976.493814429014</v>
       </c>
       <c r="H2">
-        <v>1283.443729065773</v>
+        <v>7700.662374394636</v>
       </c>
       <c r="I2">
-        <v>1694.95694261862</v>
+        <v>10169.74165571172</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -475,13 +475,13 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>198978946.2198431</v>
+        <v>1193873677.319059</v>
       </c>
       <c r="N2">
-        <v>170698015.9657478</v>
+        <v>1024188095.794487</v>
       </c>
       <c r="O2">
-        <v>225429273.3682764</v>
+        <v>1352575640.209658</v>
       </c>
     </row>
     <row r="3">
@@ -510,13 +510,13 @@
         <v>345.2228136533533</v>
       </c>
       <c r="G3">
-        <v>2800.345654439644</v>
+        <v>16802.07392663788</v>
       </c>
       <c r="H3">
-        <v>2398.034280840755</v>
+        <v>14388.20568504453</v>
       </c>
       <c r="I3">
-        <v>3176.382346427662</v>
+        <v>19058.29407856597</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -528,13 +528,13 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>372445972.0404727</v>
+        <v>2234675832.242837</v>
       </c>
       <c r="N3">
-        <v>318938559.3518204</v>
+        <v>1913631356.110922</v>
       </c>
       <c r="O3">
-        <v>422458852.0748791</v>
+        <v>2534753112.449274</v>
       </c>
     </row>
     <row r="4">
@@ -563,13 +563,13 @@
         <v>362.5262480925129</v>
       </c>
       <c r="G4">
-        <v>2705.146397241027</v>
+        <v>16230.87838344617</v>
       </c>
       <c r="H4">
-        <v>2327.685596863201</v>
+        <v>13966.11358117923</v>
       </c>
       <c r="I4">
-        <v>3058.406615907943</v>
+        <v>18350.43969544767</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -581,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>359784470.8330566</v>
+        <v>2158706824.998341</v>
       </c>
       <c r="N4">
-        <v>309582184.3828058</v>
+        <v>1857493106.296837</v>
       </c>
       <c r="O4">
-        <v>406768079.9157563</v>
+        <v>2440608479.494539</v>
       </c>
     </row>
     <row r="5">
@@ -616,13 +616,13 @@
         <v>616.2518630465624</v>
       </c>
       <c r="G5">
-        <v>4029.499713532268</v>
+        <v>24176.99828119361</v>
       </c>
       <c r="H5">
-        <v>3491.224258063326</v>
+        <v>20947.34554837996</v>
       </c>
       <c r="I5">
-        <v>4535.009658516861</v>
+        <v>27210.05795110119</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -634,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>535923461.8997917</v>
+        <v>3215540771.398751</v>
       </c>
       <c r="N5">
-        <v>464332826.3224223</v>
+        <v>2785996957.934535</v>
       </c>
       <c r="O5">
-        <v>603156284.5827426</v>
+        <v>3618937707.496459</v>
       </c>
     </row>
     <row r="6">
@@ -669,13 +669,13 @@
         <v>926.9011848085071</v>
       </c>
       <c r="G6">
-        <v>5656.876426994456</v>
+        <v>33941.25856196675</v>
       </c>
       <c r="H6">
-        <v>4894.003826190119</v>
+        <v>29364.02295714071</v>
       </c>
       <c r="I6">
-        <v>6374.022438857703</v>
+        <v>38244.13463314629</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>752364564.7902626</v>
+        <v>4514187388.741578</v>
       </c>
       <c r="N6">
-        <v>650902508.8832859</v>
+        <v>3905415053.299715</v>
       </c>
       <c r="O6">
-        <v>847744984.3680744</v>
+        <v>5086469906.208457</v>
       </c>
     </row>
     <row r="7">
@@ -722,13 +722,13 @@
         <v>1670.533151363413</v>
       </c>
       <c r="G7">
-        <v>8599.472770575207</v>
+        <v>51596.83662345119</v>
       </c>
       <c r="H7">
-        <v>7423.277370577485</v>
+        <v>44539.66422346493</v>
       </c>
       <c r="I7">
-        <v>9702.215277464307</v>
+        <v>58213.29166478587</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -740,13 +740,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>1143729878.486502</v>
+        <v>6862379270.919008</v>
       </c>
       <c r="N7">
-        <v>987295890.2868055</v>
+        <v>5923775341.720835</v>
       </c>
       <c r="O7">
-        <v>1290394631.902753</v>
+        <v>7742367791.41652</v>
       </c>
     </row>
     <row r="8">
@@ -775,13 +775,13 @@
         <v>2143.156166310431</v>
       </c>
       <c r="G8">
-        <v>9706.167113044785</v>
+        <v>58237.00267826884</v>
       </c>
       <c r="H8">
-        <v>8368.761807126506</v>
+        <v>50212.57084275907</v>
       </c>
       <c r="I8">
-        <v>10961.19088231394</v>
+        <v>65767.14529388356</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -793,13 +793,13 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>1290920226.034956</v>
+        <v>7745521356.209756</v>
       </c>
       <c r="N8">
-        <v>1113045320.347825</v>
+        <v>6678271922.086957</v>
       </c>
       <c r="O8">
-        <v>1457838387.347754</v>
+        <v>8747030324.086514</v>
       </c>
     </row>
     <row r="9">
@@ -828,13 +828,13 @@
         <v>3409.465336409344</v>
       </c>
       <c r="G9">
-        <v>12346.31833067548</v>
+        <v>74077.90998405282</v>
       </c>
       <c r="H9">
-        <v>10631.88461958973</v>
+        <v>63791.30771753832</v>
       </c>
       <c r="I9">
-        <v>13953.96005931906</v>
+        <v>83723.76035591439</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -846,13 +846,13 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>1642060337.979839</v>
+        <v>9852362027.879025</v>
       </c>
       <c r="N9">
-        <v>1414040654.405434</v>
+        <v>8484243926.432597</v>
       </c>
       <c r="O9">
-        <v>1855876687.889435</v>
+        <v>11135260127.33661</v>
       </c>
     </row>
     <row r="10">
@@ -881,13 +881,13 @@
         <v>4165.532253838414</v>
       </c>
       <c r="G10">
-        <v>12972.43251385566</v>
+        <v>77834.59508313396</v>
       </c>
       <c r="H10">
-        <v>11181.21154945163</v>
+        <v>67087.26929670975</v>
       </c>
       <c r="I10">
-        <v>14651.76612133568</v>
+        <v>87910.5967280139</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>1725333524.342802</v>
+        <v>10352001146.05682</v>
       </c>
       <c r="N10">
-        <v>1487101136.077066</v>
+        <v>8922606816.462397</v>
       </c>
       <c r="O10">
-        <v>1948684894.137646</v>
+        <v>11692109364.82585</v>
       </c>
     </row>
     <row r="11">
@@ -934,13 +934,13 @@
         <v>7628.432254583518</v>
       </c>
       <c r="G11">
-        <v>16869.17480792842</v>
+        <v>101215.0488475706</v>
       </c>
       <c r="H11">
-        <v>14629.24119403579</v>
+        <v>87775.4471642147</v>
       </c>
       <c r="I11">
-        <v>18970.71215493152</v>
+        <v>113824.2729295891</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -952,13 +952,13 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2243600249.45448</v>
+        <v>13461601496.72689</v>
       </c>
       <c r="N11">
-        <v>1945689078.80676</v>
+        <v>11674134472.84056</v>
       </c>
       <c r="O11">
-        <v>2523104716.605892</v>
+        <v>15138628299.63535</v>
       </c>
     </row>
     <row r="12">
@@ -987,13 +987,13 @@
         <v>7344.113239621301</v>
       </c>
       <c r="G12">
-        <v>12122.10086710747</v>
+        <v>72732.60520264482</v>
       </c>
       <c r="H12">
-        <v>10380.37294653721</v>
+        <v>62282.23767922331</v>
       </c>
       <c r="I12">
-        <v>13749.89273968116</v>
+        <v>82499.35643808694</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>1612239415.325294</v>
+        <v>9673436491.951761</v>
       </c>
       <c r="N12">
-        <v>1380589601.889449</v>
+        <v>8283537611.3367</v>
       </c>
       <c r="O12">
-        <v>1828735734.377594</v>
+        <v>10972414406.26556</v>
       </c>
     </row>
     <row r="13">
@@ -1040,13 +1040,13 @@
         <v>11695.0433994739</v>
       </c>
       <c r="G13">
-        <v>8702.163562565755</v>
+        <v>52212.9813753946</v>
       </c>
       <c r="H13">
-        <v>7546.0060668481</v>
+        <v>45276.0364010886</v>
       </c>
       <c r="I13">
-        <v>9787.488074784149</v>
+        <v>58724.92844870497</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1058,13 +1058,13 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>1157387753.821245</v>
+        <v>6944326522.927482</v>
       </c>
       <c r="N13">
-        <v>1003618806.890797</v>
+        <v>6021712841.344785</v>
       </c>
       <c r="O13">
-        <v>1301735913.946292</v>
+        <v>7810415483.677761</v>
       </c>
     </row>
     <row r="14">
@@ -1093,13 +1093,13 @@
         <v>12778.40144615328</v>
       </c>
       <c r="G14">
-        <v>3339.754822551085</v>
+        <v>20038.52893530652</v>
       </c>
       <c r="H14">
-        <v>2857.539313176464</v>
+        <v>17145.23587905876</v>
       </c>
       <c r="I14">
-        <v>3791.12580927367</v>
+        <v>22746.75485564202</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>444187391.3992943</v>
+        <v>2665124348.395767</v>
       </c>
       <c r="N14">
-        <v>380052728.6524696</v>
+        <v>2280316371.914815</v>
       </c>
       <c r="O14">
-        <v>504219732.6333981</v>
+        <v>3025318395.800389</v>
       </c>
     </row>
     <row r="15">
@@ -1176,7 +1176,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1190,46 +1190,46 @@
         </is>
       </c>
       <c r="D16">
-        <v>6.524435643742579</v>
+        <v>92.77833442522571</v>
       </c>
       <c r="E16">
-        <v>0.3141200395219647</v>
+        <v>57.99792248019556</v>
       </c>
       <c r="F16">
-        <v>13.19337676748551</v>
+        <v>127.1325348205727</v>
       </c>
       <c r="G16">
-        <v>4.46811642609897</v>
+        <v>368.5768165662126</v>
       </c>
       <c r="H16">
-        <v>0.1631381998496042</v>
+        <v>180.82426037114</v>
       </c>
       <c r="I16">
-        <v>11.43081632210524</v>
+        <v>615.7575036607418</v>
       </c>
       <c r="J16">
-        <v>287642.7942256792</v>
+        <v>5167938.784153922</v>
       </c>
       <c r="K16">
-        <v>13848.61018240486</v>
+        <v>3230600.277991856</v>
       </c>
       <c r="L16">
-        <v>581656.4015481338</v>
+        <v>7081536.454575542</v>
       </c>
       <c r="M16">
-        <v>594259.4846711629</v>
+        <v>49020716.60330627</v>
       </c>
       <c r="N16">
-        <v>21697.38057999736</v>
+        <v>24049626.62936161</v>
       </c>
       <c r="O16">
-        <v>1520298.570839996</v>
+        <v>81895747.98687866</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1243,46 +1243,46 @@
         </is>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>135.6490637347129</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>85.00723101728489</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>185.620177680754</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>486.8337727318624</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>239.3738190759266</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>812.2820716082424</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>7555924.148150986</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>4735072.782124808</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>10339415.13717336</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>64748891.7733377</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>31836717.93709823</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>108033515.5238962</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1296,46 +1296,46 @@
         </is>
       </c>
       <c r="D18">
-        <v>60.8230847273533</v>
+        <v>195.2293645175942</v>
       </c>
       <c r="E18">
-        <v>2.600466091717347</v>
+        <v>123.8561689258144</v>
       </c>
       <c r="F18">
-        <v>122.9740691242863</v>
+        <v>265.1937626766019</v>
       </c>
       <c r="G18">
-        <v>35.47867666754749</v>
+        <v>650.0257777616259</v>
       </c>
       <c r="H18">
-        <v>1.129745594172115</v>
+        <v>323.7681497263035</v>
       </c>
       <c r="I18">
-        <v>90.75018249868283</v>
+        <v>1076.109963456634</v>
       </c>
       <c r="J18">
-        <v>2681507.336374827</v>
+        <v>10874666.06235905</v>
       </c>
       <c r="K18">
-        <v>114646.7485855427</v>
+        <v>6899036.321505706</v>
       </c>
       <c r="L18">
-        <v>5421557.785482411</v>
+        <v>14771822.9686121</v>
       </c>
       <c r="M18">
-        <v>4718663.996783816</v>
+        <v>86453428.44229625</v>
       </c>
       <c r="N18">
-        <v>150256.1640248913</v>
+        <v>43061163.91359837</v>
       </c>
       <c r="O18">
-        <v>12069774.27232482</v>
+        <v>143122625.1397324</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1349,46 +1349,46 @@
         </is>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>290.5251973567622</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>183.4611080398511</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>397.6873695018385</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>837.8001900664822</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>415.0813938982664</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1398.103938132431</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>16182834.54316638</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>10219150.64003578</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>22151981.8559914</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>111427425.2788421</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>55205825.38846944</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>185947823.7716133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1402,46 +1402,46 @@
         </is>
       </c>
       <c r="D20">
-        <v>165.5730040268811</v>
+        <v>591.4152867432659</v>
       </c>
       <c r="E20">
-        <v>9.092994146509604</v>
+        <v>372.9800503342093</v>
       </c>
       <c r="F20">
-        <v>335.4170811235969</v>
+        <v>807.869275902249</v>
       </c>
       <c r="G20">
-        <v>79.5616186131642</v>
+        <v>1602.368178440391</v>
       </c>
       <c r="H20">
-        <v>3.244602233317705</v>
+        <v>793.6433668643126</v>
       </c>
       <c r="I20">
-        <v>203.890212974138</v>
+        <v>2667.1933778355</v>
       </c>
       <c r="J20">
-        <v>7299617.028533106</v>
+        <v>32943014.30217335</v>
       </c>
       <c r="K20">
-        <v>400882.8329371688</v>
+        <v>20775734.7637161</v>
       </c>
       <c r="L20">
-        <v>14787532.85549601</v>
+        <v>44999934.40630708</v>
       </c>
       <c r="M20">
-        <v>10581695.27555084</v>
+        <v>213114967.732572</v>
       </c>
       <c r="N20">
-        <v>431532.0970312547</v>
+        <v>105554567.7929536</v>
       </c>
       <c r="O20">
-        <v>27117398.32556035</v>
+        <v>354736719.2521214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1455,46 +1455,46 @@
         </is>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>982.7683579834647</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>615.3763349288367</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1349.63274350066</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2249.419522071234</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1105.260515098489</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>3765.336041466629</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>54742163.07639498</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>34277692.6082061</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>75177243.07847367</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>299172796.435474</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>146999648.508099</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>500789693.5150617</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1508,46 +1508,46 @@
         </is>
       </c>
       <c r="D22">
-        <v>251.7812498928661</v>
+        <v>1643.860926040004</v>
       </c>
       <c r="E22">
-        <v>12.8785804021203</v>
+        <v>1032.131013275483</v>
       </c>
       <c r="F22">
-        <v>510.2430559632525</v>
+        <v>2245.336771866513</v>
       </c>
       <c r="G22">
-        <v>89.75016191643006</v>
+        <v>3275.765213134426</v>
       </c>
       <c r="H22">
-        <v>3.477210200320016</v>
+        <v>1614.161009467949</v>
       </c>
       <c r="I22">
-        <v>230.1009824764288</v>
+        <v>5454.726309926367</v>
       </c>
       <c r="J22">
-        <v>11100279.96402676</v>
+        <v>91566341.30228034</v>
       </c>
       <c r="K22">
-        <v>567777.9741882789</v>
+        <v>57491761.70147098</v>
       </c>
       <c r="L22">
-        <v>22495085.6082519</v>
+        <v>125069748.8665085</v>
       </c>
       <c r="M22">
-        <v>11936771.5348852</v>
+        <v>435676773.3468786</v>
       </c>
       <c r="N22">
-        <v>462468.9566425622</v>
+        <v>214683414.2592373</v>
       </c>
       <c r="O22">
-        <v>30603430.66936503</v>
+        <v>725478599.2202069</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1561,46 +1561,46 @@
         </is>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>2281.869078717225</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1440.796488924802</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>3113.417919483419</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>3643.089849178938</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1804.608527162677</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>6060.952941512061</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>127104671.4227068</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>80255246.02608931</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>173423604.9510656</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>484530949.9407987</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>240012934.112636</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>806106741.2211041</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1614,46 +1614,46 @@
         </is>
       </c>
       <c r="D24">
-        <v>367.3515897515194</v>
+        <v>4738.672408902913</v>
       </c>
       <c r="E24">
-        <v>13.49720200439301</v>
+        <v>3005.445021319446</v>
       </c>
       <c r="F24">
-        <v>743.2102578403769</v>
+        <v>6429.639299581467</v>
       </c>
       <c r="G24">
-        <v>91.19776900880296</v>
+        <v>6510.008282855246</v>
       </c>
       <c r="H24">
-        <v>2.480569511427557</v>
+        <v>3242.016035246957</v>
       </c>
       <c r="I24">
-        <v>233.4223465919159</v>
+        <v>10763.93564291911</v>
       </c>
       <c r="J24">
-        <v>16195429.53737525</v>
+        <v>263953530.5207101</v>
       </c>
       <c r="K24">
-        <v>595051.1447676739</v>
+        <v>167409298.5775359</v>
       </c>
       <c r="L24">
-        <v>32765910.63740879</v>
+        <v>358143768.2652868</v>
       </c>
       <c r="M24">
-        <v>12129303.27817079</v>
+        <v>865831101.6197478</v>
       </c>
       <c r="N24">
-        <v>329915.7450198651</v>
+        <v>431188132.6878453</v>
       </c>
       <c r="O24">
-        <v>31045172.09672482</v>
+        <v>1431603440.508242</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1667,46 +1667,46 @@
         </is>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>6478.526685452082</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>4209.216951589732</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>8684.934272686958</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>6326.758000268212</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>3223.96415975527</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>10342.89060700587</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>360866893.4330518</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>234461802.6374513</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>483768208.8572096</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>841458814.0356722</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>428787233.2474509</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1375604450.73178</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1720,46 +1720,46 @@
         </is>
       </c>
       <c r="D26">
-        <v>273.0790990765894</v>
+        <v>6558.472911335218</v>
       </c>
       <c r="E26">
-        <v>13.90786850031806</v>
+        <v>4097.272051516084</v>
       </c>
       <c r="F26">
-        <v>552.7241661333888</v>
+        <v>8984.354222218995</v>
       </c>
       <c r="G26">
-        <v>39.11984434386886</v>
+        <v>5083.569533327025</v>
       </c>
       <c r="H26">
-        <v>1.387639785026647</v>
+        <v>2498.577414493875</v>
       </c>
       <c r="I26">
-        <v>100.1545251339946</v>
+        <v>8472.724292979901</v>
       </c>
       <c r="J26">
-        <v>12039238.24098959</v>
+        <v>365320058.1071944</v>
       </c>
       <c r="K26">
-        <v>613156.1985735222</v>
+        <v>228226247.8135489</v>
       </c>
       <c r="L26">
-        <v>24367950.31232272</v>
+        <v>500446498.8860425</v>
       </c>
       <c r="M26">
-        <v>5202939.297734558</v>
+        <v>676114747.9324943</v>
       </c>
       <c r="N26">
-        <v>184556.0914085441</v>
+        <v>332310796.1276854</v>
       </c>
       <c r="O26">
-        <v>13320551.84282129</v>
+        <v>1126872330.966327</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1773,46 +1773,46 @@
         </is>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>6878.835877345051</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>4399.644362797233</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>9314.878417584296</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2505.404923982068</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1256.334044640764</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>4139.709686349373</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>383164916.0398745</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>245068990.2965314</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>518857357.6162809</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>333218854.889615</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>167092427.9372216</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>550581388.2844666</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1826,46 +1826,46 @@
         </is>
       </c>
       <c r="D28">
-        <v>123.4803524342697</v>
+        <v>4754.302361004454</v>
       </c>
       <c r="E28">
-        <v>9.002095304720594</v>
+        <v>2930.534283444486</v>
       </c>
       <c r="F28">
-        <v>250.3981351859366</v>
+        <v>6579.016104825467</v>
       </c>
       <c r="G28">
-        <v>3.546360748528262</v>
+        <v>737.6467591972638</v>
       </c>
       <c r="H28">
-        <v>0.1843717431331704</v>
+        <v>355.9927499320976</v>
       </c>
       <c r="I28">
-        <v>9.103980108572381</v>
+        <v>1244.133935525461</v>
       </c>
       <c r="J28">
-        <v>5443878.29776965</v>
+        <v>264824150.11267</v>
       </c>
       <c r="K28">
-        <v>396875.3756992168</v>
+        <v>163236620.6564246</v>
       </c>
       <c r="L28">
-        <v>11039302.58594238</v>
+        <v>366464355.070988</v>
       </c>
       <c r="M28">
-        <v>471665.9795542589</v>
+        <v>98107018.97323608</v>
       </c>
       <c r="N28">
-        <v>24521.44183671167</v>
+        <v>47347035.74096899</v>
       </c>
       <c r="O28">
-        <v>1210829.354440127</v>
+        <v>165469813.4248863</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>4035.360950613182</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>2578.007879354308</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>5490.355844215614</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1897,13 +1897,13 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>224777675.6710557</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>143600194.8957937</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>305823801.2344981</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1932,46 +1932,46 @@
         </is>
       </c>
       <c r="D30">
-        <v>92.77833442522571</v>
+        <v>1529.967334197196</v>
       </c>
       <c r="E30">
-        <v>57.99792248019556</v>
+        <v>83.33406507317531</v>
       </c>
       <c r="F30">
-        <v>127.1325348205727</v>
+        <v>3096.145374802112</v>
       </c>
       <c r="G30">
-        <v>61.42946942770202</v>
+        <v>5215.155602424024</v>
       </c>
       <c r="H30">
-        <v>30.13737672852331</v>
+        <v>226.9858207426677</v>
       </c>
       <c r="I30">
-        <v>102.6262506101235</v>
+        <v>12186.693137724</v>
       </c>
       <c r="J30">
-        <v>5167938.784153922</v>
+        <v>22654226.31745791</v>
       </c>
       <c r="K30">
-        <v>3230600.277991856</v>
+        <v>1233927.501538506</v>
       </c>
       <c r="L30">
-        <v>7081536.454575542</v>
+        <v>45844624.5646948</v>
       </c>
       <c r="M30">
-        <v>8170119.433884369</v>
+        <v>693615695.1223953</v>
       </c>
       <c r="N30">
-        <v>4008271.104893601</v>
+        <v>30189114.1587748</v>
       </c>
       <c r="O30">
-        <v>13649291.33114643</v>
+        <v>1620830187.317292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1985,46 +1985,46 @@
         </is>
       </c>
       <c r="D31">
-        <v>135.6490637347129</v>
+        <v>351.6245684794629</v>
       </c>
       <c r="E31">
-        <v>85.00723101728489</v>
+        <v>18.01541696591593</v>
       </c>
       <c r="F31">
-        <v>185.620177680754</v>
+        <v>711.8170378773087</v>
       </c>
       <c r="G31">
-        <v>81.138962121977</v>
+        <v>1084.15809081903</v>
       </c>
       <c r="H31">
-        <v>39.89563651265448</v>
+        <v>44.34334659229552</v>
       </c>
       <c r="I31">
-        <v>135.3803452680405</v>
+        <v>2534.217688626623</v>
       </c>
       <c r="J31">
-        <v>7555924.148150986</v>
+        <v>5206504.985475406</v>
       </c>
       <c r="K31">
-        <v>4735072.782124808</v>
+        <v>266754.2790143174</v>
       </c>
       <c r="L31">
-        <v>10339415.13717336</v>
+        <v>10539874.8798493</v>
       </c>
       <c r="M31">
-        <v>10791481.96222294</v>
+        <v>144193026.078931</v>
       </c>
       <c r="N31">
-        <v>5306119.656183046</v>
+        <v>5897665.096775304</v>
       </c>
       <c r="O31">
-        <v>18005585.92064938</v>
+        <v>337050952.5873408</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2038,46 +2038,46 @@
         </is>
       </c>
       <c r="D32">
-        <v>195.2293645175942</v>
+        <v>2711.394525317037</v>
       </c>
       <c r="E32">
-        <v>123.8561689258144</v>
+        <v>112.329351496371</v>
       </c>
       <c r="F32">
-        <v>265.1937626766019</v>
+        <v>5482.296495174682</v>
       </c>
       <c r="G32">
-        <v>108.3376296269377</v>
+        <v>7780.144420911856</v>
       </c>
       <c r="H32">
-        <v>53.96135828771729</v>
+        <v>252.399219276486</v>
       </c>
       <c r="I32">
-        <v>179.3516605761055</v>
+        <v>18164.2909584158</v>
       </c>
       <c r="J32">
-        <v>10874666.06235905</v>
+        <v>40147618.73636941</v>
       </c>
       <c r="K32">
-        <v>6899036.321505706</v>
+        <v>1663260.707606766</v>
       </c>
       <c r="L32">
-        <v>14771822.9686121</v>
+        <v>81176364.20405152</v>
       </c>
       <c r="M32">
-        <v>14408904.74038271</v>
+        <v>1034759207.981277</v>
       </c>
       <c r="N32">
-        <v>7176860.652266399</v>
+        <v>33569096.16377264</v>
       </c>
       <c r="O32">
-        <v>23853770.85662203</v>
+        <v>2415850697.469302</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2091,46 +2091,46 @@
         </is>
       </c>
       <c r="D33">
-        <v>290.5251973567622</v>
+        <v>528.5618048818598</v>
       </c>
       <c r="E33">
-        <v>183.4611080398511</v>
+        <v>33.71872067483555</v>
       </c>
       <c r="F33">
-        <v>397.6873695018385</v>
+        <v>1069.000295128041</v>
       </c>
       <c r="G33">
-        <v>139.6333650110806</v>
+        <v>1315.627992596407</v>
       </c>
       <c r="H33">
-        <v>69.18023231637781</v>
+        <v>66.28486947710086</v>
       </c>
       <c r="I33">
-        <v>233.0173230220718</v>
+        <v>3072.478373633139</v>
       </c>
       <c r="J33">
-        <v>16182834.54316638</v>
+        <v>7826414.644885696</v>
       </c>
       <c r="K33">
-        <v>10219150.64003578</v>
+        <v>499273.0970322899</v>
       </c>
       <c r="L33">
-        <v>22151981.8559914</v>
+        <v>15828687.36996092</v>
       </c>
       <c r="M33">
-        <v>18571237.54647372</v>
+        <v>174978523.0153222</v>
       </c>
       <c r="N33">
-        <v>9200970.89807825</v>
+        <v>8815887.640454413</v>
       </c>
       <c r="O33">
-        <v>30991303.96193555</v>
+        <v>408639623.6932075</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2144,46 +2144,46 @@
         </is>
       </c>
       <c r="D34">
-        <v>591.4152867432659</v>
+        <v>3214.054712457849</v>
       </c>
       <c r="E34">
-        <v>372.9800503342093</v>
+        <v>172.628420995428</v>
       </c>
       <c r="F34">
-        <v>807.869275902249</v>
+        <v>6509.922726056692</v>
       </c>
       <c r="G34">
-        <v>267.0613630733988</v>
+        <v>7567.824427551544</v>
       </c>
       <c r="H34">
-        <v>132.2738944773852</v>
+        <v>317.5313023112167</v>
       </c>
       <c r="I34">
-        <v>444.5322296392495</v>
+        <v>17697.76191172511</v>
       </c>
       <c r="J34">
-        <v>32943014.30217335</v>
+        <v>47590508.12736341</v>
       </c>
       <c r="K34">
-        <v>20775734.7637161</v>
+        <v>2556109.029679297</v>
       </c>
       <c r="L34">
-        <v>44999934.40630708</v>
+        <v>96392425.80472146</v>
       </c>
       <c r="M34">
-        <v>35519161.28876203</v>
+        <v>1006520648.864355</v>
       </c>
       <c r="N34">
-        <v>17592427.96549223</v>
+        <v>42231663.20739182</v>
       </c>
       <c r="O34">
-        <v>59122786.54202018</v>
+        <v>2353802334.259439</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2197,46 +2197,46 @@
         </is>
       </c>
       <c r="D35">
-        <v>982.7683579834647</v>
+        <v>987.7020398794101</v>
       </c>
       <c r="E35">
-        <v>615.3763349288367</v>
+        <v>65.24137561308976</v>
       </c>
       <c r="F35">
-        <v>1349.63274350066</v>
+        <v>1998.590072062647</v>
       </c>
       <c r="G35">
-        <v>374.903253678539</v>
+        <v>1953.322719676569</v>
       </c>
       <c r="H35">
-        <v>184.2100858497481</v>
+        <v>100.8426409992467</v>
       </c>
       <c r="I35">
-        <v>627.5560069111061</v>
+        <v>4563.597512850202</v>
       </c>
       <c r="J35">
-        <v>54742163.07639498</v>
+        <v>14624904.10449442</v>
       </c>
       <c r="K35">
-        <v>34277692.6082061</v>
+        <v>966029.0487030187</v>
       </c>
       <c r="L35">
-        <v>75177243.07847367</v>
+        <v>29593123.19703162</v>
       </c>
       <c r="M35">
-        <v>49862132.73924568</v>
+        <v>259791921.7169836</v>
       </c>
       <c r="N35">
-        <v>24499941.4180165</v>
+        <v>13412071.25289981</v>
       </c>
       <c r="O35">
-        <v>83464948.91917711</v>
+        <v>606958469.2090769</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2250,46 +2250,46 @@
         </is>
       </c>
       <c r="D36">
-        <v>1643.860926040004</v>
+        <v>3968.233975973964</v>
       </c>
       <c r="E36">
-        <v>1032.131013275483</v>
+        <v>202.8770975627731</v>
       </c>
       <c r="F36">
-        <v>2245.336771866513</v>
+        <v>8041.789182934462</v>
       </c>
       <c r="G36">
-        <v>545.9608688557387</v>
+        <v>6873.101904068102</v>
       </c>
       <c r="H36">
-        <v>269.0268349113249</v>
+        <v>279.9875241173803</v>
       </c>
       <c r="I36">
-        <v>909.1210516543928</v>
+        <v>16082.8074622979</v>
       </c>
       <c r="J36">
-        <v>91566341.30228034</v>
+        <v>58757640.48224651</v>
       </c>
       <c r="K36">
-        <v>57491761.70147098</v>
+        <v>3004001.183611978</v>
       </c>
       <c r="L36">
-        <v>125069748.8665085</v>
+        <v>119074772.4317104</v>
       </c>
       <c r="M36">
-        <v>72612795.55781324</v>
+        <v>914122553.2410576</v>
       </c>
       <c r="N36">
-        <v>35780569.04320621</v>
+        <v>37238340.70761158</v>
       </c>
       <c r="O36">
-        <v>120913099.8700342</v>
+        <v>2139013392.48562</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2303,46 +2303,46 @@
         </is>
       </c>
       <c r="D37">
-        <v>2281.869078717225</v>
+        <v>1645.673537469884</v>
       </c>
       <c r="E37">
-        <v>1440.796488924802</v>
+        <v>80.88788067733796</v>
       </c>
       <c r="F37">
-        <v>3113.417919483419</v>
+        <v>3332.155664217125</v>
       </c>
       <c r="G37">
-        <v>607.181641529824</v>
+        <v>2261.808185058573</v>
       </c>
       <c r="H37">
-        <v>300.7680878604466</v>
+        <v>89.0799113376717</v>
       </c>
       <c r="I37">
-        <v>1010.158823585343</v>
+        <v>5288.39714871141</v>
       </c>
       <c r="J37">
-        <v>127104671.4227068</v>
+        <v>24367488.06931661</v>
       </c>
       <c r="K37">
-        <v>80255246.02608931</v>
+        <v>1197706.849189342</v>
       </c>
       <c r="L37">
-        <v>173423604.9510656</v>
+        <v>49339228.9200629</v>
       </c>
       <c r="M37">
-        <v>80755158.32346658</v>
+        <v>300820488.6127902</v>
       </c>
       <c r="N37">
-        <v>40002155.6854394</v>
+        <v>11847628.20791034</v>
       </c>
       <c r="O37">
-        <v>134351123.5368507</v>
+        <v>703356820.7786176</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2356,46 +2356,46 @@
         </is>
       </c>
       <c r="D38">
-        <v>4738.672408902913</v>
+        <v>4573.798369777716</v>
       </c>
       <c r="E38">
-        <v>3005.445021319446</v>
+        <v>167.0660242072252</v>
       </c>
       <c r="F38">
-        <v>6429.639299581467</v>
+        <v>9253.603057028466</v>
       </c>
       <c r="G38">
-        <v>1085.001380475874</v>
+        <v>5576.276044537542</v>
       </c>
       <c r="H38">
-        <v>540.3360058744925</v>
+        <v>158.7570029529858</v>
       </c>
       <c r="I38">
-        <v>1793.98927381985</v>
+        <v>13026.67436171904</v>
       </c>
       <c r="J38">
-        <v>263953530.5207101</v>
+        <v>67724232.46129867</v>
       </c>
       <c r="K38">
-        <v>167409298.5775359</v>
+        <v>2473746.620436382</v>
       </c>
       <c r="L38">
-        <v>358143768.2652868</v>
+        <v>137018100.4654205</v>
       </c>
       <c r="M38">
-        <v>144305183.6032913</v>
+        <v>741644713.923493</v>
       </c>
       <c r="N38">
-        <v>71864688.7813075</v>
+        <v>21114681.39274712</v>
       </c>
       <c r="O38">
-        <v>238600573.4180401</v>
+        <v>1732547690.108632</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2409,46 +2409,46 @@
         </is>
       </c>
       <c r="D39">
-        <v>6478.526685452082</v>
+        <v>3535.693014630197</v>
       </c>
       <c r="E39">
-        <v>4209.216951589732</v>
+        <v>91.4188366895562</v>
       </c>
       <c r="F39">
-        <v>8684.934272686958</v>
+        <v>7137.909023429165</v>
       </c>
       <c r="G39">
-        <v>1054.459666711367</v>
+        <v>3021.01949723733</v>
       </c>
       <c r="H39">
-        <v>537.3273599592111</v>
+        <v>62.20526915549353</v>
       </c>
       <c r="I39">
-        <v>1723.815101167645</v>
+        <v>7042.740831356094</v>
       </c>
       <c r="J39">
-        <v>360866893.4330518</v>
+        <v>52353006.46762938</v>
       </c>
       <c r="K39">
-        <v>234461802.6374513</v>
+        <v>1353638.71486226</v>
       </c>
       <c r="L39">
-        <v>483768208.8572096</v>
+        <v>105691018.9099156</v>
       </c>
       <c r="M39">
-        <v>140243135.6726118</v>
+        <v>401795593.1325649</v>
       </c>
       <c r="N39">
-        <v>71464538.87457508</v>
+        <v>8273300.797680639</v>
       </c>
       <c r="O39">
-        <v>229267408.4552968</v>
+        <v>936684530.5703604</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="D40">
-        <v>6558.472911335218</v>
+        <v>2635.607819207387</v>
       </c>
       <c r="E40">
-        <v>4097.272051516084</v>
+        <v>133.8311871921268</v>
       </c>
       <c r="F40">
-        <v>8984.354222218995</v>
+        <v>5334.512462786269</v>
       </c>
       <c r="G40">
-        <v>847.2615888878361</v>
+        <v>1841.013151513495</v>
       </c>
       <c r="H40">
-        <v>416.429569082312</v>
+        <v>68.52280192495255</v>
       </c>
       <c r="I40">
-        <v>1412.120715496651</v>
+        <v>4301.786815494082</v>
       </c>
       <c r="J40">
-        <v>365320058.1071944</v>
+        <v>39025444.97900375</v>
       </c>
       <c r="K40">
-        <v>228226247.8135489</v>
+        <v>1981638.388753821</v>
       </c>
       <c r="L40">
-        <v>500446498.8860425</v>
+        <v>78988126.03647611</v>
       </c>
       <c r="M40">
-        <v>112685791.3220822</v>
+        <v>244854749.1512948</v>
       </c>
       <c r="N40">
-        <v>55385132.6879475</v>
+        <v>9113532.656018689</v>
       </c>
       <c r="O40">
-        <v>187812055.1610546</v>
+        <v>572137646.4607128</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2515,46 +2515,46 @@
         </is>
       </c>
       <c r="D41">
-        <v>6878.835877345051</v>
+        <v>2730.305635799707</v>
       </c>
       <c r="E41">
-        <v>4399.644362797233</v>
+        <v>111.8619978530942</v>
       </c>
       <c r="F41">
-        <v>9314.878417584296</v>
+        <v>5514.504297107477</v>
       </c>
       <c r="G41">
-        <v>417.5674873303445</v>
+        <v>871.897020360177</v>
       </c>
       <c r="H41">
-        <v>209.3890074401274</v>
+        <v>30.49400547677532</v>
       </c>
       <c r="I41">
-        <v>689.9516143915623</v>
+        <v>2033.477691415485</v>
       </c>
       <c r="J41">
-        <v>383164916.0398745</v>
+        <v>40427635.54928621</v>
       </c>
       <c r="K41">
-        <v>245068990.2965314</v>
+        <v>1656340.602210766</v>
       </c>
       <c r="L41">
-        <v>518857357.6162809</v>
+        <v>81653265.12727034</v>
       </c>
       <c r="M41">
-        <v>55536475.81493582</v>
+        <v>115962303.7079035</v>
       </c>
       <c r="N41">
-        <v>27848737.98953694</v>
+        <v>4055702.728411118</v>
       </c>
       <c r="O41">
-        <v>91763564.71407779</v>
+        <v>270452532.9582595</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2568,46 +2568,46 @@
         </is>
       </c>
       <c r="D42">
-        <v>4754.302361004454</v>
+        <v>1005.945474058246</v>
       </c>
       <c r="E42">
-        <v>2930.534283444486</v>
+        <v>73.20246357788145</v>
       </c>
       <c r="F42">
-        <v>6579.016104825467</v>
+        <v>2039.936758553812</v>
       </c>
       <c r="G42">
-        <v>122.9411265328773</v>
+        <v>146.0007038745368</v>
       </c>
       <c r="H42">
-        <v>59.33212498868297</v>
+        <v>7.98812524120047</v>
       </c>
       <c r="I42">
-        <v>207.3556559209103</v>
+        <v>342.0753171333703</v>
       </c>
       <c r="J42">
-        <v>264824150.11267</v>
+        <v>14895034.63438045</v>
       </c>
       <c r="K42">
-        <v>163236620.6564246</v>
+        <v>1083908.87819769</v>
       </c>
       <c r="L42">
-        <v>366464355.070988</v>
+        <v>30205343.5839063</v>
       </c>
       <c r="M42">
-        <v>16351169.82887268</v>
+        <v>19418093.6153134</v>
       </c>
       <c r="N42">
-        <v>7891172.623494835</v>
+        <v>1062420.657079663</v>
       </c>
       <c r="O42">
-        <v>27578302.23748107</v>
+        <v>45496017.17873824</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="D43">
-        <v>4035.360950613182</v>
+        <v>1132.077078831487</v>
       </c>
       <c r="E43">
-        <v>2578.007879354308</v>
+        <v>59.67889344614661</v>
       </c>
       <c r="F43">
-        <v>5490.355844215614</v>
+        <v>2288.532401310512</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2639,13 +2639,13 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>224777675.6710557</v>
+        <v>16762665.30625782</v>
       </c>
       <c r="K43">
-        <v>143600194.8957937</v>
+        <v>883665.3752570929</v>
       </c>
       <c r="L43">
-        <v>305823801.2344981</v>
+        <v>33886299.26620474</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -2660,7 +2660,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2674,46 +2674,46 @@
         </is>
       </c>
       <c r="D44">
-        <v>1529.967334197196</v>
+        <v>185.5870583814834</v>
       </c>
       <c r="E44">
-        <v>83.33406507317531</v>
+        <v>-5.535978762212632</v>
       </c>
       <c r="F44">
-        <v>3096.145374802112</v>
+        <v>349.9266971862376</v>
       </c>
       <c r="G44">
-        <v>869.1926004040034</v>
+        <v>782.4662083830236</v>
       </c>
       <c r="H44">
-        <v>37.83097012377794</v>
+        <v>-17.46372473725598</v>
       </c>
       <c r="I44">
-        <v>2031.115522954</v>
+        <v>1873.352921200762</v>
       </c>
       <c r="J44">
-        <v>22654226.31745791</v>
+        <v>13956332.37734592</v>
       </c>
       <c r="K44">
-        <v>1233927.501538506</v>
+        <v>-416311.1388971531</v>
       </c>
       <c r="L44">
-        <v>45844624.5646948</v>
+        <v>26314837.55510223</v>
       </c>
       <c r="M44">
-        <v>115602615.8537325</v>
+        <v>104068005.7149421</v>
       </c>
       <c r="N44">
-        <v>5031519.026462466</v>
+        <v>-2322675.390055045</v>
       </c>
       <c r="O44">
-        <v>270138364.5528821</v>
+        <v>249155938.5197013</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2727,46 +2727,46 @@
         </is>
       </c>
       <c r="D45">
-        <v>351.6245684794629</v>
+        <v>214.7218666703611</v>
       </c>
       <c r="E45">
-        <v>18.01541696591593</v>
+        <v>-6.112084339133804</v>
       </c>
       <c r="F45">
-        <v>711.8170378773087</v>
+        <v>403.5188930345048</v>
       </c>
       <c r="G45">
-        <v>180.693015136505</v>
+        <v>815.7964939534165</v>
       </c>
       <c r="H45">
-        <v>7.390557765382594</v>
+        <v>-17.36296331082999</v>
       </c>
       <c r="I45">
-        <v>422.3696147711037</v>
+        <v>1946.870141027779</v>
       </c>
       <c r="J45">
-        <v>5206504.985475406</v>
+        <v>16147299.09547784</v>
       </c>
       <c r="K45">
-        <v>266754.2790143174</v>
+        <v>-459634.8543872013</v>
       </c>
       <c r="L45">
-        <v>10539874.8798493</v>
+        <v>30345024.2750878</v>
       </c>
       <c r="M45">
-        <v>24032171.01315516</v>
+        <v>108500933.6958044</v>
       </c>
       <c r="N45">
-        <v>982944.182795885</v>
+        <v>-2309274.120340388</v>
       </c>
       <c r="O45">
-        <v>56175158.7645568</v>
+        <v>258933728.7566946</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2780,46 +2780,46 @@
         </is>
       </c>
       <c r="D46">
-        <v>2711.394525317037</v>
+        <v>288.8548853658369</v>
       </c>
       <c r="E46">
-        <v>112.329351496371</v>
+        <v>-7.06956250938481</v>
       </c>
       <c r="F46">
-        <v>5482.296495174682</v>
+        <v>539.5834476896604</v>
       </c>
       <c r="G46">
-        <v>1296.690736818641</v>
+        <v>1024.036849148181</v>
       </c>
       <c r="H46">
-        <v>42.06653654608095</v>
+        <v>-18.5374980157874</v>
       </c>
       <c r="I46">
-        <v>3027.381826402629</v>
+        <v>2428.246980435859</v>
       </c>
       <c r="J46">
-        <v>40147618.73636941</v>
+        <v>21722176.23439629</v>
       </c>
       <c r="K46">
-        <v>1663260.707606766</v>
+        <v>-531638.1702682467</v>
       </c>
       <c r="L46">
-        <v>81176364.20405152</v>
+        <v>40577214.84971017</v>
       </c>
       <c r="M46">
-        <v>172459867.9968793</v>
+        <v>136196900.9367081</v>
       </c>
       <c r="N46">
-        <v>5594849.360628767</v>
+        <v>-2465487.236099725</v>
       </c>
       <c r="O46">
-        <v>402641782.9115497</v>
+        <v>322956848.3979693</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2833,46 +2833,46 @@
         </is>
       </c>
       <c r="D47">
-        <v>528.5618048818598</v>
+        <v>363.1262585033141</v>
       </c>
       <c r="E47">
-        <v>33.71872067483555</v>
+        <v>-11.57891682177796</v>
       </c>
       <c r="F47">
-        <v>1069.000295128041</v>
+        <v>685.807835483507</v>
       </c>
       <c r="G47">
-        <v>219.2713320994015</v>
+        <v>1114.426605967445</v>
       </c>
       <c r="H47">
-        <v>11.04747824618347</v>
+        <v>-26.4235735917678</v>
       </c>
       <c r="I47">
-        <v>512.079728938857</v>
+        <v>2672.047284775119</v>
       </c>
       <c r="J47">
-        <v>7826414.644885696</v>
+        <v>27307457.76570769</v>
       </c>
       <c r="K47">
-        <v>499273.0970322899</v>
+        <v>-870746.123914524</v>
       </c>
       <c r="L47">
-        <v>15828687.36996092</v>
+        <v>51573435.03619523</v>
       </c>
       <c r="M47">
-        <v>29163087.1692204</v>
+        <v>148218738.5936702</v>
       </c>
       <c r="N47">
-        <v>1469314.606742402</v>
+        <v>-3514335.287705118</v>
       </c>
       <c r="O47">
-        <v>68106603.94886798</v>
+        <v>355382288.8750909</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2886,46 +2886,46 @@
         </is>
       </c>
       <c r="D48">
-        <v>3214.054712457849</v>
+        <v>349.6400497426122</v>
       </c>
       <c r="E48">
-        <v>172.628420995428</v>
+        <v>-10.27647781950786</v>
       </c>
       <c r="F48">
-        <v>6509.922726056692</v>
+        <v>657.3666085653582</v>
       </c>
       <c r="G48">
-        <v>1261.304071258591</v>
+        <v>1015.241773073071</v>
       </c>
       <c r="H48">
-        <v>52.92188371853606</v>
+        <v>-21.9729449426028</v>
       </c>
       <c r="I48">
-        <v>2949.626985287514</v>
+        <v>2422.189702103608</v>
       </c>
       <c r="J48">
-        <v>47590508.12736341</v>
+        <v>26293281.38069417</v>
       </c>
       <c r="K48">
-        <v>2556109.029679297</v>
+        <v>-772801.4085048118</v>
       </c>
       <c r="L48">
-        <v>96392425.80472146</v>
+        <v>49434626.33072349</v>
       </c>
       <c r="M48">
-        <v>167753441.4773926</v>
+        <v>135027155.8187184</v>
       </c>
       <c r="N48">
-        <v>7038610.534565296</v>
+        <v>-2922401.677366172</v>
       </c>
       <c r="O48">
-        <v>392300389.0432394</v>
+        <v>322151230.3797799</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2939,46 +2939,46 @@
         </is>
       </c>
       <c r="D49">
-        <v>987.7020398794101</v>
+        <v>601.2194305375543</v>
       </c>
       <c r="E49">
-        <v>65.24137561308976</v>
+        <v>-19.79348812783699</v>
       </c>
       <c r="F49">
-        <v>1998.590072062647</v>
+        <v>1137.737098147544</v>
       </c>
       <c r="G49">
-        <v>325.5537866127615</v>
+        <v>1476.834490251146</v>
       </c>
       <c r="H49">
-        <v>16.80710683320778</v>
+        <v>-35.85803250917881</v>
       </c>
       <c r="I49">
-        <v>760.5995854750342</v>
+        <v>3547.056796999222</v>
       </c>
       <c r="J49">
-        <v>14624904.10449442</v>
+        <v>45212302.39585465</v>
       </c>
       <c r="K49">
-        <v>966029.0487030187</v>
+        <v>-1488490.100701469</v>
       </c>
       <c r="L49">
-        <v>29593123.19703162</v>
+        <v>85558967.51779336</v>
       </c>
       <c r="M49">
-        <v>43298653.61949728</v>
+        <v>196418987.2034025</v>
       </c>
       <c r="N49">
-        <v>2235345.208816634</v>
+        <v>-4769118.323720782</v>
       </c>
       <c r="O49">
-        <v>101159744.8681796</v>
+        <v>471758554.0008965</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2992,46 +2992,46 @@
         </is>
       </c>
       <c r="D50">
-        <v>3968.233975973964</v>
+        <v>742.6712259895587</v>
       </c>
       <c r="E50">
-        <v>202.8770975627731</v>
+        <v>-21.45511446110956</v>
       </c>
       <c r="F50">
-        <v>8041.789182934462</v>
+        <v>1396.36199999997</v>
       </c>
       <c r="G50">
-        <v>1145.51698401135</v>
+        <v>1568.450096655249</v>
       </c>
       <c r="H50">
-        <v>46.66458735289672</v>
+        <v>-33.80006313611803</v>
       </c>
       <c r="I50">
-        <v>2680.467910382984</v>
+        <v>3744.157013211116</v>
       </c>
       <c r="J50">
-        <v>58757640.48224651</v>
+        <v>55849618.86564091</v>
       </c>
       <c r="K50">
-        <v>3004001.183611978</v>
+        <v>-1613446.062589898</v>
       </c>
       <c r="L50">
-        <v>119074772.4317104</v>
+        <v>105007818.7619977</v>
       </c>
       <c r="M50">
-        <v>152353758.8735096</v>
+        <v>208603862.8551481</v>
       </c>
       <c r="N50">
-        <v>6206390.117935264</v>
+        <v>-4495408.397103698</v>
       </c>
       <c r="O50">
-        <v>356502232.0809369</v>
+        <v>497972882.7570784</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3045,46 +3045,46 @@
         </is>
       </c>
       <c r="D51">
-        <v>1645.673537469884</v>
+        <v>814.880542888134</v>
       </c>
       <c r="E51">
-        <v>80.88788067733796</v>
+        <v>-22.52893429110872</v>
       </c>
       <c r="F51">
-        <v>3332.155664217125</v>
+        <v>1528.818449922504</v>
       </c>
       <c r="G51">
-        <v>376.9680308430953</v>
+        <v>1386.901596420276</v>
       </c>
       <c r="H51">
-        <v>14.84665188961193</v>
+        <v>-28.80338179807228</v>
       </c>
       <c r="I51">
-        <v>881.3995247852351</v>
+        <v>3305.11220718546</v>
       </c>
       <c r="J51">
-        <v>24367488.06931661</v>
+        <v>61279831.70573061</v>
       </c>
       <c r="K51">
-        <v>1197706.849189342</v>
+        <v>-1694198.387625668</v>
       </c>
       <c r="L51">
-        <v>49339228.9200629</v>
+        <v>114968676.2526224</v>
       </c>
       <c r="M51">
-        <v>50136748.10213168</v>
+        <v>184457912.3238967</v>
       </c>
       <c r="N51">
-        <v>1974604.701318387</v>
+        <v>-3830849.779143613</v>
       </c>
       <c r="O51">
-        <v>117226136.7964363</v>
+        <v>439579923.5556661</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3098,46 +3098,46 @@
         </is>
       </c>
       <c r="D52">
-        <v>4573.798369777716</v>
+        <v>1095.890216667946</v>
       </c>
       <c r="E52">
-        <v>167.0660242072252</v>
+        <v>-25.72924629957917</v>
       </c>
       <c r="F52">
-        <v>9253.603057028466</v>
+        <v>2046.207897595962</v>
       </c>
       <c r="G52">
-        <v>929.3793407562565</v>
+        <v>1648.523494912906</v>
       </c>
       <c r="H52">
-        <v>26.45950049216434</v>
+        <v>-28.5523138745477</v>
       </c>
       <c r="I52">
-        <v>2171.112393619836</v>
+        <v>3906.707776423496</v>
       </c>
       <c r="J52">
-        <v>67724232.46129867</v>
+        <v>82412040.18364629</v>
       </c>
       <c r="K52">
-        <v>2473746.620436382</v>
+        <v>-1934865.050974649</v>
       </c>
       <c r="L52">
-        <v>137018100.4654205</v>
+        <v>153876880.1071142</v>
       </c>
       <c r="M52">
-        <v>123607452.3205821</v>
+        <v>219253624.8234166</v>
       </c>
       <c r="N52">
-        <v>3519113.565457857</v>
+        <v>-3797457.745314843</v>
       </c>
       <c r="O52">
-        <v>288757948.3514381</v>
+        <v>519592134.264325</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3151,46 +3151,46 @@
         </is>
       </c>
       <c r="D53">
-        <v>3535.693014630197</v>
+        <v>1106.962372774894</v>
       </c>
       <c r="E53">
-        <v>91.4188366895562</v>
+        <v>-19.9666257142896</v>
       </c>
       <c r="F53">
-        <v>7137.909023429165</v>
+        <v>2045.473937621291</v>
       </c>
       <c r="G53">
-        <v>503.5032495395552</v>
+        <v>1204.702430610568</v>
       </c>
       <c r="H53">
-        <v>10.36754485924891</v>
+        <v>-16.23555848321427</v>
       </c>
       <c r="I53">
-        <v>1173.790138559351</v>
+        <v>2826.629506820803</v>
       </c>
       <c r="J53">
-        <v>52353006.46762938</v>
+        <v>83244677.39504485</v>
       </c>
       <c r="K53">
-        <v>1353638.71486226</v>
+        <v>-1501510.220340292</v>
       </c>
       <c r="L53">
-        <v>105691018.9099156</v>
+        <v>153821685.5830586</v>
       </c>
       <c r="M53">
-        <v>66965932.18876085</v>
+        <v>160225423.2712055</v>
       </c>
       <c r="N53">
-        <v>1378883.466280106</v>
+        <v>-2159329.278267498</v>
       </c>
       <c r="O53">
-        <v>156114088.4283937</v>
+        <v>375941724.4071668</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3204,46 +3204,46 @@
         </is>
       </c>
       <c r="D54">
-        <v>2635.607819207387</v>
+        <v>398.5299843281929</v>
       </c>
       <c r="E54">
-        <v>133.8311871921268</v>
+        <v>-10.84315553427804</v>
       </c>
       <c r="F54">
-        <v>5334.512462786269</v>
+        <v>747.8256084956678</v>
       </c>
       <c r="G54">
-        <v>306.835525252249</v>
+        <v>365.5939730093746</v>
       </c>
       <c r="H54">
-        <v>11.42046698749211</v>
+        <v>-7.107783694357364</v>
       </c>
       <c r="I54">
-        <v>716.9644692490142</v>
+        <v>869.512464597321</v>
       </c>
       <c r="J54">
-        <v>39025444.97900375</v>
+        <v>29969853.35146445</v>
       </c>
       <c r="K54">
-        <v>1981638.388753821</v>
+        <v>-815416.1393332428</v>
       </c>
       <c r="L54">
-        <v>78988126.03647611</v>
+        <v>56237233.58448276</v>
       </c>
       <c r="M54">
-        <v>40809124.85854912</v>
+        <v>48623998.41024682</v>
       </c>
       <c r="N54">
-        <v>1518922.10933645</v>
+        <v>-945335.2313495295</v>
       </c>
       <c r="O54">
-        <v>95356274.41011889</v>
+        <v>115645157.7914437</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3257,46 +3257,46 @@
         </is>
       </c>
       <c r="D55">
-        <v>2730.305635799707</v>
+        <v>303.8251348119413</v>
       </c>
       <c r="E55">
-        <v>111.8619978530942</v>
+        <v>-7.417590271593657</v>
       </c>
       <c r="F55">
-        <v>5514.504297107477</v>
+        <v>567.8345574952183</v>
       </c>
       <c r="G55">
-        <v>145.3161700600295</v>
+        <v>140.5103891458834</v>
       </c>
       <c r="H55">
-        <v>5.08233424612922</v>
+        <v>-2.641806284275499</v>
       </c>
       <c r="I55">
-        <v>338.9129485692472</v>
+        <v>333.8510029984295</v>
       </c>
       <c r="J55">
-        <v>40427635.54928621</v>
+        <v>22847953.96299284</v>
       </c>
       <c r="K55">
-        <v>1656340.602210766</v>
+        <v>-557810.206014114</v>
       </c>
       <c r="L55">
-        <v>81653265.12727034</v>
+        <v>42701726.55819789</v>
       </c>
       <c r="M55">
-        <v>19327050.61798393</v>
+        <v>18687881.75640249</v>
       </c>
       <c r="N55">
-        <v>675950.4547351863</v>
+        <v>-351360.2358086414</v>
       </c>
       <c r="O55">
-        <v>45075422.15970989</v>
+        <v>44402183.39879113</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3310,46 +3310,46 @@
         </is>
       </c>
       <c r="D56">
-        <v>1005.945474058246</v>
+        <v>17.97861151488044</v>
       </c>
       <c r="E56">
-        <v>73.20246357788145</v>
+        <v>-0.6557477665686496</v>
       </c>
       <c r="F56">
-        <v>2039.936758553812</v>
+        <v>34.19631279876591</v>
       </c>
       <c r="G56">
-        <v>24.33345064575613</v>
+        <v>3.739778493585825</v>
       </c>
       <c r="H56">
-        <v>1.331354206866746</v>
+        <v>-0.09995353718723382</v>
       </c>
       <c r="I56">
-        <v>57.01255285556171</v>
+        <v>9.028380855050495</v>
       </c>
       <c r="J56">
-        <v>14895034.63438045</v>
+        <v>1352009.564530523</v>
       </c>
       <c r="K56">
-        <v>1083908.87819769</v>
+        <v>-49312.88779372896</v>
       </c>
       <c r="L56">
-        <v>30205343.5839063</v>
+        <v>2571596.918779992</v>
       </c>
       <c r="M56">
-        <v>3236348.935885565</v>
+        <v>497390.5396469147</v>
       </c>
       <c r="N56">
-        <v>177070.1095132772</v>
+        <v>-13293.8204459021</v>
       </c>
       <c r="O56">
-        <v>7582669.529789708</v>
+        <v>1200774.653721716</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="D57">
-        <v>1132.077078831487</v>
+        <v>10.75729720158576</v>
       </c>
       <c r="E57">
-        <v>59.67889344614661</v>
+        <v>-0.2716935592398143</v>
       </c>
       <c r="F57">
-        <v>2288.532401310512</v>
+        <v>20.07418993307511</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -3381,13 +3381,13 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <v>16762665.30625782</v>
+        <v>808959.506856451</v>
       </c>
       <c r="K57">
-        <v>883665.3752570929</v>
+        <v>-20431.62734839327</v>
       </c>
       <c r="L57">
-        <v>33886299.26620474</v>
+        <v>1509599.157157182</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -3402,7 +3402,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3416,46 +3416,46 @@
         </is>
       </c>
       <c r="D58">
-        <v>185.5870583814834</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>-5.535978762212632</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>349.9266971862376</v>
+        <v>0</v>
       </c>
       <c r="G58">
-        <v>130.4110347305038</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>-2.910620789542663</v>
+        <v>0</v>
       </c>
       <c r="I58">
-        <v>312.2254868667941</v>
+        <v>0</v>
       </c>
       <c r="J58">
-        <v>13956332.37734592</v>
+        <v>0</v>
       </c>
       <c r="K58">
-        <v>-416311.1388971531</v>
+        <v>0</v>
       </c>
       <c r="L58">
-        <v>26314837.55510223</v>
+        <v>0</v>
       </c>
       <c r="M58">
-        <v>17344667.61915701</v>
+        <v>0</v>
       </c>
       <c r="N58">
-        <v>-387112.5650091742</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>41525989.75328361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3469,46 +3469,46 @@
         </is>
       </c>
       <c r="D59">
-        <v>214.7218666703611</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>-6.112084339133804</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>403.5188930345048</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>135.9660823255695</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>-2.89382721847167</v>
+        <v>0</v>
       </c>
       <c r="I59">
-        <v>324.4783568379638</v>
+        <v>0</v>
       </c>
       <c r="J59">
-        <v>16147299.09547784</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>-459634.8543872013</v>
+        <v>0</v>
       </c>
       <c r="L59">
-        <v>30345024.2750878</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>18083488.94930074</v>
+        <v>0</v>
       </c>
       <c r="N59">
-        <v>-384879.0200567322</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>43155621.45944918</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3522,46 +3522,46 @@
         </is>
       </c>
       <c r="D60">
-        <v>288.8548853658369</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>-7.06956250938481</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>539.5834476896604</v>
+        <v>0</v>
       </c>
       <c r="G60">
-        <v>170.6728081913638</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>-3.089583002631229</v>
+        <v>0</v>
       </c>
       <c r="I60">
-        <v>404.7078300726433</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>21722176.23439629</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>-531638.1702682467</v>
+        <v>0</v>
       </c>
       <c r="L60">
-        <v>40577214.84971017</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>22699483.48945139</v>
+        <v>0</v>
       </c>
       <c r="N60">
-        <v>-410914.5393499535</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>53826141.39966156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3575,46 +3575,46 @@
         </is>
       </c>
       <c r="D61">
-        <v>363.1262585033141</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>-11.57891682177796</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>685.807835483507</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>185.7377676612409</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>-4.403928931961301</v>
+        <v>0</v>
       </c>
       <c r="I61">
-        <v>445.3412141291859</v>
+        <v>0</v>
       </c>
       <c r="J61">
-        <v>27307457.76570769</v>
+        <v>0</v>
       </c>
       <c r="K61">
-        <v>-870746.123914524</v>
+        <v>0</v>
       </c>
       <c r="L61">
-        <v>51573435.03619523</v>
+        <v>0</v>
       </c>
       <c r="M61">
-        <v>24703123.09894504</v>
+        <v>0</v>
       </c>
       <c r="N61">
-        <v>-585722.547950853</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>59230381.47918173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3628,46 +3628,46 @@
         </is>
       </c>
       <c r="D62">
-        <v>349.6400497426122</v>
+        <v>78.81472354754702</v>
       </c>
       <c r="E62">
-        <v>-10.27647781950786</v>
+        <v>57.68380984517101</v>
       </c>
       <c r="F62">
-        <v>657.3666085653582</v>
+        <v>97.84732847367499</v>
       </c>
       <c r="G62">
-        <v>169.2069621788453</v>
+        <v>668.2697769540392</v>
       </c>
       <c r="H62">
-        <v>-3.662157490433801</v>
+        <v>392.1833946153554</v>
       </c>
       <c r="I62">
-        <v>403.6982836839351</v>
+        <v>944.8773597848389</v>
       </c>
       <c r="J62">
-        <v>26293281.38069417</v>
+        <v>1327161.129817144</v>
       </c>
       <c r="K62">
-        <v>-772801.4085048118</v>
+        <v>971337.6739828344</v>
       </c>
       <c r="L62">
-        <v>49434626.33072349</v>
+        <v>1647651.164168213</v>
       </c>
       <c r="M62">
-        <v>22504525.96978642</v>
+        <v>88879880.33488722</v>
       </c>
       <c r="N62">
-        <v>-487066.9462276955</v>
+        <v>52160391.48384228</v>
       </c>
       <c r="O62">
-        <v>53691871.72996336</v>
+        <v>125668688.8513836</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3681,46 +3681,46 @@
         </is>
       </c>
       <c r="D63">
-        <v>601.2194305375543</v>
+        <v>64.02498018495631</v>
       </c>
       <c r="E63">
-        <v>-19.79348812783699</v>
+        <v>46.83274856631898</v>
       </c>
       <c r="F63">
-        <v>1137.737098147544</v>
+        <v>79.52992545629662</v>
       </c>
       <c r="G63">
-        <v>246.1390817085248</v>
+        <v>458.6403612130541</v>
       </c>
       <c r="H63">
-        <v>-5.976338751529815</v>
+        <v>268.927549000832</v>
       </c>
       <c r="I63">
-        <v>591.1761328332046</v>
+        <v>648.9200959470624</v>
       </c>
       <c r="J63">
-        <v>45212302.39585465</v>
+        <v>1078116.641334481</v>
       </c>
       <c r="K63">
-        <v>-1488490.100701469</v>
+        <v>788616.6531082448</v>
       </c>
       <c r="L63">
-        <v>85558967.51779336</v>
+        <v>1339204.41475858</v>
       </c>
       <c r="M63">
-        <v>32736497.8672338</v>
+        <v>60999168.0413362</v>
       </c>
       <c r="N63">
-        <v>-794853.0539534653</v>
+        <v>35767364.01711066</v>
       </c>
       <c r="O63">
-        <v>78626425.66681622</v>
+        <v>86306372.7609593</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3734,46 +3734,46 @@
         </is>
       </c>
       <c r="D64">
-        <v>742.6712259895587</v>
+        <v>190.8241947023318</v>
       </c>
       <c r="E64">
-        <v>-21.45511446110956</v>
+        <v>139.1735566697076</v>
       </c>
       <c r="F64">
-        <v>1396.36199999997</v>
+        <v>237.203009291265</v>
       </c>
       <c r="G64">
-        <v>261.4083494425415</v>
+        <v>1217.820874383868</v>
       </c>
       <c r="H64">
-        <v>-5.633343856019666</v>
+        <v>712.200900985605</v>
       </c>
       <c r="I64">
-        <v>624.026168868519</v>
+        <v>1724.174030003477</v>
       </c>
       <c r="J64">
-        <v>55849618.86564091</v>
+        <v>3213288.614592566</v>
       </c>
       <c r="K64">
-        <v>-1613446.062589898</v>
+        <v>2343543.52076121</v>
       </c>
       <c r="L64">
-        <v>105007818.7619977</v>
+        <v>3994261.473455612</v>
       </c>
       <c r="M64">
-        <v>34767310.47585802</v>
+        <v>161970176.2930545</v>
       </c>
       <c r="N64">
-        <v>-749234.7328506155</v>
+        <v>94722719.83108547</v>
       </c>
       <c r="O64">
-        <v>82995480.45951302</v>
+        <v>229315145.9904624</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3787,46 +3787,46 @@
         </is>
       </c>
       <c r="D65">
-        <v>814.880542888134</v>
+        <v>125.8624389674875</v>
       </c>
       <c r="E65">
-        <v>-22.52893429110872</v>
+        <v>91.69998716402647</v>
       </c>
       <c r="F65">
-        <v>1528.818449922504</v>
+        <v>156.5641523631771</v>
       </c>
       <c r="G65">
-        <v>231.1502660700459</v>
+        <v>643.6292795387175</v>
       </c>
       <c r="H65">
-        <v>-4.800563633012048</v>
+        <v>376.1156095775093</v>
       </c>
       <c r="I65">
-        <v>550.8520345309101</v>
+        <v>911.7453259666571</v>
       </c>
       <c r="J65">
-        <v>61279831.70573061</v>
+        <v>2119397.609773523</v>
       </c>
       <c r="K65">
-        <v>-1694198.387625668</v>
+        <v>1544136.083855041</v>
       </c>
       <c r="L65">
-        <v>114968676.2526224</v>
+        <v>2636383.76164354</v>
       </c>
       <c r="M65">
-        <v>30742985.3873161</v>
+        <v>85602694.17864943</v>
       </c>
       <c r="N65">
-        <v>-638474.9631906024</v>
+        <v>50023376.07380874</v>
       </c>
       <c r="O65">
-        <v>73263320.59261104</v>
+        <v>121262128.3535654</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3840,46 +3840,46 @@
         </is>
       </c>
       <c r="D66">
-        <v>1095.890216667946</v>
+        <v>1007.667677535077</v>
       </c>
       <c r="E66">
-        <v>-25.72924629957917</v>
+        <v>735.8342803088747</v>
       </c>
       <c r="F66">
-        <v>2046.207897595962</v>
+        <v>1250.08694930004</v>
       </c>
       <c r="G66">
-        <v>274.7539158188179</v>
+        <v>4277.480678106011</v>
       </c>
       <c r="H66">
-        <v>-4.758718979091281</v>
+        <v>2504.723141027483</v>
       </c>
       <c r="I66">
-        <v>651.1179627372494</v>
+        <v>6043.401772612404</v>
       </c>
       <c r="J66">
-        <v>82412040.18364629</v>
+        <v>16968116.02201313</v>
       </c>
       <c r="K66">
-        <v>-1934865.050974649</v>
+        <v>12390713.44612116</v>
       </c>
       <c r="L66">
-        <v>153876880.1071142</v>
+        <v>21050214.13926338</v>
       </c>
       <c r="M66">
-        <v>36542270.80390278</v>
+        <v>568904930.1880994</v>
       </c>
       <c r="N66">
-        <v>-632909.6242191404</v>
+        <v>333128177.7566552</v>
       </c>
       <c r="O66">
-        <v>86598689.04405417</v>
+        <v>803772435.7574497</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3893,46 +3893,46 @@
         </is>
       </c>
       <c r="D67">
-        <v>1106.962372774894</v>
+        <v>749.55045843161</v>
       </c>
       <c r="E67">
-        <v>-19.9666257142896</v>
+        <v>550.0261126982699</v>
       </c>
       <c r="F67">
-        <v>2045.473937621291</v>
+        <v>927.1596598372792</v>
       </c>
       <c r="G67">
-        <v>200.7837384350948</v>
+        <v>2227.418887266396</v>
       </c>
       <c r="H67">
-        <v>-2.705926413869045</v>
+        <v>1310.108147700849</v>
       </c>
       <c r="I67">
-        <v>471.1049178034675</v>
+        <v>3138.79198286973</v>
       </c>
       <c r="J67">
-        <v>83244677.39504485</v>
+        <v>12621680.16952988</v>
       </c>
       <c r="K67">
-        <v>-1501510.220340292</v>
+        <v>9261889.711726168</v>
       </c>
       <c r="L67">
-        <v>153821685.5830586</v>
+        <v>15612441.51199994</v>
       </c>
       <c r="M67">
-        <v>26704237.21186761</v>
+        <v>296246712.0064307</v>
       </c>
       <c r="N67">
-        <v>-359888.2130445829</v>
+        <v>174244383.6442129</v>
       </c>
       <c r="O67">
-        <v>62656954.06786118</v>
+        <v>417459333.721674</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3946,46 +3946,46 @@
         </is>
       </c>
       <c r="D68">
-        <v>398.5299843281929</v>
+        <v>3071.551786957531</v>
       </c>
       <c r="E68">
-        <v>-10.84315553427804</v>
+        <v>2233.183554188456</v>
       </c>
       <c r="F68">
-        <v>747.8256084956678</v>
+        <v>3823.469986871721</v>
       </c>
       <c r="G68">
-        <v>60.93232883489566</v>
+        <v>7280.279752357135</v>
       </c>
       <c r="H68">
-        <v>-1.184630615726227</v>
+        <v>4243.753632308356</v>
       </c>
       <c r="I68">
-        <v>144.9187440995535</v>
+        <v>10319.41558593031</v>
       </c>
       <c r="J68">
-        <v>29969853.35146445</v>
+        <v>51721860.54057793</v>
       </c>
       <c r="K68">
-        <v>-815416.1393332428</v>
+        <v>37604577.8689794</v>
       </c>
       <c r="L68">
-        <v>56237233.58448276</v>
+        <v>64383411.1089329</v>
       </c>
       <c r="M68">
-        <v>8103999.735041123</v>
+        <v>968277207.063499</v>
       </c>
       <c r="N68">
-        <v>-157555.8718915882</v>
+        <v>564419233.0970113</v>
       </c>
       <c r="O68">
-        <v>19274192.96524062</v>
+        <v>1372482272.928731</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3999,46 +3999,46 @@
         </is>
       </c>
       <c r="D69">
-        <v>303.8251348119413</v>
+        <v>1986.735739145131</v>
       </c>
       <c r="E69">
-        <v>-7.417590271593657</v>
+        <v>1452.898277422683</v>
       </c>
       <c r="F69">
-        <v>567.8345574952183</v>
+        <v>2463.422558519686</v>
       </c>
       <c r="G69">
-        <v>23.41839819098053</v>
+        <v>2069.944631328704</v>
       </c>
       <c r="H69">
-        <v>-0.4403010473792503</v>
+        <v>1216.812302346526</v>
       </c>
       <c r="I69">
-        <v>55.6418338330716</v>
+        <v>2919.511358320763</v>
       </c>
       <c r="J69">
-        <v>22847953.96299284</v>
+        <v>33454643.11146489</v>
       </c>
       <c r="K69">
-        <v>-557810.206014114</v>
+        <v>24465354.09352059</v>
       </c>
       <c r="L69">
-        <v>42701726.55819789</v>
+        <v>41481572.46291297</v>
       </c>
       <c r="M69">
-        <v>3114646.95940041</v>
+        <v>275302635.9667175</v>
       </c>
       <c r="N69">
-        <v>-58560.03930144029</v>
+        <v>161836036.2120879</v>
       </c>
       <c r="O69">
-        <v>7400363.899798523</v>
+        <v>388295010.6566615</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4052,46 +4052,46 @@
         </is>
       </c>
       <c r="D70">
-        <v>17.97861151488044</v>
+        <v>3941.085840300363</v>
       </c>
       <c r="E70">
-        <v>-0.6557477665686496</v>
+        <v>2856.358363443716</v>
       </c>
       <c r="F70">
-        <v>34.19631279876591</v>
+        <v>4923.021060903316</v>
       </c>
       <c r="G70">
-        <v>0.6232964155976375</v>
+        <v>1846.768564266849</v>
       </c>
       <c r="H70">
-        <v>-0.01665892286453897</v>
+        <v>1072.867857460177</v>
       </c>
       <c r="I70">
-        <v>1.504730142508414</v>
+        <v>2626.754013495045</v>
       </c>
       <c r="J70">
-        <v>1352009.564530523</v>
+        <v>66363944.46481781</v>
       </c>
       <c r="K70">
-        <v>-49312.88779372896</v>
+        <v>48098218.48202874</v>
       </c>
       <c r="L70">
-        <v>2571596.918779992</v>
+        <v>82898751.64455095</v>
       </c>
       <c r="M70">
-        <v>82898.42327448579</v>
+        <v>245620219.0474909</v>
       </c>
       <c r="N70">
-        <v>-2215.636740983683</v>
+        <v>142691425.0422035</v>
       </c>
       <c r="O70">
-        <v>200129.1089536191</v>
+        <v>349358283.7948411</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4105,13 +4105,13 @@
         </is>
       </c>
       <c r="D71">
-        <v>10.75729720158576</v>
+        <v>2273.320685652679</v>
       </c>
       <c r="E71">
-        <v>-0.2716935592398143</v>
+        <v>1665.015368791826</v>
       </c>
       <c r="F71">
-        <v>20.07418993307511</v>
+        <v>2822.755760294472</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -4123,13 +4123,13 @@
         <v>0</v>
       </c>
       <c r="J71">
-        <v>808959.506856451</v>
+        <v>38280447.02570545</v>
       </c>
       <c r="K71">
-        <v>-20431.62734839327</v>
+        <v>28037193.79508553</v>
       </c>
       <c r="L71">
-        <v>1509599.157157182</v>
+        <v>47532384.24759857</v>
       </c>
       <c r="M71">
         <v>0</v>
@@ -4144,7 +4144,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4158,22 +4158,22 @@
         </is>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>16392.98252007961</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>12083.57435196264</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>19901.29427048995</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>85194.39776882058</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>38846.04935218017</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>158057.7888454811</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4185,19 +4185,19 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>11330854903.25314</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>5166524563.839963</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>21021685916.44898</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4211,22 +4211,22 @@
         </is>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>7110.117771149636</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>5254.831696050213</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>8626.329747679581</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>33356.93025795947</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>15248.17875289934</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>61843.78796162854</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4238,19 +4238,19 @@
         <v>0</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>4436471724.308609</v>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2028007774.135612</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>8225223798.896596</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4264,22 +4264,22 @@
         </is>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>18417.76191922239</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>13663.69636938972</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>22307.72267598314</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>80496.16838772802</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>36944.60240248086</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>148970.5989018823</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4291,19 +4291,19 @@
         <v>0</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>10705990395.56783</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>4913632119.529954</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>19813089653.95035</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4317,22 +4317,22 @@
         </is>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>6872.920857533825</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>5066.274169008526</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>8348.531445157996</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>26100.33693618136</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>11902.04335460708</v>
       </c>
       <c r="I75">
-        <v>0</v>
+        <v>48446.33954738285</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4344,19 +4344,19 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>3471344812.512121</v>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1582971766.162741</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>6443363159.801919</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4370,46 +4370,46 @@
         </is>
       </c>
       <c r="D76">
-        <v>78.81472354754702</v>
+        <v>16304.61165668253</v>
       </c>
       <c r="E76">
-        <v>57.68380984517101</v>
+        <v>12054.10465935661</v>
       </c>
       <c r="F76">
-        <v>97.84732847367499</v>
+        <v>19790.34066210408</v>
       </c>
       <c r="G76">
-        <v>111.3782961590066</v>
+        <v>58411.92868458656</v>
       </c>
       <c r="H76">
-        <v>65.36389910255923</v>
+        <v>26722.6706539295</v>
       </c>
       <c r="I76">
-        <v>157.47955996414</v>
+        <v>108325.785897148</v>
       </c>
       <c r="J76">
-        <v>1327161.129817144</v>
+        <v>0</v>
       </c>
       <c r="K76">
-        <v>971337.6739828344</v>
+        <v>0</v>
       </c>
       <c r="L76">
-        <v>1647651.164168213</v>
+        <v>0</v>
       </c>
       <c r="M76">
-        <v>14813313.38914788</v>
+        <v>7768786515.050012</v>
       </c>
       <c r="N76">
-        <v>8693398.580640377</v>
+        <v>3554115196.972624</v>
       </c>
       <c r="O76">
-        <v>20944781.47523061</v>
+        <v>14407329524.32068</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4423,46 +4423,46 @@
         </is>
       </c>
       <c r="D77">
-        <v>64.02498018495631</v>
+        <v>7951.868893953908</v>
       </c>
       <c r="E77">
-        <v>46.83274856631898</v>
+        <v>5852.496497627419</v>
       </c>
       <c r="F77">
-        <v>79.52992545629662</v>
+        <v>9664.121978587777</v>
       </c>
       <c r="G77">
-        <v>76.44006020217556</v>
+        <v>24090.20834216525</v>
       </c>
       <c r="H77">
-        <v>44.82125816680529</v>
+        <v>10969.76923072312</v>
       </c>
       <c r="I77">
-        <v>108.1533493245105</v>
+        <v>44731.72850384561</v>
       </c>
       <c r="J77">
-        <v>1078116.641334481</v>
+        <v>0</v>
       </c>
       <c r="K77">
-        <v>788616.6531082448</v>
+        <v>0</v>
       </c>
       <c r="L77">
-        <v>1339204.41475858</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>10166528.00688935</v>
+        <v>3203997709.507978</v>
       </c>
       <c r="N77">
-        <v>5961227.336185103</v>
+        <v>1458979307.686175</v>
       </c>
       <c r="O77">
-        <v>14384395.46015989</v>
+        <v>5949319891.011466</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4476,46 +4476,46 @@
         </is>
       </c>
       <c r="D78">
-        <v>190.8241947023318</v>
+        <v>16719.62657776469</v>
       </c>
       <c r="E78">
-        <v>139.1735566697076</v>
+        <v>12349.12784650684</v>
       </c>
       <c r="F78">
-        <v>237.203009291265</v>
+        <v>20296.77562773579</v>
       </c>
       <c r="G78">
-        <v>202.9701457306445</v>
+        <v>44021.4916454077</v>
       </c>
       <c r="H78">
-        <v>118.7001501642673</v>
+        <v>20113.6749046825</v>
       </c>
       <c r="I78">
-        <v>287.3623383339132</v>
+        <v>81664.50484828696</v>
       </c>
       <c r="J78">
-        <v>3213288.614592566</v>
+        <v>0</v>
       </c>
       <c r="K78">
-        <v>2343543.52076121</v>
+        <v>0</v>
       </c>
       <c r="L78">
-        <v>3994261.473455612</v>
+        <v>0</v>
       </c>
       <c r="M78">
-        <v>26995029.38217571</v>
+        <v>5854858388.839224</v>
       </c>
       <c r="N78">
-        <v>15787119.97184755</v>
+        <v>2675118762.322773</v>
       </c>
       <c r="O78">
-        <v>38219190.99841046</v>
+        <v>10861379144.82217</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4529,46 +4529,46 @@
         </is>
       </c>
       <c r="D79">
-        <v>125.8624389674875</v>
+        <v>6669.909313277104</v>
       </c>
       <c r="E79">
-        <v>91.69998716402647</v>
+        <v>4933.018668473821</v>
       </c>
       <c r="F79">
-        <v>156.5641523631771</v>
+        <v>8089.542324447979</v>
       </c>
       <c r="G79">
-        <v>107.2715465897862</v>
+        <v>14123.52306640458</v>
       </c>
       <c r="H79">
-        <v>62.68593492958479</v>
+        <v>6459.427147872938</v>
       </c>
       <c r="I79">
-        <v>151.9575543277764</v>
+        <v>26178.24828656948</v>
       </c>
       <c r="J79">
-        <v>2119397.609773523</v>
+        <v>0</v>
       </c>
       <c r="K79">
-        <v>1544136.083855041</v>
+        <v>0</v>
       </c>
       <c r="L79">
-        <v>2636383.76164354</v>
+        <v>0</v>
       </c>
       <c r="M79">
-        <v>14267115.69644156</v>
+        <v>1878428567.831809</v>
       </c>
       <c r="N79">
-        <v>8337229.345634777</v>
+        <v>859103810.6671008</v>
       </c>
       <c r="O79">
-        <v>20210354.72559426</v>
+        <v>3481707022.113741</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4582,46 +4582,46 @@
         </is>
       </c>
       <c r="D80">
-        <v>1007.667677535077</v>
+        <v>19712.33820978573</v>
       </c>
       <c r="E80">
-        <v>735.8342803088747</v>
+        <v>14618.95049821876</v>
       </c>
       <c r="F80">
-        <v>1250.08694930004</v>
+        <v>23863.05711640364</v>
       </c>
       <c r="G80">
-        <v>712.9134463510014</v>
+        <v>36238.54452561509</v>
       </c>
       <c r="H80">
-        <v>417.4538568379139</v>
+        <v>16628.39878765247</v>
       </c>
       <c r="I80">
-        <v>1007.233628768734</v>
+        <v>67029.31086360192</v>
       </c>
       <c r="J80">
-        <v>16968116.02201313</v>
+        <v>0</v>
       </c>
       <c r="K80">
-        <v>12390713.44612116</v>
+        <v>0</v>
       </c>
       <c r="L80">
-        <v>21050214.13926338</v>
+        <v>0</v>
       </c>
       <c r="M80">
-        <v>94817488.3646832</v>
+        <v>4819726421.906807</v>
       </c>
       <c r="N80">
-        <v>55521362.95944255</v>
+        <v>2211577038.757778</v>
       </c>
       <c r="O80">
-        <v>133962072.6262416</v>
+        <v>8914898344.859055</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4635,46 +4635,46 @@
         </is>
       </c>
       <c r="D81">
-        <v>749.55045843161</v>
+        <v>8657.924928560615</v>
       </c>
       <c r="E81">
-        <v>550.0261126982699</v>
+        <v>6470.064105095283</v>
       </c>
       <c r="F81">
-        <v>927.1596598372792</v>
+        <v>10458.23621344677</v>
       </c>
       <c r="G81">
-        <v>371.2364812110662</v>
+        <v>11376.37552936228</v>
       </c>
       <c r="H81">
-        <v>218.3513579501413</v>
+        <v>5258.520287863576</v>
       </c>
       <c r="I81">
-        <v>523.131997144955</v>
+        <v>20999.08546081209</v>
       </c>
       <c r="J81">
-        <v>12621680.16952988</v>
+        <v>0</v>
       </c>
       <c r="K81">
-        <v>9261889.711726168</v>
+        <v>0</v>
       </c>
       <c r="L81">
-        <v>15612441.51199994</v>
+        <v>0</v>
       </c>
       <c r="M81">
-        <v>49374452.00107181</v>
+        <v>1513057945.405183</v>
       </c>
       <c r="N81">
-        <v>29040730.60736879</v>
+        <v>699383198.2858557</v>
       </c>
       <c r="O81">
-        <v>69576555.62027901</v>
+        <v>2792878366.288008</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4688,46 +4688,46 @@
         </is>
       </c>
       <c r="D82">
-        <v>3071.551786957531</v>
+        <v>13570.30213594289</v>
       </c>
       <c r="E82">
-        <v>2233.183554188456</v>
+        <v>10021.05669725616</v>
       </c>
       <c r="F82">
-        <v>3823.469986871721</v>
+        <v>16467.27459488635</v>
       </c>
       <c r="G82">
-        <v>1213.379958726188</v>
+        <v>14154.17821053992</v>
       </c>
       <c r="H82">
-        <v>707.2922720513924</v>
+        <v>6474.899936956966</v>
       </c>
       <c r="I82">
-        <v>1719.902597655054</v>
+        <v>26231.33367121931</v>
       </c>
       <c r="J82">
-        <v>51721860.54057793</v>
+        <v>0</v>
       </c>
       <c r="K82">
-        <v>37604577.8689794</v>
+        <v>0</v>
       </c>
       <c r="L82">
-        <v>64383411.1089329</v>
+        <v>0</v>
       </c>
       <c r="M82">
-        <v>161379534.510583</v>
+        <v>1882505702.001809</v>
       </c>
       <c r="N82">
-        <v>94069872.18283519</v>
+        <v>861161691.6152765</v>
       </c>
       <c r="O82">
-        <v>228747045.4881222</v>
+        <v>3488767378.272169</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4741,46 +4741,46 @@
         </is>
       </c>
       <c r="D83">
-        <v>1986.735739145131</v>
+        <v>5423.362314402823</v>
       </c>
       <c r="E83">
-        <v>1452.898277422683</v>
+        <v>4026.582730604539</v>
       </c>
       <c r="F83">
-        <v>2463.422558519686</v>
+        <v>6565.508442163536</v>
       </c>
       <c r="G83">
-        <v>344.9907718881176</v>
+        <v>2613.082363741616</v>
       </c>
       <c r="H83">
-        <v>202.8020503910877</v>
+        <v>1198.537490239515</v>
       </c>
       <c r="I83">
-        <v>486.5852263867931</v>
+        <v>4836.310719834359</v>
       </c>
       <c r="J83">
-        <v>33454643.11146489</v>
+        <v>0</v>
       </c>
       <c r="K83">
-        <v>24465354.09352059</v>
+        <v>0</v>
       </c>
       <c r="L83">
-        <v>41481572.46291297</v>
+        <v>0</v>
       </c>
       <c r="M83">
-        <v>45883772.66111964</v>
+        <v>347539954.3776349</v>
       </c>
       <c r="N83">
-        <v>26972672.70201467</v>
+        <v>159405486.2018555</v>
       </c>
       <c r="O83">
-        <v>64715835.10944349</v>
+        <v>643229325.7379698</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4794,46 +4794,46 @@
         </is>
       </c>
       <c r="D84">
-        <v>3941.085840300363</v>
+        <v>6035.532292732965</v>
       </c>
       <c r="E84">
-        <v>2856.358363443716</v>
+        <v>4427.506242407031</v>
       </c>
       <c r="F84">
-        <v>4923.021060903316</v>
+        <v>7347.834034972147</v>
       </c>
       <c r="G84">
-        <v>307.7947607111416</v>
+        <v>1312.595816738504</v>
       </c>
       <c r="H84">
-        <v>178.8113095766961</v>
+        <v>595.4080106016708</v>
       </c>
       <c r="I84">
-        <v>437.7923355825072</v>
+        <v>2440.979271843994</v>
       </c>
       <c r="J84">
-        <v>66363944.46481781</v>
+        <v>0</v>
       </c>
       <c r="K84">
-        <v>48098218.48202874</v>
+        <v>0</v>
       </c>
       <c r="L84">
-        <v>82898751.64455095</v>
+        <v>0</v>
       </c>
       <c r="M84">
-        <v>40936703.17458183</v>
+        <v>174575243.6262211</v>
       </c>
       <c r="N84">
-        <v>23781904.17370058</v>
+        <v>79189265.41002221</v>
       </c>
       <c r="O84">
-        <v>58226380.63247345</v>
+        <v>324650243.1552512</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4847,13 +4847,13 @@
         </is>
       </c>
       <c r="D85">
-        <v>2273.320685652679</v>
+        <v>2269.508437172638</v>
       </c>
       <c r="E85">
-        <v>1665.015368791826</v>
+        <v>1683.498291941293</v>
       </c>
       <c r="F85">
-        <v>2822.755760294472</v>
+        <v>2752.103781982716</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -4865,13 +4865,13 @@
         <v>0</v>
       </c>
       <c r="J85">
-        <v>38280447.02570545</v>
+        <v>0</v>
       </c>
       <c r="K85">
-        <v>28037193.79508553</v>
+        <v>0</v>
       </c>
       <c r="L85">
-        <v>47532384.24759857</v>
+        <v>0</v>
       </c>
       <c r="M85">
         <v>0</v>
@@ -4880,748 +4880,6 @@
         <v>0</v>
       </c>
       <c r="O85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>20-29</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="D86">
-        <v>16392.98252007961</v>
-      </c>
-      <c r="E86">
-        <v>12083.57435196264</v>
-      </c>
-      <c r="F86">
-        <v>19901.29427048995</v>
-      </c>
-      <c r="G86">
-        <v>28398.13258960682</v>
-      </c>
-      <c r="H86">
-        <v>12948.68311739336</v>
-      </c>
-      <c r="I86">
-        <v>52685.92961516031</v>
-      </c>
-      <c r="J86">
-        <v>0</v>
-      </c>
-      <c r="K86">
-        <v>0</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>3776951634.417707</v>
-      </c>
-      <c r="N86">
-        <v>1722174854.613317</v>
-      </c>
-      <c r="O86">
-        <v>7007228638.816321</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>20-29</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D87">
-        <v>7110.117771149636</v>
-      </c>
-      <c r="E87">
-        <v>5254.831696050213</v>
-      </c>
-      <c r="F87">
-        <v>8626.329747679581</v>
-      </c>
-      <c r="G87">
-        <v>11118.97675265317</v>
-      </c>
-      <c r="H87">
-        <v>5082.726250966446</v>
-      </c>
-      <c r="I87">
-        <v>20614.5959872095</v>
-      </c>
-      <c r="J87">
-        <v>0</v>
-      </c>
-      <c r="K87">
-        <v>0</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
-        <v>1478823908.102871</v>
-      </c>
-      <c r="N87">
-        <v>676002591.3785373</v>
-      </c>
-      <c r="O87">
-        <v>2741741266.298863</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>30-39</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="D88">
-        <v>18417.76191922239</v>
-      </c>
-      <c r="E88">
-        <v>13663.69636938972</v>
-      </c>
-      <c r="F88">
-        <v>22307.72267598314</v>
-      </c>
-      <c r="G88">
-        <v>26832.05612924271</v>
-      </c>
-      <c r="H88">
-        <v>12314.86746749361</v>
-      </c>
-      <c r="I88">
-        <v>49656.86630062746</v>
-      </c>
-      <c r="J88">
-        <v>0</v>
-      </c>
-      <c r="K88">
-        <v>0</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
-        <v>3568663465.189281</v>
-      </c>
-      <c r="N88">
-        <v>1637877373.17665</v>
-      </c>
-      <c r="O88">
-        <v>6604363217.983452</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>30-39</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D89">
-        <v>6872.920857533825</v>
-      </c>
-      <c r="E89">
-        <v>5066.274169008526</v>
-      </c>
-      <c r="F89">
-        <v>8348.531445157996</v>
-      </c>
-      <c r="G89">
-        <v>8700.112312060433</v>
-      </c>
-      <c r="H89">
-        <v>3967.347784869025</v>
-      </c>
-      <c r="I89">
-        <v>16148.7798491276</v>
-      </c>
-      <c r="J89">
-        <v>0</v>
-      </c>
-      <c r="K89">
-        <v>0</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>1157114937.504038</v>
-      </c>
-      <c r="N89">
-        <v>527657255.3875804</v>
-      </c>
-      <c r="O89">
-        <v>2147787719.933971</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="D90">
-        <v>16304.61165668253</v>
-      </c>
-      <c r="E90">
-        <v>12054.10465935661</v>
-      </c>
-      <c r="F90">
-        <v>19790.34066210408</v>
-      </c>
-      <c r="G90">
-        <v>19470.64289486219</v>
-      </c>
-      <c r="H90">
-        <v>8907.556884643174</v>
-      </c>
-      <c r="I90">
-        <v>36108.5952990493</v>
-      </c>
-      <c r="J90">
-        <v>0</v>
-      </c>
-      <c r="K90">
-        <v>0</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>2589595505.016671</v>
-      </c>
-      <c r="N90">
-        <v>1184705065.657542</v>
-      </c>
-      <c r="O90">
-        <v>4802443174.773557</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D91">
-        <v>7951.868893953908</v>
-      </c>
-      <c r="E91">
-        <v>5852.496497627419</v>
-      </c>
-      <c r="F91">
-        <v>9664.121978587777</v>
-      </c>
-      <c r="G91">
-        <v>8030.069447388422</v>
-      </c>
-      <c r="H91">
-        <v>3656.589743574377</v>
-      </c>
-      <c r="I91">
-        <v>14910.57616794854</v>
-      </c>
-      <c r="J91">
-        <v>0</v>
-      </c>
-      <c r="K91">
-        <v>0</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
-        <v>1067999236.50266</v>
-      </c>
-      <c r="N91">
-        <v>486326435.8953922</v>
-      </c>
-      <c r="O91">
-        <v>1983106630.337156</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="D92">
-        <v>16719.62657776469</v>
-      </c>
-      <c r="E92">
-        <v>12349.12784650684</v>
-      </c>
-      <c r="F92">
-        <v>20296.77562773579</v>
-      </c>
-      <c r="G92">
-        <v>14673.83054846922</v>
-      </c>
-      <c r="H92">
-        <v>6704.55830156084</v>
-      </c>
-      <c r="I92">
-        <v>27221.50161609571</v>
-      </c>
-      <c r="J92">
-        <v>0</v>
-      </c>
-      <c r="K92">
-        <v>0</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
-        <v>1951619462.946406</v>
-      </c>
-      <c r="N92">
-        <v>891706254.1075917</v>
-      </c>
-      <c r="O92">
-        <v>3620459714.940729</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D93">
-        <v>6669.909313277104</v>
-      </c>
-      <c r="E93">
-        <v>4933.018668473821</v>
-      </c>
-      <c r="F93">
-        <v>8089.542324447979</v>
-      </c>
-      <c r="G93">
-        <v>4707.841022134857</v>
-      </c>
-      <c r="H93">
-        <v>2153.142382624314</v>
-      </c>
-      <c r="I93">
-        <v>8726.082762189822</v>
-      </c>
-      <c r="J93">
-        <v>0</v>
-      </c>
-      <c r="K93">
-        <v>0</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>626142855.943936</v>
-      </c>
-      <c r="N93">
-        <v>286367936.8890337</v>
-      </c>
-      <c r="O93">
-        <v>1160569007.371246</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>60-69</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="D94">
-        <v>19712.33820978573</v>
-      </c>
-      <c r="E94">
-        <v>14618.95049821876</v>
-      </c>
-      <c r="F94">
-        <v>23863.05711640364</v>
-      </c>
-      <c r="G94">
-        <v>12079.51484187171</v>
-      </c>
-      <c r="H94">
-        <v>5542.79959588416</v>
-      </c>
-      <c r="I94">
-        <v>22343.10362120064</v>
-      </c>
-      <c r="J94">
-        <v>0</v>
-      </c>
-      <c r="K94">
-        <v>0</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <v>1606575473.968937</v>
-      </c>
-      <c r="N94">
-        <v>737192346.2525933</v>
-      </c>
-      <c r="O94">
-        <v>2971632781.619685</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>60-69</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D95">
-        <v>8657.924928560615</v>
-      </c>
-      <c r="E95">
-        <v>6470.064105095283</v>
-      </c>
-      <c r="F95">
-        <v>10458.23621344677</v>
-      </c>
-      <c r="G95">
-        <v>3792.1251764541</v>
-      </c>
-      <c r="H95">
-        <v>1752.840095954526</v>
-      </c>
-      <c r="I95">
-        <v>6999.695153604019</v>
-      </c>
-      <c r="J95">
-        <v>0</v>
-      </c>
-      <c r="K95">
-        <v>0</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
-        <v>504352648.4683953</v>
-      </c>
-      <c r="N95">
-        <v>233127732.761952</v>
-      </c>
-      <c r="O95">
-        <v>930959455.4293345</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>70-79</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="D96">
-        <v>13570.30213594289</v>
-      </c>
-      <c r="E96">
-        <v>10021.05669725616</v>
-      </c>
-      <c r="F96">
-        <v>16467.27459488635</v>
-      </c>
-      <c r="G96">
-        <v>4718.059403513306</v>
-      </c>
-      <c r="H96">
-        <v>2158.299978985651</v>
-      </c>
-      <c r="I96">
-        <v>8743.77789040644</v>
-      </c>
-      <c r="J96">
-        <v>0</v>
-      </c>
-      <c r="K96">
-        <v>0</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="M96">
-        <v>627501900.6672697</v>
-      </c>
-      <c r="N96">
-        <v>287053897.2050915</v>
-      </c>
-      <c r="O96">
-        <v>1162922459.424057</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>70-79</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D97">
-        <v>5423.362314402823</v>
-      </c>
-      <c r="E97">
-        <v>4026.582730604539</v>
-      </c>
-      <c r="F97">
-        <v>6565.508442163536</v>
-      </c>
-      <c r="G97">
-        <v>871.0274545805394</v>
-      </c>
-      <c r="H97">
-        <v>399.5124967465052</v>
-      </c>
-      <c r="I97">
-        <v>1612.10357327812</v>
-      </c>
-      <c r="J97">
-        <v>0</v>
-      </c>
-      <c r="K97">
-        <v>0</v>
-      </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="M97">
-        <v>115846651.4592117</v>
-      </c>
-      <c r="N97">
-        <v>53135162.06728519</v>
-      </c>
-      <c r="O97">
-        <v>214409775.2459899</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>80-89</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="D98">
-        <v>6035.532292732965</v>
-      </c>
-      <c r="E98">
-        <v>4427.506242407031</v>
-      </c>
-      <c r="F98">
-        <v>7347.834034972147</v>
-      </c>
-      <c r="G98">
-        <v>437.531938912835</v>
-      </c>
-      <c r="H98">
-        <v>198.4693368672236</v>
-      </c>
-      <c r="I98">
-        <v>813.6597572813315</v>
-      </c>
-      <c r="J98">
-        <v>0</v>
-      </c>
-      <c r="K98">
-        <v>0</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="M98">
-        <v>58191747.87540706</v>
-      </c>
-      <c r="N98">
-        <v>26396421.80334074</v>
-      </c>
-      <c r="O98">
-        <v>108216747.7184171</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>80-89</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D99">
-        <v>2269.508437172638</v>
-      </c>
-      <c r="E99">
-        <v>1683.498291941293</v>
-      </c>
-      <c r="F99">
-        <v>2752.103781982716</v>
-      </c>
-      <c r="G99">
-        <v>0</v>
-      </c>
-      <c r="H99">
-        <v>0</v>
-      </c>
-      <c r="I99">
-        <v>0</v>
-      </c>
-      <c r="J99">
-        <v>0</v>
-      </c>
-      <c r="K99">
-        <v>0</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
-      <c r="O99">
         <v>0</v>
       </c>
     </row>

--- a/output/Tables/2019/cases_prev_2019_sex_age.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex_age.xlsx
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="D2">
-        <v>146.4221301187112</v>
+        <v>435.2855334240849</v>
       </c>
       <c r="E2">
-        <v>125.6170451611738</v>
+        <v>289.1750659760629</v>
       </c>
       <c r="F2">
-        <v>165.8811944921929</v>
+        <v>569.7091440287641</v>
       </c>
       <c r="G2">
-        <v>8976.493814429014</v>
+        <v>26656.67924454058</v>
       </c>
       <c r="H2">
-        <v>7700.662374394636</v>
+        <v>17711.89575279102</v>
       </c>
       <c r="I2">
-        <v>10169.74165571172</v>
+        <v>34888.46698823707</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -475,13 +475,13 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>1193873677.319059</v>
+        <v>3545338339.523898</v>
       </c>
       <c r="N2">
-        <v>1024188095.794487</v>
+        <v>2355682135.121206</v>
       </c>
       <c r="O2">
-        <v>1352575640.209658</v>
+        <v>4640166109.435531</v>
       </c>
     </row>
     <row r="3">
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="D3">
-        <v>304.3972071285506</v>
+        <v>910.7050839343707</v>
       </c>
       <c r="E3">
-        <v>260.7233686243825</v>
+        <v>603.3305020902101</v>
       </c>
       <c r="F3">
-        <v>345.2228136533533</v>
+        <v>1192.852398738941</v>
       </c>
       <c r="G3">
-        <v>16802.07392663788</v>
+        <v>50233.38408387898</v>
       </c>
       <c r="H3">
-        <v>14388.20568504453</v>
+        <v>33278.50732915365</v>
       </c>
       <c r="I3">
-        <v>19058.29407856597</v>
+        <v>65799.98481281337</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -528,13 +528,13 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>2234675832.242837</v>
+        <v>6681040083.155904</v>
       </c>
       <c r="N3">
-        <v>1913631356.110922</v>
+        <v>4426041474.777435</v>
       </c>
       <c r="O3">
-        <v>2534753112.449274</v>
+        <v>8751397980.104179</v>
       </c>
     </row>
     <row r="4">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="D4">
-        <v>320.6350513976859</v>
+        <v>969.8495904103426</v>
       </c>
       <c r="E4">
-        <v>275.8725218057071</v>
+        <v>643.3726544970027</v>
       </c>
       <c r="F4">
-        <v>362.5262480925129</v>
+        <v>1268.270845943447</v>
       </c>
       <c r="G4">
-        <v>16230.87838344617</v>
+        <v>49130.46970327669</v>
       </c>
       <c r="H4">
-        <v>13966.11358117923</v>
+        <v>32589.32552905086</v>
       </c>
       <c r="I4">
-        <v>18350.43969544767</v>
+        <v>64246.56059211981</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -581,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>2158706824.998341</v>
+        <v>6534352470.535799</v>
       </c>
       <c r="N4">
-        <v>1857493106.296837</v>
+        <v>4334380295.363765</v>
       </c>
       <c r="O4">
-        <v>2440608479.494539</v>
+        <v>8544792558.751935</v>
       </c>
     </row>
     <row r="5">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="D5">
-        <v>547.6914754482884</v>
+        <v>1587.202687338412</v>
       </c>
       <c r="E5">
-        <v>474.7018882877405</v>
+        <v>1067.461366528668</v>
       </c>
       <c r="F5">
-        <v>616.2518630465624</v>
+        <v>2067.779564945326</v>
       </c>
       <c r="G5">
-        <v>24176.99828119361</v>
+        <v>70108.41790221342</v>
       </c>
       <c r="H5">
-        <v>20947.34554837996</v>
+        <v>47132.81549544881</v>
       </c>
       <c r="I5">
-        <v>27210.05795110119</v>
+        <v>91350.47321020726</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -634,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>3215540771.398751</v>
+        <v>9324419580.994385</v>
       </c>
       <c r="N5">
-        <v>2785996957.934535</v>
+        <v>6268664460.894692</v>
       </c>
       <c r="O5">
-        <v>3618937707.496459</v>
+        <v>12149612936.95757</v>
       </c>
     </row>
     <row r="6">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="D6">
-        <v>822.7254609748222</v>
+        <v>2414.15291833403</v>
       </c>
       <c r="E6">
-        <v>711.9296848723443</v>
+        <v>1616.485041377077</v>
       </c>
       <c r="F6">
-        <v>926.9011848085071</v>
+        <v>3149.639177897817</v>
       </c>
       <c r="G6">
-        <v>33941.25856196675</v>
+        <v>99706.1336105891</v>
       </c>
       <c r="H6">
-        <v>29364.02295714071</v>
+        <v>66737.7427395565</v>
       </c>
       <c r="I6">
-        <v>38244.13463314629</v>
+        <v>130092.0173749659</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>4514187388.741578</v>
+        <v>13260915770.20835</v>
       </c>
       <c r="N6">
-        <v>3905415053.299715</v>
+        <v>8876119784.361015</v>
       </c>
       <c r="O6">
-        <v>5086469906.208457</v>
+        <v>17302238310.87047</v>
       </c>
     </row>
     <row r="7">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="D7">
-        <v>1481.265888707133</v>
+        <v>4279.127768164705</v>
       </c>
       <c r="E7">
-        <v>1279.464861840598</v>
+        <v>2872.67903840573</v>
       </c>
       <c r="F7">
-        <v>1670.533151363413</v>
+        <v>5582.545217205755</v>
       </c>
       <c r="G7">
-        <v>51596.83662345119</v>
+        <v>149306.1096109553</v>
       </c>
       <c r="H7">
-        <v>44539.66422346493</v>
+        <v>100156.5667855753</v>
       </c>
       <c r="I7">
-        <v>58213.29166478587</v>
+        <v>194834.5313570297</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -740,13 +740,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>6862379270.919008</v>
+        <v>19857712578.25705</v>
       </c>
       <c r="N7">
-        <v>5923775341.720835</v>
+        <v>13320823382.48152</v>
       </c>
       <c r="O7">
-        <v>7742367791.41652</v>
+        <v>25912992670.48495</v>
       </c>
     </row>
     <row r="8">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="D8">
-        <v>1897.984648076764</v>
+        <v>5657.269409647047</v>
       </c>
       <c r="E8">
-        <v>1636.768813818004</v>
+        <v>3767.696584808534</v>
       </c>
       <c r="F8">
-        <v>2143.156166310431</v>
+        <v>7393.655306128534</v>
       </c>
       <c r="G8">
-        <v>58237.00267826884</v>
+        <v>173508.9545045595</v>
       </c>
       <c r="H8">
-        <v>50212.57084275907</v>
+        <v>115553.4367521461</v>
       </c>
       <c r="I8">
-        <v>65767.14529388356</v>
+        <v>226773.2470341208</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -793,13 +793,13 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>7745521356.209756</v>
+        <v>23076690949.10642</v>
       </c>
       <c r="N8">
-        <v>6678271922.086957</v>
+        <v>15368607088.03543</v>
       </c>
       <c r="O8">
-        <v>8747030324.086514</v>
+        <v>30160841855.53806</v>
       </c>
     </row>
     <row r="9">
@@ -819,22 +819,22 @@
         </is>
       </c>
       <c r="D9">
-        <v>3016.209784570601</v>
+        <v>8966.407293192606</v>
       </c>
       <c r="E9">
-        <v>2596.782406610738</v>
+        <v>5966.420570826935</v>
       </c>
       <c r="F9">
-        <v>3409.465336409344</v>
+        <v>11720.72996035896</v>
       </c>
       <c r="G9">
-        <v>74077.90998405282</v>
+        <v>220040.0200217852</v>
       </c>
       <c r="H9">
-        <v>63791.30771753832</v>
+        <v>146468.8768304157</v>
       </c>
       <c r="I9">
-        <v>83723.76035591439</v>
+        <v>287605.1808418927</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -846,13 +846,13 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>9852362027.879025</v>
+        <v>29265322662.89743</v>
       </c>
       <c r="N9">
-        <v>8484243926.432597</v>
+        <v>19480360618.44529</v>
       </c>
       <c r="O9">
-        <v>11135260127.33661</v>
+        <v>38251489051.97173</v>
       </c>
     </row>
     <row r="10">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="D10">
-        <v>3688.375714897353</v>
+        <v>11264.81325268051</v>
       </c>
       <c r="E10">
-        <v>3179.497927524445</v>
+        <v>7467.2687348385</v>
       </c>
       <c r="F10">
-        <v>4165.532253838414</v>
+        <v>14726.96380002632</v>
       </c>
       <c r="G10">
-        <v>77834.59508313396</v>
+        <v>238035.8809835756</v>
       </c>
       <c r="H10">
-        <v>67087.26929670975</v>
+        <v>157737.6277879707</v>
       </c>
       <c r="I10">
-        <v>87910.5967280139</v>
+        <v>311211.5600527084</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>10352001146.05682</v>
+        <v>31658772170.81556</v>
       </c>
       <c r="N10">
-        <v>8922606816.462397</v>
+        <v>20979104495.80011</v>
       </c>
       <c r="O10">
-        <v>11692109364.82585</v>
+        <v>41391137487.01022</v>
       </c>
     </row>
     <row r="11">
@@ -925,22 +925,22 @@
         </is>
       </c>
       <c r="D11">
-        <v>6786.538776640228</v>
+        <v>21013.7719089307</v>
       </c>
       <c r="E11">
-        <v>5889.43064407622</v>
+        <v>13958.46664006256</v>
       </c>
       <c r="F11">
-        <v>7628.432254583518</v>
+        <v>27396.03948766769</v>
       </c>
       <c r="G11">
-        <v>101215.0488475706</v>
+        <v>313317.1488147227</v>
       </c>
       <c r="H11">
-        <v>87775.4471642147</v>
+        <v>208028.0557796395</v>
       </c>
       <c r="I11">
-        <v>113824.2729295891</v>
+        <v>408578.2344281773</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -952,13 +952,13 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>13461601496.72689</v>
+        <v>41671180792.35812</v>
       </c>
       <c r="N11">
-        <v>11674134472.84056</v>
+        <v>27667731418.69205</v>
       </c>
       <c r="O11">
-        <v>15138628299.63535</v>
+        <v>54340905178.94758</v>
       </c>
     </row>
     <row r="12">
@@ -978,22 +978,22 @@
         </is>
       </c>
       <c r="D12">
-        <v>6476.304467184525</v>
+        <v>19214.93449885627</v>
       </c>
       <c r="E12">
-        <v>5548.101733530149</v>
+        <v>12756.23503728818</v>
       </c>
       <c r="F12">
-        <v>7344.113239621301</v>
+        <v>25163.03385888611</v>
       </c>
       <c r="G12">
-        <v>72732.60520264482</v>
+        <v>217609.0202169071</v>
       </c>
       <c r="H12">
-        <v>62282.23767922331</v>
+        <v>144191.963826087</v>
       </c>
       <c r="I12">
-        <v>82499.35643808694</v>
+        <v>285051.3310106237</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>9673436491.951761</v>
+        <v>28941999688.84864</v>
       </c>
       <c r="N12">
-        <v>8283537611.3367</v>
+        <v>19177531188.86956</v>
       </c>
       <c r="O12">
-        <v>10972414406.26556</v>
+        <v>37911827024.41296</v>
       </c>
     </row>
     <row r="13">
@@ -1031,22 +1031,22 @@
         </is>
       </c>
       <c r="D13">
-        <v>10374.11596772373</v>
+        <v>31466.83270910789</v>
       </c>
       <c r="E13">
-        <v>8964.720314821185</v>
+        <v>20929.13261593044</v>
       </c>
       <c r="F13">
-        <v>11695.0433994739</v>
+        <v>41074.48227569897</v>
       </c>
       <c r="G13">
-        <v>52212.9813753946</v>
+        <v>157278.1344808862</v>
       </c>
       <c r="H13">
-        <v>45276.0364010886</v>
+        <v>105025.1548026792</v>
       </c>
       <c r="I13">
-        <v>58724.92844870497</v>
+        <v>205016.6034841224</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1058,13 +1058,13 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>6944326522.927482</v>
+        <v>20917991885.95787</v>
       </c>
       <c r="N13">
-        <v>6021712841.344785</v>
+        <v>13968345588.75633</v>
       </c>
       <c r="O13">
-        <v>7810415483.677761</v>
+        <v>27267208263.38828</v>
       </c>
     </row>
     <row r="14">
@@ -1084,22 +1084,22 @@
         </is>
       </c>
       <c r="D14">
-        <v>11248.50302481298</v>
+        <v>32328.32246221994</v>
       </c>
       <c r="E14">
-        <v>9611.811879420429</v>
+        <v>21544.17794817125</v>
       </c>
       <c r="F14">
-        <v>12778.40144615328</v>
+        <v>42356.62800534306</v>
       </c>
       <c r="G14">
-        <v>20038.52893530652</v>
+        <v>58075.64541674264</v>
       </c>
       <c r="H14">
-        <v>17145.23587905876</v>
+        <v>38670.03783748509</v>
       </c>
       <c r="I14">
-        <v>22746.75485564202</v>
+        <v>76087.28311123743</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>2665124348.395767</v>
+        <v>7724060840.426771</v>
       </c>
       <c r="N14">
-        <v>2280316371.914815</v>
+        <v>5143115032.385517</v>
       </c>
       <c r="O14">
-        <v>3025318395.800389</v>
+        <v>10119608653.79458</v>
       </c>
     </row>
     <row r="15">
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>11697.55894851393</v>
+        <v>33821.96946999706</v>
       </c>
       <c r="E15">
-        <v>10127.7552612112</v>
+        <v>22727.00051401978</v>
       </c>
       <c r="F15">
-        <v>13171.26556683537</v>
+        <v>44074.65077734297</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1190,40 +1190,40 @@
         </is>
       </c>
       <c r="D16">
-        <v>92.77833442522571</v>
+        <v>588.3023755021495</v>
       </c>
       <c r="E16">
-        <v>57.99792248019556</v>
+        <v>390.7880633089979</v>
       </c>
       <c r="F16">
-        <v>127.1325348205727</v>
+        <v>769.9254730075888</v>
       </c>
       <c r="G16">
-        <v>368.5768165662126</v>
+        <v>2337.775120016796</v>
       </c>
       <c r="H16">
-        <v>180.82426037114</v>
+        <v>1219.014207573438</v>
       </c>
       <c r="I16">
-        <v>615.7575036607418</v>
+        <v>3729.476554758412</v>
       </c>
       <c r="J16">
-        <v>5167938.784153922</v>
+        <v>32769618.92022067</v>
       </c>
       <c r="K16">
-        <v>3230600.277991856</v>
+        <v>21767676.70243776</v>
       </c>
       <c r="L16">
-        <v>7081536.454575542</v>
+        <v>42886388.69746874</v>
       </c>
       <c r="M16">
-        <v>49020716.60330627</v>
+        <v>310924090.9622338</v>
       </c>
       <c r="N16">
-        <v>24049626.62936161</v>
+        <v>162128889.6072673</v>
       </c>
       <c r="O16">
-        <v>81895747.98687866</v>
+        <v>496020381.7828689</v>
       </c>
     </row>
     <row r="17">
@@ -1243,40 +1243,40 @@
         </is>
       </c>
       <c r="D17">
-        <v>135.6490637347129</v>
+        <v>862.1419172780883</v>
       </c>
       <c r="E17">
-        <v>85.00723101728489</v>
+        <v>571.2622204651087</v>
       </c>
       <c r="F17">
-        <v>185.620177680754</v>
+        <v>1129.314683796277</v>
       </c>
       <c r="G17">
-        <v>486.8337727318624</v>
+        <v>3094.538229261351</v>
       </c>
       <c r="H17">
-        <v>239.3738190759266</v>
+        <v>1609.328363362568</v>
       </c>
       <c r="I17">
-        <v>812.2820716082424</v>
+        <v>4941.482186065206</v>
       </c>
       <c r="J17">
-        <v>7555924.148150986</v>
+        <v>48023029.07622405</v>
       </c>
       <c r="K17">
-        <v>4735072.782124808</v>
+        <v>31820448.20434756</v>
       </c>
       <c r="L17">
-        <v>10339415.13717336</v>
+        <v>62905086.51682044</v>
       </c>
       <c r="M17">
-        <v>64748891.7733377</v>
+        <v>411573584.4917597</v>
       </c>
       <c r="N17">
-        <v>31836717.93709823</v>
+        <v>214040672.3272216</v>
       </c>
       <c r="O17">
-        <v>108033515.5238962</v>
+        <v>657217130.7466725</v>
       </c>
     </row>
     <row r="18">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D18">
-        <v>195.2293645175942</v>
+        <v>1242.362614573032</v>
       </c>
       <c r="E18">
-        <v>123.8561689258144</v>
+        <v>824.0461699609796</v>
       </c>
       <c r="F18">
-        <v>265.1937626766019</v>
+        <v>1624.368756679494</v>
       </c>
       <c r="G18">
-        <v>650.0257777616259</v>
+        <v>4136.44673959089</v>
       </c>
       <c r="H18">
-        <v>323.7681497263035</v>
+        <v>2153.242267103315</v>
       </c>
       <c r="I18">
-        <v>1076.109963456634</v>
+        <v>6592.571442464791</v>
       </c>
       <c r="J18">
-        <v>10874666.06235905</v>
+        <v>69202082.35694687</v>
       </c>
       <c r="K18">
-        <v>6899036.321505706</v>
+        <v>45901019.75916655</v>
       </c>
       <c r="L18">
-        <v>14771822.9686121</v>
+        <v>90480588.48456137</v>
       </c>
       <c r="M18">
-        <v>86453428.44229625</v>
+        <v>550147416.3655883</v>
       </c>
       <c r="N18">
-        <v>43061163.91359837</v>
+        <v>286381221.5247409</v>
       </c>
       <c r="O18">
-        <v>143122625.1397324</v>
+        <v>876812001.8478172</v>
       </c>
     </row>
     <row r="19">
@@ -1349,40 +1349,40 @@
         </is>
       </c>
       <c r="D19">
-        <v>290.5251973567622</v>
+        <v>1861.275375926888</v>
       </c>
       <c r="E19">
-        <v>183.4611080398511</v>
+        <v>1251.800585376363</v>
       </c>
       <c r="F19">
-        <v>397.6873695018385</v>
+        <v>2425.064677477481</v>
       </c>
       <c r="G19">
-        <v>837.8001900664822</v>
+        <v>5366.225194633682</v>
       </c>
       <c r="H19">
-        <v>415.0813938982664</v>
+        <v>2831.450712118654</v>
       </c>
       <c r="I19">
-        <v>1398.103938132431</v>
+        <v>8524.27540562309</v>
       </c>
       <c r="J19">
-        <v>16182834.54316638</v>
+        <v>103676760.9898791</v>
       </c>
       <c r="K19">
-        <v>10219150.64003578</v>
+        <v>69727796.20663381</v>
       </c>
       <c r="L19">
-        <v>22151981.8559914</v>
+        <v>135080952.6648503</v>
       </c>
       <c r="M19">
-        <v>111427425.2788421</v>
+        <v>713707950.8862797</v>
       </c>
       <c r="N19">
-        <v>55205825.38846944</v>
+        <v>376582944.711781</v>
       </c>
       <c r="O19">
-        <v>185947823.7716133</v>
+        <v>1133728628.947871</v>
       </c>
     </row>
     <row r="20">
@@ -1402,40 +1402,40 @@
         </is>
       </c>
       <c r="D20">
-        <v>591.4152867432659</v>
+        <v>3772.518073227711</v>
       </c>
       <c r="E20">
-        <v>372.9800503342093</v>
+        <v>2525.865681256683</v>
       </c>
       <c r="F20">
-        <v>807.869275902249</v>
+        <v>4921.37781992131</v>
       </c>
       <c r="G20">
-        <v>1602.368178440391</v>
+        <v>10223.59219287837</v>
       </c>
       <c r="H20">
-        <v>793.6433668643126</v>
+        <v>5370.357816641138</v>
       </c>
       <c r="I20">
-        <v>2667.1933778355</v>
+        <v>16259.14607686969</v>
       </c>
       <c r="J20">
-        <v>32943014.30217335</v>
+        <v>210136801.7149305</v>
       </c>
       <c r="K20">
-        <v>20775734.7637161</v>
+        <v>140695770.1773603</v>
       </c>
       <c r="L20">
-        <v>44999934.40630708</v>
+        <v>274130587.3252571</v>
       </c>
       <c r="M20">
-        <v>213114967.732572</v>
+        <v>1359737761.652823</v>
       </c>
       <c r="N20">
-        <v>105554567.7929536</v>
+        <v>714257589.6132714</v>
       </c>
       <c r="O20">
-        <v>354736719.2521214</v>
+        <v>2162466428.223668</v>
       </c>
     </row>
     <row r="21">
@@ -1455,40 +1455,40 @@
         </is>
       </c>
       <c r="D21">
-        <v>982.7683579834647</v>
+        <v>6267.890872950401</v>
       </c>
       <c r="E21">
-        <v>615.3763349288367</v>
+        <v>4200.348240623475</v>
       </c>
       <c r="F21">
-        <v>1349.63274350066</v>
+        <v>8181.718324197083</v>
       </c>
       <c r="G21">
-        <v>2249.419522071234</v>
+        <v>14341.23896952509</v>
       </c>
       <c r="H21">
-        <v>1105.260515098489</v>
+        <v>7536.952666531106</v>
       </c>
       <c r="I21">
-        <v>3765.336041466629</v>
+        <v>22825.80948510642</v>
       </c>
       <c r="J21">
-        <v>54742163.07639498</v>
+        <v>349134057.4050845</v>
       </c>
       <c r="K21">
-        <v>34277692.6082061</v>
+        <v>233967797.6992088</v>
       </c>
       <c r="L21">
-        <v>75177243.07847367</v>
+        <v>455738074.0944259</v>
       </c>
       <c r="M21">
-        <v>299172796.435474</v>
+        <v>1907384782.946837</v>
       </c>
       <c r="N21">
-        <v>146999648.508099</v>
+        <v>1002414704.648637</v>
       </c>
       <c r="O21">
-        <v>500789693.5150617</v>
+        <v>3035832661.519153</v>
       </c>
     </row>
     <row r="22">
@@ -1508,40 +1508,40 @@
         </is>
       </c>
       <c r="D22">
-        <v>1643.860926040004</v>
+        <v>10427.51345433943</v>
       </c>
       <c r="E22">
-        <v>1032.131013275483</v>
+        <v>6943.098805040554</v>
       </c>
       <c r="F22">
-        <v>2245.336771866513</v>
+        <v>13628.83739804005</v>
       </c>
       <c r="G22">
-        <v>3275.765213134426</v>
+        <v>20782.16786691479</v>
       </c>
       <c r="H22">
-        <v>1614.161009467949</v>
+        <v>10860.23543347352</v>
       </c>
       <c r="I22">
-        <v>5454.726309926367</v>
+        <v>33112.34983015166</v>
       </c>
       <c r="J22">
-        <v>91566341.30228034</v>
+        <v>580833354.433617</v>
       </c>
       <c r="K22">
-        <v>57491761.70147098</v>
+        <v>386744489.638369</v>
       </c>
       <c r="L22">
-        <v>125069748.8665085</v>
+        <v>759153500.7456278</v>
       </c>
       <c r="M22">
-        <v>435676773.3468786</v>
+        <v>2764028326.299667</v>
       </c>
       <c r="N22">
-        <v>214683414.2592373</v>
+        <v>1444411312.651979</v>
       </c>
       <c r="O22">
-        <v>725478599.2202069</v>
+        <v>4403942527.410171</v>
       </c>
     </row>
     <row r="23">
@@ -1561,40 +1561,40 @@
         </is>
       </c>
       <c r="D23">
-        <v>2281.869078717225</v>
+        <v>14565.06109939926</v>
       </c>
       <c r="E23">
-        <v>1440.796488924802</v>
+        <v>9691.498738423492</v>
       </c>
       <c r="F23">
-        <v>3113.417919483419</v>
+        <v>19040.40339821524</v>
       </c>
       <c r="G23">
-        <v>3643.089849178938</v>
+        <v>23249.50335955776</v>
       </c>
       <c r="H23">
-        <v>1804.608527162677</v>
+        <v>12146.45005999749</v>
       </c>
       <c r="I23">
-        <v>6060.952941512061</v>
+        <v>37045.46703133934</v>
       </c>
       <c r="J23">
-        <v>127104671.4227068</v>
+        <v>811303033.3587363</v>
       </c>
       <c r="K23">
-        <v>80255246.02608931</v>
+        <v>539835862.7276652</v>
       </c>
       <c r="L23">
-        <v>173423604.9510656</v>
+        <v>1060588550.087386</v>
       </c>
       <c r="M23">
-        <v>484530949.9407987</v>
+        <v>3092183946.821182</v>
       </c>
       <c r="N23">
-        <v>240012934.112636</v>
+        <v>1615477857.979666</v>
       </c>
       <c r="O23">
-        <v>806106741.2211041</v>
+        <v>4927047115.168132</v>
       </c>
     </row>
     <row r="24">
@@ -1614,40 +1614,40 @@
         </is>
       </c>
       <c r="D24">
-        <v>4738.672408902913</v>
+        <v>30062.00423447313</v>
       </c>
       <c r="E24">
-        <v>3005.445021319446</v>
+        <v>19932.22993061347</v>
       </c>
       <c r="F24">
-        <v>6429.639299581467</v>
+        <v>39294.38823186921</v>
       </c>
       <c r="G24">
-        <v>6510.008282855246</v>
+        <v>41299.4282229974</v>
       </c>
       <c r="H24">
-        <v>3242.016035246957</v>
+        <v>21484.96442683367</v>
       </c>
       <c r="I24">
-        <v>10763.93564291911</v>
+        <v>65808.5028179798</v>
       </c>
       <c r="J24">
-        <v>263953530.5207101</v>
+        <v>1674513759.868619</v>
       </c>
       <c r="K24">
-        <v>167409298.5775359</v>
+        <v>1110265071.595028</v>
       </c>
       <c r="L24">
-        <v>358143768.2652868</v>
+        <v>2188776013.291584</v>
       </c>
       <c r="M24">
-        <v>865831101.6197478</v>
+        <v>5492823953.658654</v>
       </c>
       <c r="N24">
-        <v>431188132.6878453</v>
+        <v>2857500268.768878</v>
       </c>
       <c r="O24">
-        <v>1431603440.508242</v>
+        <v>8752530874.791313</v>
       </c>
     </row>
     <row r="25">
@@ -1667,40 +1667,40 @@
         </is>
       </c>
       <c r="D25">
-        <v>6478.526685452082</v>
+        <v>41527.39025708874</v>
       </c>
       <c r="E25">
-        <v>4209.216951589732</v>
+        <v>27587.41695785157</v>
       </c>
       <c r="F25">
-        <v>8684.934272686958</v>
+        <v>54139.4127855086</v>
       </c>
       <c r="G25">
-        <v>6326.758000268212</v>
+        <v>40550.25659999363</v>
       </c>
       <c r="H25">
-        <v>3223.96415975527</v>
+        <v>21133.5830468271</v>
       </c>
       <c r="I25">
-        <v>10342.89060700587</v>
+        <v>64457.87563826534</v>
       </c>
       <c r="J25">
-        <v>360866893.4330518</v>
+        <v>2313158692.100357</v>
       </c>
       <c r="K25">
-        <v>234461802.6374513</v>
+        <v>1536674299.386242</v>
       </c>
       <c r="L25">
-        <v>483768208.8572096</v>
+        <v>3015673570.978398</v>
       </c>
       <c r="M25">
-        <v>841458814.0356722</v>
+        <v>5393184127.799153</v>
       </c>
       <c r="N25">
-        <v>428787233.2474509</v>
+        <v>2810766545.228004</v>
       </c>
       <c r="O25">
-        <v>1375604450.73178</v>
+        <v>8572897459.889291</v>
       </c>
     </row>
     <row r="26">
@@ -1720,40 +1720,40 @@
         </is>
       </c>
       <c r="D26">
-        <v>6558.472911335218</v>
+        <v>41564.39048169472</v>
       </c>
       <c r="E26">
-        <v>4097.272051516084</v>
+        <v>27542.08114549347</v>
       </c>
       <c r="F26">
-        <v>8984.354222218995</v>
+        <v>54447.1462554098</v>
       </c>
       <c r="G26">
-        <v>5083.569533327025</v>
+        <v>32206.70271333435</v>
       </c>
       <c r="H26">
-        <v>2498.577414493875</v>
+        <v>16720.53516294613</v>
       </c>
       <c r="I26">
-        <v>8472.724292979901</v>
+        <v>51441.97312017581</v>
       </c>
       <c r="J26">
-        <v>365320058.1071944</v>
+        <v>2315219678.611363</v>
       </c>
       <c r="K26">
-        <v>228226247.8135489</v>
+        <v>1534149003.966281</v>
       </c>
       <c r="L26">
-        <v>500446498.8860425</v>
+        <v>3032814940.718844</v>
       </c>
       <c r="M26">
-        <v>676114747.9324943</v>
+        <v>4283491460.873468</v>
       </c>
       <c r="N26">
-        <v>332310796.1276854</v>
+        <v>2223831176.671835</v>
       </c>
       <c r="O26">
-        <v>1126872330.966327</v>
+        <v>6841782424.983383</v>
       </c>
     </row>
     <row r="27">
@@ -1773,40 +1773,40 @@
         </is>
       </c>
       <c r="D27">
-        <v>6878.835877345051</v>
+        <v>43947.18992219883</v>
       </c>
       <c r="E27">
-        <v>4399.644362797233</v>
+        <v>29262.19071618433</v>
       </c>
       <c r="F27">
-        <v>9314.878417584296</v>
+        <v>57345.32447838437</v>
       </c>
       <c r="G27">
-        <v>2505.404923982068</v>
+        <v>15998.77204301349</v>
       </c>
       <c r="H27">
-        <v>1256.334044640764</v>
+        <v>8385.888050860196</v>
       </c>
       <c r="I27">
-        <v>4139.709686349373</v>
+        <v>25423.33587380562</v>
       </c>
       <c r="J27">
-        <v>383164916.0398745</v>
+        <v>2447946373.046322</v>
       </c>
       <c r="K27">
-        <v>245068990.2965314</v>
+        <v>1629962547.272897</v>
       </c>
       <c r="L27">
-        <v>518857357.6162809</v>
+        <v>3194249264.094966</v>
       </c>
       <c r="M27">
-        <v>333218854.889615</v>
+        <v>2127836681.720793</v>
       </c>
       <c r="N27">
-        <v>167092427.9372216</v>
+        <v>1115323110.764406</v>
       </c>
       <c r="O27">
-        <v>550581388.2844666</v>
+        <v>3381303671.216147</v>
       </c>
     </row>
     <row r="28">
@@ -1826,40 +1826,40 @@
         </is>
       </c>
       <c r="D28">
-        <v>4754.302361004454</v>
+        <v>30229.452438522</v>
       </c>
       <c r="E28">
-        <v>2930.534283444486</v>
+        <v>20126.10559937367</v>
       </c>
       <c r="F28">
-        <v>6579.016104825467</v>
+        <v>39618.78132479652</v>
       </c>
       <c r="G28">
-        <v>737.6467591972638</v>
+        <v>4672.967347965558</v>
       </c>
       <c r="H28">
-        <v>355.9927499320976</v>
+        <v>2437.111573106332</v>
       </c>
       <c r="I28">
-        <v>1244.133935525461</v>
+        <v>7469.442813196508</v>
       </c>
       <c r="J28">
-        <v>264824150.11267</v>
+        <v>1683840959.730555</v>
       </c>
       <c r="K28">
-        <v>163236620.6564246</v>
+        <v>1121064334.096312</v>
       </c>
       <c r="L28">
-        <v>366464355.070988</v>
+        <v>2206845357.353813</v>
       </c>
       <c r="M28">
-        <v>98107018.97323608</v>
+        <v>621504657.2794193</v>
       </c>
       <c r="N28">
-        <v>47347035.74096899</v>
+        <v>324135839.2231422</v>
       </c>
       <c r="O28">
-        <v>165469813.4248863</v>
+        <v>993435894.1551355</v>
       </c>
     </row>
     <row r="29">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="D29">
-        <v>4035.360950613182</v>
+        <v>26004.96328265017</v>
       </c>
       <c r="E29">
-        <v>2578.007879354308</v>
+        <v>17458.20678959009</v>
       </c>
       <c r="F29">
-        <v>5490.355844215614</v>
+        <v>33876.56247021109</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1897,13 +1897,13 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>224777675.6710557</v>
+        <v>1448528464.770181</v>
       </c>
       <c r="K29">
-        <v>143600194.8957937</v>
+        <v>972457034.5937463</v>
       </c>
       <c r="L29">
-        <v>305823801.2344981</v>
+        <v>1886992282.715702</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -1932,40 +1932,40 @@
         </is>
       </c>
       <c r="D30">
-        <v>1529.967334197196</v>
+        <v>39067.57473912447</v>
       </c>
       <c r="E30">
-        <v>83.33406507317531</v>
+        <v>25952.35490837772</v>
       </c>
       <c r="F30">
-        <v>3096.145374802112</v>
+        <v>51129.04023778993</v>
       </c>
       <c r="G30">
-        <v>5215.155602424024</v>
+        <v>133281.9358071194</v>
       </c>
       <c r="H30">
-        <v>226.9858207426677</v>
+        <v>70059.19428382514</v>
       </c>
       <c r="I30">
-        <v>12186.693137724</v>
+        <v>201415.1458295389</v>
       </c>
       <c r="J30">
-        <v>22654226.31745791</v>
+        <v>578473579.1622168</v>
       </c>
       <c r="K30">
-        <v>1233927.501538506</v>
+        <v>384276519.1283484</v>
       </c>
       <c r="L30">
-        <v>45844624.5646948</v>
+        <v>757067698.8009558</v>
       </c>
       <c r="M30">
-        <v>693615695.1223953</v>
+        <v>17726497462.34688</v>
       </c>
       <c r="N30">
-        <v>30189114.1587748</v>
+        <v>9317872839.748743</v>
       </c>
       <c r="O30">
-        <v>1620830187.317292</v>
+        <v>26788214395.32867</v>
       </c>
     </row>
     <row r="31">
@@ -1985,40 +1985,40 @@
         </is>
       </c>
       <c r="D31">
-        <v>351.6245684794629</v>
+        <v>8875.465444864987</v>
       </c>
       <c r="E31">
-        <v>18.01541696591593</v>
+        <v>5880.828272723464</v>
       </c>
       <c r="F31">
-        <v>711.8170378773087</v>
+        <v>11625.89726025813</v>
       </c>
       <c r="G31">
-        <v>1084.15809081903</v>
+        <v>27390.66513219524</v>
       </c>
       <c r="H31">
-        <v>44.34334659229552</v>
+        <v>14358.58208147701</v>
       </c>
       <c r="I31">
-        <v>2534.217688626623</v>
+        <v>41431.92644580393</v>
       </c>
       <c r="J31">
-        <v>5206504.985475406</v>
+        <v>131419016.8421159</v>
       </c>
       <c r="K31">
-        <v>266754.2790143174</v>
+        <v>87077424.23421615</v>
       </c>
       <c r="L31">
-        <v>10539874.8798493</v>
+        <v>172144660.7326424</v>
       </c>
       <c r="M31">
-        <v>144193026.078931</v>
+        <v>3642958462.581967</v>
       </c>
       <c r="N31">
-        <v>5897665.096775304</v>
+        <v>1909691416.836442</v>
       </c>
       <c r="O31">
-        <v>337050952.5873408</v>
+        <v>5510446217.291923</v>
       </c>
     </row>
     <row r="32">
@@ -2038,40 +2038,40 @@
         </is>
       </c>
       <c r="D32">
-        <v>2711.394525317037</v>
+        <v>66663.3385387524</v>
       </c>
       <c r="E32">
-        <v>112.329351496371</v>
+        <v>44211.44958610579</v>
       </c>
       <c r="F32">
-        <v>5482.296495174682</v>
+        <v>87162.53839688856</v>
       </c>
       <c r="G32">
-        <v>7780.144420911856</v>
+        <v>191110.0731452168</v>
       </c>
       <c r="H32">
-        <v>252.399219276486</v>
+        <v>100268.1254814551</v>
       </c>
       <c r="I32">
-        <v>18164.2909584158</v>
+        <v>288529.1807578096</v>
       </c>
       <c r="J32">
-        <v>40147618.73636941</v>
+        <v>987084053.7433087</v>
       </c>
       <c r="K32">
-        <v>1663260.707606766</v>
+        <v>654638934.021468</v>
       </c>
       <c r="L32">
-        <v>81176364.20405152</v>
+        <v>1290615706.042728</v>
       </c>
       <c r="M32">
-        <v>1034759207.981277</v>
+        <v>25417639728.31384</v>
       </c>
       <c r="N32">
-        <v>33569096.16377264</v>
+        <v>13335660689.03352</v>
       </c>
       <c r="O32">
-        <v>2415850697.469302</v>
+        <v>38374381040.78868</v>
       </c>
     </row>
     <row r="33">
@@ -2091,40 +2091,40 @@
         </is>
       </c>
       <c r="D33">
-        <v>528.5618048818598</v>
+        <v>13720.98042512767</v>
       </c>
       <c r="E33">
-        <v>33.71872067483555</v>
+        <v>9221.582919495293</v>
       </c>
       <c r="F33">
-        <v>1069.000295128041</v>
+        <v>17881.43256125474</v>
       </c>
       <c r="G33">
-        <v>1315.627992596407</v>
+        <v>34134.50263124902</v>
       </c>
       <c r="H33">
-        <v>66.28486947710086</v>
+        <v>18141.94845576538</v>
       </c>
       <c r="I33">
-        <v>3072.478373633139</v>
+        <v>51376.42828834646</v>
       </c>
       <c r="J33">
-        <v>7826414.644885696</v>
+        <v>203166557.1548653</v>
       </c>
       <c r="K33">
-        <v>499273.0970322899</v>
+        <v>136543978.2889671</v>
       </c>
       <c r="L33">
-        <v>15828687.36996092</v>
+        <v>264770371.9344981</v>
       </c>
       <c r="M33">
-        <v>174978523.0153222</v>
+        <v>4539888849.95612</v>
       </c>
       <c r="N33">
-        <v>8815887.640454413</v>
+        <v>2412879144.616795</v>
       </c>
       <c r="O33">
-        <v>408639623.6932075</v>
+        <v>6833064962.35008</v>
       </c>
     </row>
     <row r="34">
@@ -2144,40 +2144,40 @@
         </is>
       </c>
       <c r="D34">
-        <v>3214.054712457849</v>
+        <v>81926.66594650787</v>
       </c>
       <c r="E34">
-        <v>172.628420995428</v>
+        <v>54787.86904922353</v>
       </c>
       <c r="F34">
-        <v>6509.922726056692</v>
+        <v>106913.2168352687</v>
       </c>
       <c r="G34">
-        <v>7567.824427551544</v>
+        <v>192453.2050262274</v>
       </c>
       <c r="H34">
-        <v>317.5313023112167</v>
+        <v>101781.839798562</v>
       </c>
       <c r="I34">
-        <v>17697.76191172511</v>
+        <v>290031.4309417382</v>
       </c>
       <c r="J34">
-        <v>47590508.12736341</v>
+        <v>1213088142.669942</v>
       </c>
       <c r="K34">
-        <v>2556109.029679297</v>
+        <v>811243977.0118529</v>
       </c>
       <c r="L34">
-        <v>96392425.80472146</v>
+        <v>1583064001.679832</v>
       </c>
       <c r="M34">
-        <v>1006520648.864355</v>
+        <v>25596276268.48824</v>
       </c>
       <c r="N34">
-        <v>42231663.20739182</v>
+        <v>13536984693.20875</v>
       </c>
       <c r="O34">
-        <v>2353802334.259439</v>
+        <v>38574180315.25118</v>
       </c>
     </row>
     <row r="35">
@@ -2197,40 +2197,40 @@
         </is>
       </c>
       <c r="D35">
-        <v>987.7020398794101</v>
+        <v>25825.26008393151</v>
       </c>
       <c r="E35">
-        <v>65.24137561308976</v>
+        <v>17298.59956728726</v>
       </c>
       <c r="F35">
-        <v>1998.590072062647</v>
+        <v>33716.02634955521</v>
       </c>
       <c r="G35">
-        <v>1953.322719676569</v>
+        <v>50968.66385324585</v>
       </c>
       <c r="H35">
-        <v>100.8426409992467</v>
+        <v>26988.50916550196</v>
       </c>
       <c r="I35">
-        <v>4563.597512850202</v>
+        <v>76857.10431966322</v>
       </c>
       <c r="J35">
-        <v>14624904.10449442</v>
+        <v>382394626.0627751</v>
       </c>
       <c r="K35">
-        <v>966029.0487030187</v>
+        <v>256140363.7928228</v>
       </c>
       <c r="L35">
-        <v>29593123.19703162</v>
+        <v>499233202.1578622</v>
       </c>
       <c r="M35">
-        <v>259791921.7169836</v>
+        <v>6778832292.481697</v>
       </c>
       <c r="N35">
-        <v>13412071.25289981</v>
+        <v>3589471719.011761</v>
       </c>
       <c r="O35">
-        <v>606958469.2090769</v>
+        <v>10221994874.51521</v>
       </c>
     </row>
     <row r="36">
@@ -2250,40 +2250,40 @@
         </is>
       </c>
       <c r="D36">
-        <v>3968.233975973964</v>
+        <v>100852.5279115385</v>
       </c>
       <c r="E36">
-        <v>202.8770975627731</v>
+        <v>67163.10263595924</v>
       </c>
       <c r="F36">
-        <v>8041.789182934462</v>
+        <v>131816.1537456301</v>
       </c>
       <c r="G36">
-        <v>6873.101904068102</v>
+        <v>174723.6488214404</v>
       </c>
       <c r="H36">
-        <v>279.9875241173803</v>
+        <v>92053.92700647611</v>
       </c>
       <c r="I36">
-        <v>16082.8074622979</v>
+        <v>263710.738625097</v>
       </c>
       <c r="J36">
-        <v>58757640.48224651</v>
+        <v>1493323380.786147</v>
       </c>
       <c r="K36">
-        <v>3004001.183611978</v>
+        <v>994484060.7306439</v>
       </c>
       <c r="L36">
-        <v>119074772.4317104</v>
+        <v>1951801788.511545</v>
       </c>
       <c r="M36">
-        <v>914122553.2410576</v>
+        <v>23238245293.25157</v>
       </c>
       <c r="N36">
-        <v>37238340.70761158</v>
+        <v>12243172291.86132</v>
       </c>
       <c r="O36">
-        <v>2139013392.48562</v>
+        <v>35073528237.13789</v>
       </c>
     </row>
     <row r="37">
@@ -2303,40 +2303,40 @@
         </is>
       </c>
       <c r="D37">
-        <v>1645.673537469884</v>
+        <v>41455.11209731697</v>
       </c>
       <c r="E37">
-        <v>80.88788067733796</v>
+        <v>27589.79571270331</v>
       </c>
       <c r="F37">
-        <v>3332.155664217125</v>
+        <v>54189.00011407428</v>
       </c>
       <c r="G37">
-        <v>2261.808185058573</v>
+        <v>57091.00354380367</v>
       </c>
       <c r="H37">
-        <v>89.0799113376717</v>
+        <v>30072.90961081772</v>
       </c>
       <c r="I37">
-        <v>5288.39714871141</v>
+        <v>86164.28608842567</v>
       </c>
       <c r="J37">
-        <v>24367488.06931661</v>
+        <v>613825844.8249744</v>
       </c>
       <c r="K37">
-        <v>1197706.849189342</v>
+        <v>408522105.1179976</v>
       </c>
       <c r="L37">
-        <v>49339228.9200629</v>
+        <v>802376524.689095</v>
       </c>
       <c r="M37">
-        <v>300820488.6127902</v>
+        <v>7593103471.325889</v>
       </c>
       <c r="N37">
-        <v>11847628.20791034</v>
+        <v>3999696978.238757</v>
       </c>
       <c r="O37">
-        <v>703356820.7786176</v>
+        <v>11459850049.76061</v>
       </c>
     </row>
     <row r="38">
@@ -2356,40 +2356,40 @@
         </is>
       </c>
       <c r="D38">
-        <v>4573.798369777716</v>
+        <v>112000.3190555502</v>
       </c>
       <c r="E38">
-        <v>167.0660242072252</v>
+        <v>74198.84247421486</v>
       </c>
       <c r="F38">
-        <v>9253.603057028466</v>
+        <v>146440.7041633448</v>
       </c>
       <c r="G38">
-        <v>5576.276044537542</v>
+        <v>136340.2363290754</v>
       </c>
       <c r="H38">
-        <v>158.7570029529858</v>
+        <v>71439.93750265797</v>
       </c>
       <c r="I38">
-        <v>13026.67436171904</v>
+        <v>205855.4223423052</v>
       </c>
       <c r="J38">
-        <v>67724232.46129867</v>
+        <v>1658388724.255534</v>
       </c>
       <c r="K38">
-        <v>2473746.620436382</v>
+        <v>1098662260.515692</v>
       </c>
       <c r="L38">
-        <v>137018100.4654205</v>
+        <v>2168347506.546649</v>
       </c>
       <c r="M38">
-        <v>741644713.923493</v>
+        <v>18133251431.76702</v>
       </c>
       <c r="N38">
-        <v>21114681.39274712</v>
+        <v>9501511687.85351</v>
       </c>
       <c r="O38">
-        <v>1732547690.108632</v>
+        <v>27378771171.52659</v>
       </c>
     </row>
     <row r="39">
@@ -2409,40 +2409,40 @@
         </is>
       </c>
       <c r="D39">
-        <v>3535.693014630197</v>
+        <v>83091.92625906903</v>
       </c>
       <c r="E39">
-        <v>91.4188366895562</v>
+        <v>55180.93133155227</v>
       </c>
       <c r="F39">
-        <v>7137.909023429165</v>
+        <v>108344.4577834867</v>
       </c>
       <c r="G39">
-        <v>3021.01949723733</v>
+        <v>71030.15189528653</v>
       </c>
       <c r="H39">
-        <v>62.20526915549353</v>
+        <v>37303.03285879327</v>
       </c>
       <c r="I39">
-        <v>7042.740831356094</v>
+        <v>106970.8381459508</v>
       </c>
       <c r="J39">
-        <v>52353006.46762938</v>
+        <v>1230342152.118032</v>
       </c>
       <c r="K39">
-        <v>1353638.71486226</v>
+        <v>817064050.2262948</v>
       </c>
       <c r="L39">
-        <v>105691018.9099156</v>
+        <v>1604256386.400079</v>
       </c>
       <c r="M39">
-        <v>401795593.1325649</v>
+        <v>9447010202.073109</v>
       </c>
       <c r="N39">
-        <v>8273300.797680639</v>
+        <v>4961303370.219505</v>
       </c>
       <c r="O39">
-        <v>936684530.5703604</v>
+        <v>14227121473.41146</v>
       </c>
     </row>
     <row r="40">
@@ -2462,40 +2462,40 @@
         </is>
       </c>
       <c r="D40">
-        <v>2635.607819207387</v>
+        <v>66523.00650025051</v>
       </c>
       <c r="E40">
-        <v>133.8311871921268</v>
+        <v>44049.25396657803</v>
       </c>
       <c r="F40">
-        <v>5334.512462786269</v>
+        <v>87148.91705033979</v>
       </c>
       <c r="G40">
-        <v>1841.013151513495</v>
+        <v>45999.75675534475</v>
       </c>
       <c r="H40">
-        <v>68.52280192495255</v>
+        <v>24057.59032581822</v>
       </c>
       <c r="I40">
-        <v>4301.786815494082</v>
+        <v>69604.30389649121</v>
       </c>
       <c r="J40">
-        <v>39025444.97900375</v>
+        <v>985006157.2492068</v>
       </c>
       <c r="K40">
-        <v>1981638.388753821</v>
+        <v>652237303.483122</v>
       </c>
       <c r="L40">
-        <v>78988126.03647611</v>
+        <v>1290414014.764376</v>
       </c>
       <c r="M40">
-        <v>244854749.1512948</v>
+        <v>6117967648.460852</v>
       </c>
       <c r="N40">
-        <v>9113532.656018689</v>
+        <v>3199659513.333824</v>
       </c>
       <c r="O40">
-        <v>572137646.4607128</v>
+        <v>9257372418.233332</v>
       </c>
     </row>
     <row r="41">
@@ -2515,40 +2515,40 @@
         </is>
       </c>
       <c r="D41">
-        <v>2730.305635799707</v>
+        <v>66891.26738258103</v>
       </c>
       <c r="E41">
-        <v>111.8619978530942</v>
+        <v>44560.77015545658</v>
       </c>
       <c r="F41">
-        <v>5514.504297107477</v>
+        <v>87268.9271935774</v>
       </c>
       <c r="G41">
-        <v>871.897020360177</v>
+        <v>21561.50503879077</v>
       </c>
       <c r="H41">
-        <v>30.49400547677532</v>
+        <v>11394.69582507743</v>
       </c>
       <c r="I41">
-        <v>2033.477691415485</v>
+        <v>32453.98451928482</v>
       </c>
       <c r="J41">
-        <v>40427635.54928621</v>
+        <v>990458996.1338766</v>
       </c>
       <c r="K41">
-        <v>1656340.602210766</v>
+        <v>659811323.6918443</v>
       </c>
       <c r="L41">
-        <v>81653265.12727034</v>
+        <v>1292191004.955306</v>
       </c>
       <c r="M41">
-        <v>115962303.7079035</v>
+        <v>2867680170.159173</v>
       </c>
       <c r="N41">
-        <v>4055702.728411118</v>
+        <v>1515494544.735298</v>
       </c>
       <c r="O41">
-        <v>270452532.9582595</v>
+        <v>4316379941.06488</v>
       </c>
     </row>
     <row r="42">
@@ -2568,40 +2568,40 @@
         </is>
       </c>
       <c r="D42">
-        <v>1005.945474058246</v>
+        <v>26820.13778632225</v>
       </c>
       <c r="E42">
-        <v>73.20246357788145</v>
+        <v>17864.07810041781</v>
       </c>
       <c r="F42">
-        <v>2039.936758553812</v>
+        <v>35142.50177423227</v>
       </c>
       <c r="G42">
-        <v>146.0007038745368</v>
+        <v>3881.786037048852</v>
       </c>
       <c r="H42">
-        <v>7.98812524120047</v>
+        <v>2040.947869825431</v>
       </c>
       <c r="I42">
-        <v>342.0753171333703</v>
+        <v>5877.308827989244</v>
       </c>
       <c r="J42">
-        <v>14895034.63438045</v>
+        <v>397125780.2020734</v>
       </c>
       <c r="K42">
-        <v>1083908.87819769</v>
+        <v>264513404.4328864</v>
       </c>
       <c r="L42">
-        <v>30205343.5839063</v>
+        <v>520355023.7710565</v>
       </c>
       <c r="M42">
-        <v>19418093.6153134</v>
+        <v>516277542.9274974</v>
       </c>
       <c r="N42">
-        <v>1062420.657079663</v>
+        <v>271446066.6867824</v>
       </c>
       <c r="O42">
-        <v>45496017.17873824</v>
+        <v>781682074.1225694</v>
       </c>
     </row>
     <row r="43">
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="D43">
-        <v>1132.077078831487</v>
+        <v>28450.60571045469</v>
       </c>
       <c r="E43">
-        <v>59.67889344614661</v>
+        <v>19094.9728353892</v>
       </c>
       <c r="F43">
-        <v>2288.532401310512</v>
+        <v>37056.82778553379</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2639,13 +2639,13 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>16762665.30625782</v>
+        <v>421268118.7547022</v>
       </c>
       <c r="K43">
-        <v>883665.3752570929</v>
+        <v>282739262.7736079</v>
       </c>
       <c r="L43">
-        <v>33886299.26620474</v>
+        <v>548700449.0203989</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -2674,40 +2674,40 @@
         </is>
       </c>
       <c r="D44">
-        <v>185.5870583814834</v>
+        <v>2128.375713614892</v>
       </c>
       <c r="E44">
-        <v>-5.535978762212632</v>
+        <v>1414.019900652351</v>
       </c>
       <c r="F44">
-        <v>349.9266971862376</v>
+        <v>2785.523946170959</v>
       </c>
       <c r="G44">
-        <v>782.4662083830236</v>
+        <v>8981.389515391289</v>
       </c>
       <c r="H44">
-        <v>-17.46372473725598</v>
+        <v>4441.240626705007</v>
       </c>
       <c r="I44">
-        <v>1873.352921200762</v>
+        <v>14923.53366169142</v>
       </c>
       <c r="J44">
-        <v>13956332.37734592</v>
+        <v>160055982.0395537</v>
       </c>
       <c r="K44">
-        <v>-416311.1388971531</v>
+        <v>106335710.5489576</v>
       </c>
       <c r="L44">
-        <v>26314837.55510223</v>
+        <v>209474186.2760023</v>
       </c>
       <c r="M44">
-        <v>104068005.7149421</v>
+        <v>1194524805.547041</v>
       </c>
       <c r="N44">
-        <v>-2322675.390055045</v>
+        <v>590685003.351766</v>
       </c>
       <c r="O44">
-        <v>249155938.5197013</v>
+        <v>1984829977.00496</v>
       </c>
     </row>
     <row r="45">
@@ -2727,40 +2727,40 @@
         </is>
       </c>
       <c r="D45">
-        <v>214.7218666703611</v>
+        <v>2430.573754948357</v>
       </c>
       <c r="E45">
-        <v>-6.112084339133804</v>
+        <v>1610.514678030846</v>
       </c>
       <c r="F45">
-        <v>403.5188930345048</v>
+        <v>3183.793842164457</v>
       </c>
       <c r="G45">
-        <v>815.7964939534165</v>
+        <v>9243.354828002579</v>
       </c>
       <c r="H45">
-        <v>-17.36296331082999</v>
+        <v>4557.917632022699</v>
       </c>
       <c r="I45">
-        <v>1946.870141027779</v>
+        <v>15373.15614660167</v>
       </c>
       <c r="J45">
-        <v>16147299.09547784</v>
+        <v>182781576.9458714</v>
       </c>
       <c r="K45">
-        <v>-459634.8543872013</v>
+        <v>121112314.3025976</v>
       </c>
       <c r="L45">
-        <v>30345024.2750878</v>
+        <v>239424480.7246093</v>
       </c>
       <c r="M45">
-        <v>108500933.6958044</v>
+        <v>1229366192.124343</v>
       </c>
       <c r="N45">
-        <v>-2309274.120340388</v>
+        <v>606203045.059019</v>
       </c>
       <c r="O45">
-        <v>258933728.7566946</v>
+        <v>2044629767.498022</v>
       </c>
     </row>
     <row r="46">
@@ -2780,40 +2780,40 @@
         </is>
       </c>
       <c r="D46">
-        <v>288.8548853658369</v>
+        <v>3182.356856500297</v>
       </c>
       <c r="E46">
-        <v>-7.06956250938481</v>
+        <v>2110.512125927271</v>
       </c>
       <c r="F46">
-        <v>539.5834476896604</v>
+        <v>4160.952122089775</v>
       </c>
       <c r="G46">
-        <v>1024.036849148181</v>
+        <v>11271.32183546417</v>
       </c>
       <c r="H46">
-        <v>-18.5374980157874</v>
+        <v>5562.44983696561</v>
       </c>
       <c r="I46">
-        <v>2428.246980435859</v>
+        <v>18710.33948548563</v>
       </c>
       <c r="J46">
-        <v>21722176.23439629</v>
+        <v>239316417.9656779</v>
       </c>
       <c r="K46">
-        <v>-531638.1702682467</v>
+        <v>158712622.3818569</v>
       </c>
       <c r="L46">
-        <v>40577214.84971017</v>
+        <v>312907760.5332727</v>
       </c>
       <c r="M46">
-        <v>136196900.9367081</v>
+        <v>1499085804.116735</v>
       </c>
       <c r="N46">
-        <v>-2465487.236099725</v>
+        <v>739805828.3164262</v>
       </c>
       <c r="O46">
-        <v>322956848.3979693</v>
+        <v>2488475151.569588</v>
       </c>
     </row>
     <row r="47">
@@ -2833,40 +2833,40 @@
         </is>
       </c>
       <c r="D47">
-        <v>363.1262585033141</v>
+        <v>4233.108115012706</v>
       </c>
       <c r="E47">
-        <v>-11.57891682177796</v>
+        <v>2845.473307437681</v>
       </c>
       <c r="F47">
-        <v>685.807835483507</v>
+        <v>5516.337590803659</v>
       </c>
       <c r="G47">
-        <v>1114.426605967445</v>
+        <v>12984.6924723904</v>
       </c>
       <c r="H47">
-        <v>-26.4235735917678</v>
+        <v>6492.625970269779</v>
       </c>
       <c r="I47">
-        <v>2672.047284775119</v>
+        <v>21486.95713010003</v>
       </c>
       <c r="J47">
-        <v>27307457.76570769</v>
+        <v>318333963.357071</v>
       </c>
       <c r="K47">
-        <v>-870746.123914524</v>
+        <v>213982438.1926207</v>
       </c>
       <c r="L47">
-        <v>51573435.03619523</v>
+        <v>414834103.1660268</v>
       </c>
       <c r="M47">
-        <v>148218738.5936702</v>
+        <v>1726964098.827923</v>
       </c>
       <c r="N47">
-        <v>-3514335.287705118</v>
+        <v>863519254.0458806</v>
       </c>
       <c r="O47">
-        <v>355382288.8750909</v>
+        <v>2857765298.303304</v>
       </c>
     </row>
     <row r="48">
@@ -2886,40 +2886,40 @@
         </is>
       </c>
       <c r="D48">
-        <v>349.6400497426122</v>
+        <v>3997.632887269138</v>
       </c>
       <c r="E48">
-        <v>-10.27647781950786</v>
+        <v>2673.800218296326</v>
       </c>
       <c r="F48">
-        <v>657.3666085653582</v>
+        <v>5216.625167450964</v>
       </c>
       <c r="G48">
-        <v>1015.241773073071</v>
+        <v>11579.99558169079</v>
       </c>
       <c r="H48">
-        <v>-21.9729449426028</v>
+        <v>5761.568337677563</v>
       </c>
       <c r="I48">
-        <v>2422.189702103608</v>
+        <v>19187.06058491481</v>
       </c>
       <c r="J48">
-        <v>26293281.38069417</v>
+        <v>300625990.7555266</v>
       </c>
       <c r="K48">
-        <v>-772801.4085048118</v>
+        <v>201072450.2161024</v>
       </c>
       <c r="L48">
-        <v>49434626.33072349</v>
+        <v>392295429.2174788</v>
       </c>
       <c r="M48">
-        <v>135027155.8187184</v>
+        <v>1540139412.364875</v>
       </c>
       <c r="N48">
-        <v>-2922401.677366172</v>
+        <v>766288588.9111159</v>
       </c>
       <c r="O48">
-        <v>322151230.3797799</v>
+        <v>2551879057.793669</v>
       </c>
     </row>
     <row r="49">
@@ -2939,40 +2939,40 @@
         </is>
       </c>
       <c r="D49">
-        <v>601.2194305375543</v>
+        <v>7049.778664148803</v>
       </c>
       <c r="E49">
-        <v>-19.79348812783699</v>
+        <v>4719.84196179191</v>
       </c>
       <c r="F49">
-        <v>1137.737098147544</v>
+        <v>9205.374723572655</v>
       </c>
       <c r="G49">
-        <v>1476.834490251146</v>
+        <v>17280.52286903256</v>
       </c>
       <c r="H49">
-        <v>-35.85803250917881</v>
+        <v>8602.737484499537</v>
       </c>
       <c r="I49">
-        <v>3547.056796999222</v>
+        <v>28655.69835937288</v>
       </c>
       <c r="J49">
-        <v>45212302.39585465</v>
+        <v>530150405.3226538</v>
       </c>
       <c r="K49">
-        <v>-1488490.100701469</v>
+        <v>354936835.3687125</v>
       </c>
       <c r="L49">
-        <v>85558967.51779336</v>
+        <v>692253384.5873871</v>
       </c>
       <c r="M49">
-        <v>196418987.2034025</v>
+        <v>2298309541.58133</v>
       </c>
       <c r="N49">
-        <v>-4769118.323720782</v>
+        <v>1144164085.438438</v>
       </c>
       <c r="O49">
-        <v>471758554.0008965</v>
+        <v>3811207881.796593</v>
       </c>
     </row>
     <row r="50">
@@ -2992,40 +2992,40 @@
         </is>
       </c>
       <c r="D50">
-        <v>742.6712259895587</v>
+        <v>8450.50477382248</v>
       </c>
       <c r="E50">
-        <v>-21.45511446110956</v>
+        <v>5626.757634007604</v>
       </c>
       <c r="F50">
-        <v>1396.36199999997</v>
+        <v>11044.87641158799</v>
       </c>
       <c r="G50">
-        <v>1568.450096655249</v>
+        <v>17850.40308756479</v>
       </c>
       <c r="H50">
-        <v>-33.80006313611803</v>
+        <v>8844.806129313036</v>
       </c>
       <c r="I50">
-        <v>3744.157013211116</v>
+        <v>29622.35091703741</v>
       </c>
       <c r="J50">
-        <v>55849618.86564091</v>
+        <v>635486409.4962243</v>
       </c>
       <c r="K50">
-        <v>-1613446.062589898</v>
+        <v>423137800.8350056</v>
       </c>
       <c r="L50">
-        <v>105007818.7619977</v>
+        <v>830585751.0278291</v>
       </c>
       <c r="M50">
-        <v>208603862.8551481</v>
+        <v>2374103610.646117</v>
       </c>
       <c r="N50">
-        <v>-4495408.397103698</v>
+        <v>1176359215.198634</v>
       </c>
       <c r="O50">
-        <v>497972882.7570784</v>
+        <v>3939772671.965975</v>
       </c>
     </row>
     <row r="51">
@@ -3045,40 +3045,40 @@
         </is>
       </c>
       <c r="D51">
-        <v>814.880542888134</v>
+        <v>9201.153569779655</v>
       </c>
       <c r="E51">
-        <v>-22.52893429110872</v>
+        <v>6124.378832428379</v>
       </c>
       <c r="F51">
-        <v>1528.818449922504</v>
+        <v>12027.03986119458</v>
       </c>
       <c r="G51">
-        <v>1386.901596420276</v>
+        <v>15693.79088104586</v>
       </c>
       <c r="H51">
-        <v>-28.80338179807228</v>
+        <v>7776.988429756413</v>
       </c>
       <c r="I51">
-        <v>3305.11220718546</v>
+        <v>26041.67227945443</v>
       </c>
       <c r="J51">
-        <v>61279831.70573061</v>
+        <v>691935949.6009979</v>
       </c>
       <c r="K51">
-        <v>-1694198.387625668</v>
+        <v>460559412.5774464</v>
       </c>
       <c r="L51">
-        <v>114968676.2526224</v>
+        <v>904445424.6016954</v>
       </c>
       <c r="M51">
-        <v>184457912.3238967</v>
+        <v>2087274187.1791</v>
       </c>
       <c r="N51">
-        <v>-3830849.779143613</v>
+        <v>1034339461.157603</v>
       </c>
       <c r="O51">
-        <v>439579923.5556661</v>
+        <v>3463542413.167439</v>
       </c>
     </row>
     <row r="52">
@@ -3098,40 +3098,40 @@
         </is>
       </c>
       <c r="D52">
-        <v>1095.890216667946</v>
+        <v>12021.31192377861</v>
       </c>
       <c r="E52">
-        <v>-25.72924629957917</v>
+        <v>7964.134402776361</v>
       </c>
       <c r="F52">
-        <v>2046.207897595962</v>
+        <v>15717.7806970149</v>
       </c>
       <c r="G52">
-        <v>1648.523494912906</v>
+        <v>18055.03716905628</v>
       </c>
       <c r="H52">
-        <v>-28.5523138745477</v>
+        <v>8899.057477914277</v>
       </c>
       <c r="I52">
-        <v>3906.707776423496</v>
+        <v>29973.21205235752</v>
       </c>
       <c r="J52">
-        <v>82412040.18364629</v>
+        <v>904014677.980077</v>
       </c>
       <c r="K52">
-        <v>-1934865.050974649</v>
+        <v>598910871.2231845</v>
       </c>
       <c r="L52">
-        <v>153876880.1071142</v>
+        <v>1181992826.196218</v>
       </c>
       <c r="M52">
-        <v>219253624.8234166</v>
+        <v>2401319943.484485</v>
       </c>
       <c r="N52">
-        <v>-3797457.745314843</v>
+        <v>1183574644.562599</v>
       </c>
       <c r="O52">
-        <v>519592134.264325</v>
+        <v>3986437202.96355</v>
       </c>
     </row>
     <row r="53">
@@ -3151,40 +3151,40 @@
         </is>
       </c>
       <c r="D53">
-        <v>1106.962372774894</v>
+        <v>11642.2266278658</v>
       </c>
       <c r="E53">
-        <v>-19.9666257142896</v>
+        <v>7727.457091810651</v>
       </c>
       <c r="F53">
-        <v>2045.473937621291</v>
+        <v>15184.20964974746</v>
       </c>
       <c r="G53">
-        <v>1204.702430610568</v>
+        <v>12675.16056365996</v>
       </c>
       <c r="H53">
-        <v>-16.23555848321427</v>
+        <v>6258.305934046525</v>
       </c>
       <c r="I53">
-        <v>2826.629506820803</v>
+        <v>20993.11578436348</v>
       </c>
       <c r="J53">
-        <v>83244677.39504485</v>
+        <v>875507084.6421368</v>
       </c>
       <c r="K53">
-        <v>-1501510.220340292</v>
+        <v>581112500.7612549</v>
       </c>
       <c r="L53">
-        <v>153821685.5830586</v>
+        <v>1141867749.870657</v>
       </c>
       <c r="M53">
-        <v>160225423.2712055</v>
+        <v>1685796354.966775</v>
       </c>
       <c r="N53">
-        <v>-2159329.278267498</v>
+        <v>832354689.2281878</v>
       </c>
       <c r="O53">
-        <v>375941724.4071668</v>
+        <v>2792084399.320343</v>
       </c>
     </row>
     <row r="54">
@@ -3204,40 +3204,40 @@
         </is>
       </c>
       <c r="D54">
-        <v>398.5299843281929</v>
+        <v>4470.391851826272</v>
       </c>
       <c r="E54">
-        <v>-10.84315553427804</v>
+        <v>2956.575184050956</v>
       </c>
       <c r="F54">
-        <v>747.8256084956678</v>
+        <v>5857.299181337289</v>
       </c>
       <c r="G54">
-        <v>365.5939730093746</v>
+        <v>4066.884565096484</v>
       </c>
       <c r="H54">
-        <v>-7.107783694357364</v>
+        <v>1998.744477088951</v>
       </c>
       <c r="I54">
-        <v>869.512464597321</v>
+        <v>6767.031518708039</v>
       </c>
       <c r="J54">
-        <v>29969853.35146445</v>
+        <v>336177937.649187</v>
       </c>
       <c r="K54">
-        <v>-815416.1393332428</v>
+        <v>222337410.415816</v>
       </c>
       <c r="L54">
-        <v>56237233.58448276</v>
+        <v>440474755.7357454</v>
       </c>
       <c r="M54">
-        <v>48623998.41024682</v>
+        <v>540895647.1578324</v>
       </c>
       <c r="N54">
-        <v>-945335.2313495295</v>
+        <v>265833015.4528305</v>
       </c>
       <c r="O54">
-        <v>115645157.7914437</v>
+        <v>900015191.9881692</v>
       </c>
     </row>
     <row r="55">
@@ -3257,40 +3257,40 @@
         </is>
       </c>
       <c r="D55">
-        <v>303.8251348119413</v>
+        <v>3361.404081900295</v>
       </c>
       <c r="E55">
-        <v>-7.417590271593657</v>
+        <v>2245.079840475632</v>
       </c>
       <c r="F55">
-        <v>567.8345574952183</v>
+        <v>4381.202233862354</v>
       </c>
       <c r="G55">
-        <v>140.5103891458834</v>
+        <v>1564.290121345929</v>
       </c>
       <c r="H55">
-        <v>-2.641806284275499</v>
+        <v>778.3596799814077</v>
       </c>
       <c r="I55">
-        <v>333.8510029984295</v>
+        <v>2588.053468758002</v>
       </c>
       <c r="J55">
-        <v>22847953.96299284</v>
+        <v>252780948.362984</v>
       </c>
       <c r="K55">
-        <v>-557810.206014114</v>
+        <v>168832249.0836083</v>
       </c>
       <c r="L55">
-        <v>42701726.55819789</v>
+        <v>329470789.1886827</v>
       </c>
       <c r="M55">
-        <v>18687881.75640249</v>
+        <v>208050586.1390085</v>
       </c>
       <c r="N55">
-        <v>-351360.2358086414</v>
+        <v>103521837.4375272</v>
       </c>
       <c r="O55">
-        <v>44402183.39879113</v>
+        <v>344211111.3448143</v>
       </c>
     </row>
     <row r="56">
@@ -3310,40 +3310,40 @@
         </is>
       </c>
       <c r="D56">
-        <v>17.97861151488044</v>
+        <v>215.3181879619881</v>
       </c>
       <c r="E56">
-        <v>-0.6557477665686496</v>
+        <v>143.5367294046864</v>
       </c>
       <c r="F56">
-        <v>34.19631279876591</v>
+        <v>282.0090425013231</v>
       </c>
       <c r="G56">
-        <v>3.739778493585825</v>
+        <v>44.62966472731185</v>
       </c>
       <c r="H56">
-        <v>-0.09995353718723382</v>
+        <v>22.0759193371762</v>
       </c>
       <c r="I56">
-        <v>9.028380855050495</v>
+        <v>74.29139380149944</v>
       </c>
       <c r="J56">
-        <v>1352009.564530523</v>
+        <v>16192143.05292945</v>
       </c>
       <c r="K56">
-        <v>-49312.88779372896</v>
+        <v>10794105.58796182</v>
       </c>
       <c r="L56">
-        <v>2571596.918779992</v>
+        <v>21207362.005142</v>
       </c>
       <c r="M56">
-        <v>497390.5396469147</v>
+        <v>5935745.408732476</v>
       </c>
       <c r="N56">
-        <v>-13293.8204459021</v>
+        <v>2936097.271844435</v>
       </c>
       <c r="O56">
-        <v>1200774.653721716</v>
+        <v>9880755.375599425</v>
       </c>
     </row>
     <row r="57">
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="D57">
-        <v>10.75729720158576</v>
+        <v>119.442332009186</v>
       </c>
       <c r="E57">
-        <v>-0.2716935592398143</v>
+        <v>80.11059567183932</v>
       </c>
       <c r="F57">
-        <v>20.07418993307511</v>
+        <v>155.5125938791939</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -3381,13 +3381,13 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <v>808959.506856451</v>
+        <v>8982182.809422789</v>
       </c>
       <c r="K57">
-        <v>-20431.62734839327</v>
+        <v>6024396.905117994</v>
       </c>
       <c r="L57">
-        <v>1509599.157157182</v>
+        <v>11694702.57230924</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -3628,40 +3628,40 @@
         </is>
       </c>
       <c r="D62">
-        <v>78.81472354754702</v>
+        <v>331.0015880058301</v>
       </c>
       <c r="E62">
-        <v>57.68380984517101</v>
+        <v>222.0449792370445</v>
       </c>
       <c r="F62">
-        <v>97.84732847367499</v>
+        <v>431.5625089129514</v>
       </c>
       <c r="G62">
-        <v>668.2697769540392</v>
+        <v>2808.20033348626</v>
       </c>
       <c r="H62">
-        <v>392.1833946153554</v>
+        <v>1510.137014015815</v>
       </c>
       <c r="I62">
-        <v>944.8773597848389</v>
+        <v>4170.15855527352</v>
       </c>
       <c r="J62">
-        <v>1327161.129817144</v>
+        <v>5573735.740430183</v>
       </c>
       <c r="K62">
-        <v>971337.6739828344</v>
+        <v>3739015.405372587</v>
       </c>
       <c r="L62">
-        <v>1647651.164168213</v>
+        <v>7267081.087585175</v>
       </c>
       <c r="M62">
-        <v>88879880.33488722</v>
+        <v>373490644.3536726</v>
       </c>
       <c r="N62">
-        <v>52160391.48384228</v>
+        <v>200848222.8641034</v>
       </c>
       <c r="O62">
-        <v>125668688.8513836</v>
+        <v>554631087.8513781</v>
       </c>
     </row>
     <row r="63">
@@ -3681,40 +3681,40 @@
         </is>
       </c>
       <c r="D63">
-        <v>64.02498018495631</v>
+        <v>268.4861584062957</v>
       </c>
       <c r="E63">
-        <v>46.83274856631898</v>
+        <v>180.1774644685256</v>
       </c>
       <c r="F63">
-        <v>79.52992545629662</v>
+        <v>350.2929610619991</v>
       </c>
       <c r="G63">
-        <v>458.6403612130541</v>
+        <v>1922.593870246065</v>
       </c>
       <c r="H63">
-        <v>268.927549000832</v>
+        <v>1033.873116864379</v>
       </c>
       <c r="I63">
-        <v>648.9200959470624</v>
+        <v>2857.529851682409</v>
       </c>
       <c r="J63">
-        <v>1078116.641334481</v>
+        <v>4521038.421403624</v>
       </c>
       <c r="K63">
-        <v>788616.6531082448</v>
+        <v>3034008.324185501</v>
       </c>
       <c r="L63">
-        <v>1339204.41475858</v>
+        <v>5898583.17132301</v>
       </c>
       <c r="M63">
-        <v>60999168.0413362</v>
+        <v>255704984.7427267</v>
       </c>
       <c r="N63">
-        <v>35767364.01711066</v>
+        <v>137505124.5429624</v>
       </c>
       <c r="O63">
-        <v>86306372.7609593</v>
+        <v>380051470.2737604</v>
       </c>
     </row>
     <row r="64">
@@ -3734,40 +3734,40 @@
         </is>
       </c>
       <c r="D64">
-        <v>190.8241947023318</v>
+        <v>797.3706795531649</v>
       </c>
       <c r="E64">
-        <v>139.1735566697076</v>
+        <v>530.9640887438489</v>
       </c>
       <c r="F64">
-        <v>237.203009291265</v>
+        <v>1042.173511784846</v>
       </c>
       <c r="G64">
-        <v>1217.820874383868</v>
+        <v>5089.734120992931</v>
       </c>
       <c r="H64">
-        <v>712.200900985605</v>
+        <v>2717.727125781523</v>
       </c>
       <c r="I64">
-        <v>1724.174030003477</v>
+        <v>7576.681997972503</v>
       </c>
       <c r="J64">
-        <v>3213288.614592566</v>
+        <v>13426924.87299572</v>
       </c>
       <c r="K64">
-        <v>2343543.52076121</v>
+        <v>8940904.290357661</v>
       </c>
       <c r="L64">
-        <v>3994261.473455612</v>
+        <v>17549159.76494507</v>
       </c>
       <c r="M64">
-        <v>161970176.2930545</v>
+        <v>676934638.0920599</v>
       </c>
       <c r="N64">
-        <v>94722719.83108547</v>
+        <v>361457707.7289426</v>
       </c>
       <c r="O64">
-        <v>229315145.9904624</v>
+        <v>1007698705.730343</v>
       </c>
     </row>
     <row r="65">
@@ -3787,40 +3787,40 @@
         </is>
       </c>
       <c r="D65">
-        <v>125.8624389674875</v>
+        <v>531.5134489435633</v>
       </c>
       <c r="E65">
-        <v>91.69998716402647</v>
+        <v>353.7403815184295</v>
       </c>
       <c r="F65">
-        <v>156.5641523631771</v>
+        <v>694.7799943065845</v>
       </c>
       <c r="G65">
-        <v>643.6292795387175</v>
+        <v>2716.41367961149</v>
       </c>
       <c r="H65">
-        <v>376.1156095775093</v>
+        <v>1450.320617145016</v>
       </c>
       <c r="I65">
-        <v>911.7453259666571</v>
+        <v>4043.577876188424</v>
       </c>
       <c r="J65">
-        <v>2119397.609773523</v>
+        <v>8950154.966760663</v>
       </c>
       <c r="K65">
-        <v>1544136.083855041</v>
+        <v>5956634.284388828</v>
       </c>
       <c r="L65">
-        <v>2636383.76164354</v>
+        <v>11699400.3241286</v>
       </c>
       <c r="M65">
-        <v>85602694.17864943</v>
+        <v>361283019.3883281</v>
       </c>
       <c r="N65">
-        <v>50023376.07380874</v>
+        <v>192892642.0802871</v>
       </c>
       <c r="O65">
-        <v>121262128.3535654</v>
+        <v>537795857.5330604</v>
       </c>
     </row>
     <row r="66">
@@ -3840,40 +3840,40 @@
         </is>
       </c>
       <c r="D66">
-        <v>1007.667677535077</v>
+        <v>4224.229452115431</v>
       </c>
       <c r="E66">
-        <v>735.8342803088747</v>
+        <v>2802.87766753775</v>
       </c>
       <c r="F66">
-        <v>1250.08694930004</v>
+        <v>5520.074890444685</v>
       </c>
       <c r="G66">
-        <v>4277.480678106011</v>
+        <v>17937.84918539585</v>
       </c>
       <c r="H66">
-        <v>2504.723141027483</v>
+        <v>9541.387696151751</v>
       </c>
       <c r="I66">
-        <v>6043.401772612404</v>
+        <v>26697.50238566957</v>
       </c>
       <c r="J66">
-        <v>16968116.02201313</v>
+        <v>71131799.7441719</v>
       </c>
       <c r="K66">
-        <v>12390713.44612116</v>
+        <v>47197657.04366823</v>
       </c>
       <c r="L66">
-        <v>21050214.13926338</v>
+        <v>92952541.08019832</v>
       </c>
       <c r="M66">
-        <v>568904930.1880994</v>
+        <v>2385733941.657649</v>
       </c>
       <c r="N66">
-        <v>333128177.7566552</v>
+        <v>1269004563.588183</v>
       </c>
       <c r="O66">
-        <v>803772435.7574497</v>
+        <v>3550767817.294052</v>
       </c>
     </row>
     <row r="67">
@@ -3893,40 +3893,40 @@
         </is>
       </c>
       <c r="D67">
-        <v>749.55045843161</v>
+        <v>3213.104765336501</v>
       </c>
       <c r="E67">
-        <v>550.0261126982699</v>
+        <v>2136.07997992664</v>
       </c>
       <c r="F67">
-        <v>927.1596598372792</v>
+        <v>4187.496807979571</v>
       </c>
       <c r="G67">
-        <v>2227.418887266396</v>
+        <v>9546.749315197838</v>
       </c>
       <c r="H67">
-        <v>1310.108147700849</v>
+        <v>5087.470489688612</v>
       </c>
       <c r="I67">
-        <v>3138.79198286973</v>
+        <v>14173.07169245878</v>
       </c>
       <c r="J67">
-        <v>12621680.16952988</v>
+        <v>54105471.14350144</v>
       </c>
       <c r="K67">
-        <v>9261889.711726168</v>
+        <v>35969450.7819847</v>
       </c>
       <c r="L67">
-        <v>15612441.51199994</v>
+        <v>70513258.74956796</v>
       </c>
       <c r="M67">
-        <v>296246712.0064307</v>
+        <v>1269717658.921312</v>
       </c>
       <c r="N67">
-        <v>174244383.6442129</v>
+        <v>676633575.1285855</v>
       </c>
       <c r="O67">
-        <v>417459333.721674</v>
+        <v>1885018535.097018</v>
       </c>
     </row>
     <row r="68">
@@ -3946,40 +3946,40 @@
         </is>
       </c>
       <c r="D68">
-        <v>3071.551786957531</v>
+        <v>12786.16529131855</v>
       </c>
       <c r="E68">
-        <v>2233.183554188456</v>
+        <v>8478.339629470836</v>
       </c>
       <c r="F68">
-        <v>3823.469986871721</v>
+        <v>16747.85394632648</v>
       </c>
       <c r="G68">
-        <v>7280.279752357135</v>
+        <v>30328.25165285584</v>
       </c>
       <c r="H68">
-        <v>4243.753632308356</v>
+        <v>16097.74824799975</v>
       </c>
       <c r="I68">
-        <v>10319.41558593031</v>
+        <v>45254.67698983937</v>
       </c>
       <c r="J68">
-        <v>51721860.54057793</v>
+        <v>215306237.3405128</v>
       </c>
       <c r="K68">
-        <v>37604577.8689794</v>
+        <v>142766761.0206592</v>
       </c>
       <c r="L68">
-        <v>64383411.1089329</v>
+        <v>282017112.6021909</v>
       </c>
       <c r="M68">
-        <v>968277207.063499</v>
+        <v>4033657469.829826</v>
       </c>
       <c r="N68">
-        <v>564419233.0970113</v>
+        <v>2141000516.983967</v>
       </c>
       <c r="O68">
-        <v>1372482272.928731</v>
+        <v>6018872039.648636</v>
       </c>
     </row>
     <row r="69">
@@ -3999,40 +3999,40 @@
         </is>
       </c>
       <c r="D69">
-        <v>1986.735739145131</v>
+        <v>8430.382120382201</v>
       </c>
       <c r="E69">
-        <v>1452.898277422683</v>
+        <v>5604.714553814894</v>
       </c>
       <c r="F69">
-        <v>2463.422558519686</v>
+        <v>11006.80360384436</v>
       </c>
       <c r="G69">
-        <v>2069.944631328704</v>
+        <v>8760.212956570698</v>
       </c>
       <c r="H69">
-        <v>1216.812302346526</v>
+        <v>4687.710678858264</v>
       </c>
       <c r="I69">
-        <v>2919.511358320763</v>
+        <v>13009.25456062023</v>
       </c>
       <c r="J69">
-        <v>33454643.11146489</v>
+        <v>141959204.5251159</v>
       </c>
       <c r="K69">
-        <v>24465354.09352059</v>
+        <v>94377788.37168917</v>
       </c>
       <c r="L69">
-        <v>41481572.46291297</v>
+        <v>185343565.8851351</v>
       </c>
       <c r="M69">
-        <v>275302635.9667175</v>
+        <v>1165108323.223903</v>
       </c>
       <c r="N69">
-        <v>161836036.2120879</v>
+        <v>623465520.2881491</v>
       </c>
       <c r="O69">
-        <v>388295010.6566615</v>
+        <v>1730230856.56249</v>
       </c>
     </row>
     <row r="70">
@@ -4052,40 +4052,40 @@
         </is>
       </c>
       <c r="D70">
-        <v>3941.085840300363</v>
+        <v>16439.42729134161</v>
       </c>
       <c r="E70">
-        <v>2856.358363443716</v>
+        <v>10942.20471982914</v>
       </c>
       <c r="F70">
-        <v>4923.021060903316</v>
+        <v>21548.42526245123</v>
       </c>
       <c r="G70">
-        <v>1846.768564266849</v>
+        <v>7657.868833340328</v>
       </c>
       <c r="H70">
-        <v>1072.867857460177</v>
+        <v>4080.242380342541</v>
       </c>
       <c r="I70">
-        <v>2626.754013495045</v>
+        <v>11436.68958623405</v>
       </c>
       <c r="J70">
-        <v>66363944.46481781</v>
+        <v>276823516.1589017</v>
       </c>
       <c r="K70">
-        <v>48098218.48202874</v>
+        <v>184255785.2772028</v>
       </c>
       <c r="L70">
-        <v>82898751.64455095</v>
+        <v>362853932.9944159</v>
       </c>
       <c r="M70">
-        <v>245620219.0474909</v>
+        <v>1018496554.834264</v>
       </c>
       <c r="N70">
-        <v>142691425.0422035</v>
+        <v>542672236.5855579</v>
       </c>
       <c r="O70">
-        <v>349358283.7948411</v>
+        <v>1521079714.969129</v>
       </c>
     </row>
     <row r="71">
@@ -4105,13 +4105,13 @@
         </is>
       </c>
       <c r="D71">
-        <v>2273.320685652679</v>
+        <v>9736.133270505154</v>
       </c>
       <c r="E71">
-        <v>1665.015368791826</v>
+        <v>6538.02393589133</v>
       </c>
       <c r="F71">
-        <v>2822.755760294472</v>
+        <v>12685.17327028729</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -4123,13 +4123,13 @@
         <v>0</v>
       </c>
       <c r="J71">
-        <v>38280447.02570545</v>
+        <v>163946748.1420363</v>
       </c>
       <c r="K71">
-        <v>28037193.79508553</v>
+        <v>110093785.0564743</v>
       </c>
       <c r="L71">
-        <v>47532384.24759857</v>
+        <v>213605632.6983677</v>
       </c>
       <c r="M71">
         <v>0</v>
@@ -4158,22 +4158,22 @@
         </is>
       </c>
       <c r="D72">
-        <v>16392.98252007961</v>
+        <v>117449.9592111887</v>
       </c>
       <c r="E72">
-        <v>12083.57435196264</v>
+        <v>78047.47138210885</v>
       </c>
       <c r="F72">
-        <v>19901.29427048995</v>
+        <v>153718.8328017704</v>
       </c>
       <c r="G72">
-        <v>85194.39776882058</v>
+        <v>610859.5665333228</v>
       </c>
       <c r="H72">
-        <v>38846.04935218017</v>
+        <v>251144.9353675141</v>
       </c>
       <c r="I72">
-        <v>158057.7888454811</v>
+        <v>1221676.079039337</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4185,13 +4185,13 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>11330854903.25314</v>
+        <v>81244322348.93193</v>
       </c>
       <c r="N72">
-        <v>5166524563.839963</v>
+        <v>33402276403.87937</v>
       </c>
       <c r="O72">
-        <v>21021685916.44898</v>
+        <v>162482918512.2319</v>
       </c>
     </row>
     <row r="73">
@@ -4211,22 +4211,22 @@
         </is>
       </c>
       <c r="D73">
-        <v>7110.117771149636</v>
+        <v>50308.67808479814</v>
       </c>
       <c r="E73">
-        <v>5254.831696050213</v>
+        <v>33333.13492151527</v>
       </c>
       <c r="F73">
-        <v>8626.329747679581</v>
+        <v>65898.71406351426</v>
       </c>
       <c r="G73">
-        <v>33356.93025795947</v>
+        <v>236196.5542037221</v>
       </c>
       <c r="H73">
-        <v>15248.17875289934</v>
+        <v>96809.01678436036</v>
       </c>
       <c r="I73">
-        <v>61843.78796162854</v>
+        <v>472796.638263986</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4238,13 +4238,13 @@
         <v>0</v>
       </c>
       <c r="M73">
-        <v>4436471724.308609</v>
+        <v>31414141709.09504</v>
       </c>
       <c r="N73">
-        <v>2028007774.135612</v>
+        <v>12875599232.31993</v>
       </c>
       <c r="O73">
-        <v>8225223798.896596</v>
+        <v>62881952889.11015</v>
       </c>
     </row>
     <row r="74">
@@ -4264,22 +4264,22 @@
         </is>
       </c>
       <c r="D74">
-        <v>18417.76191922239</v>
+        <v>127469.0889507604</v>
       </c>
       <c r="E74">
-        <v>13663.69636938972</v>
+        <v>84524.38052291665</v>
       </c>
       <c r="F74">
-        <v>22307.72267598314</v>
+        <v>166669.4613428348</v>
       </c>
       <c r="G74">
-        <v>80496.16838772802</v>
+        <v>556656.0359584261</v>
       </c>
       <c r="H74">
-        <v>36944.60240248086</v>
+        <v>228319.4919124387</v>
       </c>
       <c r="I74">
-        <v>148970.5989018823</v>
+        <v>1112170.167893</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4291,13 +4291,13 @@
         <v>0</v>
       </c>
       <c r="M74">
-        <v>10705990395.56783</v>
+        <v>74035252782.47067</v>
       </c>
       <c r="N74">
-        <v>4913632119.529954</v>
+        <v>30366492424.35435</v>
       </c>
       <c r="O74">
-        <v>19813089653.95035</v>
+        <v>147918632329.769</v>
       </c>
     </row>
     <row r="75">
@@ -4317,22 +4317,22 @@
         </is>
       </c>
       <c r="D75">
-        <v>6872.920857533825</v>
+        <v>49766.01428269965</v>
       </c>
       <c r="E75">
-        <v>5066.274169008526</v>
+        <v>33421.25566217426</v>
       </c>
       <c r="F75">
-        <v>8348.531445157996</v>
+        <v>64872.91236136949</v>
       </c>
       <c r="G75">
-        <v>26100.33693618136</v>
+        <v>188901.6628687369</v>
       </c>
       <c r="H75">
-        <v>11902.04335460708</v>
+        <v>78438.66686168735</v>
       </c>
       <c r="I75">
-        <v>48446.33954738285</v>
+        <v>376351.376114049</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4344,13 +4344,13 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>3471344812.512121</v>
+        <v>25123921161.54201</v>
       </c>
       <c r="N75">
-        <v>1582971766.162741</v>
+        <v>10432342692.60442</v>
       </c>
       <c r="O75">
-        <v>6443363159.801919</v>
+        <v>50054733023.16852</v>
       </c>
     </row>
     <row r="76">
@@ -4370,22 +4370,22 @@
         </is>
       </c>
       <c r="D76">
-        <v>16304.61165668253</v>
+        <v>116294.3438943201</v>
       </c>
       <c r="E76">
-        <v>12054.10465935661</v>
+        <v>77736.29638655805</v>
       </c>
       <c r="F76">
-        <v>19790.34066210408</v>
+        <v>151782.2097276842</v>
       </c>
       <c r="G76">
-        <v>58411.92868458656</v>
+        <v>415816.1753789237</v>
       </c>
       <c r="H76">
-        <v>26722.6706539295</v>
+        <v>171869.857305057</v>
       </c>
       <c r="I76">
-        <v>108325.785897148</v>
+        <v>829369.0429792689</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4397,13 +4397,13 @@
         <v>0</v>
       </c>
       <c r="M76">
-        <v>7768786515.050012</v>
+        <v>55303551325.39684</v>
       </c>
       <c r="N76">
-        <v>3554115196.972624</v>
+        <v>22858691021.57258</v>
       </c>
       <c r="O76">
-        <v>14407329524.32068</v>
+        <v>110306082716.2428</v>
       </c>
     </row>
     <row r="77">
@@ -4423,22 +4423,22 @@
         </is>
       </c>
       <c r="D77">
-        <v>7951.868893953908</v>
+        <v>57902.36537637158</v>
       </c>
       <c r="E77">
-        <v>5852.496497627419</v>
+        <v>38750.77894091354</v>
       </c>
       <c r="F77">
-        <v>9664.121978587777</v>
+        <v>75617.17885888871</v>
       </c>
       <c r="G77">
-        <v>24090.20834216525</v>
+        <v>175088.095982592</v>
       </c>
       <c r="H77">
-        <v>10969.76923072312</v>
+        <v>72425.86906499378</v>
       </c>
       <c r="I77">
-        <v>44731.72850384561</v>
+        <v>349492.9260856113</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -4450,13 +4450,13 @@
         <v>0</v>
       </c>
       <c r="M77">
-        <v>3203997709.507978</v>
+        <v>23286716765.68474</v>
       </c>
       <c r="N77">
-        <v>1458979307.686175</v>
+        <v>9632640585.644173</v>
       </c>
       <c r="O77">
-        <v>5949319891.011466</v>
+        <v>46482559169.38631</v>
       </c>
     </row>
     <row r="78">
@@ -4476,22 +4476,22 @@
         </is>
       </c>
       <c r="D78">
-        <v>16719.62657776469</v>
+        <v>119159.2597022754</v>
       </c>
       <c r="E78">
-        <v>12349.12784650684</v>
+        <v>79357.09920860821</v>
       </c>
       <c r="F78">
-        <v>20296.77562773579</v>
+        <v>155743.6645432333</v>
       </c>
       <c r="G78">
-        <v>44021.4916454077</v>
+        <v>313825.5920952569</v>
       </c>
       <c r="H78">
-        <v>20113.6749046825</v>
+        <v>129282.205528266</v>
       </c>
       <c r="I78">
-        <v>81664.50484828696</v>
+        <v>626809.5281271862</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -4503,13 +4503,13 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>5854858388.839224</v>
+        <v>41738803748.66917</v>
       </c>
       <c r="N78">
-        <v>2675118762.322773</v>
+        <v>17194533335.25937</v>
       </c>
       <c r="O78">
-        <v>10861379144.82217</v>
+        <v>83365667240.91577</v>
       </c>
     </row>
     <row r="79">
@@ -4529,22 +4529,22 @@
         </is>
       </c>
       <c r="D79">
-        <v>6669.909313277104</v>
+        <v>47227.55973112589</v>
       </c>
       <c r="E79">
-        <v>4933.018668473821</v>
+        <v>31450.41069075277</v>
       </c>
       <c r="F79">
-        <v>8089.542324447979</v>
+        <v>61722.1596117357</v>
       </c>
       <c r="G79">
-        <v>14123.52306640458</v>
+        <v>100197.6167228411</v>
       </c>
       <c r="H79">
-        <v>6459.427147872938</v>
+        <v>41295.13116208087</v>
       </c>
       <c r="I79">
-        <v>26178.24828656948</v>
+        <v>200074.6352631762</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4556,13 +4556,13 @@
         <v>0</v>
       </c>
       <c r="M79">
-        <v>1878428567.831809</v>
+        <v>13326283024.13787</v>
       </c>
       <c r="N79">
-        <v>859103810.6671008</v>
+        <v>5492252444.556756</v>
       </c>
       <c r="O79">
-        <v>3481707022.113741</v>
+        <v>26609926490.00243</v>
       </c>
     </row>
     <row r="80">
@@ -4582,22 +4582,22 @@
         </is>
       </c>
       <c r="D80">
-        <v>19712.33820978573</v>
+        <v>136009.6920779614</v>
       </c>
       <c r="E80">
-        <v>14618.95049821876</v>
+        <v>90117.34690635341</v>
       </c>
       <c r="F80">
-        <v>23863.05711640364</v>
+        <v>177824.0600448392</v>
       </c>
       <c r="G80">
-        <v>36238.54452561509</v>
+        <v>249701.4420198741</v>
       </c>
       <c r="H80">
-        <v>16628.39878765247</v>
+        <v>102315.0714602079</v>
       </c>
       <c r="I80">
-        <v>67029.31086360192</v>
+        <v>498894.3735682509</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4609,13 +4609,13 @@
         <v>0</v>
       </c>
       <c r="M80">
-        <v>4819726421.906807</v>
+        <v>33210291788.64325</v>
       </c>
       <c r="N80">
-        <v>2211577038.757778</v>
+        <v>13607904504.20765</v>
       </c>
       <c r="O80">
-        <v>8914898344.859055</v>
+        <v>66352951684.57736</v>
       </c>
     </row>
     <row r="81">
@@ -4635,22 +4635,22 @@
         </is>
       </c>
       <c r="D81">
-        <v>8657.924928560615</v>
+        <v>57737.10130106875</v>
       </c>
       <c r="E81">
-        <v>6470.064105095283</v>
+        <v>38333.87146572913</v>
       </c>
       <c r="F81">
-        <v>10458.23621344677</v>
+        <v>75292.40706923835</v>
       </c>
       <c r="G81">
-        <v>11376.37552936228</v>
+        <v>75888.41494589458</v>
       </c>
       <c r="H81">
-        <v>5258.520287863576</v>
+        <v>31154.6684303483</v>
       </c>
       <c r="I81">
-        <v>20999.08546081209</v>
+        <v>151256.5832190351</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -4662,13 +4662,13 @@
         <v>0</v>
       </c>
       <c r="M81">
-        <v>1513057945.405183</v>
+        <v>10093159187.80398</v>
       </c>
       <c r="N81">
-        <v>699383198.2858557</v>
+        <v>4143570901.236324</v>
       </c>
       <c r="O81">
-        <v>2792878366.288008</v>
+        <v>20117125568.13167</v>
       </c>
     </row>
     <row r="82">
@@ -4688,22 +4688,22 @@
         </is>
       </c>
       <c r="D82">
-        <v>13570.30213594289</v>
+        <v>96219.48311088032</v>
       </c>
       <c r="E82">
-        <v>10021.05669725616</v>
+        <v>63729.49967083869</v>
       </c>
       <c r="F82">
-        <v>16467.27459488635</v>
+        <v>126049.1944097201</v>
       </c>
       <c r="G82">
-        <v>14154.17821053992</v>
+        <v>99485.17176504392</v>
       </c>
       <c r="H82">
-        <v>6474.899936956966</v>
+        <v>40690.86026852311</v>
       </c>
       <c r="I82">
-        <v>26231.33367121931</v>
+        <v>199203.1970441432</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -4715,13 +4715,13 @@
         <v>0</v>
       </c>
       <c r="M82">
-        <v>1882505702.001809</v>
+        <v>13231527844.75084</v>
       </c>
       <c r="N82">
-        <v>861161691.6152765</v>
+        <v>5411884415.713573</v>
       </c>
       <c r="O82">
-        <v>3488767378.272169</v>
+        <v>26494025206.87104</v>
       </c>
     </row>
     <row r="83">
@@ -4741,22 +4741,22 @@
         </is>
       </c>
       <c r="D83">
-        <v>5423.362314402823</v>
+        <v>37440.12022508903</v>
       </c>
       <c r="E83">
-        <v>4026.582730604539</v>
+        <v>24939.04507956756</v>
       </c>
       <c r="F83">
-        <v>6565.508442163536</v>
+        <v>48847.51590175272</v>
       </c>
       <c r="G83">
-        <v>2613.082363741616</v>
+        <v>18187.43632656063</v>
       </c>
       <c r="H83">
-        <v>1198.537490239515</v>
+        <v>7514.893970173445</v>
       </c>
       <c r="I83">
-        <v>4836.310719834359</v>
+        <v>36227.32767603017</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -4768,13 +4768,13 @@
         <v>0</v>
       </c>
       <c r="M83">
-        <v>347539954.3776349</v>
+        <v>2418929031.432564</v>
       </c>
       <c r="N83">
-        <v>159405486.2018555</v>
+        <v>999480898.0330682</v>
       </c>
       <c r="O83">
-        <v>643229325.7379698</v>
+        <v>4818234580.912013</v>
       </c>
     </row>
     <row r="84">
@@ -4794,22 +4794,22 @@
         </is>
       </c>
       <c r="D84">
-        <v>6035.532292732965</v>
+        <v>44736.40676615943</v>
       </c>
       <c r="E84">
-        <v>4427.506242407031</v>
+        <v>29795.73181676869</v>
       </c>
       <c r="F84">
-        <v>7347.834034972147</v>
+        <v>58620.11550103458</v>
       </c>
       <c r="G84">
-        <v>1312.595816738504</v>
+        <v>9702.535232827504</v>
       </c>
       <c r="H84">
-        <v>595.4080106016708</v>
+        <v>3988.637818389395</v>
       </c>
       <c r="I84">
-        <v>2440.979271843994</v>
+        <v>19440.39650054752</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -4821,13 +4821,13 @@
         <v>0</v>
       </c>
       <c r="M84">
-        <v>174575243.6262211</v>
+        <v>1290437185.966058</v>
       </c>
       <c r="N84">
-        <v>79189265.41002221</v>
+        <v>530488829.8457895</v>
       </c>
       <c r="O84">
-        <v>324650243.1552512</v>
+        <v>2585572734.572821</v>
       </c>
     </row>
     <row r="85">
@@ -4847,13 +4847,13 @@
         </is>
       </c>
       <c r="D85">
-        <v>2269.508437172638</v>
+        <v>16012.91996929153</v>
       </c>
       <c r="E85">
-        <v>1683.498291941293</v>
+        <v>10746.68333943685</v>
       </c>
       <c r="F85">
-        <v>2752.103781982716</v>
+        <v>20856.13035275497</v>
       </c>
       <c r="G85">
         <v>0</v>

--- a/output/Tables/2019/cases_prev_2019_sex_age.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex_age.xlsx
@@ -1176,7 +1176,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1190,46 +1190,46 @@
         </is>
       </c>
       <c r="D16">
-        <v>588.3023755021495</v>
+        <v>39067.57473912447</v>
       </c>
       <c r="E16">
-        <v>390.7880633089979</v>
+        <v>25952.35490837772</v>
       </c>
       <c r="F16">
-        <v>769.9254730075888</v>
+        <v>51129.04023778993</v>
       </c>
       <c r="G16">
-        <v>2337.775120016796</v>
+        <v>133281.9358071194</v>
       </c>
       <c r="H16">
-        <v>1219.014207573438</v>
+        <v>70059.19428382514</v>
       </c>
       <c r="I16">
-        <v>3729.476554758412</v>
+        <v>201415.1458295389</v>
       </c>
       <c r="J16">
-        <v>32769618.92022067</v>
+        <v>578473579.1622168</v>
       </c>
       <c r="K16">
-        <v>21767676.70243776</v>
+        <v>384276519.1283484</v>
       </c>
       <c r="L16">
-        <v>42886388.69746874</v>
+        <v>757067698.8009558</v>
       </c>
       <c r="M16">
-        <v>310924090.9622338</v>
+        <v>17726497462.34688</v>
       </c>
       <c r="N16">
-        <v>162128889.6072673</v>
+        <v>9317872839.748743</v>
       </c>
       <c r="O16">
-        <v>496020381.7828689</v>
+        <v>26788214395.32867</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1243,46 +1243,46 @@
         </is>
       </c>
       <c r="D17">
-        <v>862.1419172780883</v>
+        <v>8875.465444864987</v>
       </c>
       <c r="E17">
-        <v>571.2622204651087</v>
+        <v>5880.828272723464</v>
       </c>
       <c r="F17">
-        <v>1129.314683796277</v>
+        <v>11625.89726025813</v>
       </c>
       <c r="G17">
-        <v>3094.538229261351</v>
+        <v>27390.66513219524</v>
       </c>
       <c r="H17">
-        <v>1609.328363362568</v>
+        <v>14358.58208147701</v>
       </c>
       <c r="I17">
-        <v>4941.482186065206</v>
+        <v>41431.92644580393</v>
       </c>
       <c r="J17">
-        <v>48023029.07622405</v>
+        <v>131419016.8421159</v>
       </c>
       <c r="K17">
-        <v>31820448.20434756</v>
+        <v>87077424.23421615</v>
       </c>
       <c r="L17">
-        <v>62905086.51682044</v>
+        <v>172144660.7326424</v>
       </c>
       <c r="M17">
-        <v>411573584.4917597</v>
+        <v>3642958462.581967</v>
       </c>
       <c r="N17">
-        <v>214040672.3272216</v>
+        <v>1909691416.836442</v>
       </c>
       <c r="O17">
-        <v>657217130.7466725</v>
+        <v>5510446217.291923</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1296,46 +1296,46 @@
         </is>
       </c>
       <c r="D18">
-        <v>1242.362614573032</v>
+        <v>66663.3385387524</v>
       </c>
       <c r="E18">
-        <v>824.0461699609796</v>
+        <v>44211.44958610579</v>
       </c>
       <c r="F18">
-        <v>1624.368756679494</v>
+        <v>87162.53839688856</v>
       </c>
       <c r="G18">
-        <v>4136.44673959089</v>
+        <v>191110.0731452168</v>
       </c>
       <c r="H18">
-        <v>2153.242267103315</v>
+        <v>100268.1254814551</v>
       </c>
       <c r="I18">
-        <v>6592.571442464791</v>
+        <v>288529.1807578096</v>
       </c>
       <c r="J18">
-        <v>69202082.35694687</v>
+        <v>987084053.7433087</v>
       </c>
       <c r="K18">
-        <v>45901019.75916655</v>
+        <v>654638934.021468</v>
       </c>
       <c r="L18">
-        <v>90480588.48456137</v>
+        <v>1290615706.042728</v>
       </c>
       <c r="M18">
-        <v>550147416.3655883</v>
+        <v>25417639728.31384</v>
       </c>
       <c r="N18">
-        <v>286381221.5247409</v>
+        <v>13335660689.03352</v>
       </c>
       <c r="O18">
-        <v>876812001.8478172</v>
+        <v>38374381040.78868</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1349,46 +1349,46 @@
         </is>
       </c>
       <c r="D19">
-        <v>1861.275375926888</v>
+        <v>13720.98042512767</v>
       </c>
       <c r="E19">
-        <v>1251.800585376363</v>
+        <v>9221.582919495293</v>
       </c>
       <c r="F19">
-        <v>2425.064677477481</v>
+        <v>17881.43256125474</v>
       </c>
       <c r="G19">
-        <v>5366.225194633682</v>
+        <v>34134.50263124902</v>
       </c>
       <c r="H19">
-        <v>2831.450712118654</v>
+        <v>18141.94845576538</v>
       </c>
       <c r="I19">
-        <v>8524.27540562309</v>
+        <v>51376.42828834646</v>
       </c>
       <c r="J19">
-        <v>103676760.9898791</v>
+        <v>203166557.1548653</v>
       </c>
       <c r="K19">
-        <v>69727796.20663381</v>
+        <v>136543978.2889671</v>
       </c>
       <c r="L19">
-        <v>135080952.6648503</v>
+        <v>264770371.9344981</v>
       </c>
       <c r="M19">
-        <v>713707950.8862797</v>
+        <v>4539888849.95612</v>
       </c>
       <c r="N19">
-        <v>376582944.711781</v>
+        <v>2412879144.616795</v>
       </c>
       <c r="O19">
-        <v>1133728628.947871</v>
+        <v>6833064962.35008</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1402,46 +1402,46 @@
         </is>
       </c>
       <c r="D20">
-        <v>3772.518073227711</v>
+        <v>81926.66594650787</v>
       </c>
       <c r="E20">
-        <v>2525.865681256683</v>
+        <v>54787.86904922353</v>
       </c>
       <c r="F20">
-        <v>4921.37781992131</v>
+        <v>106913.2168352687</v>
       </c>
       <c r="G20">
-        <v>10223.59219287837</v>
+        <v>192453.2050262274</v>
       </c>
       <c r="H20">
-        <v>5370.357816641138</v>
+        <v>101781.839798562</v>
       </c>
       <c r="I20">
-        <v>16259.14607686969</v>
+        <v>290031.4309417382</v>
       </c>
       <c r="J20">
-        <v>210136801.7149305</v>
+        <v>1213088142.669942</v>
       </c>
       <c r="K20">
-        <v>140695770.1773603</v>
+        <v>811243977.0118529</v>
       </c>
       <c r="L20">
-        <v>274130587.3252571</v>
+        <v>1583064001.679832</v>
       </c>
       <c r="M20">
-        <v>1359737761.652823</v>
+        <v>25596276268.48824</v>
       </c>
       <c r="N20">
-        <v>714257589.6132714</v>
+        <v>13536984693.20875</v>
       </c>
       <c r="O20">
-        <v>2162466428.223668</v>
+        <v>38574180315.25118</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1455,46 +1455,46 @@
         </is>
       </c>
       <c r="D21">
-        <v>6267.890872950401</v>
+        <v>25825.26008393151</v>
       </c>
       <c r="E21">
-        <v>4200.348240623475</v>
+        <v>17298.59956728726</v>
       </c>
       <c r="F21">
-        <v>8181.718324197083</v>
+        <v>33716.02634955521</v>
       </c>
       <c r="G21">
-        <v>14341.23896952509</v>
+        <v>50968.66385324585</v>
       </c>
       <c r="H21">
-        <v>7536.952666531106</v>
+        <v>26988.50916550196</v>
       </c>
       <c r="I21">
-        <v>22825.80948510642</v>
+        <v>76857.10431966322</v>
       </c>
       <c r="J21">
-        <v>349134057.4050845</v>
+        <v>382394626.0627751</v>
       </c>
       <c r="K21">
-        <v>233967797.6992088</v>
+        <v>256140363.7928228</v>
       </c>
       <c r="L21">
-        <v>455738074.0944259</v>
+        <v>499233202.1578622</v>
       </c>
       <c r="M21">
-        <v>1907384782.946837</v>
+        <v>6778832292.481697</v>
       </c>
       <c r="N21">
-        <v>1002414704.648637</v>
+        <v>3589471719.011761</v>
       </c>
       <c r="O21">
-        <v>3035832661.519153</v>
+        <v>10221994874.51521</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1508,46 +1508,46 @@
         </is>
       </c>
       <c r="D22">
-        <v>10427.51345433943</v>
+        <v>100852.5279115385</v>
       </c>
       <c r="E22">
-        <v>6943.098805040554</v>
+        <v>67163.10263595924</v>
       </c>
       <c r="F22">
-        <v>13628.83739804005</v>
+        <v>131816.1537456301</v>
       </c>
       <c r="G22">
-        <v>20782.16786691479</v>
+        <v>174723.6488214404</v>
       </c>
       <c r="H22">
-        <v>10860.23543347352</v>
+        <v>92053.92700647611</v>
       </c>
       <c r="I22">
-        <v>33112.34983015166</v>
+        <v>263710.738625097</v>
       </c>
       <c r="J22">
-        <v>580833354.433617</v>
+        <v>1493323380.786147</v>
       </c>
       <c r="K22">
-        <v>386744489.638369</v>
+        <v>994484060.7306439</v>
       </c>
       <c r="L22">
-        <v>759153500.7456278</v>
+        <v>1951801788.511545</v>
       </c>
       <c r="M22">
-        <v>2764028326.299667</v>
+        <v>23238245293.25157</v>
       </c>
       <c r="N22">
-        <v>1444411312.651979</v>
+        <v>12243172291.86132</v>
       </c>
       <c r="O22">
-        <v>4403942527.410171</v>
+        <v>35073528237.13789</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1561,46 +1561,46 @@
         </is>
       </c>
       <c r="D23">
-        <v>14565.06109939926</v>
+        <v>41455.11209731697</v>
       </c>
       <c r="E23">
-        <v>9691.498738423492</v>
+        <v>27589.79571270331</v>
       </c>
       <c r="F23">
-        <v>19040.40339821524</v>
+        <v>54189.00011407428</v>
       </c>
       <c r="G23">
-        <v>23249.50335955776</v>
+        <v>57091.00354380367</v>
       </c>
       <c r="H23">
-        <v>12146.45005999749</v>
+        <v>30072.90961081772</v>
       </c>
       <c r="I23">
-        <v>37045.46703133934</v>
+        <v>86164.28608842567</v>
       </c>
       <c r="J23">
-        <v>811303033.3587363</v>
+        <v>613825844.8249744</v>
       </c>
       <c r="K23">
-        <v>539835862.7276652</v>
+        <v>408522105.1179976</v>
       </c>
       <c r="L23">
-        <v>1060588550.087386</v>
+        <v>802376524.689095</v>
       </c>
       <c r="M23">
-        <v>3092183946.821182</v>
+        <v>7593103471.325889</v>
       </c>
       <c r="N23">
-        <v>1615477857.979666</v>
+        <v>3999696978.238757</v>
       </c>
       <c r="O23">
-        <v>4927047115.168132</v>
+        <v>11459850049.76061</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1614,46 +1614,46 @@
         </is>
       </c>
       <c r="D24">
-        <v>30062.00423447313</v>
+        <v>112000.3190555502</v>
       </c>
       <c r="E24">
-        <v>19932.22993061347</v>
+        <v>74198.84247421486</v>
       </c>
       <c r="F24">
-        <v>39294.38823186921</v>
+        <v>146440.7041633448</v>
       </c>
       <c r="G24">
-        <v>41299.4282229974</v>
+        <v>136340.2363290754</v>
       </c>
       <c r="H24">
-        <v>21484.96442683367</v>
+        <v>71439.93750265797</v>
       </c>
       <c r="I24">
-        <v>65808.5028179798</v>
+        <v>205855.4223423052</v>
       </c>
       <c r="J24">
-        <v>1674513759.868619</v>
+        <v>1658388724.255534</v>
       </c>
       <c r="K24">
-        <v>1110265071.595028</v>
+        <v>1098662260.515692</v>
       </c>
       <c r="L24">
-        <v>2188776013.291584</v>
+        <v>2168347506.546649</v>
       </c>
       <c r="M24">
-        <v>5492823953.658654</v>
+        <v>18133251431.76702</v>
       </c>
       <c r="N24">
-        <v>2857500268.768878</v>
+        <v>9501511687.85351</v>
       </c>
       <c r="O24">
-        <v>8752530874.791313</v>
+        <v>27378771171.52659</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1667,46 +1667,46 @@
         </is>
       </c>
       <c r="D25">
-        <v>41527.39025708874</v>
+        <v>83091.92625906903</v>
       </c>
       <c r="E25">
-        <v>27587.41695785157</v>
+        <v>55180.93133155227</v>
       </c>
       <c r="F25">
-        <v>54139.4127855086</v>
+        <v>108344.4577834867</v>
       </c>
       <c r="G25">
-        <v>40550.25659999363</v>
+        <v>71030.15189528653</v>
       </c>
       <c r="H25">
-        <v>21133.5830468271</v>
+        <v>37303.03285879327</v>
       </c>
       <c r="I25">
-        <v>64457.87563826534</v>
+        <v>106970.8381459508</v>
       </c>
       <c r="J25">
-        <v>2313158692.100357</v>
+        <v>1230342152.118032</v>
       </c>
       <c r="K25">
-        <v>1536674299.386242</v>
+        <v>817064050.2262948</v>
       </c>
       <c r="L25">
-        <v>3015673570.978398</v>
+        <v>1604256386.400079</v>
       </c>
       <c r="M25">
-        <v>5393184127.799153</v>
+        <v>9447010202.073109</v>
       </c>
       <c r="N25">
-        <v>2810766545.228004</v>
+        <v>4961303370.219505</v>
       </c>
       <c r="O25">
-        <v>8572897459.889291</v>
+        <v>14227121473.41146</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1720,46 +1720,46 @@
         </is>
       </c>
       <c r="D26">
-        <v>41564.39048169472</v>
+        <v>66523.00650025051</v>
       </c>
       <c r="E26">
-        <v>27542.08114549347</v>
+        <v>44049.25396657803</v>
       </c>
       <c r="F26">
-        <v>54447.1462554098</v>
+        <v>87148.91705033979</v>
       </c>
       <c r="G26">
-        <v>32206.70271333435</v>
+        <v>45999.75675534475</v>
       </c>
       <c r="H26">
-        <v>16720.53516294613</v>
+        <v>24057.59032581822</v>
       </c>
       <c r="I26">
-        <v>51441.97312017581</v>
+        <v>69604.30389649121</v>
       </c>
       <c r="J26">
-        <v>2315219678.611363</v>
+        <v>985006157.2492068</v>
       </c>
       <c r="K26">
-        <v>1534149003.966281</v>
+        <v>652237303.483122</v>
       </c>
       <c r="L26">
-        <v>3032814940.718844</v>
+        <v>1290414014.764376</v>
       </c>
       <c r="M26">
-        <v>4283491460.873468</v>
+        <v>6117967648.460852</v>
       </c>
       <c r="N26">
-        <v>2223831176.671835</v>
+        <v>3199659513.333824</v>
       </c>
       <c r="O26">
-        <v>6841782424.983383</v>
+        <v>9257372418.233332</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1773,46 +1773,46 @@
         </is>
       </c>
       <c r="D27">
-        <v>43947.18992219883</v>
+        <v>66891.26738258103</v>
       </c>
       <c r="E27">
-        <v>29262.19071618433</v>
+        <v>44560.77015545658</v>
       </c>
       <c r="F27">
-        <v>57345.32447838437</v>
+        <v>87268.9271935774</v>
       </c>
       <c r="G27">
-        <v>15998.77204301349</v>
+        <v>21561.50503879077</v>
       </c>
       <c r="H27">
-        <v>8385.888050860196</v>
+        <v>11394.69582507743</v>
       </c>
       <c r="I27">
-        <v>25423.33587380562</v>
+        <v>32453.98451928482</v>
       </c>
       <c r="J27">
-        <v>2447946373.046322</v>
+        <v>990458996.1338766</v>
       </c>
       <c r="K27">
-        <v>1629962547.272897</v>
+        <v>659811323.6918443</v>
       </c>
       <c r="L27">
-        <v>3194249264.094966</v>
+        <v>1292191004.955306</v>
       </c>
       <c r="M27">
-        <v>2127836681.720793</v>
+        <v>2867680170.159173</v>
       </c>
       <c r="N27">
-        <v>1115323110.764406</v>
+        <v>1515494544.735298</v>
       </c>
       <c r="O27">
-        <v>3381303671.216147</v>
+        <v>4316379941.06488</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1826,46 +1826,46 @@
         </is>
       </c>
       <c r="D28">
-        <v>30229.452438522</v>
+        <v>26820.13778632225</v>
       </c>
       <c r="E28">
-        <v>20126.10559937367</v>
+        <v>17864.07810041781</v>
       </c>
       <c r="F28">
-        <v>39618.78132479652</v>
+        <v>35142.50177423227</v>
       </c>
       <c r="G28">
-        <v>4672.967347965558</v>
+        <v>3881.786037048852</v>
       </c>
       <c r="H28">
-        <v>2437.111573106332</v>
+        <v>2040.947869825431</v>
       </c>
       <c r="I28">
-        <v>7469.442813196508</v>
+        <v>5877.308827989244</v>
       </c>
       <c r="J28">
-        <v>1683840959.730555</v>
+        <v>397125780.2020734</v>
       </c>
       <c r="K28">
-        <v>1121064334.096312</v>
+        <v>264513404.4328864</v>
       </c>
       <c r="L28">
-        <v>2206845357.353813</v>
+        <v>520355023.7710565</v>
       </c>
       <c r="M28">
-        <v>621504657.2794193</v>
+        <v>516277542.9274974</v>
       </c>
       <c r="N28">
-        <v>324135839.2231422</v>
+        <v>271446066.6867824</v>
       </c>
       <c r="O28">
-        <v>993435894.1551355</v>
+        <v>781682074.1225694</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="D29">
-        <v>26004.96328265017</v>
+        <v>28450.60571045469</v>
       </c>
       <c r="E29">
-        <v>17458.20678959009</v>
+        <v>19094.9728353892</v>
       </c>
       <c r="F29">
-        <v>33876.56247021109</v>
+        <v>37056.82778553379</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1897,13 +1897,13 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>1448528464.770181</v>
+        <v>421268118.7547022</v>
       </c>
       <c r="K29">
-        <v>972457034.5937463</v>
+        <v>282739262.7736079</v>
       </c>
       <c r="L29">
-        <v>1886992282.715702</v>
+        <v>548700449.0203989</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1932,46 +1932,46 @@
         </is>
       </c>
       <c r="D30">
-        <v>39067.57473912447</v>
+        <v>588.3023755021495</v>
       </c>
       <c r="E30">
-        <v>25952.35490837772</v>
+        <v>390.7880633089979</v>
       </c>
       <c r="F30">
-        <v>51129.04023778993</v>
+        <v>769.9254730075888</v>
       </c>
       <c r="G30">
-        <v>133281.9358071194</v>
+        <v>2337.775120016796</v>
       </c>
       <c r="H30">
-        <v>70059.19428382514</v>
+        <v>1219.014207573438</v>
       </c>
       <c r="I30">
-        <v>201415.1458295389</v>
+        <v>3729.476554758412</v>
       </c>
       <c r="J30">
-        <v>578473579.1622168</v>
+        <v>32769618.92022067</v>
       </c>
       <c r="K30">
-        <v>384276519.1283484</v>
+        <v>21767676.70243776</v>
       </c>
       <c r="L30">
-        <v>757067698.8009558</v>
+        <v>42886388.69746874</v>
       </c>
       <c r="M30">
-        <v>17726497462.34688</v>
+        <v>310924090.9622338</v>
       </c>
       <c r="N30">
-        <v>9317872839.748743</v>
+        <v>162128889.6072673</v>
       </c>
       <c r="O30">
-        <v>26788214395.32867</v>
+        <v>496020381.7828689</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1985,46 +1985,46 @@
         </is>
       </c>
       <c r="D31">
-        <v>8875.465444864987</v>
+        <v>862.1419172780883</v>
       </c>
       <c r="E31">
-        <v>5880.828272723464</v>
+        <v>571.2622204651087</v>
       </c>
       <c r="F31">
-        <v>11625.89726025813</v>
+        <v>1129.314683796277</v>
       </c>
       <c r="G31">
-        <v>27390.66513219524</v>
+        <v>3094.538229261351</v>
       </c>
       <c r="H31">
-        <v>14358.58208147701</v>
+        <v>1609.328363362568</v>
       </c>
       <c r="I31">
-        <v>41431.92644580393</v>
+        <v>4941.482186065206</v>
       </c>
       <c r="J31">
-        <v>131419016.8421159</v>
+        <v>48023029.07622405</v>
       </c>
       <c r="K31">
-        <v>87077424.23421615</v>
+        <v>31820448.20434756</v>
       </c>
       <c r="L31">
-        <v>172144660.7326424</v>
+        <v>62905086.51682044</v>
       </c>
       <c r="M31">
-        <v>3642958462.581967</v>
+        <v>411573584.4917597</v>
       </c>
       <c r="N31">
-        <v>1909691416.836442</v>
+        <v>214040672.3272216</v>
       </c>
       <c r="O31">
-        <v>5510446217.291923</v>
+        <v>657217130.7466725</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2038,46 +2038,46 @@
         </is>
       </c>
       <c r="D32">
-        <v>66663.3385387524</v>
+        <v>1242.362614573032</v>
       </c>
       <c r="E32">
-        <v>44211.44958610579</v>
+        <v>824.0461699609796</v>
       </c>
       <c r="F32">
-        <v>87162.53839688856</v>
+        <v>1624.368756679494</v>
       </c>
       <c r="G32">
-        <v>191110.0731452168</v>
+        <v>4136.44673959089</v>
       </c>
       <c r="H32">
-        <v>100268.1254814551</v>
+        <v>2153.242267103315</v>
       </c>
       <c r="I32">
-        <v>288529.1807578096</v>
+        <v>6592.571442464791</v>
       </c>
       <c r="J32">
-        <v>987084053.7433087</v>
+        <v>69202082.35694687</v>
       </c>
       <c r="K32">
-        <v>654638934.021468</v>
+        <v>45901019.75916655</v>
       </c>
       <c r="L32">
-        <v>1290615706.042728</v>
+        <v>90480588.48456137</v>
       </c>
       <c r="M32">
-        <v>25417639728.31384</v>
+        <v>550147416.3655883</v>
       </c>
       <c r="N32">
-        <v>13335660689.03352</v>
+        <v>286381221.5247409</v>
       </c>
       <c r="O32">
-        <v>38374381040.78868</v>
+        <v>876812001.8478172</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2091,46 +2091,46 @@
         </is>
       </c>
       <c r="D33">
-        <v>13720.98042512767</v>
+        <v>1861.275375926888</v>
       </c>
       <c r="E33">
-        <v>9221.582919495293</v>
+        <v>1251.800585376363</v>
       </c>
       <c r="F33">
-        <v>17881.43256125474</v>
+        <v>2425.064677477481</v>
       </c>
       <c r="G33">
-        <v>34134.50263124902</v>
+        <v>5366.225194633682</v>
       </c>
       <c r="H33">
-        <v>18141.94845576538</v>
+        <v>2831.450712118654</v>
       </c>
       <c r="I33">
-        <v>51376.42828834646</v>
+        <v>8524.27540562309</v>
       </c>
       <c r="J33">
-        <v>203166557.1548653</v>
+        <v>103676760.9898791</v>
       </c>
       <c r="K33">
-        <v>136543978.2889671</v>
+        <v>69727796.20663381</v>
       </c>
       <c r="L33">
-        <v>264770371.9344981</v>
+        <v>135080952.6648503</v>
       </c>
       <c r="M33">
-        <v>4539888849.95612</v>
+        <v>713707950.8862797</v>
       </c>
       <c r="N33">
-        <v>2412879144.616795</v>
+        <v>376582944.711781</v>
       </c>
       <c r="O33">
-        <v>6833064962.35008</v>
+        <v>1133728628.947871</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2144,46 +2144,46 @@
         </is>
       </c>
       <c r="D34">
-        <v>81926.66594650787</v>
+        <v>3772.518073227711</v>
       </c>
       <c r="E34">
-        <v>54787.86904922353</v>
+        <v>2525.865681256683</v>
       </c>
       <c r="F34">
-        <v>106913.2168352687</v>
+        <v>4921.37781992131</v>
       </c>
       <c r="G34">
-        <v>192453.2050262274</v>
+        <v>10223.59219287837</v>
       </c>
       <c r="H34">
-        <v>101781.839798562</v>
+        <v>5370.357816641138</v>
       </c>
       <c r="I34">
-        <v>290031.4309417382</v>
+        <v>16259.14607686969</v>
       </c>
       <c r="J34">
-        <v>1213088142.669942</v>
+        <v>210136801.7149305</v>
       </c>
       <c r="K34">
-        <v>811243977.0118529</v>
+        <v>140695770.1773603</v>
       </c>
       <c r="L34">
-        <v>1583064001.679832</v>
+        <v>274130587.3252571</v>
       </c>
       <c r="M34">
-        <v>25596276268.48824</v>
+        <v>1359737761.652823</v>
       </c>
       <c r="N34">
-        <v>13536984693.20875</v>
+        <v>714257589.6132714</v>
       </c>
       <c r="O34">
-        <v>38574180315.25118</v>
+        <v>2162466428.223668</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2197,46 +2197,46 @@
         </is>
       </c>
       <c r="D35">
-        <v>25825.26008393151</v>
+        <v>6267.890872950401</v>
       </c>
       <c r="E35">
-        <v>17298.59956728726</v>
+        <v>4200.348240623475</v>
       </c>
       <c r="F35">
-        <v>33716.02634955521</v>
+        <v>8181.718324197083</v>
       </c>
       <c r="G35">
-        <v>50968.66385324585</v>
+        <v>14341.23896952509</v>
       </c>
       <c r="H35">
-        <v>26988.50916550196</v>
+        <v>7536.952666531106</v>
       </c>
       <c r="I35">
-        <v>76857.10431966322</v>
+        <v>22825.80948510642</v>
       </c>
       <c r="J35">
-        <v>382394626.0627751</v>
+        <v>349134057.4050845</v>
       </c>
       <c r="K35">
-        <v>256140363.7928228</v>
+        <v>233967797.6992088</v>
       </c>
       <c r="L35">
-        <v>499233202.1578622</v>
+        <v>455738074.0944259</v>
       </c>
       <c r="M35">
-        <v>6778832292.481697</v>
+        <v>1907384782.946837</v>
       </c>
       <c r="N35">
-        <v>3589471719.011761</v>
+        <v>1002414704.648637</v>
       </c>
       <c r="O35">
-        <v>10221994874.51521</v>
+        <v>3035832661.519153</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2250,46 +2250,46 @@
         </is>
       </c>
       <c r="D36">
-        <v>100852.5279115385</v>
+        <v>10427.51345433943</v>
       </c>
       <c r="E36">
-        <v>67163.10263595924</v>
+        <v>6943.098805040554</v>
       </c>
       <c r="F36">
-        <v>131816.1537456301</v>
+        <v>13628.83739804005</v>
       </c>
       <c r="G36">
-        <v>174723.6488214404</v>
+        <v>20782.16786691479</v>
       </c>
       <c r="H36">
-        <v>92053.92700647611</v>
+        <v>10860.23543347352</v>
       </c>
       <c r="I36">
-        <v>263710.738625097</v>
+        <v>33112.34983015166</v>
       </c>
       <c r="J36">
-        <v>1493323380.786147</v>
+        <v>580833354.433617</v>
       </c>
       <c r="K36">
-        <v>994484060.7306439</v>
+        <v>386744489.638369</v>
       </c>
       <c r="L36">
-        <v>1951801788.511545</v>
+        <v>759153500.7456278</v>
       </c>
       <c r="M36">
-        <v>23238245293.25157</v>
+        <v>2764028326.299667</v>
       </c>
       <c r="N36">
-        <v>12243172291.86132</v>
+        <v>1444411312.651979</v>
       </c>
       <c r="O36">
-        <v>35073528237.13789</v>
+        <v>4403942527.410171</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2303,46 +2303,46 @@
         </is>
       </c>
       <c r="D37">
-        <v>41455.11209731697</v>
+        <v>14565.06109939926</v>
       </c>
       <c r="E37">
-        <v>27589.79571270331</v>
+        <v>9691.498738423492</v>
       </c>
       <c r="F37">
-        <v>54189.00011407428</v>
+        <v>19040.40339821524</v>
       </c>
       <c r="G37">
-        <v>57091.00354380367</v>
+        <v>23249.50335955776</v>
       </c>
       <c r="H37">
-        <v>30072.90961081772</v>
+        <v>12146.45005999749</v>
       </c>
       <c r="I37">
-        <v>86164.28608842567</v>
+        <v>37045.46703133934</v>
       </c>
       <c r="J37">
-        <v>613825844.8249744</v>
+        <v>811303033.3587363</v>
       </c>
       <c r="K37">
-        <v>408522105.1179976</v>
+        <v>539835862.7276652</v>
       </c>
       <c r="L37">
-        <v>802376524.689095</v>
+        <v>1060588550.087386</v>
       </c>
       <c r="M37">
-        <v>7593103471.325889</v>
+        <v>3092183946.821182</v>
       </c>
       <c r="N37">
-        <v>3999696978.238757</v>
+        <v>1615477857.979666</v>
       </c>
       <c r="O37">
-        <v>11459850049.76061</v>
+        <v>4927047115.168132</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2356,46 +2356,46 @@
         </is>
       </c>
       <c r="D38">
-        <v>112000.3190555502</v>
+        <v>30062.00423447313</v>
       </c>
       <c r="E38">
-        <v>74198.84247421486</v>
+        <v>19932.22993061347</v>
       </c>
       <c r="F38">
-        <v>146440.7041633448</v>
+        <v>39294.38823186921</v>
       </c>
       <c r="G38">
-        <v>136340.2363290754</v>
+        <v>41299.4282229974</v>
       </c>
       <c r="H38">
-        <v>71439.93750265797</v>
+        <v>21484.96442683367</v>
       </c>
       <c r="I38">
-        <v>205855.4223423052</v>
+        <v>65808.5028179798</v>
       </c>
       <c r="J38">
-        <v>1658388724.255534</v>
+        <v>1674513759.868619</v>
       </c>
       <c r="K38">
-        <v>1098662260.515692</v>
+        <v>1110265071.595028</v>
       </c>
       <c r="L38">
-        <v>2168347506.546649</v>
+        <v>2188776013.291584</v>
       </c>
       <c r="M38">
-        <v>18133251431.76702</v>
+        <v>5492823953.658654</v>
       </c>
       <c r="N38">
-        <v>9501511687.85351</v>
+        <v>2857500268.768878</v>
       </c>
       <c r="O38">
-        <v>27378771171.52659</v>
+        <v>8752530874.791313</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2409,46 +2409,46 @@
         </is>
       </c>
       <c r="D39">
-        <v>83091.92625906903</v>
+        <v>41527.39025708874</v>
       </c>
       <c r="E39">
-        <v>55180.93133155227</v>
+        <v>27587.41695785157</v>
       </c>
       <c r="F39">
-        <v>108344.4577834867</v>
+        <v>54139.4127855086</v>
       </c>
       <c r="G39">
-        <v>71030.15189528653</v>
+        <v>40550.25659999363</v>
       </c>
       <c r="H39">
-        <v>37303.03285879327</v>
+        <v>21133.5830468271</v>
       </c>
       <c r="I39">
-        <v>106970.8381459508</v>
+        <v>64457.87563826534</v>
       </c>
       <c r="J39">
-        <v>1230342152.118032</v>
+        <v>2313158692.100357</v>
       </c>
       <c r="K39">
-        <v>817064050.2262948</v>
+        <v>1536674299.386242</v>
       </c>
       <c r="L39">
-        <v>1604256386.400079</v>
+        <v>3015673570.978398</v>
       </c>
       <c r="M39">
-        <v>9447010202.073109</v>
+        <v>5393184127.799153</v>
       </c>
       <c r="N39">
-        <v>4961303370.219505</v>
+        <v>2810766545.228004</v>
       </c>
       <c r="O39">
-        <v>14227121473.41146</v>
+        <v>8572897459.889291</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="D40">
-        <v>66523.00650025051</v>
+        <v>41564.39048169472</v>
       </c>
       <c r="E40">
-        <v>44049.25396657803</v>
+        <v>27542.08114549347</v>
       </c>
       <c r="F40">
-        <v>87148.91705033979</v>
+        <v>54447.1462554098</v>
       </c>
       <c r="G40">
-        <v>45999.75675534475</v>
+        <v>32206.70271333435</v>
       </c>
       <c r="H40">
-        <v>24057.59032581822</v>
+        <v>16720.53516294613</v>
       </c>
       <c r="I40">
-        <v>69604.30389649121</v>
+        <v>51441.97312017581</v>
       </c>
       <c r="J40">
-        <v>985006157.2492068</v>
+        <v>2315219678.611363</v>
       </c>
       <c r="K40">
-        <v>652237303.483122</v>
+        <v>1534149003.966281</v>
       </c>
       <c r="L40">
-        <v>1290414014.764376</v>
+        <v>3032814940.718844</v>
       </c>
       <c r="M40">
-        <v>6117967648.460852</v>
+        <v>4283491460.873468</v>
       </c>
       <c r="N40">
-        <v>3199659513.333824</v>
+        <v>2223831176.671835</v>
       </c>
       <c r="O40">
-        <v>9257372418.233332</v>
+        <v>6841782424.983383</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2515,46 +2515,46 @@
         </is>
       </c>
       <c r="D41">
-        <v>66891.26738258103</v>
+        <v>43947.18992219883</v>
       </c>
       <c r="E41">
-        <v>44560.77015545658</v>
+        <v>29262.19071618433</v>
       </c>
       <c r="F41">
-        <v>87268.9271935774</v>
+        <v>57345.32447838437</v>
       </c>
       <c r="G41">
-        <v>21561.50503879077</v>
+        <v>15998.77204301349</v>
       </c>
       <c r="H41">
-        <v>11394.69582507743</v>
+        <v>8385.888050860196</v>
       </c>
       <c r="I41">
-        <v>32453.98451928482</v>
+        <v>25423.33587380562</v>
       </c>
       <c r="J41">
-        <v>990458996.1338766</v>
+        <v>2447946373.046322</v>
       </c>
       <c r="K41">
-        <v>659811323.6918443</v>
+        <v>1629962547.272897</v>
       </c>
       <c r="L41">
-        <v>1292191004.955306</v>
+        <v>3194249264.094966</v>
       </c>
       <c r="M41">
-        <v>2867680170.159173</v>
+        <v>2127836681.720793</v>
       </c>
       <c r="N41">
-        <v>1515494544.735298</v>
+        <v>1115323110.764406</v>
       </c>
       <c r="O41">
-        <v>4316379941.06488</v>
+        <v>3381303671.216147</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2568,46 +2568,46 @@
         </is>
       </c>
       <c r="D42">
-        <v>26820.13778632225</v>
+        <v>30229.452438522</v>
       </c>
       <c r="E42">
-        <v>17864.07810041781</v>
+        <v>20126.10559937367</v>
       </c>
       <c r="F42">
-        <v>35142.50177423227</v>
+        <v>39618.78132479652</v>
       </c>
       <c r="G42">
-        <v>3881.786037048852</v>
+        <v>4672.967347965558</v>
       </c>
       <c r="H42">
-        <v>2040.947869825431</v>
+        <v>2437.111573106332</v>
       </c>
       <c r="I42">
-        <v>5877.308827989244</v>
+        <v>7469.442813196508</v>
       </c>
       <c r="J42">
-        <v>397125780.2020734</v>
+        <v>1683840959.730555</v>
       </c>
       <c r="K42">
-        <v>264513404.4328864</v>
+        <v>1121064334.096312</v>
       </c>
       <c r="L42">
-        <v>520355023.7710565</v>
+        <v>2206845357.353813</v>
       </c>
       <c r="M42">
-        <v>516277542.9274974</v>
+        <v>621504657.2794193</v>
       </c>
       <c r="N42">
-        <v>271446066.6867824</v>
+        <v>324135839.2231422</v>
       </c>
       <c r="O42">
-        <v>781682074.1225694</v>
+        <v>993435894.1551355</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="D43">
-        <v>28450.60571045469</v>
+        <v>26004.96328265017</v>
       </c>
       <c r="E43">
-        <v>19094.9728353892</v>
+        <v>17458.20678959009</v>
       </c>
       <c r="F43">
-        <v>37056.82778553379</v>
+        <v>33876.56247021109</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2639,13 +2639,13 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>421268118.7547022</v>
+        <v>1448528464.770181</v>
       </c>
       <c r="K43">
-        <v>282739262.7736079</v>
+        <v>972457034.5937463</v>
       </c>
       <c r="L43">
-        <v>548700449.0203989</v>
+        <v>1886992282.715702</v>
       </c>
       <c r="M43">
         <v>0</v>
